--- a/Pauta_de_Audiencias.xlsx
+++ b/Pauta_de_Audiencias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\blu\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7D76B860-D602-44BF-A3B4-07E5ACC7A3E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9493D6DC-746A-4C16-A3DA-075A5DBFE45A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BFD1EC26-1664-43BA-94B0-9598598C706A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{244918ED-C88A-4CAC-94C8-DAF859EC66CD}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="223">
   <si>
     <t>Código P&amp;C</t>
   </si>
@@ -98,47 +98,344 @@
     <t>Audiência Instrução - Presencial</t>
   </si>
   <si>
-    <t>0011274-93.2025.5.15.0081</t>
+    <t>0010456-08.2026.5.15.0017</t>
+  </si>
+  <si>
+    <t>Moema Bioenergia S.A. - Moema</t>
+  </si>
+  <si>
+    <t>Maurinho Dos Santos</t>
+  </si>
+  <si>
+    <t>SÃO JOSÉ DO RIO PRETO</t>
+  </si>
+  <si>
+    <t>SP</t>
+  </si>
+  <si>
+    <t>01ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>Instrução</t>
+  </si>
+  <si>
+    <t>Reclamação Trabalhista</t>
+  </si>
+  <si>
+    <t>CENTRAL</t>
+  </si>
+  <si>
+    <t>R$             215.000,00</t>
+  </si>
+  <si>
+    <t>Grupo E2</t>
+  </si>
+  <si>
+    <t>Correspondente - doc9</t>
+  </si>
+  <si>
+    <t>RYL</t>
+  </si>
+  <si>
+    <t>Presencial | Advogada - Kelly Cristina Perez kelly.perez@terra.com.br (17) 99111-4699</t>
+  </si>
+  <si>
+    <t>Audiência Una - Presencial</t>
+  </si>
+  <si>
+    <t>1001128-23.2026.5.02.0462</t>
+  </si>
+  <si>
+    <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
+  </si>
+  <si>
+    <t>Jordilino Antonio Dos Santos</t>
+  </si>
+  <si>
+    <t>SÃO BERNARDO DO CAMPO</t>
+  </si>
+  <si>
+    <t>02ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             253.327,72</t>
+  </si>
+  <si>
+    <t>Grupo B1</t>
+  </si>
+  <si>
+    <t>JPE</t>
+  </si>
+  <si>
+    <t>TAM</t>
+  </si>
+  <si>
+    <t>Presencial</t>
+  </si>
+  <si>
+    <t>Audiência Inicial -  Telepresencial</t>
+  </si>
+  <si>
+    <t>0012105-94.2025.5.15.0032</t>
+  </si>
+  <si>
+    <t>Alexandre Tomaz Ramos</t>
+  </si>
+  <si>
+    <t>CAMPINAS</t>
+  </si>
+  <si>
+    <t>R$             228.143,32</t>
+  </si>
+  <si>
+    <t>BSO</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/89978823106?pwd=TlFNRkViSE1yUjJyWjUvY2hSd2lVUT09 ID da reunião: 899 7882 3106 Senha: 112233</t>
+  </si>
+  <si>
+    <t>Audiência Una - Telepresencial</t>
+  </si>
+  <si>
+    <t>0001090-76.2026.5.08.0101</t>
+  </si>
+  <si>
+    <t>Fertilizantes Tocantins S.A</t>
+  </si>
+  <si>
+    <t>Alex De Jesus Da Silva Santana</t>
+  </si>
+  <si>
+    <t>ABAETETUBA</t>
+  </si>
+  <si>
+    <t>PA</t>
+  </si>
+  <si>
+    <t>Conhecimento</t>
+  </si>
+  <si>
+    <t>R$             100.000,00</t>
+  </si>
+  <si>
+    <t>https://trt8-jus-br.zoom.us/j/85053969243?pwd=RVArVU1FbVNNeFhZMVdxd2x0dEpkdz09 ID: 850  5396  9243 Senha: 1VTAbaete</t>
+  </si>
+  <si>
+    <t>0010968-56.2026.5.03.0168</t>
+  </si>
+  <si>
+    <t>Santa Juliana Bioernegia Ltda</t>
+  </si>
+  <si>
+    <t>Jonathan De Souza Pinheiro</t>
+  </si>
+  <si>
+    <t>UBERABA</t>
+  </si>
+  <si>
+    <t>MG</t>
+  </si>
+  <si>
+    <t>04ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             128.947,54</t>
+  </si>
+  <si>
+    <t>BBO</t>
+  </si>
+  <si>
+    <t>CAL</t>
+  </si>
+  <si>
+    <t>https://trt3-jus-br.zoom.us/j/88339690698 ID da reunião: 883 3969 0698</t>
+  </si>
+  <si>
+    <t>0000628-40.2026.5.05.0122</t>
+  </si>
+  <si>
+    <t>Salitre Fertilizantes Ltda.</t>
+  </si>
+  <si>
+    <t>Jonisson Dos Santos De Matos</t>
+  </si>
+  <si>
+    <t>CANDEIAS</t>
+  </si>
+  <si>
+    <t>BA</t>
+  </si>
+  <si>
+    <t>VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$               78.299,07</t>
+  </si>
+  <si>
+    <t>LWP</t>
+  </si>
+  <si>
+    <t>https://trt5-jus-br.zoom.us/j/83940886130?pwd=uh6aTpOi4nBJhI9bs2SbD7QP09VKAf.1</t>
+  </si>
+  <si>
+    <t>0010631-68.2025.5.15.0071</t>
+  </si>
+  <si>
+    <t>Mahle Metal Leve S.A.</t>
+  </si>
+  <si>
+    <t>Leandro Da Silva Mateus</t>
+  </si>
+  <si>
+    <t>MOGI GUAÇU</t>
+  </si>
+  <si>
+    <t>Inicial</t>
+  </si>
+  <si>
+    <t>R$             162.081,57</t>
+  </si>
+  <si>
+    <t>Grupo E1</t>
+  </si>
+  <si>
+    <t>PSI</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/5326391733?pwd=Qjc4RFBXWjZNbVd1bG5wNldjR3dWZz09 ID da reunião: 532 639 1733 Senha de acesso: 959215</t>
+  </si>
+  <si>
+    <t>0010848-83.2026.5.03.0080</t>
+  </si>
+  <si>
+    <t>Luiz Augusto Dias</t>
+  </si>
+  <si>
+    <t>PATROCÍNIO</t>
+  </si>
+  <si>
+    <t>R$             172.931,17</t>
+  </si>
+  <si>
+    <t>https://trt3-jus-br.zoom.us/my/vt.patrocinio</t>
+  </si>
+  <si>
+    <t>0011198-32.2025.5.15.0061</t>
+  </si>
+  <si>
+    <t>Viterra Bioenergia S.A.</t>
+  </si>
+  <si>
+    <t>Vinicius Jose Dos Santos</t>
+  </si>
+  <si>
+    <t>ARAÇATUBA</t>
+  </si>
+  <si>
+    <t>R$             191.463,95</t>
+  </si>
+  <si>
+    <t>Correspondente - Carla</t>
+  </si>
+  <si>
+    <t>Presencial | Advogada - Carla audiencias@cbpz.com.br (19) 98182-3518</t>
+  </si>
+  <si>
+    <t>1001231-86.2026.5.02.0411</t>
+  </si>
+  <si>
+    <t>Companhia Brasileira De Cartuchos</t>
+  </si>
+  <si>
+    <t>Fabio Renan Cardoso Dos Santos</t>
+  </si>
+  <si>
+    <t>RIBEIRÃO PIRES</t>
+  </si>
+  <si>
+    <t>R$               27.502,99</t>
+  </si>
+  <si>
+    <t>Grupo B3</t>
+  </si>
+  <si>
+    <t>LMI</t>
+  </si>
+  <si>
+    <t>Audiência de Conciliação - Telepresencial</t>
+  </si>
+  <si>
+    <t>0010130-25.2021.5.15.0049</t>
+  </si>
+  <si>
+    <t>Syngenta Proteção De Cultivos Ltda.</t>
+  </si>
+  <si>
+    <t>Jeferson De Souza Cordeiro Da Silva</t>
+  </si>
+  <si>
+    <t>ITÁPOLIS</t>
+  </si>
+  <si>
+    <t>CEJUSC</t>
+  </si>
+  <si>
+    <t>Execução</t>
+  </si>
+  <si>
+    <t>R$             183.480,00</t>
+  </si>
+  <si>
+    <t>JPL</t>
+  </si>
+  <si>
+    <t>JRM</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/81581929446?pwd=HwuH5UatcagW2qaS7YHxHEKhABetR6.1 ID da reunião: 815 8192 9446 e Senha: 581435</t>
+  </si>
+  <si>
+    <t>1001047-67.2026.5.02.0432</t>
+  </si>
+  <si>
+    <t>Edson Cavasso</t>
+  </si>
+  <si>
+    <t>SANTO ANDRÉ</t>
+  </si>
+  <si>
+    <t>R$             109.767,05</t>
+  </si>
+  <si>
+    <t>Correspondente - Hebert</t>
+  </si>
+  <si>
+    <t>Audiência Inicial - Presencial</t>
+  </si>
+  <si>
+    <t>0001882-07.2026.5.10.0802</t>
   </si>
   <si>
     <t>Syngenta Seeds Ltda.</t>
   </si>
   <si>
-    <t>Agata Fernanda Da Silva Rocha</t>
-  </si>
-  <si>
-    <t>MATÃO</t>
-  </si>
-  <si>
-    <t>SP</t>
-  </si>
-  <si>
-    <t>VARA DO TRABALHO</t>
+    <t>Vitoria Lima De Sa</t>
+  </si>
+  <si>
+    <t>PALMAS</t>
+  </si>
+  <si>
+    <t>TO</t>
   </si>
   <si>
     <t>1ª Instância</t>
   </si>
   <si>
-    <t>Reclamação Trabalhista</t>
-  </si>
-  <si>
-    <t>CENTRAL</t>
-  </si>
-  <si>
-    <t>R$               61.602,49</t>
-  </si>
-  <si>
-    <t>Grupo E1</t>
-  </si>
-  <si>
-    <t>Correspondente - doc9</t>
-  </si>
-  <si>
-    <t>GVM</t>
+    <t>R$             867.079,60</t>
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Presencial | Advogada - Gabriella Fernanda Vizicati (16) 993811319 </t>
+      <t xml:space="preserve">Presencial | Advogada - Bruna Cristina Alves Lemos </t>
     </r>
     <r>
       <rPr>
@@ -147,7 +444,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>gabriellavizicati.adv@gmail.com</t>
+      <t>advlemosbruna@gmail.com</t>
     </r>
     <r>
       <rPr>
@@ -156,7 +453,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> | Preposto - Ketelyn Caroline Maria da Silva Ferreira(16) 997725288 </t>
+      <t xml:space="preserve"> 63981224188 | Preposto - Gabriella Aparecida da Silva Nascimento </t>
     </r>
     <r>
       <rPr>
@@ -165,299 +462,266 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>ketelynmaria7@gmail.com</t>
+      <t>gabrielladr20@gmail.com</t>
     </r>
-  </si>
-  <si>
-    <t>Audiência Inicial -  Telepresencial</t>
-  </si>
-  <si>
-    <t>0000473-65.2026.5.09.0303</t>
-  </si>
-  <si>
-    <t>Companhia Act De Participações E Companhia Aix De Participações</t>
-  </si>
-  <si>
-    <t>Gabriel Goncalves De Jesus</t>
-  </si>
-  <si>
-    <t>FOZ DO IGUAÇU</t>
-  </si>
-  <si>
-    <t>PR</t>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (63)9911-44291</t>
+    </r>
+  </si>
+  <si>
+    <t>1001000-15.2026.5.02.0361</t>
+  </si>
+  <si>
+    <t>Alessandro Felix Da Silva Coutinho</t>
+  </si>
+  <si>
+    <t>MAUÁ</t>
+  </si>
+  <si>
+    <t>R$               85.247,00</t>
+  </si>
+  <si>
+    <t>GSM</t>
+  </si>
+  <si>
+    <t>Sessão de Julgamento TRT - Presencial</t>
+  </si>
+  <si>
+    <t>1001426-12.2025.5.02.0054</t>
+  </si>
+  <si>
+    <t>Telefonica Brasil S.A.</t>
+  </si>
+  <si>
+    <t>Flavia Dias De Oliveira Faria</t>
+  </si>
+  <si>
+    <t>SÃO PAULO</t>
+  </si>
+  <si>
+    <t>13ª TURMA</t>
+  </si>
+  <si>
+    <t>Recursal</t>
+  </si>
+  <si>
+    <t>R$          2.092.449,00</t>
+  </si>
+  <si>
+    <t>Grupo C</t>
+  </si>
+  <si>
+    <t>TFR</t>
+  </si>
+  <si>
+    <t>1001884-56.2025.5.02.0433</t>
+  </si>
+  <si>
+    <t>Fernando Roberto Orlando</t>
+  </si>
+  <si>
+    <t>09ª TURMA</t>
+  </si>
+  <si>
+    <t>R$          3.065.837,45</t>
+  </si>
+  <si>
+    <t>NRG</t>
+  </si>
+  <si>
+    <t>Audiência Instrução - Telepresencial</t>
+  </si>
+  <si>
+    <t>0010336-32.2026.5.15.0027</t>
+  </si>
+  <si>
+    <t>Guariroba Bioenergia Ltda.</t>
+  </si>
+  <si>
+    <t>Laerte Machado De Freitas</t>
+  </si>
+  <si>
+    <t>VOTUPORANGA</t>
+  </si>
+  <si>
+    <t>R$             189.750,00</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/89939880446?pwd=ZHhwbjhhMUk2aGtDbmUwRTdELzhZUT09 ID da reunião: 899 3988 0446 Senha: 608226</t>
+  </si>
+  <si>
+    <t>1001792-72.2025.5.02.0435</t>
+  </si>
+  <si>
+    <t>Ricardo Aparecido De Lima</t>
+  </si>
+  <si>
+    <t>11ª TURMA</t>
+  </si>
+  <si>
+    <t>R$             242.576,46</t>
+  </si>
+  <si>
+    <t>RFE</t>
+  </si>
+  <si>
+    <t>0011680-08.2025.5.15.0084</t>
+  </si>
+  <si>
+    <t>Embraer S.A.</t>
+  </si>
+  <si>
+    <t>Carlos Alberto Craveiro Grillo</t>
+  </si>
+  <si>
+    <t>SÃO JOSÉ DOS CAMPOS</t>
+  </si>
+  <si>
+    <t>R$               86.961,75</t>
+  </si>
+  <si>
+    <t>Grupo B2</t>
+  </si>
+  <si>
+    <t>VCR</t>
+  </si>
+  <si>
+    <t>0011114-70.2025.5.03.0156</t>
+  </si>
+  <si>
+    <t>Itapagipe Bioenergia Ltda.</t>
+  </si>
+  <si>
+    <t>Weslei Da Silva</t>
+  </si>
+  <si>
+    <t>FRUTAL</t>
+  </si>
+  <si>
+    <t>R$             291.472,09</t>
+  </si>
+  <si>
+    <t>BTF</t>
+  </si>
+  <si>
+    <t>MBF</t>
+  </si>
+  <si>
+    <t>https://trt3-jus-br.zoom.us/my/vtfrutal</t>
+  </si>
+  <si>
+    <t>0010638-85.2026.5.15.0019</t>
+  </si>
+  <si>
+    <t>Andre Luiz Gilbertoni</t>
+  </si>
+  <si>
+    <t>R$               72.346,49</t>
+  </si>
+  <si>
+    <t>RRU</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/83908076312?pwd=VnVGRnpYWFZmZjFwN3k4eVpnYTNSZz09 ID da reunião: 839 0807 6312 Senha de acesso: 248026</t>
+  </si>
+  <si>
+    <t>Sessão de Julgamento TRT - Telepresencial</t>
+  </si>
+  <si>
+    <t>0010938-02.2025.5.15.0013</t>
+  </si>
+  <si>
+    <t>Elaine Cibele Doring Leitao</t>
+  </si>
+  <si>
+    <t>01ª TURMA</t>
+  </si>
+  <si>
+    <t>Recursal TRT</t>
+  </si>
+  <si>
+    <t>R$               74.842,11</t>
+  </si>
+  <si>
+    <t>ANB</t>
+  </si>
+  <si>
+    <t>BCF</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/83745237918?pwd=KiNXAEnTw6TJnBMSmJXps8zLpMf92o.1</t>
+  </si>
+  <si>
+    <t>Audiência Inicial - Telepresencial</t>
+  </si>
+  <si>
+    <t>0010577-30.2026.5.15.0019</t>
+  </si>
+  <si>
+    <t>Alexsandro Da Silva Reis</t>
+  </si>
+  <si>
+    <t>R$               65.939,71</t>
+  </si>
+  <si>
+    <t>1000517-96.2026.5.02.0421</t>
+  </si>
+  <si>
+    <t>Alpha1 Empreendimento Imobiliario Spe Ltda</t>
+  </si>
+  <si>
+    <t>Romeu Francisco Xavier</t>
+  </si>
+  <si>
+    <t>SANTANA DE PARNAÍBA</t>
+  </si>
+  <si>
+    <t>R$               64.849,87</t>
+  </si>
+  <si>
+    <t>ARC</t>
+  </si>
+  <si>
+    <t>https://trt2-jus-br.zoom.us/j/85417780826?pwd=tB9EQBXo3d57eAtjrzEEibiyZkWRVr.1 ID da reunião: 854 1778 0826 Senha de acesso: 001027</t>
+  </si>
+  <si>
+    <t>Audiência de Instrução - Presencial</t>
+  </si>
+  <si>
+    <t>0010379-29.2025.5.15.0083</t>
+  </si>
+  <si>
+    <t>Jeziel Antonio Da Costa</t>
   </si>
   <si>
     <t>03ª VARA DO TRABALHO</t>
   </si>
   <si>
-    <t>Instrução</t>
-  </si>
-  <si>
-    <t>R$               44.000,00</t>
-  </si>
-  <si>
-    <t>Grupo C</t>
-  </si>
-  <si>
-    <t>VSI</t>
-  </si>
-  <si>
-    <t>https://url.trt9.jus.br/k9rj6 ID da reunião: 81873598553 Senha de acesso: 3vxqUEfxil</t>
-  </si>
-  <si>
-    <t>0000854-73.2026.5.09.0303</t>
-  </si>
-  <si>
-    <t>R$             371.600,00</t>
-  </si>
-  <si>
-    <t>https://url.trt9.jus.br/v45lh ID da reunião: 83746953609 Senha de acesso: fmLDmfFrpD</t>
-  </si>
-  <si>
-    <t>0010054-90.2026.5.15.0092</t>
-  </si>
-  <si>
-    <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
-  </si>
-  <si>
-    <t>Silvio Cesar De Oliveira</t>
-  </si>
-  <si>
-    <t>CAMPINAS</t>
-  </si>
-  <si>
-    <t>05ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$             584.709,77</t>
-  </si>
-  <si>
-    <t>Grupo B1</t>
-  </si>
-  <si>
-    <t>BSO</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/84146096644?pwd=STloZzBJSTFaMW5PeXZRYlIrRGlIdz09</t>
-  </si>
-  <si>
-    <t>0012129-83.2025.5.15.0045</t>
-  </si>
-  <si>
-    <t>Embraer S.A.</t>
-  </si>
-  <si>
-    <t>Luiz Gustavo Nitta Dos Santos</t>
-  </si>
-  <si>
-    <t>SÃO JOSÉ DOS CAMPOS</t>
-  </si>
-  <si>
-    <t>02ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>Inicial</t>
-  </si>
-  <si>
-    <t>R$               93.500,00</t>
-  </si>
-  <si>
-    <t>Grupo B2</t>
-  </si>
-  <si>
-    <t>VCR</t>
-  </si>
-  <si>
-    <t>BCF</t>
-  </si>
-  <si>
-    <t>Presencial</t>
-  </si>
-  <si>
-    <t>1000703-80.2026.5.02.0434</t>
-  </si>
-  <si>
-    <t>Welber Lepore</t>
-  </si>
-  <si>
-    <t>SANTO ANDRÉ</t>
-  </si>
-  <si>
-    <t>R$             500.000,00</t>
-  </si>
-  <si>
-    <t>JPE</t>
-  </si>
-  <si>
-    <t>RFE</t>
-  </si>
-  <si>
-    <t>0011497-91.2024.5.15.0045</t>
-  </si>
-  <si>
-    <t>Sociedade Fogás Ltda</t>
-  </si>
-  <si>
-    <t>Willian Januario Ferreira</t>
-  </si>
-  <si>
-    <t>R$             320.364,80</t>
-  </si>
-  <si>
-    <t>RCF</t>
-  </si>
-  <si>
-    <t>0011213-20.2025.5.15.0087</t>
-  </si>
-  <si>
-    <t>Syngenta Proteção De Cultivos Ltda.</t>
-  </si>
-  <si>
-    <t>Adelvan Barbosa Mendes</t>
-  </si>
-  <si>
-    <t>PAULÍNIA</t>
-  </si>
-  <si>
-    <t>01ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$                 4.305,55</t>
-  </si>
-  <si>
-    <t>Correspondente - Carlos Florian</t>
-  </si>
-  <si>
-    <t>Presencial | Advogada - Dra. Eliane Mendes, (15) 99949-8727</t>
-  </si>
-  <si>
-    <t>Audiência de Instrução - Semipresencial</t>
-  </si>
-  <si>
-    <t>0011639-67.2025.5.15.0043</t>
-  </si>
-  <si>
-    <t>Marcos Aparecido Martins</t>
-  </si>
-  <si>
-    <t>R$             102.072,18</t>
-  </si>
-  <si>
-    <t>ANB</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/83871847087?pwd=Ebt1CpRUX1UTa0fVvv9MzLp1q3Nviv.1 ID da reunião: 838 7184 7087 Senha: TRT15</t>
-  </si>
-  <si>
-    <t>Audiência Inicial - Telepresencial</t>
-  </si>
-  <si>
-    <t>0010254-83.2026.5.15.0032</t>
-  </si>
-  <si>
-    <t>Telefonica Brasil S.A.</t>
-  </si>
-  <si>
-    <t>Fabiana Gambetta de Souza</t>
-  </si>
-  <si>
-    <t>São Paulo</t>
-  </si>
-  <si>
-    <t>VARA ÚNICA</t>
-  </si>
-  <si>
-    <t>R$          1.747.335,00</t>
-  </si>
-  <si>
-    <t>TFR</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/4525285196?pwd=cG1ieCtlVVdHZERxcVRTM2lzSGt3dz09 ID da reunião: 452 528 5196 Senha de acesso: 702632</t>
-  </si>
-  <si>
-    <t>0010126-72.2024.5.15.0084</t>
-  </si>
-  <si>
-    <t>Sergio Monteiro</t>
-  </si>
-  <si>
-    <t>04ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$             229.387,00</t>
-  </si>
-  <si>
-    <t>1000430-23.2026.5.02.0363</t>
-  </si>
-  <si>
-    <t>Erivaldo Barbosa De Souza</t>
-  </si>
-  <si>
-    <t>MAUÁ</t>
-  </si>
-  <si>
-    <t>R$             428.326,17</t>
-  </si>
-  <si>
-    <t>GSM</t>
-  </si>
-  <si>
-    <t>TAM</t>
-  </si>
-  <si>
-    <t>Audiência Una - Presencial</t>
-  </si>
-  <si>
-    <t>1001217-05.2026.5.02.0411</t>
-  </si>
-  <si>
-    <t>Companhia Brasileira De Cartuchos</t>
-  </si>
-  <si>
-    <t>Diego Marcos Gomes</t>
-  </si>
-  <si>
-    <t>RIBEIRÃO PIRES</t>
-  </si>
-  <si>
-    <t>R$               35.831,63</t>
-  </si>
-  <si>
-    <t>Grupo B3</t>
-  </si>
-  <si>
-    <t>LMI</t>
-  </si>
-  <si>
-    <t>0011021-83.2026.5.15.0077</t>
-  </si>
-  <si>
-    <t>Valdirene Maria Bispo De Santana</t>
-  </si>
-  <si>
-    <t>INDAIATUBA</t>
-  </si>
-  <si>
-    <t>R$             232.705,51</t>
-  </si>
-  <si>
-    <t>JPL</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/88215751954?pwd=GWf0av1x8hFikMFre3DVbJa2NJn80H.1</t>
-  </si>
-  <si>
-    <t>Audiência de Conciliação - Telepresencial</t>
-  </si>
-  <si>
-    <t>0000955-98.2026.5.18.0129</t>
-  </si>
-  <si>
-    <t>Spic Brasil Energia Participacoes S.A.</t>
-  </si>
-  <si>
-    <t>Antonio Marques Ferreira</t>
+    <t>0010113-15.2024.5.15.0071</t>
+  </si>
+  <si>
+    <t>Daniel Gilliard Da Cunha</t>
+  </si>
+  <si>
+    <t>R$               77.100,65</t>
+  </si>
+  <si>
+    <t>Correspondente - Ana</t>
+  </si>
+  <si>
+    <t>0000942-02.2026.5.18.0129</t>
+  </si>
+  <si>
+    <t>Spic Brasil Energia Participações S.A.</t>
+  </si>
+  <si>
+    <t>Marcia Helena De Jesus</t>
   </si>
   <si>
     <t>QUIRINÓPOLIS</t>
@@ -466,10 +730,7 @@
     <t>GO</t>
   </si>
   <si>
-    <t>Conhecimento</t>
-  </si>
-  <si>
-    <t>R$               45.609,10</t>
+    <t>R$               30.037,01</t>
   </si>
   <si>
     <t>ECO</t>
@@ -478,185 +739,20 @@
     <t>https://trt18-jus-br.zoom.us/my/cejuscdigital.manha</t>
   </si>
   <si>
-    <t>0000954-16.2026.5.18.0129</t>
-  </si>
-  <si>
-    <t>Genesio Carolino de Souza</t>
-  </si>
-  <si>
-    <t>1000911-89.2026.5.02.0361</t>
-  </si>
-  <si>
-    <t>Jose Leite De Sousa</t>
-  </si>
-  <si>
-    <t>R$             424.757,26</t>
-  </si>
-  <si>
-    <t>Sessão de Julgamento TRT - Presencial</t>
-  </si>
-  <si>
-    <t>1001902-80.2025.5.02.0432</t>
-  </si>
-  <si>
-    <t>Rodrigo Ramiro Da Silva</t>
-  </si>
-  <si>
-    <t>17ª TURMA</t>
-  </si>
-  <si>
-    <t>Recursal</t>
-  </si>
-  <si>
-    <t>R$             235.838,22</t>
-  </si>
-  <si>
-    <t>0000270-46.2026.5.09.0322</t>
-  </si>
-  <si>
-    <t>Fertilizantes Heringer S.A.</t>
-  </si>
-  <si>
-    <t>Gabriel Da Silva Pinheiro</t>
-  </si>
-  <si>
-    <t>PARANAGUÁ</t>
-  </si>
-  <si>
-    <t>R$               81.500,00</t>
-  </si>
-  <si>
-    <t>Grupo E2</t>
-  </si>
-  <si>
-    <t>RRU</t>
-  </si>
-  <si>
-    <t>Presencial - Carlos José Luiz lisbonten@gmail.com (41)9152-4057</t>
-  </si>
-  <si>
-    <t>Audiência MPT - Telepresencial</t>
-  </si>
-  <si>
-    <t>000013.2008.15.005/5</t>
-  </si>
-  <si>
-    <t>Viterra Bioenergia S.A.</t>
-  </si>
-  <si>
-    <t>Ministério Público Do Trabalho</t>
-  </si>
-  <si>
-    <t>PRESIDENTE PRUDENTE</t>
-  </si>
-  <si>
-    <t>PROCURADORIA REGIONAL DO TRABALHO</t>
-  </si>
-  <si>
-    <t>Ação Civil Pública</t>
-  </si>
-  <si>
-    <t>Procuradoria Regional do Trabalho</t>
-  </si>
-  <si>
-    <t>R$                            -  </t>
-  </si>
-  <si>
-    <t>AAP</t>
-  </si>
-  <si>
-    <t>https://link.mpt.mp.br/xveNFA1</t>
-  </si>
-  <si>
-    <t>0010380-36.2026.5.03.0140</t>
-  </si>
-  <si>
-    <t>Sistenge Construções E Comércio Ltda.</t>
-  </si>
-  <si>
-    <t>Alex Alves Da Silva Batista</t>
-  </si>
-  <si>
-    <t>CONTAGEM</t>
-  </si>
-  <si>
-    <t>MG</t>
-  </si>
-  <si>
-    <t>R$             114.705,18</t>
-  </si>
-  <si>
-    <t>BBO</t>
-  </si>
-  <si>
-    <t>RYL</t>
-  </si>
-  <si>
-    <t>https://trt3-jus-br.zoom.us/my/vt1.contagem  id da reunião: 951 137 6811</t>
-  </si>
-  <si>
-    <t>0010292-31.2026.5.03.0032</t>
-  </si>
-  <si>
-    <t>Deivid Dos Santos Purcina</t>
-  </si>
-  <si>
-    <t>R$             102.504,89</t>
-  </si>
-  <si>
-    <t>Presencial | Advogada - Gelseli Candido da Silva Ribeiro gelseli45@gmail.com (31) 99219306</t>
-  </si>
-  <si>
-    <t>Audiência Instrução - Telepresencial</t>
-  </si>
-  <si>
-    <t>0010591-18.2026.5.15.0050</t>
-  </si>
-  <si>
-    <t>Allyson Hian Ladeia Lira De Souza</t>
-  </si>
-  <si>
-    <t>DRACENA</t>
-  </si>
-  <si>
-    <t>R$               63.021,36</t>
-  </si>
-  <si>
-    <t>https://trt15-jus.br.zoom.us/j/87527564652?pwd=d3YrZ2diWXk5UjgzbmVkNExteWVMQT09 ID da reunião: 875 2756 4652 Senha de acesso: 246680</t>
-  </si>
-  <si>
-    <t>1000269-26.2018.5.02.0320</t>
-  </si>
-  <si>
-    <t>Rosangela Aparecida Cassiano Silva Pinto</t>
-  </si>
-  <si>
-    <t>GUARULHOS</t>
-  </si>
-  <si>
-    <t>CEJUSC GUARULHOS</t>
-  </si>
-  <si>
-    <t>Execução</t>
-  </si>
-  <si>
-    <t>Central</t>
-  </si>
-  <si>
-    <t>R$               27.294,86</t>
-  </si>
-  <si>
-    <t>TLI</t>
-  </si>
-  <si>
-    <t>https://trt2-jus-br.zoom.us/j/81052513141?pwd=OWZwN1k3RUNBdFZSWU5OR2d6aE4xUT09 ID da reunião: 810 5251 3141 Senha de acesso: 1212</t>
+    <t>1000683-89.2026.5.02.0434</t>
+  </si>
+  <si>
+    <t>Victor Hugo Lima Salvador</t>
+  </si>
+  <si>
+    <t>R$             125.000,00</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -683,6 +779,14 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -704,7 +808,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -738,16 +842,14 @@
     </border>
     <border>
       <left style="medium">
-        <color rgb="FFBFBFBF"/>
+        <color indexed="64"/>
       </left>
       <right style="medium">
-        <color rgb="FFBFBFBF"/>
+        <color indexed="64"/>
       </right>
-      <top style="medium">
-        <color rgb="FFBFBFBF"/>
-      </top>
+      <top/>
       <bottom style="medium">
-        <color rgb="FFBFBFBF"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -756,19 +858,27 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
+      <top/>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -791,8 +901,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1124,30 +1241,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD2D74DD-DFB2-44BA-AD0D-3BE59E9A8464}">
-  <dimension ref="A1:R25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABE9468D-D1FF-4904-873D-77C916924E2F}">
+  <dimension ref="A1:R29"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="47.21875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="29.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="29.88671875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="24.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.21875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="26.88671875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="28.6640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="136.6640625" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:18" ht="60" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1203,15 +1301,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" ht="173.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4">
-        <v>102127</v>
+        <v>104278</v>
       </c>
       <c r="B2" s="5">
-        <v>46275</v>
+        <v>46280</v>
       </c>
       <c r="C2" s="6">
-        <v>0.33333333333333331</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>18</v>
@@ -1255,19 +1353,19 @@
       <c r="Q2" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="R2" s="7" t="s">
+      <c r="R2" s="8" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4">
-        <v>104547</v>
+        <v>105535</v>
       </c>
       <c r="B3" s="5">
-        <v>46275</v>
+        <v>46280</v>
       </c>
       <c r="C3" s="6">
-        <v>0.34722222222222221</v>
+        <v>0.3611111111111111</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>33</v>
@@ -1285,13 +1383,13 @@
         <v>37</v>
       </c>
       <c r="I3" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J3" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="J3" s="7" t="s">
-        <v>39</v>
-      </c>
       <c r="K3" s="7" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="L3" s="7" t="s">
         <v>26</v>
@@ -1300,33 +1398,33 @@
         <v>27</v>
       </c>
       <c r="N3" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="O3" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="P3" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="O3" s="7" t="s">
+      <c r="Q3" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="P3" s="7" t="s">
+      <c r="R3" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="Q3" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="R3" s="7" t="s">
+    </row>
+    <row r="4" spans="1:18" ht="231" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="4">
+        <v>103336</v>
+      </c>
+      <c r="B4" s="5">
+        <v>46280</v>
+      </c>
+      <c r="C4" s="6">
+        <v>0.37152777777777779</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>44</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="4">
-        <v>105203</v>
-      </c>
-      <c r="B4" s="5">
-        <v>46275</v>
-      </c>
-      <c r="C4" s="6">
-        <v>0.34930555555555554</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>33</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>45</v>
@@ -1335,19 +1433,19 @@
         <v>35</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="I4" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J4" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="J4" s="7" t="s">
-        <v>39</v>
-      </c>
       <c r="K4" s="7" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="L4" s="7" t="s">
         <v>26</v>
@@ -1356,54 +1454,54 @@
         <v>27</v>
       </c>
       <c r="N4" s="7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O4" s="7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="P4" s="7" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="Q4" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="R4" s="7" t="s">
-        <v>47</v>
+        <v>49</v>
+      </c>
+      <c r="R4" s="8" t="s">
+        <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:18" ht="231" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4">
-        <v>103762</v>
+        <v>105405</v>
       </c>
       <c r="B5" s="5">
-        <v>46275</v>
+        <v>46280</v>
       </c>
       <c r="C5" s="6">
-        <v>0.35902777777777778</v>
+        <v>0.375</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="L5" s="7" t="s">
         <v>26</v>
@@ -1412,54 +1510,54 @@
         <v>27</v>
       </c>
       <c r="N5" s="7" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="O5" s="7" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="P5" s="7" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="Q5" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="R5" s="7" t="s">
-        <v>56</v>
+        <v>31</v>
+      </c>
+      <c r="R5" s="8" t="s">
+        <v>59</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:18" ht="130.19999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4">
-        <v>103233</v>
+        <v>105962</v>
       </c>
       <c r="B6" s="5">
-        <v>46275</v>
+        <v>46280</v>
       </c>
       <c r="C6" s="6">
-        <v>0.3611111111111111</v>
+        <v>0.3923611111111111</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>62</v>
+        <v>25</v>
       </c>
       <c r="L6" s="7" t="s">
         <v>26</v>
@@ -1468,54 +1566,54 @@
         <v>27</v>
       </c>
       <c r="N6" s="7" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="O6" s="7" t="s">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="P6" s="7" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q6" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="R6" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R6" s="8" t="s">
+        <v>69</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:18" ht="144.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4">
-        <v>104765</v>
+        <v>106072</v>
       </c>
       <c r="B7" s="5">
-        <v>46275</v>
+        <v>46280</v>
       </c>
       <c r="C7" s="6">
-        <v>0.3888888888888889</v>
+        <v>0.3923611111111111</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>23</v>
+        <v>74</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>39</v>
+        <v>75</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="L7" s="7" t="s">
         <v>26</v>
@@ -1524,54 +1622,54 @@
         <v>27</v>
       </c>
       <c r="N7" s="7" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="O7" s="7" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="P7" s="7" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="Q7" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="R7" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R7" s="8" t="s">
+        <v>78</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:18" ht="245.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4">
-        <v>101073</v>
+        <v>100357</v>
       </c>
       <c r="B8" s="5">
-        <v>46275</v>
+        <v>46280</v>
       </c>
       <c r="C8" s="6">
-        <v>0.39583333333333331</v>
+        <v>0.40972222222222221</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="I8" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="L8" s="7" t="s">
         <v>26</v>
@@ -1580,54 +1678,54 @@
         <v>27</v>
       </c>
       <c r="N8" s="7" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="O8" s="7" t="s">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="P8" s="7" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="Q8" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="R8" s="7" t="s">
-        <v>67</v>
+        <v>86</v>
+      </c>
+      <c r="R8" s="8" t="s">
+        <v>87</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:18" ht="87" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4">
-        <v>101929</v>
+        <v>105662</v>
       </c>
       <c r="B9" s="5">
-        <v>46275</v>
+        <v>46280</v>
       </c>
       <c r="C9" s="6">
-        <v>0.4201388888888889</v>
+        <v>0.4236111111111111</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="L9" s="7" t="s">
         <v>26</v>
@@ -1636,54 +1734,54 @@
         <v>27</v>
       </c>
       <c r="N9" s="7" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="O9" s="7" t="s">
         <v>29</v>
       </c>
       <c r="P9" s="7" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="Q9" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R9" s="7" t="s">
-        <v>86</v>
+        <v>68</v>
+      </c>
+      <c r="R9" s="8" t="s">
+        <v>92</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:18" ht="144.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4">
-        <v>101921</v>
+        <v>103151</v>
       </c>
       <c r="B10" s="5">
-        <v>46275</v>
+        <v>46280</v>
       </c>
       <c r="C10" s="6">
-        <v>0.43055555555555558</v>
+        <v>0.4375</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>87</v>
+        <v>18</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>49</v>
+        <v>94</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>51</v>
+        <v>96</v>
       </c>
       <c r="I10" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="L10" s="7" t="s">
         <v>26</v>
@@ -1692,54 +1790,54 @@
         <v>27</v>
       </c>
       <c r="N10" s="7" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="O10" s="7" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="P10" s="7" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="Q10" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="R10" s="7" t="s">
-        <v>92</v>
+        <v>31</v>
+      </c>
+      <c r="R10" s="8" t="s">
+        <v>99</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4">
-        <v>104629</v>
+        <v>105901</v>
       </c>
       <c r="B11" s="5">
-        <v>46275</v>
+        <v>46280</v>
       </c>
       <c r="C11" s="6">
-        <v>0.43055555555555558</v>
+        <v>0.4375</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>93</v>
+        <v>33</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="I11" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="L11" s="7" t="s">
         <v>26</v>
@@ -1748,54 +1846,54 @@
         <v>27</v>
       </c>
       <c r="N11" s="7" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="O11" s="7" t="s">
-        <v>42</v>
+        <v>105</v>
       </c>
       <c r="P11" s="7" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="Q11" s="7" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="R11" s="7" t="s">
-        <v>101</v>
+        <v>43</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:18" ht="231" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="4">
-        <v>97164</v>
+        <v>78840</v>
       </c>
       <c r="B12" s="5">
-        <v>46275</v>
+        <v>46280</v>
       </c>
       <c r="C12" s="6">
-        <v>0.44444444444444442</v>
+        <v>0.43819444444444444</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>18</v>
+        <v>107</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="I12" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>62</v>
+        <v>113</v>
       </c>
       <c r="L12" s="7" t="s">
         <v>26</v>
@@ -1804,54 +1902,54 @@
         <v>27</v>
       </c>
       <c r="N12" s="7" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="O12" s="7" t="s">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="P12" s="7" t="s">
-        <v>66</v>
+        <v>115</v>
       </c>
       <c r="Q12" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="R12" s="7" t="s">
-        <v>67</v>
+        <v>116</v>
+      </c>
+      <c r="R12" s="8" t="s">
+        <v>117</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4">
-        <v>104652</v>
+        <v>105141</v>
       </c>
       <c r="B13" s="5">
-        <v>46275</v>
+        <v>46280</v>
       </c>
       <c r="C13" s="6">
         <v>0.4513888888888889</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="I13" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="L13" s="7" t="s">
         <v>26</v>
@@ -1860,54 +1958,54 @@
         <v>27</v>
       </c>
       <c r="N13" s="7" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="O13" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="P13" s="7" t="s">
-        <v>110</v>
+        <v>40</v>
+      </c>
+      <c r="P13" s="9" t="s">
+        <v>122</v>
       </c>
       <c r="Q13" s="7" t="s">
-        <v>111</v>
+        <v>42</v>
       </c>
       <c r="R13" s="7" t="s">
-        <v>67</v>
+        <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:18" ht="264.60000000000002" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="4">
-        <v>105880</v>
+        <v>105436</v>
       </c>
       <c r="B14" s="5">
-        <v>46275</v>
+        <v>46280</v>
       </c>
       <c r="C14" s="6">
-        <v>0.4513888888888889</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D14" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="J14" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="E14" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="H14" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="I14" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="J14" s="7" t="s">
-        <v>24</v>
-      </c>
       <c r="K14" s="7" t="s">
-        <v>40</v>
+        <v>129</v>
       </c>
       <c r="L14" s="7" t="s">
         <v>26</v>
@@ -1916,45 +2014,45 @@
         <v>27</v>
       </c>
       <c r="N14" s="7" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="O14" s="7" t="s">
-        <v>118</v>
+        <v>85</v>
       </c>
       <c r="P14" s="7" t="s">
-        <v>119</v>
+        <v>30</v>
       </c>
       <c r="Q14" s="7" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="R14" s="7" t="s">
-        <v>67</v>
+        <v>131</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4">
-        <v>104473</v>
+        <v>105637</v>
       </c>
       <c r="B15" s="5">
-        <v>46275</v>
+        <v>46280</v>
       </c>
       <c r="C15" s="6">
-        <v>0.45833333333333331</v>
+        <v>0.52777777777777779</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>80</v>
+        <v>35</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="I15" s="7" t="s">
         <v>23</v>
@@ -1972,54 +2070,54 @@
         <v>27</v>
       </c>
       <c r="N15" s="7" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="O15" s="7" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="P15" s="7" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="Q15" s="7" t="s">
-        <v>124</v>
+        <v>49</v>
       </c>
       <c r="R15" s="7" t="s">
-        <v>125</v>
+        <v>43</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="4">
-        <v>105816</v>
+        <v>104374</v>
       </c>
       <c r="B16" s="5">
-        <v>46275</v>
+        <v>46280</v>
       </c>
       <c r="C16" s="6">
-        <v>0.45833333333333331</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>131</v>
+        <v>23</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>24</v>
+        <v>142</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="L16" s="7" t="s">
         <v>26</v>
@@ -2028,54 +2126,54 @@
         <v>27</v>
       </c>
       <c r="N16" s="7" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="O16" s="7" t="s">
-        <v>42</v>
+        <v>145</v>
       </c>
       <c r="P16" s="7" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="Q16" s="7" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="R16" s="7" t="s">
-        <v>135</v>
+        <v>43</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="4">
-        <v>105819</v>
+        <v>102888</v>
       </c>
       <c r="B17" s="5">
-        <v>46275</v>
+        <v>46280</v>
       </c>
       <c r="C17" s="6">
-        <v>0.46527777777777779</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>128</v>
+        <v>35</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>131</v>
+        <v>23</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>24</v>
+        <v>149</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="L17" s="7" t="s">
         <v>26</v>
@@ -2084,54 +2182,54 @@
         <v>27</v>
       </c>
       <c r="N17" s="7" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="O17" s="7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="P17" s="7" t="s">
-        <v>134</v>
+        <v>151</v>
       </c>
       <c r="Q17" s="7" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="R17" s="7" t="s">
-        <v>135</v>
+        <v>43</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:18" ht="231" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="4">
-        <v>105464</v>
+        <v>104497</v>
       </c>
       <c r="B18" s="5">
-        <v>46275</v>
+        <v>46280</v>
       </c>
       <c r="C18" s="6">
-        <v>0.52777777777777779</v>
+        <v>0.5625</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>18</v>
+        <v>152</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>49</v>
+        <v>154</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>108</v>
+        <v>156</v>
       </c>
       <c r="I18" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="L18" s="7" t="s">
         <v>26</v>
@@ -2140,54 +2238,54 @@
         <v>27</v>
       </c>
       <c r="N18" s="7" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="O18" s="7" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="P18" s="7" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="Q18" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="R18" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R18" s="8" t="s">
+        <v>158</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="4">
-        <v>102935</v>
+        <v>102783</v>
       </c>
       <c r="B19" s="5">
-        <v>46275</v>
+        <v>46280</v>
       </c>
       <c r="C19" s="6">
-        <v>0.54166666666666663</v>
+        <v>0.5625</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="I19" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L19" s="7" t="s">
         <v>26</v>
@@ -2196,54 +2294,54 @@
         <v>27</v>
       </c>
       <c r="N19" s="7" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="O19" s="7" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="P19" s="7" t="s">
-        <v>111</v>
+        <v>49</v>
       </c>
       <c r="Q19" s="7" t="s">
-        <v>73</v>
+        <v>163</v>
       </c>
       <c r="R19" s="7" t="s">
-        <v>67</v>
+        <v>43</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="4">
-        <v>104730</v>
+        <v>102145</v>
       </c>
       <c r="B20" s="5">
-        <v>46275</v>
+        <v>46280</v>
       </c>
       <c r="C20" s="6">
-        <v>0.58333333333333337</v>
+        <v>0.56944444444444442</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="K20" s="7" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="L20" s="7" t="s">
         <v>26</v>
@@ -2252,110 +2350,110 @@
         <v>27</v>
       </c>
       <c r="N20" s="7" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
       <c r="O20" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="P20" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="Q20" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="R20" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="4">
+        <v>103544</v>
+      </c>
+      <c r="B21" s="5">
+        <v>46280</v>
+      </c>
+      <c r="C21" s="6">
+        <v>0.56944444444444442</v>
+      </c>
+      <c r="D21" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="P20" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q20" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="R20" s="7" t="s">
-        <v>154</v>
+      <c r="E21" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="K21" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L21" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M21" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N21" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="O21" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P21" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q21" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="R21" s="8" t="s">
+        <v>178</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="4">
-        <v>105817</v>
-      </c>
-      <c r="B21" s="5">
-        <v>46275</v>
-      </c>
-      <c r="C21" s="6">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="G21" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="H21" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="I21" s="7" t="s">
+    <row r="22" spans="1:18" ht="245.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="4">
+        <v>105070</v>
+      </c>
+      <c r="B22" s="5">
+        <v>46280</v>
+      </c>
+      <c r="C22" s="6">
+        <v>0.58680555555555558</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="I22" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J21" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="K21" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="L21" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="M21" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="N21" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="O21" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="P21" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="Q21" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="R21" s="7" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="4">
-        <v>104705</v>
-      </c>
-      <c r="B22" s="5">
-        <v>46275</v>
-      </c>
-      <c r="C22" s="6">
-        <v>0.58402777777777781</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="F22" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="G22" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="H22" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="I22" s="7" t="s">
-        <v>170</v>
-      </c>
       <c r="J22" s="7" t="s">
-        <v>83</v>
+        <v>24</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="L22" s="7" t="s">
         <v>26</v>
@@ -2364,54 +2462,54 @@
         <v>27</v>
       </c>
       <c r="N22" s="7" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="O22" s="7" t="s">
-        <v>152</v>
+        <v>29</v>
       </c>
       <c r="P22" s="7" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="Q22" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="R22" s="7" t="s">
-        <v>174</v>
+        <v>31</v>
+      </c>
+      <c r="R22" s="8" t="s">
+        <v>183</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:18" ht="144.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="4">
-        <v>104245</v>
+        <v>100963</v>
       </c>
       <c r="B23" s="5">
-        <v>46275</v>
+        <v>46280</v>
       </c>
       <c r="C23" s="6">
-        <v>0.61111111111111116</v>
+        <v>0.58750000000000002</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>87</v>
+        <v>184</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="F23" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="H23" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="G23" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="H23" s="7" t="s">
-        <v>169</v>
-      </c>
       <c r="I23" s="7" t="s">
-        <v>170</v>
+        <v>23</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>104</v>
+        <v>187</v>
       </c>
       <c r="K23" s="7" t="s">
-        <v>40</v>
+        <v>188</v>
       </c>
       <c r="L23" s="7" t="s">
         <v>26</v>
@@ -2420,45 +2518,45 @@
         <v>27</v>
       </c>
       <c r="N23" s="7" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="O23" s="7" t="s">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="P23" s="7" t="s">
-        <v>30</v>
+        <v>190</v>
       </c>
       <c r="Q23" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="R23" s="7" t="s">
-        <v>178</v>
+        <v>191</v>
+      </c>
+      <c r="R23" s="8" t="s">
+        <v>192</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:18" ht="245.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="4">
-        <v>104922</v>
+        <v>104996</v>
       </c>
       <c r="B24" s="5">
-        <v>46275</v>
+        <v>46280</v>
       </c>
       <c r="C24" s="6">
-        <v>0.625</v>
+        <v>0.59722222222222221</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>157</v>
+        <v>94</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>182</v>
+        <v>96</v>
       </c>
       <c r="I24" s="7" t="s">
         <v>23</v>
@@ -2467,7 +2565,7 @@
         <v>24</v>
       </c>
       <c r="K24" s="7" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="L24" s="7" t="s">
         <v>26</v>
@@ -2476,93 +2574,319 @@
         <v>27</v>
       </c>
       <c r="N24" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="O24" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P24" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q24" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="R24" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="O24" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="P24" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="Q24" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="R24" s="7" t="s">
-        <v>184</v>
-      </c>
     </row>
-    <row r="25" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:18" ht="245.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="4">
-        <v>66355</v>
+        <v>105922</v>
       </c>
       <c r="B25" s="5">
-        <v>46275</v>
+        <v>46280</v>
       </c>
       <c r="C25" s="6">
-        <v>0.65277777777777779</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>126</v>
+        <v>51</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="I25" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>188</v>
+        <v>24</v>
       </c>
       <c r="K25" s="7" t="s">
-        <v>189</v>
+        <v>57</v>
       </c>
       <c r="L25" s="7" t="s">
         <v>26</v>
       </c>
       <c r="M25" s="7" t="s">
-        <v>190</v>
+        <v>27</v>
       </c>
       <c r="N25" s="7" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="O25" s="7" t="s">
         <v>29</v>
       </c>
       <c r="P25" s="7" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="Q25" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R25" s="7" t="s">
-        <v>193</v>
+        <v>202</v>
+      </c>
+      <c r="R25" s="8" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="4">
+        <v>100168</v>
+      </c>
+      <c r="B26" s="5">
+        <v>46280</v>
+      </c>
+      <c r="C26" s="6">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="I26" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J26" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="K26" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="L26" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M26" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N26" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="O26" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="P26" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q26" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="R26" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="4">
+        <v>97093</v>
+      </c>
+      <c r="B27" s="5">
+        <v>46280</v>
+      </c>
+      <c r="C27" s="6">
+        <v>0.625</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="I27" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J27" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="K27" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L27" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M27" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N27" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="O27" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="P27" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="Q27" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="R27" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" ht="87" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="4">
+        <v>105812</v>
+      </c>
+      <c r="B28" s="5">
+        <v>46280</v>
+      </c>
+      <c r="C28" s="6">
+        <v>0.625</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="H28" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="I28" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="J28" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="K28" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L28" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M28" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N28" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="O28" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="P28" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="Q28" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="R28" s="8" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="4">
+        <v>104732</v>
+      </c>
+      <c r="B29" s="5">
+        <v>46280</v>
+      </c>
+      <c r="C29" s="6">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="H29" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="I29" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J29" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="K29" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L29" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M29" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N29" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="O29" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="P29" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q29" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="R29" s="7" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="R3" r:id="rId1" xr:uid="{6EFA8E9F-C59D-49D2-97A9-47035D61B6B0}"/>
-    <hyperlink ref="R4" r:id="rId2" xr:uid="{54294A7B-A98D-4A22-B70A-D03C49B0AA7A}"/>
-    <hyperlink ref="R5" r:id="rId3" xr:uid="{B6AA696A-C9BA-44B6-8708-561E285BCC2C}"/>
-    <hyperlink ref="R10" r:id="rId4" display="https://trt15-jus-br.zoom.us/j/83871847087?pwd=Ebt1CpRUX1UTa0fVvv9MzLp1q3Nviv.1%20ID%20da%20reunião:%20838%207184%207087%20Senha:%20TRT15" xr:uid="{95E9564A-3937-4976-99FB-CC71AFBCE5F2}"/>
-    <hyperlink ref="R11" r:id="rId5" display="https://trt15-jus-br.zoom.us/j/4525285196?pwd=cG1ieCtlVVdHZERxcVRTM2lzSGt3dz09%20ID%20da%20reunião:%20452%20528%205196%20Senha%20de%20acesso:%20702632" xr:uid="{7AD27C08-A580-4CCF-A35B-B40DEBD19780}"/>
-    <hyperlink ref="R15" r:id="rId6" xr:uid="{A43C92EE-A1DA-4389-97FE-A948489217B1}"/>
-    <hyperlink ref="R16" r:id="rId7" xr:uid="{E32B90FE-4C30-4C9B-8C73-9C9F9E951E6B}"/>
-    <hyperlink ref="R17" r:id="rId8" xr:uid="{26B08CFF-EF0B-4537-90EA-BC0B97BA68F1}"/>
-    <hyperlink ref="R20" r:id="rId9" display="mailto:lisbonten@gmail.com" xr:uid="{9095D122-A69A-44B0-B4D3-3EA8EBA61F78}"/>
-    <hyperlink ref="R21" r:id="rId10" xr:uid="{5180BE93-DE02-440F-B893-38BD30CA0961}"/>
-    <hyperlink ref="R22" r:id="rId11" display="https://trt3-jus-br.zoom.us/my/vt1.contagem  id da reunião: 951 137 6811" xr:uid="{6727428F-44D0-476D-9837-8068BD565468}"/>
-    <hyperlink ref="R23" r:id="rId12" display="mailto:gelseli45@gmail.com" xr:uid="{36B47A19-C3E1-4C99-B9C7-1F1C65EC2A3C}"/>
-    <hyperlink ref="R24" r:id="rId13" display="https://trt15-jus.br.zoom.us/j/87527564652?pwd=d3YrZ2diWXk5UjgzbmVkNExteWVMQT09%20ID%20da%20reunião:%20875%202756%204652%20Senha%20de%20acesso:%20246680" xr:uid="{3AF867D0-4803-4F73-81E9-7FB544EB202C}"/>
-    <hyperlink ref="R25" r:id="rId14" display="https://trt2-jus-br.zoom.us/j/81052513141?pwd=OWZwN1k3RUNBdFZSWU5OR2d6aE4xUT09%20ID%20da%20reunião:%20810%205251%203141%20Senha%20de%20acesso:%201212" xr:uid="{D25B88C6-8137-4550-87BE-D5D458A6ECA7}"/>
+    <hyperlink ref="R2" r:id="rId1" display="mailto:kelly.perez@terra.com.br" xr:uid="{83CFD0D8-3D60-4874-9972-F9E5B033D03B}"/>
+    <hyperlink ref="R4" r:id="rId2" display="https://trt15-jus-br.zoom.us/j/89978823106?pwd=TlFNRkViSE1yUjJyWjUvY2hSd2lVUT09%20ID%20da%20reunião:%20899%207882%203106%20Senha:%20112233" xr:uid="{308A6C86-4F88-44D1-8C38-822D9F52ABA9}"/>
+    <hyperlink ref="R5" r:id="rId3" display="https://trt8-jus-br.zoom.us/j/85053969243?pwd=RVArVU1FbVNNeFhZMVdxd2x0dEpkdz09%20ID:%20850%20%205396%20%209243%20Senha:%201VTAbaete" xr:uid="{EEF5C60F-CCD3-4A1D-BF91-B29484856A67}"/>
+    <hyperlink ref="R6" r:id="rId4" xr:uid="{B4B508E0-08B3-4B9B-AA9D-2E6A1BEA9028}"/>
+    <hyperlink ref="R7" r:id="rId5" xr:uid="{7E5C26C1-4348-427B-9695-C83F11E5B3CB}"/>
+    <hyperlink ref="R8" r:id="rId6" display="https://trt15-jus-br.zoom.us/j/5326391733?pwd=Qjc4RFBXWjZNbVd1bG5wNldjR3dWZz09%20ID%20da%20reunião:%20532%20639%201733%20Senha%20de%20acesso:%20959215" xr:uid="{4A9F7261-CC7F-4644-92EC-14BF76841151}"/>
+    <hyperlink ref="R9" r:id="rId7" xr:uid="{293F93CD-271D-4417-AEC2-5BDD286D5D1A}"/>
+    <hyperlink ref="R10" r:id="rId8" display="mailto:audiencias@cbpz.com.br" xr:uid="{C05C6D54-C733-4075-87CF-10E44B7B1653}"/>
+    <hyperlink ref="R12" r:id="rId9" display="https://trt15-jus-br.zoom.us/j/81581929446?pwd=HwuH5UatcagW2qaS7YHxHEKhABetR6.1%20ID%20da%20reunião:%20815%208192%209446%20e%20Senha:%20581435" xr:uid="{736CB56E-1973-4134-80D9-38D7C9E549BB}"/>
+    <hyperlink ref="R18" r:id="rId10" display="https://trt15-jus-br.zoom.us/j/89939880446?pwd=ZHhwbjhhMUk2aGtDbmUwRTdELzhZUT09%20ID%20da%20reunião:%20899%203988%200446%20Senha:%20608226" xr:uid="{A15A4B6C-06E4-4283-9E1A-1F42204A1708}"/>
+    <hyperlink ref="R21" r:id="rId11" xr:uid="{4415CF3F-9A5D-4219-86E7-6C91B9A8B7F3}"/>
+    <hyperlink ref="R22" r:id="rId12" display="https://trt15-jus-br.zoom.us/j/83908076312?pwd=VnVGRnpYWFZmZjFwN3k4eVpnYTNSZz09%20ID%20da%20reunião:%20839%200807%206312%20Senha%20de%20acesso:%20248026" xr:uid="{36BC2742-5EF3-4E42-A290-E6651388C5F7}"/>
+    <hyperlink ref="R23" r:id="rId13" xr:uid="{6D215882-AB6F-4C56-B5CF-D4EFC7118F60}"/>
+    <hyperlink ref="R24" r:id="rId14" display="https://trt15-jus-br.zoom.us/j/83908076312?pwd=VnVGRnpYWFZmZjFwN3k4eVpnYTNSZz09%20ID%20da%20reunião:%20839%200807%206312%20Senha%20de%20acesso:%20248026" xr:uid="{997A0A0F-DA33-4DF4-90CE-A79F9A9A8516}"/>
+    <hyperlink ref="R25" r:id="rId15" display="https://trt2-jus-br.zoom.us/j/85417780826?pwd=tB9EQBXo3d57eAtjrzEEibiyZkWRVr.1%20ID%20da%20reunião:%20854%201778%200826%20Senha%20de%20acesso:%20001027" xr:uid="{5ACFB79A-2B84-4958-9A53-FB5E4F1ECD25}"/>
+    <hyperlink ref="R28" r:id="rId16" xr:uid="{3FC0FE84-3C48-40D8-9929-5B0F2B45E8CE}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/Pauta_de_Audiencias.xlsx
+++ b/Pauta_de_Audiencias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\blu\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{49CAA082-9C51-445F-94E5-2CB9CC5EB9C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F584DDCF-A90A-4406-9E99-FC7A1030FF4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6CB71E6B-948F-40D0-AC72-CCC62D97B3A8}"/>
+    <workbookView xWindow="-20610" yWindow="2610" windowWidth="20730" windowHeight="11040" xr2:uid="{7E902B11-52F8-4CA8-A84C-9493BB8ADF16}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="167">
   <si>
     <t>Código P&amp;C</t>
   </si>
@@ -95,113 +95,458 @@
     <t>Link/Observações</t>
   </si>
   <si>
-    <t>Audiência de Instrução - Semipresencial</t>
-  </si>
-  <si>
-    <t>1000956-71.2026.5.02.0433</t>
+    <t>Perícia Técnica</t>
+  </si>
+  <si>
+    <t>0010062-91.2026.5.15.0084</t>
+  </si>
+  <si>
+    <t>Embraer S.A</t>
+  </si>
+  <si>
+    <t>Denis Rodolfo Brouzatto</t>
+  </si>
+  <si>
+    <t>SÃO JOSÉ DOS CAMPOS</t>
+  </si>
+  <si>
+    <t>SP</t>
+  </si>
+  <si>
+    <t>04ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>Instrução</t>
+  </si>
+  <si>
+    <t>Reclamação Trabalhista</t>
+  </si>
+  <si>
+    <t>CENTRAL</t>
+  </si>
+  <si>
+    <t>R$             175.235,05</t>
+  </si>
+  <si>
+    <t>Grupo B2</t>
+  </si>
+  <si>
+    <t>VCR</t>
+  </si>
+  <si>
+    <t>Iremos acompanhar</t>
+  </si>
+  <si>
+    <t>Audiência Inicial -  Telepresencial</t>
+  </si>
+  <si>
+    <t>0011014-18.2026.5.03.0080</t>
+  </si>
+  <si>
+    <t>Salitre Fertilizantes Ltda</t>
+  </si>
+  <si>
+    <t>Christian Monteiro Miranda</t>
+  </si>
+  <si>
+    <t>PATROCÍNIO</t>
+  </si>
+  <si>
+    <t>MG</t>
+  </si>
+  <si>
+    <t>VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             143.700,00</t>
+  </si>
+  <si>
+    <t>Grupo E2</t>
+  </si>
+  <si>
+    <t>MBF</t>
+  </si>
+  <si>
+    <t>CAL</t>
+  </si>
+  <si>
+    <t>https://trt3-jus-br.zoom.us/my/vt.patrocinio</t>
+  </si>
+  <si>
+    <t>0011015-03.2026.5.03.0080</t>
+  </si>
+  <si>
+    <t>Yury Goncalves De Oliveira</t>
+  </si>
+  <si>
+    <t>R$               77.600,00</t>
+  </si>
+  <si>
+    <t>Audiência Instrução - Presencial</t>
+  </si>
+  <si>
+    <t>1000223-02.2026.5.02.0435</t>
   </si>
   <si>
     <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
   </si>
   <si>
-    <t>Bruno Farabotti Clemente</t>
+    <t>Rafael Jonathas Leite</t>
   </si>
   <si>
     <t>SANTO ANDRÉ</t>
   </si>
   <si>
-    <t>SP</t>
+    <t>05ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$          1.138.821,89</t>
+  </si>
+  <si>
+    <t>Grupo B1</t>
+  </si>
+  <si>
+    <t>JPE</t>
+  </si>
+  <si>
+    <t>GSM</t>
+  </si>
+  <si>
+    <t>Presencial</t>
+  </si>
+  <si>
+    <t>1000211-85.2026.5.02.0435</t>
+  </si>
+  <si>
+    <t>Rafael Martins De Souza</t>
   </si>
   <si>
     <t>03ª VARA DO TRABALHO</t>
   </si>
   <si>
-    <t>Instrução</t>
-  </si>
-  <si>
-    <t>Reclamação Trabalhista</t>
-  </si>
-  <si>
-    <t>CENTRAL</t>
-  </si>
-  <si>
-    <t>R$               85.454,67</t>
-  </si>
-  <si>
-    <t>Grupo B1</t>
+    <t>R$             540.549,47</t>
+  </si>
+  <si>
+    <t>Correspondente - Hebert</t>
+  </si>
+  <si>
+    <t>RFE</t>
+  </si>
+  <si>
+    <t>Audiência de Conciliação - Telepresencial</t>
+  </si>
+  <si>
+    <t>0011539-67.2024.5.15.0037</t>
+  </si>
+  <si>
+    <t>Ouroeste Bioenergia Ltda.</t>
+  </si>
+  <si>
+    <t>Kurlan Diego Almeida Correa</t>
+  </si>
+  <si>
+    <t>FERNANDÓPOLIS</t>
+  </si>
+  <si>
+    <t>CEJUSC</t>
+  </si>
+  <si>
+    <t>Liquidação</t>
+  </si>
+  <si>
+    <t>R$             114.000,00</t>
+  </si>
+  <si>
+    <t>LWP</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/89156255965?pwd=TFJ1SndHRXo5ZlJuQmZoVzRCQkpsUT09</t>
+  </si>
+  <si>
+    <t>Audiência Una - Presencial</t>
+  </si>
+  <si>
+    <t>1000893-52.2026.5.02.0431</t>
+  </si>
+  <si>
+    <t>Ricardo Gabriel Rigonatt</t>
+  </si>
+  <si>
+    <t>02ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             915.429,45</t>
+  </si>
+  <si>
+    <t>0000205-04.2026.5.05.0018</t>
+  </si>
+  <si>
+    <t>Eurochem Comercio De Produtos Quimicos Ltda.</t>
+  </si>
+  <si>
+    <t>Sergio Miguel Conceicao Silva</t>
+  </si>
+  <si>
+    <t>SALVADOR</t>
+  </si>
+  <si>
+    <t>BA</t>
+  </si>
+  <si>
+    <t>38ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>Conhecimento</t>
+  </si>
+  <si>
+    <t>R$               65.000,00</t>
+  </si>
+  <si>
+    <t>Correspondente - doc9</t>
+  </si>
+  <si>
+    <t>Presencial | Advogado - Tiago Artur França de Oliveira Pimentel 71987320186 tafos2002@hotmail.com | Preposta - Fernanda de Jesus Silva (71)9281-5171 fjs1402saj@gmail.com</t>
+  </si>
+  <si>
+    <t>0010349-74.2026.5.15.0045</t>
+  </si>
+  <si>
+    <t>Embraer S.A.</t>
+  </si>
+  <si>
+    <t>Felipe Augusto Ribeiro Teodoro</t>
+  </si>
+  <si>
+    <t>R$               96.500,00</t>
+  </si>
+  <si>
+    <t>0010384-23.2026.5.15.0081</t>
+  </si>
+  <si>
+    <t>Syngenta Seeds Ltda.</t>
+  </si>
+  <si>
+    <t>Samara De Deus E Silva</t>
+  </si>
+  <si>
+    <t>MATÃO</t>
+  </si>
+  <si>
+    <t>1ª Instância</t>
+  </si>
+  <si>
+    <t>R$             211.278,00</t>
+  </si>
+  <si>
+    <t>Grupo E1</t>
+  </si>
+  <si>
+    <t>JRM</t>
+  </si>
+  <si>
+    <t>VRO</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/85873566791?pwd=RnpEWnZUM3RZcm5PU3lISmlydm9yZz09</t>
+  </si>
+  <si>
+    <t>Audiência Inicial -  Presencial</t>
+  </si>
+  <si>
+    <t>1001663-33.2026.5.02.0435</t>
+  </si>
+  <si>
+    <t>Rafael Rodrigues Maineti</t>
+  </si>
+  <si>
+    <t>R$          1.425.198,40</t>
+  </si>
+  <si>
+    <t>1001519-71.2026.5.02.0431</t>
+  </si>
+  <si>
+    <t>Helio Correia Da Silva</t>
+  </si>
+  <si>
+    <t>01ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             108.334,30</t>
   </si>
   <si>
     <t>BSO</t>
   </si>
   <si>
-    <t>TAM</t>
-  </si>
-  <si>
-    <t>https://trt2-jus-br.zoom.us/j/86266293042?pwd=dHpGOENGZTFYY1duYmlIRnBWeEVjUT09 ID da reunião: 862 6629 3042 Senha de acesso: 09400940</t>
-  </si>
-  <si>
-    <t>Audiência Una - Presencial</t>
-  </si>
-  <si>
-    <t>1000940-17.2026.5.02.0434</t>
-  </si>
-  <si>
-    <t>Eduardo Antonio De Souza Braga</t>
-  </si>
-  <si>
-    <t>02ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$          1.210.674,31</t>
-  </si>
-  <si>
-    <t>Correspondente - Hebert</t>
-  </si>
-  <si>
-    <t>GSM</t>
-  </si>
-  <si>
-    <t>Presencial</t>
-  </si>
-  <si>
-    <t>Audiência Una - Telepresencial</t>
-  </si>
-  <si>
-    <t>0010583-13.2026.5.15.0027</t>
-  </si>
-  <si>
-    <t>Guariroba Bioenergia Ltda.</t>
-  </si>
-  <si>
-    <t>Matheus Borges Do Prado</t>
-  </si>
-  <si>
-    <t>VOTUPORANGA</t>
-  </si>
-  <si>
-    <t>VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$               52.651,00</t>
-  </si>
-  <si>
-    <t>Grupo E2</t>
-  </si>
-  <si>
-    <t>RYL</t>
-  </si>
-  <si>
-    <t>CAL</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/89770082465?pwd=K09aQWhUOW5ESytiRUdCOUFSa2E4dz09 ID da reunião: 897 7008 2465 Senha de acesso: 908050</t>
+    <t>1000604-32.2026.5.02.0072</t>
+  </si>
+  <si>
+    <t>Telefonica Brasil S.A.</t>
+  </si>
+  <si>
+    <t>Renato Goncalves</t>
+  </si>
+  <si>
+    <t>SÃO PAULO</t>
+  </si>
+  <si>
+    <t>72ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$          1.869.250,00</t>
+  </si>
+  <si>
+    <t>Grupo C</t>
+  </si>
+  <si>
+    <t>VSI</t>
+  </si>
+  <si>
+    <t>TFR</t>
+  </si>
+  <si>
+    <t>1001727-49.2025.5.02.0024</t>
+  </si>
+  <si>
+    <t>Marcelo Alexandre Laurato</t>
+  </si>
+  <si>
+    <t>24ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$          4.056.666,00</t>
+  </si>
+  <si>
+    <t>Audiência Instrução - Telepresencial</t>
+  </si>
+  <si>
+    <t>0000558-91.2026.5.09.0128</t>
+  </si>
+  <si>
+    <t>Companhia Act De Participações E Companhia Aix De Participações</t>
+  </si>
+  <si>
+    <t>Yuri Martim Kaufmann Daverca</t>
+  </si>
+  <si>
+    <t>CASCAVEL</t>
+  </si>
+  <si>
+    <t>PR</t>
+  </si>
+  <si>
+    <t>R$             370.000,00</t>
+  </si>
+  <si>
+    <t>ECO</t>
+  </si>
+  <si>
+    <t>https://url.trt9.jus.br/b34ky ID da reunião: 84768334944 Senha de acesso: SnZ9g7C974</t>
+  </si>
+  <si>
+    <t>Sessão de Julgamento TST - Presencial</t>
+  </si>
+  <si>
+    <t>1010219-05.2025.5.02.0000</t>
+  </si>
+  <si>
+    <t>Sindicato Nacional Das Empresas Distribuidoras De Gas Liquefeito De Petroleo - Sindigas</t>
+  </si>
+  <si>
+    <t>Sindicato Dos Empregados Vendedores E Viajantes Do Comercio No Estado De Sao Paulo</t>
+  </si>
+  <si>
+    <t>SEÇÃO ESPECIALIZADA EM DISSÍDIOS COLETIVOS</t>
+  </si>
+  <si>
+    <t>Recursal</t>
+  </si>
+  <si>
+    <t>Dissídio Coletivo</t>
+  </si>
+  <si>
+    <t>R$                 1.000,00</t>
+  </si>
+  <si>
+    <t>RCF</t>
+  </si>
+  <si>
+    <t>0011693-70.2026.5.15.0084</t>
+  </si>
+  <si>
+    <t>Alexandre Antonio Da Silva</t>
+  </si>
+  <si>
+    <t>R$               14.976,61</t>
+  </si>
+  <si>
+    <t>BCF</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/89966319264?pwd=NDFlY0lCVTExV0FxdE5WTW5wUEJzUT09</t>
+  </si>
+  <si>
+    <t>0011613-12.2026.5.15.0083</t>
+  </si>
+  <si>
+    <t>Allysson Biacchi Dos Santos</t>
+  </si>
+  <si>
+    <t>R$             206.883,40</t>
+  </si>
+  <si>
+    <t>ANB</t>
+  </si>
+  <si>
+    <t>0000587-53.2026.5.18.0141</t>
+  </si>
+  <si>
+    <t>Fertilizantes Tocantins S.A.</t>
+  </si>
+  <si>
+    <t>Leandro Silvestre Da Silva</t>
+  </si>
+  <si>
+    <t>CATALÃO</t>
+  </si>
+  <si>
+    <t>GO</t>
+  </si>
+  <si>
+    <t>R$               36.555,57</t>
+  </si>
+  <si>
+    <t>Presencial | Advogada - Grazielle Dias Macedo graziellemacedoadv@gmail.com 64981693490 | Preposto - Julia de Souza Pozzebon juliadesouzapoz@gmail.com</t>
+  </si>
+  <si>
+    <t>0010172-38.2026.5.03.0080</t>
+  </si>
+  <si>
+    <t>Salitre Fertilizantes Ltda.</t>
+  </si>
+  <si>
+    <t>Hermes Ribeiro Da Assuncao Filho</t>
+  </si>
+  <si>
+    <t>R$          1.194.249,70</t>
+  </si>
+  <si>
+    <t>ARC</t>
+  </si>
+  <si>
+    <t>1000198-89.2026.5.02.0434</t>
+  </si>
+  <si>
+    <t>Bruno Do Nascimento</t>
+  </si>
+  <si>
+    <t>R$             157.153,47</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -209,49 +554,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF44546A"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="5">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -259,88 +571,16 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -672,258 +912,1246 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5128853-25C9-4B76-B7C0-743A219B4FAF}">
-  <dimension ref="A1:R4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1142822-FD19-4B3B-8E4A-A971A3F8ED2C}">
+  <dimension ref="A1:R22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="34.21875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.5546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.21875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="26.88671875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="28.6640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="122.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="R1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="22.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="4">
-        <v>105037</v>
-      </c>
-      <c r="B2" s="5">
-        <v>46283</v>
-      </c>
-      <c r="C2" s="6">
-        <v>0.40277777777777779</v>
-      </c>
-      <c r="D2" s="7" t="s">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>103788</v>
+      </c>
+      <c r="B2" s="1">
+        <v>46286</v>
+      </c>
+      <c r="C2" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D2" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" t="s">
         <v>20</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" t="s">
         <v>21</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" t="s">
         <v>23</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="J2" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="7" t="s">
+      <c r="K2" t="s">
         <v>25</v>
       </c>
-      <c r="L2" s="7" t="s">
+      <c r="L2" t="s">
         <v>26</v>
       </c>
-      <c r="M2" s="7" t="s">
+      <c r="M2" t="s">
         <v>27</v>
       </c>
-      <c r="N2" s="7" t="s">
+      <c r="N2" t="s">
         <v>28</v>
       </c>
-      <c r="O2" s="7" t="s">
+      <c r="O2" t="s">
         <v>29</v>
       </c>
-      <c r="P2" s="7" t="s">
+      <c r="P2" t="s">
         <v>30</v>
       </c>
-      <c r="Q2" s="7" t="s">
+      <c r="Q2" t="s">
+        <v>30</v>
+      </c>
+      <c r="R2" t="s">
         <v>31</v>
       </c>
-      <c r="R2" s="8" t="s">
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>105968</v>
+      </c>
+      <c r="B3" s="1">
+        <v>46286</v>
+      </c>
+      <c r="C3" s="2">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D3" t="s">
         <v>32</v>
       </c>
+      <c r="E3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J3" t="s">
+        <v>38</v>
+      </c>
+      <c r="K3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P3" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>42</v>
+      </c>
+      <c r="R3" t="s">
+        <v>43</v>
+      </c>
     </row>
-    <row r="3" spans="1:18" ht="22.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="4">
-        <v>105054</v>
-      </c>
-      <c r="B3" s="5">
-        <v>46283</v>
-      </c>
-      <c r="C3" s="6">
-        <v>0.44097222222222221</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E3" s="7" t="s">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>105967</v>
+      </c>
+      <c r="B4" s="1">
+        <v>46286</v>
+      </c>
+      <c r="C4" s="2">
+        <v>0.3576388888888889</v>
+      </c>
+      <c r="D4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F4" t="s">
         <v>34</v>
       </c>
-      <c r="F3" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="H3" s="7" t="s">
+      <c r="G4" t="s">
+        <v>45</v>
+      </c>
+      <c r="H4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J4" t="s">
+        <v>38</v>
+      </c>
+      <c r="K4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L4" t="s">
+        <v>26</v>
+      </c>
+      <c r="M4" t="s">
+        <v>27</v>
+      </c>
+      <c r="N4" t="s">
+        <v>46</v>
+      </c>
+      <c r="O4" t="s">
+        <v>40</v>
+      </c>
+      <c r="P4" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>42</v>
+      </c>
+      <c r="R4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>103985</v>
+      </c>
+      <c r="B5" s="1">
+        <v>46286</v>
+      </c>
+      <c r="C5" s="2">
+        <v>0.3611111111111111</v>
+      </c>
+      <c r="D5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" t="s">
+        <v>49</v>
+      </c>
+      <c r="G5" t="s">
+        <v>50</v>
+      </c>
+      <c r="H5" t="s">
+        <v>51</v>
+      </c>
+      <c r="I5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J5" t="s">
+        <v>52</v>
+      </c>
+      <c r="K5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L5" t="s">
+        <v>26</v>
+      </c>
+      <c r="M5" t="s">
+        <v>27</v>
+      </c>
+      <c r="N5" t="s">
+        <v>53</v>
+      </c>
+      <c r="O5" t="s">
+        <v>54</v>
+      </c>
+      <c r="P5" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>56</v>
+      </c>
+      <c r="R5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>103984</v>
+      </c>
+      <c r="B6" s="1">
+        <v>46286</v>
+      </c>
+      <c r="C6" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="D6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6" t="s">
+        <v>58</v>
+      </c>
+      <c r="F6" t="s">
+        <v>49</v>
+      </c>
+      <c r="G6" t="s">
+        <v>59</v>
+      </c>
+      <c r="H6" t="s">
+        <v>51</v>
+      </c>
+      <c r="I6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J6" t="s">
+        <v>60</v>
+      </c>
+      <c r="K6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M6" t="s">
+        <v>27</v>
+      </c>
+      <c r="N6" t="s">
+        <v>61</v>
+      </c>
+      <c r="O6" t="s">
+        <v>54</v>
+      </c>
+      <c r="P6" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>63</v>
+      </c>
+      <c r="R6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>98696</v>
+      </c>
+      <c r="B7" s="1">
+        <v>46286</v>
+      </c>
+      <c r="C7" s="2">
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="D7" t="s">
+        <v>64</v>
+      </c>
+      <c r="E7" t="s">
+        <v>65</v>
+      </c>
+      <c r="F7" t="s">
+        <v>66</v>
+      </c>
+      <c r="G7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H7" t="s">
+        <v>68</v>
+      </c>
+      <c r="I7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J7" t="s">
+        <v>69</v>
+      </c>
+      <c r="K7" t="s">
+        <v>70</v>
+      </c>
+      <c r="L7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N7" t="s">
+        <v>71</v>
+      </c>
+      <c r="O7" t="s">
+        <v>40</v>
+      </c>
+      <c r="P7" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>41</v>
+      </c>
+      <c r="R7" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>105109</v>
+      </c>
+      <c r="B8" s="1">
+        <v>46286</v>
+      </c>
+      <c r="C8" s="2">
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="D8" t="s">
+        <v>74</v>
+      </c>
+      <c r="E8" t="s">
+        <v>75</v>
+      </c>
+      <c r="F8" t="s">
+        <v>49</v>
+      </c>
+      <c r="G8" t="s">
+        <v>76</v>
+      </c>
+      <c r="H8" t="s">
+        <v>51</v>
+      </c>
+      <c r="I8" t="s">
+        <v>23</v>
+      </c>
+      <c r="J8" t="s">
+        <v>77</v>
+      </c>
+      <c r="K8" t="s">
+        <v>25</v>
+      </c>
+      <c r="L8" t="s">
+        <v>26</v>
+      </c>
+      <c r="M8" t="s">
+        <v>27</v>
+      </c>
+      <c r="N8" t="s">
+        <v>78</v>
+      </c>
+      <c r="O8" t="s">
+        <v>54</v>
+      </c>
+      <c r="P8" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>56</v>
+      </c>
+      <c r="R8" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>104650</v>
+      </c>
+      <c r="B9" s="1">
+        <v>46286</v>
+      </c>
+      <c r="C9" s="2">
+        <v>0.3923611111111111</v>
+      </c>
+      <c r="D9" t="s">
+        <v>47</v>
+      </c>
+      <c r="E9" t="s">
+        <v>79</v>
+      </c>
+      <c r="F9" t="s">
+        <v>80</v>
+      </c>
+      <c r="G9" t="s">
+        <v>81</v>
+      </c>
+      <c r="H9" t="s">
+        <v>82</v>
+      </c>
+      <c r="I9" t="s">
+        <v>83</v>
+      </c>
+      <c r="J9" t="s">
+        <v>84</v>
+      </c>
+      <c r="K9" t="s">
+        <v>85</v>
+      </c>
+      <c r="L9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M9" t="s">
+        <v>27</v>
+      </c>
+      <c r="N9" t="s">
+        <v>86</v>
+      </c>
+      <c r="O9" t="s">
+        <v>40</v>
+      </c>
+      <c r="P9" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>42</v>
+      </c>
+      <c r="R9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>104305</v>
+      </c>
+      <c r="B10" s="1">
+        <v>46286</v>
+      </c>
+      <c r="C10" s="2">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" t="s">
+        <v>89</v>
+      </c>
+      <c r="F10" t="s">
+        <v>90</v>
+      </c>
+      <c r="G10" t="s">
+        <v>91</v>
+      </c>
+      <c r="H10" t="s">
         <v>22</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I10" t="s">
         <v>23</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J10" t="s">
+        <v>77</v>
+      </c>
+      <c r="K10" t="s">
+        <v>25</v>
+      </c>
+      <c r="L10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M10" t="s">
+        <v>27</v>
+      </c>
+      <c r="N10" t="s">
+        <v>92</v>
+      </c>
+      <c r="O10" t="s">
+        <v>29</v>
+      </c>
+      <c r="P10" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>30</v>
+      </c>
+      <c r="R10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>104700</v>
+      </c>
+      <c r="B11" s="1">
+        <v>46286</v>
+      </c>
+      <c r="C11" s="2">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D11" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" t="s">
+        <v>93</v>
+      </c>
+      <c r="F11" t="s">
+        <v>94</v>
+      </c>
+      <c r="G11" t="s">
+        <v>95</v>
+      </c>
+      <c r="H11" t="s">
+        <v>96</v>
+      </c>
+      <c r="I11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J11" t="s">
+        <v>38</v>
+      </c>
+      <c r="K11" t="s">
+        <v>97</v>
+      </c>
+      <c r="L11" t="s">
+        <v>26</v>
+      </c>
+      <c r="M11" t="s">
+        <v>27</v>
+      </c>
+      <c r="N11" t="s">
+        <v>98</v>
+      </c>
+      <c r="O11" t="s">
+        <v>99</v>
+      </c>
+      <c r="P11" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>101</v>
+      </c>
+      <c r="R11" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>106085</v>
+      </c>
+      <c r="B12" s="1">
+        <v>46286</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="D12" t="s">
+        <v>103</v>
+      </c>
+      <c r="E12" t="s">
+        <v>104</v>
+      </c>
+      <c r="F12" t="s">
+        <v>49</v>
+      </c>
+      <c r="G12" t="s">
+        <v>105</v>
+      </c>
+      <c r="H12" t="s">
+        <v>51</v>
+      </c>
+      <c r="I12" t="s">
+        <v>23</v>
+      </c>
+      <c r="J12" t="s">
+        <v>52</v>
+      </c>
+      <c r="K12" t="s">
+        <v>25</v>
+      </c>
+      <c r="L12" t="s">
+        <v>26</v>
+      </c>
+      <c r="M12" t="s">
+        <v>27</v>
+      </c>
+      <c r="N12" t="s">
+        <v>106</v>
+      </c>
+      <c r="O12" t="s">
+        <v>54</v>
+      </c>
+      <c r="P12" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>56</v>
+      </c>
+      <c r="R12" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>105832</v>
+      </c>
+      <c r="B13" s="1">
+        <v>46286</v>
+      </c>
+      <c r="C13" s="2">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E13" t="s">
+        <v>107</v>
+      </c>
+      <c r="F13" t="s">
+        <v>49</v>
+      </c>
+      <c r="G13" t="s">
+        <v>108</v>
+      </c>
+      <c r="H13" t="s">
+        <v>51</v>
+      </c>
+      <c r="I13" t="s">
+        <v>23</v>
+      </c>
+      <c r="J13" t="s">
+        <v>109</v>
+      </c>
+      <c r="K13" t="s">
+        <v>25</v>
+      </c>
+      <c r="L13" t="s">
+        <v>26</v>
+      </c>
+      <c r="M13" t="s">
+        <v>27</v>
+      </c>
+      <c r="N13" t="s">
+        <v>110</v>
+      </c>
+      <c r="O13" t="s">
+        <v>54</v>
+      </c>
+      <c r="P13" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>111</v>
+      </c>
+      <c r="R13" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>104826</v>
+      </c>
+      <c r="B14" s="1">
+        <v>46286</v>
+      </c>
+      <c r="C14" s="2">
+        <v>0.4861111111111111</v>
+      </c>
+      <c r="D14" t="s">
+        <v>47</v>
+      </c>
+      <c r="E14" t="s">
+        <v>112</v>
+      </c>
+      <c r="F14" t="s">
+        <v>113</v>
+      </c>
+      <c r="G14" t="s">
+        <v>114</v>
+      </c>
+      <c r="H14" t="s">
+        <v>115</v>
+      </c>
+      <c r="I14" t="s">
+        <v>23</v>
+      </c>
+      <c r="J14" t="s">
+        <v>116</v>
+      </c>
+      <c r="K14" t="s">
+        <v>25</v>
+      </c>
+      <c r="L14" t="s">
+        <v>26</v>
+      </c>
+      <c r="M14" t="s">
+        <v>27</v>
+      </c>
+      <c r="N14" t="s">
+        <v>117</v>
+      </c>
+      <c r="O14" t="s">
+        <v>118</v>
+      </c>
+      <c r="P14" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>120</v>
+      </c>
+      <c r="R14" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>105043</v>
+      </c>
+      <c r="B15" s="1">
+        <v>46286</v>
+      </c>
+      <c r="C15" s="2">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D15" t="s">
+        <v>47</v>
+      </c>
+      <c r="E15" t="s">
+        <v>121</v>
+      </c>
+      <c r="F15" t="s">
+        <v>113</v>
+      </c>
+      <c r="G15" t="s">
+        <v>122</v>
+      </c>
+      <c r="H15" t="s">
+        <v>115</v>
+      </c>
+      <c r="I15" t="s">
+        <v>23</v>
+      </c>
+      <c r="J15" t="s">
+        <v>123</v>
+      </c>
+      <c r="K15" t="s">
+        <v>25</v>
+      </c>
+      <c r="L15" t="s">
+        <v>26</v>
+      </c>
+      <c r="M15" t="s">
+        <v>27</v>
+      </c>
+      <c r="N15" t="s">
+        <v>124</v>
+      </c>
+      <c r="O15" t="s">
+        <v>118</v>
+      </c>
+      <c r="P15" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>120</v>
+      </c>
+      <c r="R15" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>104665</v>
+      </c>
+      <c r="B16" s="1">
+        <v>46286</v>
+      </c>
+      <c r="C16" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="D16" t="s">
+        <v>125</v>
+      </c>
+      <c r="E16" t="s">
+        <v>126</v>
+      </c>
+      <c r="F16" t="s">
+        <v>127</v>
+      </c>
+      <c r="G16" t="s">
+        <v>128</v>
+      </c>
+      <c r="H16" t="s">
+        <v>129</v>
+      </c>
+      <c r="I16" t="s">
+        <v>130</v>
+      </c>
+      <c r="J16" t="s">
+        <v>24</v>
+      </c>
+      <c r="K16" t="s">
+        <v>25</v>
+      </c>
+      <c r="L16" t="s">
+        <v>26</v>
+      </c>
+      <c r="M16" t="s">
+        <v>27</v>
+      </c>
+      <c r="N16" t="s">
+        <v>131</v>
+      </c>
+      <c r="O16" t="s">
+        <v>118</v>
+      </c>
+      <c r="P16" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>119</v>
+      </c>
+      <c r="R16" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>105225</v>
+      </c>
+      <c r="B17" s="1">
+        <v>46286</v>
+      </c>
+      <c r="C17" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="D17" t="s">
+        <v>134</v>
+      </c>
+      <c r="E17" t="s">
+        <v>135</v>
+      </c>
+      <c r="F17" t="s">
+        <v>136</v>
+      </c>
+      <c r="G17" t="s">
+        <v>137</v>
+      </c>
+      <c r="H17" t="s">
+        <v>115</v>
+      </c>
+      <c r="I17" t="s">
+        <v>23</v>
+      </c>
+      <c r="J17" t="s">
+        <v>138</v>
+      </c>
+      <c r="K17" t="s">
+        <v>139</v>
+      </c>
+      <c r="L17" t="s">
+        <v>140</v>
+      </c>
+      <c r="M17" t="s">
+        <v>27</v>
+      </c>
+      <c r="N17" t="s">
+        <v>141</v>
+      </c>
+      <c r="O17" t="s">
+        <v>118</v>
+      </c>
+      <c r="P17" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>142</v>
+      </c>
+      <c r="R17" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>105725</v>
+      </c>
+      <c r="B18" s="1">
+        <v>46286</v>
+      </c>
+      <c r="C18" s="2">
+        <v>0.56944444444444442</v>
+      </c>
+      <c r="D18" t="s">
+        <v>32</v>
+      </c>
+      <c r="E18" t="s">
+        <v>143</v>
+      </c>
+      <c r="F18" t="s">
+        <v>90</v>
+      </c>
+      <c r="G18" t="s">
+        <v>144</v>
+      </c>
+      <c r="H18" t="s">
+        <v>22</v>
+      </c>
+      <c r="I18" t="s">
+        <v>23</v>
+      </c>
+      <c r="J18" t="s">
+        <v>24</v>
+      </c>
+      <c r="K18" t="s">
+        <v>25</v>
+      </c>
+      <c r="L18" t="s">
+        <v>26</v>
+      </c>
+      <c r="M18" t="s">
+        <v>27</v>
+      </c>
+      <c r="N18" t="s">
+        <v>145</v>
+      </c>
+      <c r="O18" t="s">
+        <v>29</v>
+      </c>
+      <c r="P18" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>146</v>
+      </c>
+      <c r="R18" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>105891</v>
+      </c>
+      <c r="B19" s="1">
+        <v>46286</v>
+      </c>
+      <c r="C19" s="2">
+        <v>0.57638888888888884</v>
+      </c>
+      <c r="D19" t="s">
+        <v>32</v>
+      </c>
+      <c r="E19" t="s">
+        <v>148</v>
+      </c>
+      <c r="F19" t="s">
+        <v>90</v>
+      </c>
+      <c r="G19" t="s">
+        <v>149</v>
+      </c>
+      <c r="H19" t="s">
+        <v>22</v>
+      </c>
+      <c r="I19" t="s">
+        <v>23</v>
+      </c>
+      <c r="J19" t="s">
+        <v>60</v>
+      </c>
+      <c r="K19" t="s">
+        <v>25</v>
+      </c>
+      <c r="L19" t="s">
+        <v>26</v>
+      </c>
+      <c r="M19" t="s">
+        <v>27</v>
+      </c>
+      <c r="N19" t="s">
+        <v>150</v>
+      </c>
+      <c r="O19" t="s">
+        <v>29</v>
+      </c>
+      <c r="P19" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>30</v>
+      </c>
+      <c r="R19" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>104647</v>
+      </c>
+      <c r="B20" s="1">
+        <v>46286</v>
+      </c>
+      <c r="C20" s="2">
+        <v>0.59097222222222223</v>
+      </c>
+      <c r="D20" t="s">
+        <v>47</v>
+      </c>
+      <c r="E20" t="s">
+        <v>152</v>
+      </c>
+      <c r="F20" t="s">
+        <v>153</v>
+      </c>
+      <c r="G20" t="s">
+        <v>154</v>
+      </c>
+      <c r="H20" t="s">
+        <v>155</v>
+      </c>
+      <c r="I20" t="s">
+        <v>156</v>
+      </c>
+      <c r="J20" t="s">
+        <v>38</v>
+      </c>
+      <c r="K20" t="s">
+        <v>25</v>
+      </c>
+      <c r="L20" t="s">
+        <v>26</v>
+      </c>
+      <c r="M20" t="s">
+        <v>27</v>
+      </c>
+      <c r="N20" t="s">
+        <v>157</v>
+      </c>
+      <c r="O20" t="s">
+        <v>40</v>
+      </c>
+      <c r="P20" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>42</v>
+      </c>
+      <c r="R20" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>104214</v>
+      </c>
+      <c r="B21" s="1">
+        <v>46286</v>
+      </c>
+      <c r="C21" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="D21" t="s">
+        <v>125</v>
+      </c>
+      <c r="E21" t="s">
+        <v>159</v>
+      </c>
+      <c r="F21" t="s">
+        <v>160</v>
+      </c>
+      <c r="G21" t="s">
+        <v>161</v>
+      </c>
+      <c r="H21" t="s">
         <v>36</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="I21" t="s">
+        <v>37</v>
+      </c>
+      <c r="J21" t="s">
+        <v>38</v>
+      </c>
+      <c r="K21" t="s">
         <v>25</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="L21" t="s">
         <v>26</v>
       </c>
-      <c r="M3" s="7" t="s">
+      <c r="M21" t="s">
         <v>27</v>
       </c>
-      <c r="N3" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="O3" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="P3" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q3" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="R3" s="8" t="s">
+      <c r="N21" t="s">
+        <v>162</v>
+      </c>
+      <c r="O21" t="s">
         <v>40</v>
       </c>
+      <c r="P21" t="s">
+        <v>163</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>163</v>
+      </c>
+      <c r="R21" t="s">
+        <v>43</v>
+      </c>
     </row>
-    <row r="4" spans="1:18" ht="22.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="4">
-        <v>105444</v>
-      </c>
-      <c r="B4" s="5">
-        <v>46283</v>
-      </c>
-      <c r="C4" s="6">
-        <v>0.59722222222222221</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="I4" s="7" t="s">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>103964</v>
+      </c>
+      <c r="B22" s="1">
+        <v>46286</v>
+      </c>
+      <c r="C22" s="2">
+        <v>0.63888888888888884</v>
+      </c>
+      <c r="D22" t="s">
+        <v>47</v>
+      </c>
+      <c r="E22" t="s">
+        <v>164</v>
+      </c>
+      <c r="F22" t="s">
+        <v>49</v>
+      </c>
+      <c r="G22" t="s">
+        <v>165</v>
+      </c>
+      <c r="H22" t="s">
+        <v>51</v>
+      </c>
+      <c r="I22" t="s">
         <v>23</v>
       </c>
-      <c r="J4" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="K4" s="7" t="s">
+      <c r="J22" t="s">
+        <v>24</v>
+      </c>
+      <c r="K22" t="s">
         <v>25</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="L22" t="s">
         <v>26</v>
       </c>
-      <c r="M4" s="7" t="s">
+      <c r="M22" t="s">
         <v>27</v>
       </c>
-      <c r="N4" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="O4" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="P4" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q4" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="R4" s="8" t="s">
-        <v>51</v>
+      <c r="N22" t="s">
+        <v>166</v>
+      </c>
+      <c r="O22" t="s">
+        <v>54</v>
+      </c>
+      <c r="P22" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>63</v>
+      </c>
+      <c r="R22" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="R2" r:id="rId1" display="https://trt2-jus-br.zoom.us/j/86266293042?pwd=dHpGOENGZTFYY1duYmlIRnBWeEVjUT09%20ID%20da%20reunião:%20862%206629%203042%20Senha%20de%20acesso:%2009400940" xr:uid="{3428CDB3-9346-443B-B958-7A864D67AA09}"/>
-    <hyperlink ref="R4" r:id="rId2" display="https://trt15-jus-br.zoom.us/j/89770082465?pwd=K09aQWhUOW5ESytiRUdCOUFSa2E4dz09%20ID%20da%20reunião:%20897%207008%202465%20Senha%20de%20acesso:%20908050" xr:uid="{7CA507F5-D878-4C10-9028-A16415C0DBA4}"/>
-  </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/Pauta_de_Audiencias.xlsx
+++ b/Pauta_de_Audiencias.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\blu\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{24E8972E-1A08-4D20-8D86-42CA994911D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{120DBA39-A601-40C7-A58A-FE3076E307C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A899EBA7-3EE3-4652-A6F1-216D7279BFBD}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6D6B21FF-2EAF-46D9-8784-D252B7A6E2FD}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_Hlk139463631" localSheetId="0">Planilha1!$A$3</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="201">
   <si>
     <t>Código P&amp;C</t>
   </si>
@@ -95,37 +98,298 @@
     <t>Link/Observações</t>
   </si>
   <si>
+    <t>Audiência Instrução - Presencial</t>
+  </si>
+  <si>
+    <t>1000794-70.2026.5.02.0435</t>
+  </si>
+  <si>
+    <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
+  </si>
+  <si>
+    <t>Gabriel Goncalves Alvares</t>
+  </si>
+  <si>
+    <t>SANTO ANDRÉ</t>
+  </si>
+  <si>
+    <t>SP</t>
+  </si>
+  <si>
+    <t>05ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>Instrução</t>
+  </si>
+  <si>
+    <t>Reclamação Trabalhista</t>
+  </si>
+  <si>
+    <t>CENTRAL</t>
+  </si>
+  <si>
+    <t>R$          2.322.472,80</t>
+  </si>
+  <si>
+    <t>Grupo B1</t>
+  </si>
+  <si>
+    <t>Correspondente - Hebert</t>
+  </si>
+  <si>
+    <t>GSM</t>
+  </si>
+  <si>
+    <t>Presencial</t>
+  </si>
+  <si>
+    <t>Audiência Instrução - Telepresencial</t>
+  </si>
+  <si>
+    <t>0000463-74.2026.5.14.0111</t>
+  </si>
+  <si>
+    <t>Syngenta Digital Ltda.</t>
+  </si>
+  <si>
+    <t>Lucas Rafael Chiquito De Souza</t>
+  </si>
+  <si>
+    <t>PIMENTA BUENO</t>
+  </si>
+  <si>
+    <t>RO</t>
+  </si>
+  <si>
+    <t>VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>1ª Instância</t>
+  </si>
+  <si>
+    <t>R$             235.287,92</t>
+  </si>
+  <si>
+    <t>Grupo E1</t>
+  </si>
+  <si>
+    <t>VRO</t>
+  </si>
+  <si>
+    <t>https://trt14-jus-br.zoom.us/j/87479999418?pwd=Dvi882AxlC4NHugWXyiLgR5Tm3zg5W.1 ID da reunião: 874 7999 9418 Senha: 986377</t>
+  </si>
+  <si>
+    <t>Audiência Una - Presencial</t>
+  </si>
+  <si>
+    <t>1001214-26.2026.5.02.0031</t>
+  </si>
+  <si>
+    <t>Spic Brasil Energia Participações S.A.</t>
+  </si>
+  <si>
+    <t>Martha Ferreira Machado</t>
+  </si>
+  <si>
+    <t>SÃO PAULO</t>
+  </si>
+  <si>
+    <t>31ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$               40.763,68</t>
+  </si>
+  <si>
+    <t>Grupo C</t>
+  </si>
+  <si>
+    <t>ECO</t>
+  </si>
+  <si>
+    <t>Sessão de Julgamento TRT - Presencial</t>
+  </si>
+  <si>
+    <t>0000184-21.2025.5.05.0161</t>
+  </si>
+  <si>
+    <t>Companhia Act De Participações E Companhia Aix De Participações</t>
+  </si>
+  <si>
+    <t>Walney De Oliveira Rodrigues</t>
+  </si>
+  <si>
+    <t>SANTO AMARO</t>
+  </si>
+  <si>
+    <t>BA</t>
+  </si>
+  <si>
+    <t>03ª TURMA</t>
+  </si>
+  <si>
+    <t>Recursal</t>
+  </si>
+  <si>
+    <t>R$             331.871,09</t>
+  </si>
+  <si>
+    <t>VSI</t>
+  </si>
+  <si>
+    <t>link pendente</t>
+  </si>
+  <si>
+    <t>0000717-33.2026.5.05.0132</t>
+  </si>
+  <si>
+    <t>Salitre Fertilizantes Ltda.</t>
+  </si>
+  <si>
+    <t>Silvan Dos Anjos Dos Santos</t>
+  </si>
+  <si>
+    <t>CAMAÇARI</t>
+  </si>
+  <si>
+    <t>02ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>Conhecimento</t>
+  </si>
+  <si>
+    <t>R$               15.684,57</t>
+  </si>
+  <si>
+    <t>Grupo E2</t>
+  </si>
+  <si>
+    <t>RYL</t>
+  </si>
+  <si>
+    <t>CAL</t>
+  </si>
+  <si>
+    <t>https://trt5-jus-br.zoom.us/my/sl2vtcam</t>
+  </si>
+  <si>
+    <t>Audiência Una - Telepresencial</t>
+  </si>
+  <si>
+    <t>1000970-83.2026.5.02.0068</t>
+  </si>
+  <si>
+    <t>Whirlpool S.A</t>
+  </si>
+  <si>
+    <t>Eduardo Akira Kawabata E Electrolux Do Brasil S/A</t>
+  </si>
+  <si>
+    <t>68ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$               65.000,00</t>
+  </si>
+  <si>
+    <t>Grupo A3</t>
+  </si>
+  <si>
+    <t>PBS</t>
+  </si>
+  <si>
+    <t>SOF</t>
+  </si>
+  <si>
+    <t>https://trt2-jus-br.zoom.us/j/81486768468?pwd=TvPkyvfbko93aYtBiWMTAIPOUojzNS.1</t>
+  </si>
+  <si>
+    <t>Audiência Una- Telepresencial</t>
+  </si>
+  <si>
+    <t>0024175-55.2026.5.24.0066</t>
+  </si>
+  <si>
+    <t>Moema Bioenergia S.A. - Monteverde</t>
+  </si>
+  <si>
+    <t>Dionaty Sousa Dos Santos</t>
+  </si>
+  <si>
+    <t>PONTA PORÃ</t>
+  </si>
+  <si>
+    <t>MS</t>
+  </si>
+  <si>
+    <t>R$               55.756,42</t>
+  </si>
+  <si>
+    <t>LWP</t>
+  </si>
+  <si>
+    <t>https://trt24-jus-br.zoom.us/j/88062331360</t>
+  </si>
+  <si>
     <t>Audiência Inicial -  Presencial</t>
   </si>
   <si>
-    <t>1001200-66.2026.5.02.0411</t>
-  </si>
-  <si>
-    <t>Companhia Brasileira De Cartuchos</t>
-  </si>
-  <si>
-    <t>Anderson Fernando Da Silva</t>
+    <t>1001646-97.2026.5.02.0434</t>
+  </si>
+  <si>
+    <t>Flavio Eduardo Basilio</t>
+  </si>
+  <si>
+    <t>R$             287.397,44</t>
+  </si>
+  <si>
+    <t>BSO</t>
+  </si>
+  <si>
+    <t>Audiência de Instrução - Telepresencial</t>
+  </si>
+  <si>
+    <t>0010763-85.2025.5.03.0160</t>
+  </si>
+  <si>
+    <t>Fertilizantes Heringer S.A. - Iguatama - Igt</t>
+  </si>
+  <si>
+    <t>Marcus Vinicios Dos Santos Correia Alves</t>
+  </si>
+  <si>
+    <t>FORMIGA</t>
+  </si>
+  <si>
+    <t>MG</t>
+  </si>
+  <si>
+    <t>R$               66.235,85</t>
+  </si>
+  <si>
+    <t>RRU</t>
+  </si>
+  <si>
+    <t>BBO</t>
+  </si>
+  <si>
+    <t>https://trt3-jus-br.zoom.us/my/vt2formiga</t>
+  </si>
+  <si>
+    <t>Audiência de Instrução - Presencial</t>
+  </si>
+  <si>
+    <t>1000646-34.2026.5.02.0411</t>
+  </si>
+  <si>
+    <t>Cbc - Companhia Brasileira De Cartuchos</t>
+  </si>
+  <si>
+    <t>Danilo Domingos Da Silva</t>
   </si>
   <si>
     <t>RIBEIRÃO PIRES</t>
   </si>
   <si>
-    <t>SP</t>
-  </si>
-  <si>
-    <t>VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>Instrução</t>
-  </si>
-  <si>
-    <t>Reclamação Trabalhista</t>
-  </si>
-  <si>
-    <t>CENTRAL</t>
-  </si>
-  <si>
-    <t>R$               83.648,82</t>
+    <t>R$             121.724,54</t>
   </si>
   <si>
     <t>Grupo B3</t>
@@ -134,502 +398,253 @@
     <t>LMI</t>
   </si>
   <si>
-    <t>Presencial</t>
+    <t>0024052-57.2026.5.24.0066</t>
+  </si>
+  <si>
+    <t>Moema Bioenergia S.A. - Moema</t>
+  </si>
+  <si>
+    <t>Anadirson Alem Dos Santos De Oliveira</t>
+  </si>
+  <si>
+    <t>R$             141.500,00</t>
+  </si>
+  <si>
+    <t>BTF</t>
+  </si>
+  <si>
+    <t>MBF</t>
+  </si>
+  <si>
+    <t>https://trt24-jus-br.zoom.us/j/85366509499</t>
+  </si>
+  <si>
+    <t>1001307-41.2026.5.02.0434</t>
+  </si>
+  <si>
+    <t>Paulo Souza De Almeida</t>
+  </si>
+  <si>
+    <t>04ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$               80.000,00</t>
+  </si>
+  <si>
+    <t>JPE</t>
+  </si>
+  <si>
+    <t>TAM</t>
+  </si>
+  <si>
+    <t>1001691-98.2026.5.02.0435</t>
+  </si>
+  <si>
+    <t>Daiane Silva Nascimento Dos Santos</t>
+  </si>
+  <si>
+    <t>R$             144.115,98</t>
+  </si>
+  <si>
+    <t>RFE</t>
+  </si>
+  <si>
+    <t>1001738-84.2026.5.02.0431</t>
+  </si>
+  <si>
+    <t>Bridgestone Do Brasil Indústria E Comércio Ltda</t>
+  </si>
+  <si>
+    <t>Gregory Leonardo Fernandes</t>
+  </si>
+  <si>
+    <t>01ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$               65.480,35</t>
+  </si>
+  <si>
+    <t>1001157-66.2026.5.02.0432</t>
+  </si>
+  <si>
+    <t>Gustavo Pereira Dos Reis</t>
+  </si>
+  <si>
+    <t>R$               35.699,15</t>
   </si>
   <si>
     <t>Audiência Inicial -  Telepresencial</t>
   </si>
   <si>
-    <t>0010496-56.2026.5.15.0092</t>
-  </si>
-  <si>
-    <t>Telefonica Brasil S.A.</t>
-  </si>
-  <si>
-    <t>Daniel Ferreira Souto</t>
-  </si>
-  <si>
-    <t>CAMPINAS</t>
-  </si>
-  <si>
-    <t>05ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$          1.957.403,00</t>
-  </si>
-  <si>
-    <t>Grupo C</t>
+    <t>0000723-50.2026.5.22.0105</t>
+  </si>
+  <si>
+    <t>Pedro Afonso Bioenergia Ltda.</t>
+  </si>
+  <si>
+    <t>Antonio Da Silva Sousa</t>
+  </si>
+  <si>
+    <t>PIRIPIRI</t>
+  </si>
+  <si>
+    <t>PI</t>
+  </si>
+  <si>
+    <t>R$               19.164,34</t>
+  </si>
+  <si>
+    <t>https://trt22-jus-br.zoom.us/j/86414266800</t>
+  </si>
+  <si>
+    <t>0000724-35.2026.5.22.0105</t>
+  </si>
+  <si>
+    <t>Antonio Marcos Da Silva Penha</t>
+  </si>
+  <si>
+    <t>Inicial</t>
+  </si>
+  <si>
+    <t>R$               19.679,83</t>
+  </si>
+  <si>
+    <t>0000725-20.2026.5.22.0105</t>
+  </si>
+  <si>
+    <t>Antonio Carlos Do Nascimento Leite</t>
+  </si>
+  <si>
+    <t>R$               17.931,44</t>
+  </si>
+  <si>
+    <t>Audiência de Conciliação - Telepresencial</t>
+  </si>
+  <si>
+    <t>0000928-73.2024.5.05.0121</t>
+  </si>
+  <si>
+    <t>Fertilizantes Heringer S.A. - Candeias - Can</t>
+  </si>
+  <si>
+    <t>Eric Fabricio Dos Santos Pereira</t>
+  </si>
+  <si>
+    <t>CANDEIAS</t>
+  </si>
+  <si>
+    <t>CEJUSC</t>
+  </si>
+  <si>
+    <t>R$               23.207,48</t>
+  </si>
+  <si>
+    <t>https://trt5-jus-br.zoom.us/my/cejusc1sala18</t>
+  </si>
+  <si>
+    <t>0000447-03.2026.5.09.0195</t>
+  </si>
+  <si>
+    <t>Anderson Felipe Ferri</t>
+  </si>
+  <si>
+    <t>CASCAVEL</t>
+  </si>
+  <si>
+    <t>PR</t>
+  </si>
+  <si>
+    <t>03ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             881.000,00</t>
+  </si>
+  <si>
+    <t>https://url.trt9.jus.br/s8jj9 ID da Reunião: 83482068288 Senha: sM3uxxhDB0</t>
+  </si>
+  <si>
+    <t>Audiência de Encerramento de Instrução</t>
+  </si>
+  <si>
+    <t>0000049-63.2026.5.09.0128</t>
+  </si>
+  <si>
+    <t>Edison Luiz Souza</t>
+  </si>
+  <si>
+    <t>R$               61.000,00</t>
   </si>
   <si>
     <t>TFR</t>
   </si>
   <si>
-    <t>https://trt15-jus-br.zoom.us/j/84146096644?pwd=STloZzBJSTFaMW5PeXZRYlIrRGlIdz0</t>
-  </si>
-  <si>
-    <t>Audiência Instrução - Presencial</t>
-  </si>
-  <si>
-    <t>1000629-33.2026.5.02.0464</t>
-  </si>
-  <si>
-    <t>Mahle Metal Leve S.A.</t>
-  </si>
-  <si>
-    <t>Dario Pereira</t>
-  </si>
-  <si>
-    <t>SÃO BERNARDO DO CAMPO</t>
-  </si>
-  <si>
-    <t>04ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$             310.000,00</t>
-  </si>
-  <si>
-    <t>Grupo E1</t>
-  </si>
-  <si>
-    <t>VRO</t>
-  </si>
-  <si>
-    <t>Audiência Una - Presencial</t>
-  </si>
-  <si>
-    <t>1001092-71.2026.5.02.0432</t>
-  </si>
-  <si>
-    <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
-  </si>
-  <si>
-    <t>Edson Da Silva Morgado</t>
-  </si>
-  <si>
-    <t>SANTO ANDRÉ</t>
-  </si>
-  <si>
-    <t>02ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$          2.126.834,60</t>
-  </si>
-  <si>
-    <t>Grupo B1</t>
-  </si>
-  <si>
-    <t>GSM</t>
-  </si>
-  <si>
-    <t>0011184-68.2026.5.15.0140</t>
-  </si>
-  <si>
-    <t>Grammer Do Brasil</t>
-  </si>
-  <si>
-    <t>David Estevao Junior</t>
-  </si>
-  <si>
-    <t>ATIBAIA</t>
-  </si>
-  <si>
-    <t>R$               56.846,94</t>
+    <t>https://url.trt9.jus.br/rypyv ID da reunião: 87526086719 Senha de acesso: C9wehw1Pg0</t>
+  </si>
+  <si>
+    <t>0000183-90.2026.5.09.0128</t>
+  </si>
+  <si>
+    <t>R$             205.600,00</t>
+  </si>
+  <si>
+    <t>0010657-94.2026.5.03.0029</t>
+  </si>
+  <si>
+    <t>Sistenge Construções E Comércio Ltda.</t>
+  </si>
+  <si>
+    <t>Rodrigo Junio De Souza</t>
+  </si>
+  <si>
+    <t>CONTAGEM</t>
+  </si>
+  <si>
+    <t>Acordo</t>
+  </si>
+  <si>
+    <t>R$               34.332,73</t>
+  </si>
+  <si>
+    <t>https://trt3-jus-br.zoom.us/my/vt1.contagem</t>
+  </si>
+  <si>
+    <t>0010622-38.2026.5.15.0050</t>
+  </si>
+  <si>
+    <t>Viterra Bioenergia S.A.</t>
+  </si>
+  <si>
+    <t>Jeferson De Souza Alves Antonio</t>
+  </si>
+  <si>
+    <t>DRACENA</t>
+  </si>
+  <si>
+    <t>R$             323.874,68</t>
   </si>
   <si>
     <t>AAP</t>
   </si>
   <si>
-    <t>JPL</t>
-  </si>
-  <si>
-    <t>0011283-47.2025.5.15.0019</t>
-  </si>
-  <si>
-    <t>Viterra Bioenergia S.A.</t>
-  </si>
-  <si>
-    <t>Bruno Cesar Alves</t>
-  </si>
-  <si>
-    <t>ARAÇATUBA</t>
-  </si>
-  <si>
-    <t>01ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$             319.333,36</t>
-  </si>
-  <si>
-    <t>Grupo E2</t>
-  </si>
-  <si>
-    <t>Correspondente - Carla</t>
-  </si>
-  <si>
-    <t>1001101-96.2026.5.02.0411</t>
-  </si>
-  <si>
-    <t>Sidnei Da Silva Dantas</t>
-  </si>
-  <si>
-    <t>R$               46.770,44</t>
-  </si>
-  <si>
-    <t>Audiência Instrução - Telepresencial</t>
-  </si>
-  <si>
-    <t>0010412-48.2026.5.03.0073</t>
-  </si>
-  <si>
-    <t>Hrz Energia</t>
-  </si>
-  <si>
-    <t>Alexandre Nery Ferreira</t>
-  </si>
-  <si>
-    <t>POÇOS DE CALDAS</t>
-  </si>
-  <si>
-    <t>MG</t>
-  </si>
-  <si>
-    <t>R$             644.064,82</t>
-  </si>
-  <si>
-    <t>Grupo B2</t>
-  </si>
-  <si>
-    <t>NRG</t>
-  </si>
-  <si>
-    <t>https://trt3-jus-br.zoom.us/my/vt2.passos</t>
-  </si>
-  <si>
-    <t>Audiência de Conciliação - Telepresencial</t>
-  </si>
-  <si>
-    <t>0010265-04.2026.5.03.0176</t>
-  </si>
-  <si>
-    <t>Uhe São Simão Energia S.A.</t>
-  </si>
-  <si>
-    <t>Luis Felipe Pereira Andrade</t>
-  </si>
-  <si>
-    <t>ITUIUTABA</t>
-  </si>
-  <si>
-    <t>R$               63.000,00</t>
-  </si>
-  <si>
-    <t>ECO</t>
-  </si>
-  <si>
-    <t>https://trt3-jus-br.zoom.us/j/83446217509</t>
-  </si>
-  <si>
-    <t>1001135-11.2026.5.02.0431</t>
-  </si>
-  <si>
-    <t>Marcos Aurelio Rodrigues Goncalves</t>
-  </si>
-  <si>
-    <t>R$             807.744,00</t>
-  </si>
-  <si>
-    <t>JPE</t>
-  </si>
-  <si>
-    <t>BSO</t>
-  </si>
-  <si>
-    <t>0010827-38.2025.5.15.0071</t>
-  </si>
-  <si>
-    <t>Rafael Querubim Medici Amorim</t>
-  </si>
-  <si>
-    <t>MOGI GUAÇU</t>
-  </si>
-  <si>
-    <t>Inicial</t>
-  </si>
-  <si>
-    <t>R$             331.734,05</t>
-  </si>
-  <si>
-    <t>PSI</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/5326391733?pwd=Qjc4RFBXWjZNbVd1bG5wNldjR3dWZz09</t>
-  </si>
-  <si>
-    <t>1000533-30.2026.5.02.0363</t>
-  </si>
-  <si>
-    <t>Renato Fernandes Heleno</t>
-  </si>
-  <si>
-    <t>MAUÁ</t>
-  </si>
-  <si>
-    <t>03ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$             571.654,41</t>
-  </si>
-  <si>
-    <t>RFE</t>
-  </si>
-  <si>
-    <t>0010620-68.2026.5.15.0050</t>
-  </si>
-  <si>
-    <t>Marcio Aragao De Melo</t>
-  </si>
-  <si>
-    <t>DRACENA</t>
-  </si>
-  <si>
-    <t>R$               35.458,88</t>
-  </si>
-  <si>
-    <t>MBF</t>
-  </si>
-  <si>
-    <t>CAL</t>
-  </si>
-  <si>
     <t>https://trt15-jus.br.zoom.us/j/87527564652?pwd=d3YrZ2diWXk5UjgzbmVkNExteWVMQT09</t>
   </si>
   <si>
-    <t>0010089-36.2026.5.15.0129</t>
-  </si>
-  <si>
-    <t>Lucas De Oliveira Lima</t>
-  </si>
-  <si>
-    <t>10ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$               32.965,01</t>
-  </si>
-  <si>
-    <t>Correspondente - Carlos Florian</t>
-  </si>
-  <si>
-    <t>Presencial | Advogada - Dra. Isis Zuri, (19) 99287-5454 | Preposta - Juliana da Silva Oliveira, CPF 285.253.868-71, RG 359894124, (19) 98743-4081</t>
-  </si>
-  <si>
-    <t>Sessão de Julgamento TRT - Telepresencial</t>
-  </si>
-  <si>
-    <t>0010625-64.2021.5.15.0083</t>
-  </si>
-  <si>
-    <t>Yaborã Indústria Aeronáutica S.A.</t>
-  </si>
-  <si>
-    <t>Rogerio Nacimento Costa Pinto</t>
-  </si>
-  <si>
-    <t>SÃO JOSÉ DOS CAMPOS</t>
-  </si>
-  <si>
-    <t>03ª TURMA</t>
-  </si>
-  <si>
-    <t>Recursal</t>
-  </si>
-  <si>
-    <t>R$             193.321,78</t>
-  </si>
-  <si>
-    <t>BCF</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/89948955228?pwd=Vxka0xpnjrrjCMbWqVbY0TE64PtkXn.1</t>
-  </si>
-  <si>
-    <t>0010499-82.2026.5.15.0133</t>
-  </si>
-  <si>
-    <t>Syngenta Proteção De Cultivos Ltda.</t>
-  </si>
-  <si>
-    <t>Jose Luiz Dos Santos</t>
-  </si>
-  <si>
-    <t>SÃO JOSÉ DO RIO PRETO</t>
-  </si>
-  <si>
-    <t>1ª Instância</t>
-  </si>
-  <si>
-    <t>R$             471.779,49</t>
-  </si>
-  <si>
-    <t>GVM</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/7871570572?pwd=KzBzUnVURkZwc0gxd21YU3pUWWhJQT09</t>
-  </si>
-  <si>
-    <t>Audiência Una - Telepresencial</t>
-  </si>
-  <si>
-    <t>0012204-93.2025.5.15.0087</t>
-  </si>
-  <si>
-    <t>Renato Ranulfo Seviolla Magalhaes</t>
-  </si>
-  <si>
-    <t>PAULÍNIA</t>
-  </si>
-  <si>
-    <t>R$             372.859,54</t>
-  </si>
-  <si>
-    <t>JRM</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/85267876480?pwd=tETOC8GDaqZZdf9WNGOaW98aPE2MQx.1</t>
-  </si>
-  <si>
-    <t>0011355-05.2026.5.15.0082</t>
-  </si>
-  <si>
-    <t>Moema Bioenergia S.A. - Moema</t>
-  </si>
-  <si>
-    <t>Floresvaldo Sampaio</t>
-  </si>
-  <si>
-    <t>R$             162.160,00</t>
-  </si>
-  <si>
-    <t>LWP</t>
+    <t>0010451-53.2026.5.15.0027</t>
+  </si>
+  <si>
+    <t>Guariroba Bioenergia Ltda.</t>
+  </si>
+  <si>
+    <t>Valdeir Cesar De Oliveira</t>
+  </si>
+  <si>
+    <t>VOTUPORANGA</t>
+  </si>
+  <si>
+    <t>R$             474.192,34</t>
   </si>
   <si>
     <t>https://trt15-jus-br.zoom.us/j/88542672682?pwd=7pQ4QRhZmRG9RAQAWKowymbwNawa7t.1</t>
-  </si>
-  <si>
-    <t>0010628-45.2026.5.15.0050</t>
-  </si>
-  <si>
-    <t>Jose Graciel Felix De Souza</t>
-  </si>
-  <si>
-    <t>R$               64.436,81</t>
-  </si>
-  <si>
-    <t>RYL</t>
-  </si>
-  <si>
-    <t>Sessão de Julgamento TRT - Presencial</t>
-  </si>
-  <si>
-    <t>0010928-75.2025.5.15.0071</t>
-  </si>
-  <si>
-    <t>Mislene Santos Do Nascimento</t>
-  </si>
-  <si>
-    <t>04ª TURMA</t>
-  </si>
-  <si>
-    <t>R$             763.302,38</t>
-  </si>
-  <si>
-    <t>KBM</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/81338233394?pwd=9sZYKqQDl9HW1PQRiyWxtnDNoRMuzq.1 ID da reunião: 813 3823 3394 Senha: 181436</t>
-  </si>
-  <si>
-    <t>0010480-82.2025.5.15.0013</t>
-  </si>
-  <si>
-    <t>Embraer S.A.</t>
-  </si>
-  <si>
-    <t>Paulo Pereira Cabral Da Silva</t>
-  </si>
-  <si>
-    <t>R$               39.651,24</t>
-  </si>
-  <si>
-    <t>ANB</t>
-  </si>
-  <si>
-    <t>0010408-53.2026.5.03.0156</t>
-  </si>
-  <si>
-    <t>Itapagipe Bioenergia Ltda.</t>
-  </si>
-  <si>
-    <t>Bruno Da Silva Maia</t>
-  </si>
-  <si>
-    <t>FRUTAL</t>
-  </si>
-  <si>
-    <t>R$             100.607,86</t>
-  </si>
-  <si>
-    <t>https://trt3-jus-br.zoom.us/my/vtfrutal</t>
-  </si>
-  <si>
-    <t>1002113-47.2024.5.02.0434</t>
-  </si>
-  <si>
-    <t>Felipe Eduardo Albano De Freitas</t>
-  </si>
-  <si>
-    <t>CEJUSC ABC</t>
-  </si>
-  <si>
-    <t>Execução</t>
-  </si>
-  <si>
-    <t>R$             660.679,72</t>
-  </si>
-  <si>
-    <t>https://trt2-jus-br.zoom.us/j/86579309928?pwd=ZXdjSDg5U0llVFZYWktxT3h5SzRRZz09 ID da reunião: 865 7930 9928 Senha de acesso: 171003</t>
-  </si>
-  <si>
-    <t>0010656-76.2026.5.15.0126</t>
-  </si>
-  <si>
-    <t>Manoel Messias Ferreira</t>
-  </si>
-  <si>
-    <t>R$             242.003,29</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/83352065501?pwd=Lzc2WUJGSVpVWmJyZjB3Y0NvUmJPZz09</t>
-  </si>
-  <si>
-    <t>0011217-57.2023.5.15.0045</t>
-  </si>
-  <si>
-    <t>Valmir Henrique Franca</t>
-  </si>
-  <si>
-    <t>CEJUSC TST</t>
-  </si>
-  <si>
-    <t>Recursal TST</t>
-  </si>
-  <si>
-    <t>R$             752.419,84</t>
-  </si>
-  <si>
-    <t>VCR</t>
-  </si>
-  <si>
-    <t>bit.ly/Cejusc2026</t>
   </si>
 </sst>
 </file>
@@ -1094,30 +1109,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DC6FEC1-4DBD-4FE8-A541-E3012D8A8A90}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4BA9B5F-64AD-40BE-A136-29A2274B0B14}">
   <dimension ref="A1:R26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="34.21875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="26.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.88671875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.5546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.21875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="52.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="39.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.21875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.77734375" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="26.88671875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="28.6640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="99.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="27.109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="28.88671875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="101" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1175,13 +1190,13 @@
     </row>
     <row r="2" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4">
-        <v>105869</v>
+        <v>104857</v>
       </c>
       <c r="B2" s="5">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C2" s="6">
-        <v>0.3611111111111111</v>
+        <v>0.36805555555555558</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>18</v>
@@ -1223,45 +1238,45 @@
         <v>30</v>
       </c>
       <c r="Q2" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="R2" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4">
-        <v>106141</v>
+        <v>105754</v>
       </c>
       <c r="B3" s="5">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C3" s="6">
-        <v>0.3611111111111111</v>
+        <v>0.375</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="L3" s="7" t="s">
         <v>26</v>
@@ -1270,51 +1285,51 @@
         <v>27</v>
       </c>
       <c r="N3" s="7" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="O3" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="P3" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="Q3" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R3" s="7" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4">
-        <v>104807</v>
+        <v>105874</v>
       </c>
       <c r="B4" s="5">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C4" s="6">
         <v>0.375</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I4" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="K4" s="7" t="s">
         <v>25</v>
@@ -1326,54 +1341,54 @@
         <v>27</v>
       </c>
       <c r="N4" s="7" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="O4" s="7" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="P4" s="7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="Q4" s="7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="R4" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4">
-        <v>105231</v>
+        <v>103592</v>
       </c>
       <c r="B5" s="5">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C5" s="6">
-        <v>0.3888888888888889</v>
+        <v>0.375</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="L5" s="7" t="s">
         <v>26</v>
@@ -1382,54 +1397,54 @@
         <v>27</v>
       </c>
       <c r="N5" s="7" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="O5" s="7" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="P5" s="7" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="Q5" s="7" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="R5" s="7" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4">
-        <v>104933</v>
+        <v>105674</v>
       </c>
       <c r="B6" s="5">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C6" s="6">
-        <v>0.44791666666666669</v>
+        <v>0.38194444444444442</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>24</v>
+        <v>69</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="L6" s="7" t="s">
         <v>26</v>
@@ -1438,51 +1453,51 @@
         <v>27</v>
       </c>
       <c r="N6" s="7" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="O6" s="7" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="P6" s="7" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="Q6" s="7" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="R6" s="7" t="s">
-        <v>31</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4">
-        <v>103325</v>
+        <v>105272</v>
       </c>
       <c r="B7" s="5">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C7" s="6">
-        <v>0.4513888888888889</v>
+        <v>0.39583333333333331</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>42</v>
+        <v>76</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="I7" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="K7" s="7" t="s">
         <v>25</v>
@@ -1494,51 +1509,51 @@
         <v>27</v>
       </c>
       <c r="N7" s="7" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="O7" s="7" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="P7" s="7" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="Q7" s="7" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="R7" s="7" t="s">
-        <v>31</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4">
-        <v>105668</v>
+        <v>104492</v>
       </c>
       <c r="B8" s="5">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C8" s="6">
-        <v>0.4513888888888889</v>
+        <v>0.39583333333333331</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>51</v>
+        <v>86</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>23</v>
+        <v>91</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="K8" s="7" t="s">
         <v>25</v>
@@ -1550,51 +1565,51 @@
         <v>27</v>
       </c>
       <c r="N8" s="7" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="O8" s="7" t="s">
-        <v>29</v>
+        <v>72</v>
       </c>
       <c r="P8" s="7" t="s">
-        <v>30</v>
+        <v>74</v>
       </c>
       <c r="Q8" s="7" t="s">
-        <v>30</v>
+        <v>93</v>
       </c>
       <c r="R8" s="7" t="s">
-        <v>31</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4">
-        <v>105368</v>
+        <v>105935</v>
       </c>
       <c r="B9" s="5">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C9" s="6">
-        <v>0.45833333333333331</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>83</v>
+        <v>23</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="K9" s="7" t="s">
         <v>25</v>
@@ -1606,51 +1621,51 @@
         <v>27</v>
       </c>
       <c r="N9" s="7" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="O9" s="7" t="s">
-        <v>85</v>
+        <v>29</v>
       </c>
       <c r="P9" s="7" t="s">
-        <v>86</v>
+        <v>30</v>
       </c>
       <c r="Q9" s="7" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="R9" s="7" t="s">
-        <v>87</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4">
-        <v>104575</v>
+        <v>102444</v>
       </c>
       <c r="B10" s="5">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C10" s="6">
-        <v>0.46527777777777779</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>83</v>
+        <v>105</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="K10" s="7" t="s">
         <v>25</v>
@@ -1662,51 +1677,51 @@
         <v>27</v>
       </c>
       <c r="N10" s="7" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="O10" s="7" t="s">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="P10" s="7" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="Q10" s="7" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="R10" s="7" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4">
-        <v>105261</v>
+        <v>104855</v>
       </c>
       <c r="B11" s="5">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C11" s="6">
-        <v>0.47222222222222221</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>42</v>
+        <v>110</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>53</v>
+        <v>112</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>55</v>
+        <v>114</v>
       </c>
       <c r="I11" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="K11" s="7" t="s">
         <v>25</v>
@@ -1718,54 +1733,54 @@
         <v>27</v>
       </c>
       <c r="N11" s="7" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="O11" s="7" t="s">
-        <v>58</v>
+        <v>116</v>
       </c>
       <c r="P11" s="7" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="Q11" s="7" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="R11" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="4">
-        <v>101325</v>
+        <v>104198</v>
       </c>
       <c r="B12" s="5">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C12" s="6">
-        <v>0.49305555555555558</v>
+        <v>0.43055555555555558</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>44</v>
+        <v>119</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>23</v>
+        <v>91</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>104</v>
+        <v>25</v>
       </c>
       <c r="L12" s="7" t="s">
         <v>26</v>
@@ -1774,51 +1789,51 @@
         <v>27</v>
       </c>
       <c r="N12" s="7" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="O12" s="7" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="P12" s="7" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="Q12" s="7" t="s">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="R12" s="7" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4">
-        <v>104806</v>
+        <v>105579</v>
       </c>
       <c r="B13" s="5">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C13" s="6">
-        <v>0.49305555555555558</v>
+        <v>0.4375</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>110</v>
+        <v>22</v>
       </c>
       <c r="I13" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="K13" s="7" t="s">
         <v>25</v>
@@ -1830,45 +1845,45 @@
         <v>27</v>
       </c>
       <c r="N13" s="7" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="O13" s="7" t="s">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="P13" s="7" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="Q13" s="7" t="s">
-        <v>59</v>
+        <v>130</v>
       </c>
       <c r="R13" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="4">
-        <v>104967</v>
+        <v>105955</v>
       </c>
       <c r="B14" s="5">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C14" s="6">
-        <v>0.54166666666666663</v>
+        <v>0.4513888888888889</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>116</v>
+        <v>22</v>
       </c>
       <c r="I14" s="7" t="s">
         <v>23</v>
@@ -1886,51 +1901,51 @@
         <v>27</v>
       </c>
       <c r="N14" s="7" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="O14" s="7" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="P14" s="7" t="s">
-        <v>118</v>
+        <v>30</v>
       </c>
       <c r="Q14" s="7" t="s">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="R14" s="7" t="s">
-        <v>120</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4">
-        <v>103814</v>
+        <v>106017</v>
       </c>
       <c r="B15" s="5">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C15" s="6">
-        <v>0.54861111111111116</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>53</v>
+        <v>136</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="I15" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="K15" s="7" t="s">
         <v>25</v>
@@ -1942,54 +1957,54 @@
         <v>27</v>
       </c>
       <c r="N15" s="7" t="s">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="O15" s="7" t="s">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="P15" s="7" t="s">
-        <v>125</v>
+        <v>31</v>
       </c>
       <c r="Q15" s="7" t="s">
-        <v>100</v>
+        <v>134</v>
       </c>
       <c r="R15" s="7" t="s">
-        <v>126</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="4">
-        <v>79991</v>
+        <v>105295</v>
       </c>
       <c r="B16" s="5">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C16" s="6">
-        <v>0.5625</v>
+        <v>0.46180555555555558</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>127</v>
+        <v>45</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>129</v>
+        <v>20</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>131</v>
+        <v>22</v>
       </c>
       <c r="I16" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>132</v>
+        <v>69</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>133</v>
+        <v>25</v>
       </c>
       <c r="L16" s="7" t="s">
         <v>26</v>
@@ -1998,54 +2013,54 @@
         <v>27</v>
       </c>
       <c r="N16" s="7" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="O16" s="7" t="s">
-        <v>85</v>
+        <v>29</v>
       </c>
       <c r="P16" s="7" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="Q16" s="7" t="s">
-        <v>135</v>
+        <v>99</v>
       </c>
       <c r="R16" s="7" t="s">
-        <v>136</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="4">
-        <v>104334</v>
+        <v>105544</v>
       </c>
       <c r="B17" s="5">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C17" s="6">
-        <v>0.58333333333333337</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>78</v>
+        <v>143</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>23</v>
+        <v>148</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>141</v>
+        <v>25</v>
       </c>
       <c r="L17" s="7" t="s">
         <v>26</v>
@@ -2054,54 +2069,54 @@
         <v>27</v>
       </c>
       <c r="N17" s="7" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="O17" s="7" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="P17" s="7" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="Q17" s="7" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="R17" s="7" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
     </row>
     <row r="18" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="4">
-        <v>103649</v>
+        <v>105545</v>
       </c>
       <c r="B18" s="5">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C18" s="6">
-        <v>0.59722222222222221</v>
+        <v>0.4826388888888889</v>
       </c>
       <c r="D18" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="F18" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="E18" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>138</v>
-      </c>
       <c r="G18" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="H18" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="H18" s="7" t="s">
+      <c r="I18" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="I18" s="7" t="s">
-        <v>23</v>
-      </c>
       <c r="J18" s="7" t="s">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="L18" s="7" t="s">
         <v>26</v>
@@ -2110,54 +2125,54 @@
         <v>27</v>
       </c>
       <c r="N18" s="7" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="O18" s="7" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="P18" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q18" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="R18" s="7" t="s">
         <v>150</v>
-      </c>
-      <c r="Q18" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="R18" s="7" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="19" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="4">
-        <v>105341</v>
+        <v>105546</v>
       </c>
       <c r="B19" s="5">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C19" s="6">
-        <v>0.59722222222222221</v>
+        <v>0.4861111111111111</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>32</v>
+        <v>143</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="F19" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="K19" s="7" t="s">
         <v>153</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="I19" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="J19" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="K19" s="7" t="s">
-        <v>25</v>
       </c>
       <c r="L19" s="7" t="s">
         <v>26</v>
@@ -2166,54 +2181,54 @@
         <v>27</v>
       </c>
       <c r="N19" s="7" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="O19" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P19" s="7" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="Q19" s="7" t="s">
-        <v>156</v>
+        <v>123</v>
       </c>
       <c r="R19" s="7" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
     </row>
     <row r="20" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="4">
-        <v>104968</v>
+        <v>102261</v>
       </c>
       <c r="B20" s="5">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C20" s="6">
-        <v>0.60416666666666663</v>
+        <v>0.4861111111111111</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>78</v>
+        <v>158</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>68</v>
+        <v>160</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>116</v>
+        <v>162</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>24</v>
+        <v>163</v>
       </c>
       <c r="K20" s="7" t="s">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="L20" s="7" t="s">
         <v>26</v>
@@ -2222,54 +2237,54 @@
         <v>27</v>
       </c>
       <c r="N20" s="7" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="O20" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P20" s="7" t="s">
-        <v>118</v>
+        <v>74</v>
       </c>
       <c r="Q20" s="7" t="s">
-        <v>161</v>
+        <v>108</v>
       </c>
       <c r="R20" s="7" t="s">
-        <v>120</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="4">
-        <v>101050</v>
+        <v>104518</v>
       </c>
       <c r="B21" s="5">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C21" s="6">
-        <v>0.60416666666666663</v>
+        <v>0.5625</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>162</v>
+        <v>33</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>103</v>
+        <v>168</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>23</v>
+        <v>169</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>133</v>
+        <v>25</v>
       </c>
       <c r="L21" s="7" t="s">
         <v>26</v>
@@ -2278,54 +2293,54 @@
         <v>27</v>
       </c>
       <c r="N21" s="7" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="O21" s="7" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="P21" s="7" t="s">
-        <v>167</v>
+        <v>53</v>
       </c>
       <c r="Q21" s="7" t="s">
-        <v>106</v>
+        <v>63</v>
       </c>
       <c r="R21" s="7" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
     </row>
     <row r="22" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="4">
-        <v>100167</v>
+        <v>103768</v>
       </c>
       <c r="B22" s="5">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C22" s="6">
-        <v>0.60416666666666663</v>
+        <v>0.5625</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="E22" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="I22" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="F22" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="G22" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="H22" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="I22" s="7" t="s">
-        <v>23</v>
-      </c>
       <c r="J22" s="7" t="s">
-        <v>165</v>
+        <v>69</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>133</v>
+        <v>25</v>
       </c>
       <c r="L22" s="7" t="s">
         <v>26</v>
@@ -2334,51 +2349,51 @@
         <v>27</v>
       </c>
       <c r="N22" s="7" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="O22" s="7" t="s">
-        <v>85</v>
+        <v>52</v>
       </c>
       <c r="P22" s="7" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="Q22" s="7" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="R22" s="7" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
     </row>
     <row r="23" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="4">
-        <v>104959</v>
+        <v>104017</v>
       </c>
       <c r="B23" s="5">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C23" s="6">
-        <v>0.61111111111111116</v>
+        <v>0.56319444444444444</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>78</v>
+        <v>173</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="F23" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="G23" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="G23" s="7" t="s">
-        <v>176</v>
-      </c>
       <c r="H23" s="7" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>83</v>
+        <v>169</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>24</v>
+        <v>69</v>
       </c>
       <c r="K23" s="7" t="s">
         <v>25</v>
@@ -2390,54 +2405,54 @@
         <v>27</v>
       </c>
       <c r="N23" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="O23" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="P23" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q23" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="R23" s="7" t="s">
         <v>178</v>
-      </c>
-      <c r="O23" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="P23" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="Q23" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="R23" s="7" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="24" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="4">
-        <v>99358</v>
+        <v>104768</v>
       </c>
       <c r="B24" s="5">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C24" s="6">
-        <v>0.65555555555555556</v>
+        <v>0.59375</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>88</v>
+        <v>158</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>53</v>
+        <v>182</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>55</v>
+        <v>184</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>23</v>
+        <v>105</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>182</v>
+        <v>138</v>
       </c>
       <c r="K24" s="7" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="L24" s="7" t="s">
         <v>26</v>
@@ -2446,54 +2461,54 @@
         <v>27</v>
       </c>
       <c r="N24" s="7" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="O24" s="7" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="P24" s="7" t="s">
-        <v>99</v>
+        <v>73</v>
       </c>
       <c r="Q24" s="7" t="s">
-        <v>99</v>
+        <v>73</v>
       </c>
       <c r="R24" s="7" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="25" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="4">
-        <v>104930</v>
+        <v>105106</v>
       </c>
       <c r="B25" s="5">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C25" s="6">
-        <v>0.67361111111111116</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>145</v>
+        <v>33</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>138</v>
+        <v>189</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>148</v>
+        <v>191</v>
       </c>
       <c r="I25" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="K25" s="7" t="s">
-        <v>141</v>
+        <v>70</v>
       </c>
       <c r="L25" s="7" t="s">
         <v>26</v>
@@ -2502,54 +2517,54 @@
         <v>27</v>
       </c>
       <c r="N25" s="7" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="O25" s="7" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="P25" s="7" t="s">
-        <v>66</v>
+        <v>193</v>
       </c>
       <c r="Q25" s="7" t="s">
-        <v>143</v>
+        <v>193</v>
       </c>
       <c r="R25" s="7" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
     </row>
     <row r="26" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="4">
-        <v>95035</v>
+        <v>104811</v>
       </c>
       <c r="B26" s="5">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C26" s="6">
-        <v>0.68055555555555558</v>
+        <v>0.63541666666666663</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>88</v>
+        <v>33</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>170</v>
+        <v>196</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>131</v>
+        <v>198</v>
       </c>
       <c r="I26" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>192</v>
+        <v>39</v>
       </c>
       <c r="K26" s="7" t="s">
-        <v>193</v>
+        <v>25</v>
       </c>
       <c r="L26" s="7" t="s">
         <v>26</v>
@@ -2558,38 +2573,39 @@
         <v>27</v>
       </c>
       <c r="N26" s="7" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="O26" s="7" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="P26" s="7" t="s">
-        <v>195</v>
+        <v>123</v>
       </c>
       <c r="Q26" s="7" t="s">
-        <v>195</v>
+        <v>74</v>
       </c>
       <c r="R26" s="7" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="R3" r:id="rId1" xr:uid="{21390778-6B75-4737-BBF0-016C2BC00A37}"/>
-    <hyperlink ref="R9" r:id="rId2" xr:uid="{AAAE512A-B78E-4531-962D-BD2BE128CA20}"/>
-    <hyperlink ref="R10" r:id="rId3" xr:uid="{F795E5B6-5162-4CD5-8F9D-24AA106958F2}"/>
-    <hyperlink ref="R12" r:id="rId4" xr:uid="{31523305-119F-4B4A-83EA-ED37981E65B4}"/>
-    <hyperlink ref="R14" r:id="rId5" xr:uid="{F1833C40-B8B5-4BF0-A281-29379D2E307A}"/>
-    <hyperlink ref="R16" r:id="rId6" xr:uid="{12737FC0-59B3-4D41-B038-877F94886E44}"/>
-    <hyperlink ref="R17" r:id="rId7" xr:uid="{688E861C-3DA6-4E58-BC84-316E52BDB333}"/>
-    <hyperlink ref="R18" r:id="rId8" xr:uid="{DB3BD961-3D16-4085-85E0-CCFE7F1F6F7A}"/>
-    <hyperlink ref="R19" r:id="rId9" xr:uid="{1D600027-95A5-42D9-B3C3-7ECBEBCF1E8B}"/>
-    <hyperlink ref="R20" r:id="rId10" xr:uid="{CCDC4D54-A201-4377-8698-74741A7985E6}"/>
-    <hyperlink ref="R21" r:id="rId11" display="https://trt15-jus-br.zoom.us/j/81338233394?pwd=9sZYKqQDl9HW1PQRiyWxtnDNoRMuzq.1%20ID%20da%20reunião:%20813%203823%203394%20Senha:%20181436" xr:uid="{F1142A8A-F128-4FBD-8F21-AF02939D23F1}"/>
-    <hyperlink ref="R22" r:id="rId12" display="https://trt15-jus-br.zoom.us/j/81338233394?pwd=9sZYKqQDl9HW1PQRiyWxtnDNoRMuzq.1%20ID%20da%20reunião:%20813%203823%203394%20Senha:%20181436" xr:uid="{57711ECA-04ED-4D43-8768-7703BCA0506E}"/>
-    <hyperlink ref="R23" r:id="rId13" xr:uid="{4DE35AFD-F454-4875-A32A-C963088278B6}"/>
-    <hyperlink ref="R24" r:id="rId14" display="https://trt2-jus-br.zoom.us/j/86579309928?pwd=ZXdjSDg5U0llVFZYWktxT3h5SzRRZz09%20ID%20da%20reunião:%20865%207930%209928%20Senha%20de%20acesso:%20171003" xr:uid="{B1DA8C29-1140-4F09-AB5C-D7EBC161A31E}"/>
-    <hyperlink ref="R25" r:id="rId15" xr:uid="{5708E9C2-AEBF-413A-BF6D-9D265BBA5E59}"/>
+    <hyperlink ref="R3" r:id="rId1" display="https://trt14-jus-br.zoom.us/j/87479999418?pwd=Dvi882AxlC4NHugWXyiLgR5Tm3zg5W.1%20ID%20da%20reunião:%20874%207999%209418%20Senha:%20986377" xr:uid="{673EF94E-78A6-492F-8648-55A3D099E909}"/>
+    <hyperlink ref="R6" r:id="rId2" xr:uid="{AA314538-1C38-4354-86E5-68E87B982D8E}"/>
+    <hyperlink ref="R7" r:id="rId3" xr:uid="{2994172D-10B1-4E38-8B17-6E40060423C8}"/>
+    <hyperlink ref="R8" r:id="rId4" xr:uid="{337F0E7C-9834-4F6A-9366-2EE1C8C3ED34}"/>
+    <hyperlink ref="R10" r:id="rId5" xr:uid="{39C64E5E-477A-4E44-89F4-F4BDC7900F55}"/>
+    <hyperlink ref="R12" r:id="rId6" xr:uid="{BC5523E5-17AF-4C68-A62F-E6DF014877CF}"/>
+    <hyperlink ref="R17" r:id="rId7" display="https://trt24-jus-br.zoom.us/j/85366509499" xr:uid="{DB0C2D5F-E147-4E7A-8BE4-F33AE0556B4F}"/>
+    <hyperlink ref="R18" r:id="rId8" display="https://trt24-jus-br.zoom.us/j/85366509499" xr:uid="{491C03DC-F319-4A89-97E1-7591FFD1A851}"/>
+    <hyperlink ref="R19" r:id="rId9" display="https://trt24-jus-br.zoom.us/j/85366509499" xr:uid="{6881F188-59F0-4EF1-99F9-84F5B01E0687}"/>
+    <hyperlink ref="R20" r:id="rId10" xr:uid="{C40BC2D4-5634-4A74-BD93-2B0CB2A7D70C}"/>
+    <hyperlink ref="R21" r:id="rId11" xr:uid="{40E68771-6D02-4BFF-9A46-E2B165D419BF}"/>
+    <hyperlink ref="R22" r:id="rId12" xr:uid="{F94979A7-0CE2-472D-85F0-6E4C831FD8B8}"/>
+    <hyperlink ref="R23" r:id="rId13" xr:uid="{C4163228-EBAE-4ACB-9A5A-BF01A833E4C2}"/>
+    <hyperlink ref="R24" r:id="rId14" xr:uid="{8E3D49F9-3FE0-4C21-9505-73904F08F907}"/>
+    <hyperlink ref="R25" r:id="rId15" xr:uid="{93E3311E-435F-49CB-9DDA-D716D182C785}"/>
+    <hyperlink ref="R26" r:id="rId16" xr:uid="{0905EEA3-9A4C-4F86-82A7-9C748403172B}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/Pauta_de_Audiencias.xlsx
+++ b/Pauta_de_Audiencias.xlsx
@@ -8,16 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\blu\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{120DBA39-A601-40C7-A58A-FE3076E307C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{47AC427A-0537-44A3-A3B2-0E94906756EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6D6B21FF-2EAF-46D9-8784-D252B7A6E2FD}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5D4BF5D8-B7F5-4533-9060-885CACD260B3}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_Hlk139463631" localSheetId="0">Planilha1!$A$3</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -42,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="193">
   <si>
     <t>Código P&amp;C</t>
   </si>
@@ -98,553 +95,529 @@
     <t>Link/Observações</t>
   </si>
   <si>
+    <t>Audiência Inicial -  Presencial</t>
+  </si>
+  <si>
+    <t>1001620-02.2026.5.02.0434</t>
+  </si>
+  <si>
+    <t>Bridgestone Do Brasil Industria E Comercio Ltda.</t>
+  </si>
+  <si>
+    <t>Donizeti Felipe Da Silva</t>
+  </si>
+  <si>
+    <t>SANTO ANDRÉ</t>
+  </si>
+  <si>
+    <t>SP</t>
+  </si>
+  <si>
+    <t>05ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>Instrução</t>
+  </si>
+  <si>
+    <t>Reclamação Trabalhista</t>
+  </si>
+  <si>
+    <t>CENTRAL</t>
+  </si>
+  <si>
+    <t>R$          1.439.654,64</t>
+  </si>
+  <si>
+    <t>Grupo B1</t>
+  </si>
+  <si>
+    <t>Correspondente - Hebert</t>
+  </si>
+  <si>
+    <t>GSM</t>
+  </si>
+  <si>
+    <t>Presencial</t>
+  </si>
+  <si>
     <t>Audiência Instrução - Presencial</t>
   </si>
   <si>
-    <t>1000794-70.2026.5.02.0435</t>
+    <t>1000801-62.2026.5.02.0435</t>
   </si>
   <si>
     <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
   </si>
   <si>
-    <t>Gabriel Goncalves Alvares</t>
-  </si>
-  <si>
-    <t>SANTO ANDRÉ</t>
-  </si>
-  <si>
-    <t>SP</t>
-  </si>
-  <si>
-    <t>05ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>Instrução</t>
-  </si>
-  <si>
-    <t>Reclamação Trabalhista</t>
-  </si>
-  <si>
-    <t>CENTRAL</t>
-  </si>
-  <si>
-    <t>R$          2.322.472,80</t>
-  </si>
-  <si>
-    <t>Grupo B1</t>
-  </si>
-  <si>
-    <t>Correspondente - Hebert</t>
-  </si>
-  <si>
-    <t>GSM</t>
-  </si>
-  <si>
-    <t>Presencial</t>
+    <t>Ivan Simao Da Costa</t>
+  </si>
+  <si>
+    <t>R$          1.486.150,88</t>
+  </si>
+  <si>
+    <t>TAM</t>
+  </si>
+  <si>
+    <t>1001377-21.2026.5.02.0608</t>
+  </si>
+  <si>
+    <t>Cepam Panificadora E Restaurante Ltda</t>
+  </si>
+  <si>
+    <t>Maria Valdirene Lima Da Silva</t>
+  </si>
+  <si>
+    <t>SÃO PAULO - ZONA LESTE</t>
+  </si>
+  <si>
+    <t>08ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>ZONA LESTE</t>
+  </si>
+  <si>
+    <t>R$             102.760,38</t>
+  </si>
+  <si>
+    <t>Grupo E2</t>
+  </si>
+  <si>
+    <t>RYL</t>
+  </si>
+  <si>
+    <t>CAL</t>
+  </si>
+  <si>
+    <t>Audiência Una - Presencial</t>
+  </si>
+  <si>
+    <t>1001786-34.2026.5.02.0434</t>
+  </si>
+  <si>
+    <t>Valdeci Barbosa Goncalves</t>
+  </si>
+  <si>
+    <t>01ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             202.469,88</t>
+  </si>
+  <si>
+    <t>JPE</t>
+  </si>
+  <si>
+    <t>BSO</t>
+  </si>
+  <si>
+    <t>Audiência Una- Telepresencial</t>
+  </si>
+  <si>
+    <t>0000931-61.2026.5.08.0125</t>
+  </si>
+  <si>
+    <t>Fertilizantes Tocantins S.A</t>
+  </si>
+  <si>
+    <t>Jose Rogerio Campos Martins</t>
+  </si>
+  <si>
+    <t>ABAETETUBA</t>
+  </si>
+  <si>
+    <t>PA</t>
+  </si>
+  <si>
+    <t>02ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>Conhecimento</t>
+  </si>
+  <si>
+    <t>R$               83.979,11</t>
+  </si>
+  <si>
+    <t>BTF</t>
+  </si>
+  <si>
+    <t>https://trt8-jus-br.zoom.us/j/89696538657?pwd=maStgugzlk2DGEc2NZ3sCDFuEanHeM.1</t>
+  </si>
+  <si>
+    <t>Audiência de Instrução - Telepresencial</t>
+  </si>
+  <si>
+    <t>0010494-28.2024.5.03.0048</t>
+  </si>
+  <si>
+    <t>Santa Juliana Bioenergia Ltda.</t>
+  </si>
+  <si>
+    <t>Helio Alves Moura</t>
+  </si>
+  <si>
+    <t>ARAXÁ</t>
+  </si>
+  <si>
+    <t>MG</t>
+  </si>
+  <si>
+    <t>VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             720.476,47</t>
+  </si>
+  <si>
+    <t>ARC</t>
+  </si>
+  <si>
+    <t>https://trt3-jus-br.zoom.us/my/vt.araxa</t>
+  </si>
+  <si>
+    <t>1001080-23.2026.5.02.0411</t>
+  </si>
+  <si>
+    <t>Companhia Brasileira De Cartuchos</t>
+  </si>
+  <si>
+    <t>Wesley Vitor Martins</t>
+  </si>
+  <si>
+    <t>RIBEIRÃO PIRES</t>
+  </si>
+  <si>
+    <t>R$             344.408,19</t>
+  </si>
+  <si>
+    <t>Grupo B3</t>
+  </si>
+  <si>
+    <t>LMI</t>
+  </si>
+  <si>
+    <t>1001252-50.2026.5.02.0609</t>
+  </si>
+  <si>
+    <t>Carlos Alberto Ferreira Da Silva</t>
+  </si>
+  <si>
+    <t>R$               90.849,52</t>
+  </si>
+  <si>
+    <t>0010292-51.2024.5.03.0048</t>
+  </si>
+  <si>
+    <t>Jose Isaias De Oliveira Santos</t>
+  </si>
+  <si>
+    <t>R$             542.599,57</t>
+  </si>
+  <si>
+    <t>1001353-37.2026.5.02.0464</t>
+  </si>
+  <si>
+    <t>Ferrero Do Brasil Industria Doceira E Alimentar Ltda.</t>
+  </si>
+  <si>
+    <t>Claudinei Silva</t>
+  </si>
+  <si>
+    <t>SÃO BERNARDO DO CAMPO</t>
+  </si>
+  <si>
+    <t>04ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$          1.583.882,35</t>
+  </si>
+  <si>
+    <t>ANB</t>
+  </si>
+  <si>
+    <t>Audiência de Instrução - Semipresencial</t>
+  </si>
+  <si>
+    <t>0011586-04.2024.5.03.0028</t>
+  </si>
+  <si>
+    <t>Pilkington Brasil Ltda.</t>
+  </si>
+  <si>
+    <t>Julhia Firteman Doria Dos Santos</t>
+  </si>
+  <si>
+    <t>BETIM</t>
+  </si>
+  <si>
+    <t>03ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$               62.000,00</t>
+  </si>
+  <si>
+    <t>MBF</t>
+  </si>
+  <si>
+    <t>https://trt3-jus-br.zoom.us/j/9035055441</t>
+  </si>
+  <si>
+    <t>1000515-64.2026.5.02.0086</t>
+  </si>
+  <si>
+    <t>L. Sant'Angelo Pinturas Ltda.</t>
+  </si>
+  <si>
+    <t>Wesley Ramos Fernandes Rejes</t>
+  </si>
+  <si>
+    <t>SÃO PAULO</t>
+  </si>
+  <si>
+    <t>86ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             115.544,82</t>
+  </si>
+  <si>
+    <t>Audiência Inicial -  Telepresencial</t>
+  </si>
+  <si>
+    <t>0001166-37.2026.5.18.0129</t>
+  </si>
+  <si>
+    <t>Spic Brasil Energia Participacoes S.A.</t>
+  </si>
+  <si>
+    <t>Jose Cicero Da Silva</t>
+  </si>
+  <si>
+    <t>QUIRINÓPOLIS</t>
+  </si>
+  <si>
+    <t>GO</t>
+  </si>
+  <si>
+    <t>R$               45.609,10</t>
+  </si>
+  <si>
+    <t>Grupo C</t>
+  </si>
+  <si>
+    <t>ECO</t>
+  </si>
+  <si>
+    <t>https://trt18-jus-br.zoom.us/my/cejuscdigital.manha</t>
+  </si>
+  <si>
+    <t>Audiência Inicial - Telepresencial</t>
+  </si>
+  <si>
+    <t>0001167-22.2026.5.18.0129</t>
+  </si>
+  <si>
+    <t>Celma Aparecida Dos Santos</t>
+  </si>
+  <si>
+    <t>R$               28.175,65</t>
+  </si>
+  <si>
+    <t>0001168-07.2026.5.18.0129</t>
+  </si>
+  <si>
+    <t>Spic Brasil Energia Participações S.A</t>
+  </si>
+  <si>
+    <t>Reginaldo Pereira Santos</t>
+  </si>
+  <si>
+    <t>R$               29.450,02</t>
+  </si>
+  <si>
+    <t>0001172-44.2026.5.18.0129</t>
+  </si>
+  <si>
+    <t>Gabriel Da Silva Auto Alves</t>
+  </si>
+  <si>
+    <t>R$               51.526,06</t>
+  </si>
+  <si>
+    <t>1000676-62.2026.5.02.0381</t>
+  </si>
+  <si>
+    <t>Sinthoresp - Sindicato Dos Empregados No Comércio Hoteleiro E Similares De São Paulo</t>
+  </si>
+  <si>
+    <t>Alex Alves Dos Santos</t>
+  </si>
+  <si>
+    <t>OSASCO</t>
+  </si>
+  <si>
+    <t>R$          6.258.083,13</t>
+  </si>
+  <si>
+    <t>Grupo A2</t>
+  </si>
+  <si>
+    <t>NBG</t>
+  </si>
+  <si>
+    <t>https://trt2-jus-br.zoom.us/j/87232620877?pwd=aU6nYtaZy6CU9OwlgcKSsb6r5uexb1.1 ID da reunião: 872 3262 0877 Senha de acesso: 795431</t>
+  </si>
+  <si>
+    <t>Audiência de Conciliação - Telepresencial</t>
+  </si>
+  <si>
+    <t>0011753-68.2025.5.15.0087</t>
+  </si>
+  <si>
+    <t>Syngenta Proteção De Cultivos Ltda.</t>
+  </si>
+  <si>
+    <t>Roberto Carlos De Sousa</t>
+  </si>
+  <si>
+    <t>PAULÍNIA</t>
+  </si>
+  <si>
+    <t>CEJUSC 2º GRAU</t>
+  </si>
+  <si>
+    <t>2ª Instância</t>
+  </si>
+  <si>
+    <t>R$               22.242,37</t>
+  </si>
+  <si>
+    <t>Grupo E1</t>
+  </si>
+  <si>
+    <t>JPL</t>
+  </si>
+  <si>
+    <t>GVM</t>
+  </si>
+  <si>
+    <t>bit.ly/cejusc2grau</t>
+  </si>
+  <si>
+    <t>1000329-80.2026.5.02.0073</t>
+  </si>
+  <si>
+    <t>Mahle Metal Leve S.A.</t>
+  </si>
+  <si>
+    <t>Terezinha Soares De Sousa</t>
+  </si>
+  <si>
+    <t>CEJUSC ABC</t>
+  </si>
+  <si>
+    <t>R$             160.233,95</t>
+  </si>
+  <si>
+    <t>PSI</t>
+  </si>
+  <si>
+    <t>TLI</t>
+  </si>
+  <si>
+    <t>https://trt2-jus-br.zoom.us/j/81881873237?pwd=aEs5S29DM2srNHRuRGFVM2ZEYkVUZz09 ID da reunião: 818 8187 3237 Senha de acesso: 459217</t>
   </si>
   <si>
     <t>Audiência Instrução - Telepresencial</t>
   </si>
   <si>
-    <t>0000463-74.2026.5.14.0111</t>
-  </si>
-  <si>
-    <t>Syngenta Digital Ltda.</t>
-  </si>
-  <si>
-    <t>Lucas Rafael Chiquito De Souza</t>
-  </si>
-  <si>
-    <t>PIMENTA BUENO</t>
-  </si>
-  <si>
-    <t>RO</t>
-  </si>
-  <si>
-    <t>VARA DO TRABALHO</t>
+    <t>0010494-81.2026.5.15.0126</t>
+  </si>
+  <si>
+    <t>Antonio Jose Dos Santos Oliveira</t>
   </si>
   <si>
     <t>1ª Instância</t>
   </si>
   <si>
-    <t>R$             235.287,92</t>
-  </si>
-  <si>
-    <t>Grupo E1</t>
-  </si>
-  <si>
-    <t>VRO</t>
-  </si>
-  <si>
-    <t>https://trt14-jus-br.zoom.us/j/87479999418?pwd=Dvi882AxlC4NHugWXyiLgR5Tm3zg5W.1 ID da reunião: 874 7999 9418 Senha: 986377</t>
-  </si>
-  <si>
-    <t>Audiência Una - Presencial</t>
-  </si>
-  <si>
-    <t>1001214-26.2026.5.02.0031</t>
-  </si>
-  <si>
-    <t>Spic Brasil Energia Participações S.A.</t>
-  </si>
-  <si>
-    <t>Martha Ferreira Machado</t>
-  </si>
-  <si>
-    <t>SÃO PAULO</t>
-  </si>
-  <si>
-    <t>31ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$               40.763,68</t>
-  </si>
-  <si>
-    <t>Grupo C</t>
-  </si>
-  <si>
-    <t>ECO</t>
-  </si>
-  <si>
-    <t>Sessão de Julgamento TRT - Presencial</t>
-  </si>
-  <si>
-    <t>0000184-21.2025.5.05.0161</t>
-  </si>
-  <si>
-    <t>Companhia Act De Participações E Companhia Aix De Participações</t>
-  </si>
-  <si>
-    <t>Walney De Oliveira Rodrigues</t>
-  </si>
-  <si>
-    <t>SANTO AMARO</t>
-  </si>
-  <si>
-    <t>BA</t>
-  </si>
-  <si>
-    <t>03ª TURMA</t>
-  </si>
-  <si>
-    <t>Recursal</t>
-  </si>
-  <si>
-    <t>R$             331.871,09</t>
-  </si>
-  <si>
-    <t>VSI</t>
-  </si>
-  <si>
-    <t>link pendente</t>
-  </si>
-  <si>
-    <t>0000717-33.2026.5.05.0132</t>
-  </si>
-  <si>
-    <t>Salitre Fertilizantes Ltda.</t>
-  </si>
-  <si>
-    <t>Silvan Dos Anjos Dos Santos</t>
-  </si>
-  <si>
-    <t>CAMAÇARI</t>
-  </si>
-  <si>
-    <t>02ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>Conhecimento</t>
-  </si>
-  <si>
-    <t>R$               15.684,57</t>
-  </si>
-  <si>
-    <t>Grupo E2</t>
-  </si>
-  <si>
-    <t>RYL</t>
-  </si>
-  <si>
-    <t>CAL</t>
-  </si>
-  <si>
-    <t>https://trt5-jus-br.zoom.us/my/sl2vtcam</t>
+    <t>R$                 8.761,58</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/83059104477?pwd=h7VDkteaYgzZ4FIU9CoepcQo5ErUHA.1 ID da reunião: 830 5910 4477 Senha: 005974</t>
   </si>
   <si>
     <t>Audiência Una - Telepresencial</t>
   </si>
   <si>
-    <t>1000970-83.2026.5.02.0068</t>
-  </si>
-  <si>
-    <t>Whirlpool S.A</t>
-  </si>
-  <si>
-    <t>Eduardo Akira Kawabata E Electrolux Do Brasil S/A</t>
-  </si>
-  <si>
-    <t>68ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$               65.000,00</t>
-  </si>
-  <si>
-    <t>Grupo A3</t>
-  </si>
-  <si>
-    <t>PBS</t>
-  </si>
-  <si>
-    <t>SOF</t>
-  </si>
-  <si>
-    <t>https://trt2-jus-br.zoom.us/j/81486768468?pwd=TvPkyvfbko93aYtBiWMTAIPOUojzNS.1</t>
-  </si>
-  <si>
-    <t>Audiência Una- Telepresencial</t>
-  </si>
-  <si>
-    <t>0024175-55.2026.5.24.0066</t>
-  </si>
-  <si>
-    <t>Moema Bioenergia S.A. - Monteverde</t>
-  </si>
-  <si>
-    <t>Dionaty Sousa Dos Santos</t>
-  </si>
-  <si>
-    <t>PONTA PORÃ</t>
-  </si>
-  <si>
-    <t>MS</t>
-  </si>
-  <si>
-    <t>R$               55.756,42</t>
+    <t>0010413-55.2026.5.15.0087</t>
+  </si>
+  <si>
+    <t>Guilherme Henrique Rodrigues</t>
+  </si>
+  <si>
+    <t>R$             422.113,53</t>
+  </si>
+  <si>
+    <t>JRM</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/85267876480?pwd=tETOC8GDaqZZdf9WNGOaW98aPE2MQx.1</t>
+  </si>
+  <si>
+    <t>0010741-68.2026.5.15.0027</t>
+  </si>
+  <si>
+    <t>Moema Bioenergia S.A. - Moema</t>
+  </si>
+  <si>
+    <t>Ketlyn Goncalves Silva</t>
+  </si>
+  <si>
+    <t>VOTUPORANGA</t>
+  </si>
+  <si>
+    <t>R$             102.723,20</t>
+  </si>
+  <si>
+    <t>BBO</t>
   </si>
   <si>
     <t>LWP</t>
   </si>
   <si>
-    <t>https://trt24-jus-br.zoom.us/j/88062331360</t>
-  </si>
-  <si>
-    <t>Audiência Inicial -  Presencial</t>
-  </si>
-  <si>
-    <t>1001646-97.2026.5.02.0434</t>
-  </si>
-  <si>
-    <t>Flavio Eduardo Basilio</t>
-  </si>
-  <si>
-    <t>R$             287.397,44</t>
-  </si>
-  <si>
-    <t>BSO</t>
-  </si>
-  <si>
-    <t>Audiência de Instrução - Telepresencial</t>
-  </si>
-  <si>
-    <t>0010763-85.2025.5.03.0160</t>
-  </si>
-  <si>
-    <t>Fertilizantes Heringer S.A. - Iguatama - Igt</t>
-  </si>
-  <si>
-    <t>Marcus Vinicios Dos Santos Correia Alves</t>
-  </si>
-  <si>
-    <t>FORMIGA</t>
-  </si>
-  <si>
-    <t>MG</t>
-  </si>
-  <si>
-    <t>R$               66.235,85</t>
-  </si>
-  <si>
-    <t>RRU</t>
-  </si>
-  <si>
-    <t>BBO</t>
-  </si>
-  <si>
-    <t>https://trt3-jus-br.zoom.us/my/vt2formiga</t>
-  </si>
-  <si>
-    <t>Audiência de Instrução - Presencial</t>
-  </si>
-  <si>
-    <t>1000646-34.2026.5.02.0411</t>
-  </si>
-  <si>
-    <t>Cbc - Companhia Brasileira De Cartuchos</t>
-  </si>
-  <si>
-    <t>Danilo Domingos Da Silva</t>
-  </si>
-  <si>
-    <t>RIBEIRÃO PIRES</t>
-  </si>
-  <si>
-    <t>R$             121.724,54</t>
-  </si>
-  <si>
-    <t>Grupo B3</t>
-  </si>
-  <si>
-    <t>LMI</t>
-  </si>
-  <si>
-    <t>0024052-57.2026.5.24.0066</t>
-  </si>
-  <si>
-    <t>Moema Bioenergia S.A. - Moema</t>
-  </si>
-  <si>
-    <t>Anadirson Alem Dos Santos De Oliveira</t>
-  </si>
-  <si>
-    <t>R$             141.500,00</t>
-  </si>
-  <si>
-    <t>BTF</t>
-  </si>
-  <si>
-    <t>MBF</t>
-  </si>
-  <si>
-    <t>https://trt24-jus-br.zoom.us/j/85366509499</t>
-  </si>
-  <si>
-    <t>1001307-41.2026.5.02.0434</t>
-  </si>
-  <si>
-    <t>Paulo Souza De Almeida</t>
-  </si>
-  <si>
-    <t>04ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$               80.000,00</t>
-  </si>
-  <si>
-    <t>JPE</t>
-  </si>
-  <si>
-    <t>TAM</t>
-  </si>
-  <si>
-    <t>1001691-98.2026.5.02.0435</t>
-  </si>
-  <si>
-    <t>Daiane Silva Nascimento Dos Santos</t>
-  </si>
-  <si>
-    <t>R$             144.115,98</t>
-  </si>
-  <si>
-    <t>RFE</t>
-  </si>
-  <si>
-    <t>1001738-84.2026.5.02.0431</t>
-  </si>
-  <si>
-    <t>Bridgestone Do Brasil Indústria E Comércio Ltda</t>
-  </si>
-  <si>
-    <t>Gregory Leonardo Fernandes</t>
-  </si>
-  <si>
-    <t>01ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$               65.480,35</t>
-  </si>
-  <si>
-    <t>1001157-66.2026.5.02.0432</t>
-  </si>
-  <si>
-    <t>Gustavo Pereira Dos Reis</t>
-  </si>
-  <si>
-    <t>R$               35.699,15</t>
-  </si>
-  <si>
-    <t>Audiência Inicial -  Telepresencial</t>
-  </si>
-  <si>
-    <t>0000723-50.2026.5.22.0105</t>
-  </si>
-  <si>
-    <t>Pedro Afonso Bioenergia Ltda.</t>
-  </si>
-  <si>
-    <t>Antonio Da Silva Sousa</t>
-  </si>
-  <si>
-    <t>PIRIPIRI</t>
-  </si>
-  <si>
-    <t>PI</t>
-  </si>
-  <si>
-    <t>R$               19.164,34</t>
-  </si>
-  <si>
-    <t>https://trt22-jus-br.zoom.us/j/86414266800</t>
-  </si>
-  <si>
-    <t>0000724-35.2026.5.22.0105</t>
-  </si>
-  <si>
-    <t>Antonio Marcos Da Silva Penha</t>
-  </si>
-  <si>
-    <t>Inicial</t>
-  </si>
-  <si>
-    <t>R$               19.679,83</t>
-  </si>
-  <si>
-    <t>0000725-20.2026.5.22.0105</t>
-  </si>
-  <si>
-    <t>Antonio Carlos Do Nascimento Leite</t>
-  </si>
-  <si>
-    <t>R$               17.931,44</t>
-  </si>
-  <si>
-    <t>Audiência de Conciliação - Telepresencial</t>
-  </si>
-  <si>
-    <t>0000928-73.2024.5.05.0121</t>
-  </si>
-  <si>
-    <t>Fertilizantes Heringer S.A. - Candeias - Can</t>
-  </si>
-  <si>
-    <t>Eric Fabricio Dos Santos Pereira</t>
-  </si>
-  <si>
-    <t>CANDEIAS</t>
-  </si>
-  <si>
-    <t>CEJUSC</t>
-  </si>
-  <si>
-    <t>R$               23.207,48</t>
-  </si>
-  <si>
-    <t>https://trt5-jus-br.zoom.us/my/cejusc1sala18</t>
-  </si>
-  <si>
-    <t>0000447-03.2026.5.09.0195</t>
-  </si>
-  <si>
-    <t>Anderson Felipe Ferri</t>
-  </si>
-  <si>
-    <t>CASCAVEL</t>
-  </si>
-  <si>
-    <t>PR</t>
-  </si>
-  <si>
-    <t>03ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$             881.000,00</t>
-  </si>
-  <si>
-    <t>https://url.trt9.jus.br/s8jj9 ID da Reunião: 83482068288 Senha: sM3uxxhDB0</t>
-  </si>
-  <si>
-    <t>Audiência de Encerramento de Instrução</t>
-  </si>
-  <si>
-    <t>0000049-63.2026.5.09.0128</t>
-  </si>
-  <si>
-    <t>Edison Luiz Souza</t>
-  </si>
-  <si>
-    <t>R$               61.000,00</t>
-  </si>
-  <si>
-    <t>TFR</t>
-  </si>
-  <si>
-    <t>https://url.trt9.jus.br/rypyv ID da reunião: 87526086719 Senha de acesso: C9wehw1Pg0</t>
-  </si>
-  <si>
-    <t>0000183-90.2026.5.09.0128</t>
-  </si>
-  <si>
-    <t>R$             205.600,00</t>
-  </si>
-  <si>
-    <t>0010657-94.2026.5.03.0029</t>
-  </si>
-  <si>
-    <t>Sistenge Construções E Comércio Ltda.</t>
-  </si>
-  <si>
-    <t>Rodrigo Junio De Souza</t>
-  </si>
-  <si>
-    <t>CONTAGEM</t>
-  </si>
-  <si>
-    <t>Acordo</t>
-  </si>
-  <si>
-    <t>R$               34.332,73</t>
-  </si>
-  <si>
-    <t>https://trt3-jus-br.zoom.us/my/vt1.contagem</t>
-  </si>
-  <si>
-    <t>0010622-38.2026.5.15.0050</t>
+    <t>https://us02web.zoom.us/j/82212757993?pwd=aSt4Q29rc0JRMnFXSTU0UzdCVVZyQT09</t>
+  </si>
+  <si>
+    <t>0010680-45.2026.5.15.0081</t>
+  </si>
+  <si>
+    <t>Syngenta Seeds Ltda.</t>
+  </si>
+  <si>
+    <t>Rafaelly Cristina Neri Amorim</t>
+  </si>
+  <si>
+    <t>MATÃO</t>
+  </si>
+  <si>
+    <t>R$               30.000,00</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/85873566791?pwd=RnpEWnZUM3RZcm5PU3lISmlydm9yZz09</t>
+  </si>
+  <si>
+    <t>0010761-24.2025.5.15.0050</t>
   </si>
   <si>
     <t>Viterra Bioenergia S.A.</t>
   </si>
   <si>
-    <t>Jeferson De Souza Alves Antonio</t>
+    <t>Ademir Lemes Dos Santos</t>
   </si>
   <si>
     <t>DRACENA</t>
   </si>
   <si>
-    <t>R$             323.874,68</t>
-  </si>
-  <si>
-    <t>AAP</t>
-  </si>
-  <si>
-    <t>https://trt15-jus.br.zoom.us/j/87527564652?pwd=d3YrZ2diWXk5UjgzbmVkNExteWVMQT09</t>
-  </si>
-  <si>
-    <t>0010451-53.2026.5.15.0027</t>
-  </si>
-  <si>
-    <t>Guariroba Bioenergia Ltda.</t>
-  </si>
-  <si>
-    <t>Valdeir Cesar De Oliveira</t>
-  </si>
-  <si>
-    <t>VOTUPORANGA</t>
-  </si>
-  <si>
-    <t>R$             474.192,34</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/88542672682?pwd=7pQ4QRhZmRG9RAQAWKowymbwNawa7t.1</t>
+    <t>R$             408.240,44</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/87527564652?pwd=d3YrZ2diWXk5UjgzbmVkNExteWVMQT09</t>
   </si>
 </sst>
 </file>
@@ -727,14 +700,16 @@
     </border>
     <border>
       <left style="medium">
-        <color indexed="64"/>
+        <color rgb="FFBFBFBF"/>
       </left>
       <right style="medium">
-        <color indexed="64"/>
+        <color rgb="FFBFBFBF"/>
       </right>
-      <top/>
+      <top style="medium">
+        <color rgb="FFBFBFBF"/>
+      </top>
       <bottom style="medium">
-        <color indexed="64"/>
+        <color rgb="FFBFBFBF"/>
       </bottom>
       <diagonal/>
     </border>
@@ -743,7 +718,9 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
@@ -1109,30 +1086,29 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4BA9B5F-64AD-40BE-A136-29A2274B0B14}">
-  <dimension ref="A1:R26"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16806513-4B38-4AD3-9B2F-E6CFF800ECB7}">
+  <dimension ref="A1:R25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="33.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="52.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="39.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="38.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.21875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="5.5546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.6640625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.21875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="15.77734375" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14.33203125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="27.109375" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="28.88671875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="101" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="19.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1188,15 +1164,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4">
-        <v>104857</v>
+        <v>105879</v>
       </c>
       <c r="B2" s="5">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C2" s="6">
-        <v>0.36805555555555558</v>
+        <v>0.34722222222222221</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>18</v>
@@ -1244,15 +1220,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4">
-        <v>105754</v>
+        <v>104858</v>
       </c>
       <c r="B3" s="5">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C3" s="6">
-        <v>0.375</v>
+        <v>0.36805555555555558</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>33</v>
@@ -1267,16 +1243,16 @@
         <v>36</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="L3" s="7" t="s">
         <v>26</v>
@@ -1285,51 +1261,51 @@
         <v>27</v>
       </c>
       <c r="N3" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="O3" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P3" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q3" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="R3" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="4">
+        <v>105406</v>
+      </c>
+      <c r="B4" s="5">
+        <v>46289</v>
+      </c>
+      <c r="C4" s="6">
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G4" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="O3" s="7" t="s">
+      <c r="H4" s="7" t="s">
         <v>42</v>
-      </c>
-      <c r="P3" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q3" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="R3" s="7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="4">
-        <v>105874</v>
-      </c>
-      <c r="B4" s="5">
-        <v>46288</v>
-      </c>
-      <c r="C4" s="6">
-        <v>0.375</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>49</v>
       </c>
       <c r="I4" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="K4" s="7" t="s">
         <v>25</v>
@@ -1338,57 +1314,57 @@
         <v>26</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="N4" s="7" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="O4" s="7" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="P4" s="7" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="Q4" s="7" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="R4" s="7" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4">
-        <v>103592</v>
+        <v>106155</v>
       </c>
       <c r="B5" s="5">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C5" s="6">
-        <v>0.375</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="L5" s="7" t="s">
         <v>26</v>
@@ -1397,54 +1373,54 @@
         <v>27</v>
       </c>
       <c r="N5" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="O5" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P5" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q5" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="R5" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="4">
+        <v>105178</v>
+      </c>
+      <c r="B6" s="5">
+        <v>46289</v>
+      </c>
+      <c r="C6" s="6">
+        <v>0.40625</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J6" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="O5" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="P5" s="7" t="s">
+      <c r="K6" s="7" t="s">
         <v>63</v>
-      </c>
-      <c r="Q5" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="R5" s="7" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="4">
-        <v>105674</v>
-      </c>
-      <c r="B6" s="5">
-        <v>46288</v>
-      </c>
-      <c r="C6" s="6">
-        <v>0.38194444444444442</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="K6" s="7" t="s">
-        <v>70</v>
       </c>
       <c r="L6" s="7" t="s">
         <v>26</v>
@@ -1453,51 +1429,51 @@
         <v>27</v>
       </c>
       <c r="N6" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="O6" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="P6" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q6" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="R6" s="7" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="4">
+        <v>97433</v>
+      </c>
+      <c r="B7" s="5">
+        <v>46289</v>
+      </c>
+      <c r="C7" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="H7" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="O6" s="7" t="s">
+      <c r="I7" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="P6" s="7" t="s">
+      <c r="J7" s="7" t="s">
         <v>73</v>
-      </c>
-      <c r="Q6" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="R6" s="7" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="4">
-        <v>105272</v>
-      </c>
-      <c r="B7" s="5">
-        <v>46288</v>
-      </c>
-      <c r="C7" s="6">
-        <v>0.39583333333333331</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>80</v>
       </c>
       <c r="K7" s="7" t="s">
         <v>25</v>
@@ -1509,51 +1485,51 @@
         <v>27</v>
       </c>
       <c r="N7" s="7" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="O7" s="7" t="s">
-        <v>82</v>
+        <v>46</v>
       </c>
       <c r="P7" s="7" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="Q7" s="7" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="R7" s="7" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4">
-        <v>104492</v>
+        <v>105642</v>
       </c>
       <c r="B8" s="5">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C8" s="6">
-        <v>0.39583333333333331</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>91</v>
+        <v>23</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="K8" s="7" t="s">
         <v>25</v>
@@ -1565,51 +1541,51 @@
         <v>27</v>
       </c>
       <c r="N8" s="7" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="O8" s="7" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="P8" s="7" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="Q8" s="7" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="R8" s="7" t="s">
-        <v>94</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4">
-        <v>105935</v>
+        <v>105143</v>
       </c>
       <c r="B9" s="5">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C9" s="6">
-        <v>0.41666666666666669</v>
+        <v>0.4236111111111111</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>95</v>
+        <v>18</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>20</v>
+        <v>78</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="I9" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="K9" s="7" t="s">
         <v>25</v>
@@ -1621,51 +1597,51 @@
         <v>27</v>
       </c>
       <c r="N9" s="7" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="O9" s="7" t="s">
-        <v>29</v>
+        <v>82</v>
       </c>
       <c r="P9" s="7" t="s">
-        <v>30</v>
+        <v>83</v>
       </c>
       <c r="Q9" s="7" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="R9" s="7" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4">
-        <v>102444</v>
+        <v>97257</v>
       </c>
       <c r="B10" s="5">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C10" s="6">
-        <v>0.41666666666666669</v>
+        <v>0.4375</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>102</v>
+        <v>69</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>105</v>
+        <v>72</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="K10" s="7" t="s">
         <v>25</v>
@@ -1677,51 +1653,51 @@
         <v>27</v>
       </c>
       <c r="N10" s="7" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="O10" s="7" t="s">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="P10" s="7" t="s">
-        <v>107</v>
+        <v>75</v>
       </c>
       <c r="Q10" s="7" t="s">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="R10" s="7" t="s">
-        <v>109</v>
+        <v>76</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4">
-        <v>104855</v>
+        <v>105881</v>
       </c>
       <c r="B11" s="5">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C11" s="6">
-        <v>0.41666666666666669</v>
+        <v>0.4375</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>110</v>
+        <v>49</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="I11" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>39</v>
+        <v>94</v>
       </c>
       <c r="K11" s="7" t="s">
         <v>25</v>
@@ -1733,51 +1709,51 @@
         <v>27</v>
       </c>
       <c r="N11" s="7" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="O11" s="7" t="s">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="P11" s="7" t="s">
-        <v>117</v>
+        <v>96</v>
       </c>
       <c r="Q11" s="7" t="s">
-        <v>117</v>
+        <v>96</v>
       </c>
       <c r="R11" s="7" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="4">
-        <v>104198</v>
+        <v>99704</v>
       </c>
       <c r="B12" s="5">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C12" s="6">
-        <v>0.43055555555555558</v>
+        <v>0.44444444444444442</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>33</v>
+        <v>97</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>39</v>
+        <v>102</v>
       </c>
       <c r="K12" s="7" t="s">
         <v>25</v>
@@ -1789,51 +1765,51 @@
         <v>27</v>
       </c>
       <c r="N12" s="7" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="O12" s="7" t="s">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="P12" s="7" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="Q12" s="7" t="s">
-        <v>123</v>
+        <v>75</v>
       </c>
       <c r="R12" s="7" t="s">
-        <v>124</v>
+        <v>105</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4">
-        <v>105579</v>
+        <v>104670</v>
       </c>
       <c r="B13" s="5">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C13" s="6">
-        <v>0.4375</v>
+        <v>0.44444444444444442</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>20</v>
+        <v>107</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>22</v>
+        <v>109</v>
       </c>
       <c r="I13" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="K13" s="7" t="s">
         <v>25</v>
@@ -1845,51 +1821,51 @@
         <v>27</v>
       </c>
       <c r="N13" s="7" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="O13" s="7" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="P13" s="7" t="s">
-        <v>129</v>
+        <v>48</v>
       </c>
       <c r="Q13" s="7" t="s">
-        <v>130</v>
+        <v>48</v>
       </c>
       <c r="R13" s="7" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="4">
-        <v>105955</v>
+        <v>106251</v>
       </c>
       <c r="B14" s="5">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C14" s="6">
-        <v>0.4513888888888889</v>
+        <v>0.47222222222222221</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>20</v>
+        <v>114</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>22</v>
+        <v>116</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>23</v>
+        <v>117</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="K14" s="7" t="s">
         <v>25</v>
@@ -1901,51 +1877,51 @@
         <v>27</v>
       </c>
       <c r="N14" s="7" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="O14" s="7" t="s">
-        <v>29</v>
+        <v>119</v>
       </c>
       <c r="P14" s="7" t="s">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="Q14" s="7" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="R14" s="7" t="s">
-        <v>32</v>
+        <v>121</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4">
-        <v>106017</v>
+        <v>106250</v>
       </c>
       <c r="B15" s="5">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C15" s="6">
-        <v>0.45833333333333331</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>45</v>
+        <v>122</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>22</v>
+        <v>116</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>23</v>
+        <v>117</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>138</v>
+        <v>73</v>
       </c>
       <c r="K15" s="7" t="s">
         <v>25</v>
@@ -1957,51 +1933,51 @@
         <v>27</v>
       </c>
       <c r="N15" s="7" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="O15" s="7" t="s">
-        <v>29</v>
+        <v>119</v>
       </c>
       <c r="P15" s="7" t="s">
-        <v>31</v>
+        <v>120</v>
       </c>
       <c r="Q15" s="7" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="R15" s="7" t="s">
-        <v>32</v>
+        <v>121</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="4">
-        <v>105295</v>
+        <v>106243</v>
       </c>
       <c r="B16" s="5">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C16" s="6">
-        <v>0.46180555555555558</v>
+        <v>0.4861111111111111</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>45</v>
+        <v>122</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>20</v>
+        <v>127</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>22</v>
+        <v>116</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>23</v>
+        <v>117</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="K16" s="7" t="s">
         <v>25</v>
@@ -2013,51 +1989,51 @@
         <v>27</v>
       </c>
       <c r="N16" s="7" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="O16" s="7" t="s">
-        <v>29</v>
+        <v>119</v>
       </c>
       <c r="P16" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q16" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="R16" s="7" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="4">
+        <v>106249</v>
+      </c>
+      <c r="B17" s="5">
+        <v>46289</v>
+      </c>
+      <c r="C17" s="6">
+        <v>0.49305555555555558</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="E17" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="Q16" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="R16" s="7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="4">
-        <v>105544</v>
-      </c>
-      <c r="B17" s="5">
-        <v>46288</v>
-      </c>
-      <c r="C17" s="6">
-        <v>0.47916666666666669</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>144</v>
-      </c>
       <c r="F17" s="7" t="s">
-        <v>145</v>
+        <v>114</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>147</v>
+        <v>116</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>148</v>
+        <v>117</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="K17" s="7" t="s">
         <v>25</v>
@@ -2069,54 +2045,54 @@
         <v>27</v>
       </c>
       <c r="N17" s="7" t="s">
-        <v>149</v>
+        <v>132</v>
       </c>
       <c r="O17" s="7" t="s">
-        <v>72</v>
+        <v>119</v>
       </c>
       <c r="P17" s="7" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="Q17" s="7" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="R17" s="7" t="s">
-        <v>150</v>
+        <v>121</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="4">
-        <v>105545</v>
+        <v>104761</v>
       </c>
       <c r="B18" s="5">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C18" s="6">
-        <v>0.4826388888888889</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>143</v>
+        <v>67</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>152</v>
+        <v>135</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>148</v>
+        <v>23</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>153</v>
+        <v>25</v>
       </c>
       <c r="L18" s="7" t="s">
         <v>26</v>
@@ -2125,54 +2101,54 @@
         <v>27</v>
       </c>
       <c r="N18" s="7" t="s">
-        <v>154</v>
+        <v>137</v>
       </c>
       <c r="O18" s="7" t="s">
-        <v>72</v>
+        <v>138</v>
       </c>
       <c r="P18" s="7" t="s">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="Q18" s="7" t="s">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="R18" s="7" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="4">
-        <v>105546</v>
+        <v>102975</v>
       </c>
       <c r="B19" s="5">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C19" s="6">
-        <v>0.4861111111111111</v>
+        <v>0.56597222222222221</v>
       </c>
       <c r="D19" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="F19" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="E19" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="F19" s="7" t="s">
+      <c r="G19" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="H19" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="G19" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="H19" s="7" t="s">
+      <c r="I19" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="K19" s="7" t="s">
         <v>147</v>
-      </c>
-      <c r="I19" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="J19" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="K19" s="7" t="s">
-        <v>153</v>
       </c>
       <c r="L19" s="7" t="s">
         <v>26</v>
@@ -2181,54 +2157,54 @@
         <v>27</v>
       </c>
       <c r="N19" s="7" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="O19" s="7" t="s">
-        <v>72</v>
+        <v>149</v>
       </c>
       <c r="P19" s="7" t="s">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="Q19" s="7" t="s">
-        <v>123</v>
+        <v>151</v>
       </c>
       <c r="R19" s="7" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="4">
-        <v>102261</v>
+        <v>104312</v>
       </c>
       <c r="B20" s="5">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C20" s="6">
-        <v>0.4861111111111111</v>
+        <v>0.5708333333333333</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>162</v>
+        <v>109</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="K20" s="7" t="s">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="L20" s="7" t="s">
         <v>26</v>
@@ -2237,54 +2213,54 @@
         <v>27</v>
       </c>
       <c r="N20" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="O20" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="P20" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q20" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="R20" s="7" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="4">
+        <v>104625</v>
+      </c>
+      <c r="B21" s="5">
+        <v>46289</v>
+      </c>
+      <c r="C21" s="6">
+        <v>0.58680555555555558</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="K21" s="7" t="s">
         <v>164</v>
-      </c>
-      <c r="O20" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="P20" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q20" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="R20" s="7" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="4">
-        <v>104518</v>
-      </c>
-      <c r="B21" s="5">
-        <v>46288</v>
-      </c>
-      <c r="C21" s="6">
-        <v>0.5625</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="G21" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="H21" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="I21" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="J21" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="K21" s="7" t="s">
-        <v>25</v>
       </c>
       <c r="L21" s="7" t="s">
         <v>26</v>
@@ -2293,54 +2269,54 @@
         <v>27</v>
       </c>
       <c r="N21" s="7" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="O21" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="P21" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q21" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="R21" s="7" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="4">
+        <v>104516</v>
+      </c>
+      <c r="B22" s="5">
+        <v>46289</v>
+      </c>
+      <c r="C22" s="6">
+        <v>0.59722222222222221</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="I22" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J22" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="P21" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q21" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="R21" s="7" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="4">
-        <v>103768</v>
-      </c>
-      <c r="B22" s="5">
-        <v>46288</v>
-      </c>
-      <c r="C22" s="6">
-        <v>0.5625</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="F22" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="G22" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="H22" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="I22" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="J22" s="7" t="s">
-        <v>69</v>
-      </c>
       <c r="K22" s="7" t="s">
-        <v>25</v>
+        <v>164</v>
       </c>
       <c r="L22" s="7" t="s">
         <v>26</v>
@@ -2349,51 +2325,51 @@
         <v>27</v>
       </c>
       <c r="N22" s="7" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="O22" s="7" t="s">
-        <v>52</v>
+        <v>149</v>
       </c>
       <c r="P22" s="7" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="Q22" s="7" t="s">
-        <v>63</v>
+        <v>151</v>
       </c>
       <c r="R22" s="7" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="4">
-        <v>104017</v>
+        <v>105227</v>
       </c>
       <c r="B23" s="5">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C23" s="6">
-        <v>0.56319444444444444</v>
+        <v>0.59722222222222221</v>
       </c>
       <c r="D23" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="E23" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="E23" s="7" t="s">
-        <v>179</v>
-      </c>
       <c r="F23" s="7" t="s">
-        <v>56</v>
+        <v>174</v>
       </c>
       <c r="G23" s="7" t="s">
         <v>175</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>169</v>
+        <v>23</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="K23" s="7" t="s">
         <v>25</v>
@@ -2405,33 +2381,33 @@
         <v>27</v>
       </c>
       <c r="N23" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="O23" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="P23" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q23" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="R23" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="O23" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="P23" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="Q23" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="R23" s="7" t="s">
-        <v>178</v>
-      </c>
     </row>
-    <row r="24" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="4">
-        <v>104768</v>
+        <v>104851</v>
       </c>
       <c r="B24" s="5">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C24" s="6">
-        <v>0.59375</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>158</v>
+        <v>56</v>
       </c>
       <c r="E24" s="7" t="s">
         <v>181</v>
@@ -2446,13 +2422,13 @@
         <v>184</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>105</v>
+        <v>23</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>138</v>
+        <v>73</v>
       </c>
       <c r="K24" s="7" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="L24" s="7" t="s">
         <v>26</v>
@@ -2461,54 +2437,54 @@
         <v>27</v>
       </c>
       <c r="N24" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="O24" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="P24" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q24" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="R24" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="O24" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="P24" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q24" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="R24" s="7" t="s">
-        <v>187</v>
-      </c>
     </row>
-    <row r="25" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="4">
-        <v>105106</v>
+        <v>101585</v>
       </c>
       <c r="B25" s="5">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C25" s="6">
         <v>0.60416666666666663</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>33</v>
+        <v>161</v>
       </c>
       <c r="E25" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="F25" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="F25" s="7" t="s">
+      <c r="G25" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="G25" s="7" t="s">
+      <c r="H25" s="7" t="s">
         <v>190</v>
-      </c>
-      <c r="H25" s="7" t="s">
-        <v>191</v>
       </c>
       <c r="I25" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="K25" s="7" t="s">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="L25" s="7" t="s">
         <v>26</v>
@@ -2517,95 +2493,38 @@
         <v>27</v>
       </c>
       <c r="N25" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="O25" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="P25" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q25" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="R25" s="7" t="s">
         <v>192</v>
-      </c>
-      <c r="O25" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="P25" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="Q25" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="R25" s="7" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="4">
-        <v>104811</v>
-      </c>
-      <c r="B26" s="5">
-        <v>46288</v>
-      </c>
-      <c r="C26" s="6">
-        <v>0.63541666666666663</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="G26" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="H26" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="I26" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="J26" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="K26" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="L26" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="M26" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="N26" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="O26" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="P26" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="Q26" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="R26" s="7" t="s">
-        <v>200</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="R3" r:id="rId1" display="https://trt14-jus-br.zoom.us/j/87479999418?pwd=Dvi882AxlC4NHugWXyiLgR5Tm3zg5W.1%20ID%20da%20reunião:%20874%207999%209418%20Senha:%20986377" xr:uid="{673EF94E-78A6-492F-8648-55A3D099E909}"/>
-    <hyperlink ref="R6" r:id="rId2" xr:uid="{AA314538-1C38-4354-86E5-68E87B982D8E}"/>
-    <hyperlink ref="R7" r:id="rId3" xr:uid="{2994172D-10B1-4E38-8B17-6E40060423C8}"/>
-    <hyperlink ref="R8" r:id="rId4" xr:uid="{337F0E7C-9834-4F6A-9366-2EE1C8C3ED34}"/>
-    <hyperlink ref="R10" r:id="rId5" xr:uid="{39C64E5E-477A-4E44-89F4-F4BDC7900F55}"/>
-    <hyperlink ref="R12" r:id="rId6" xr:uid="{BC5523E5-17AF-4C68-A62F-E6DF014877CF}"/>
-    <hyperlink ref="R17" r:id="rId7" display="https://trt24-jus-br.zoom.us/j/85366509499" xr:uid="{DB0C2D5F-E147-4E7A-8BE4-F33AE0556B4F}"/>
-    <hyperlink ref="R18" r:id="rId8" display="https://trt24-jus-br.zoom.us/j/85366509499" xr:uid="{491C03DC-F319-4A89-97E1-7591FFD1A851}"/>
-    <hyperlink ref="R19" r:id="rId9" display="https://trt24-jus-br.zoom.us/j/85366509499" xr:uid="{6881F188-59F0-4EF1-99F9-84F5B01E0687}"/>
-    <hyperlink ref="R20" r:id="rId10" xr:uid="{C40BC2D4-5634-4A74-BD93-2B0CB2A7D70C}"/>
-    <hyperlink ref="R21" r:id="rId11" xr:uid="{40E68771-6D02-4BFF-9A46-E2B165D419BF}"/>
-    <hyperlink ref="R22" r:id="rId12" xr:uid="{F94979A7-0CE2-472D-85F0-6E4C831FD8B8}"/>
-    <hyperlink ref="R23" r:id="rId13" xr:uid="{C4163228-EBAE-4ACB-9A5A-BF01A833E4C2}"/>
-    <hyperlink ref="R24" r:id="rId14" xr:uid="{8E3D49F9-3FE0-4C21-9505-73904F08F907}"/>
-    <hyperlink ref="R25" r:id="rId15" xr:uid="{93E3311E-435F-49CB-9DDA-D716D182C785}"/>
-    <hyperlink ref="R26" r:id="rId16" xr:uid="{0905EEA3-9A4C-4F86-82A7-9C748403172B}"/>
+    <hyperlink ref="R6" r:id="rId1" xr:uid="{3E9B6637-28EE-42D8-BC78-3387D892015F}"/>
+    <hyperlink ref="R7" r:id="rId2" xr:uid="{4C57AC64-FBCB-4F98-9973-0B81CB88B645}"/>
+    <hyperlink ref="R10" r:id="rId3" xr:uid="{7D4096F0-BB86-487C-9793-8AEEEC51B77D}"/>
+    <hyperlink ref="R12" r:id="rId4" xr:uid="{93185851-7152-45A8-9E5E-80C7C4BAB5FE}"/>
+    <hyperlink ref="R14" r:id="rId5" xr:uid="{859183C6-5DB0-4335-A3AC-5B109435652E}"/>
+    <hyperlink ref="R15" r:id="rId6" xr:uid="{E5707CEA-F214-467F-80DF-E7A88CEED67D}"/>
+    <hyperlink ref="R16" r:id="rId7" xr:uid="{EB3BD9D2-D36F-4A97-B2FD-9B6223E5C3CA}"/>
+    <hyperlink ref="R17" r:id="rId8" xr:uid="{DFC88F85-6460-4D05-996F-E4C443E0CAA5}"/>
+    <hyperlink ref="R18" r:id="rId9" display="https://trt2-jus-br.zoom.us/j/87232620877?pwd=aU6nYtaZy6CU9OwlgcKSsb6r5uexb1.1%20ID%20da%20reunião:%20872%203262%200877%20Senha%20de%20acesso:%20795431" xr:uid="{F599FCB0-6A84-44AE-8EAD-B03296957A44}"/>
+    <hyperlink ref="R20" r:id="rId10" display="https://trt2-jus-br.zoom.us/j/81881873237?pwd=aEs5S29DM2srNHRuRGFVM2ZEYkVUZz09%20ID%20da%20reunião:%20818%208187%203237%20Senha%20de%20acesso:%20459217" xr:uid="{8C646F10-FBC8-44BD-92C9-CF384BAE15D8}"/>
+    <hyperlink ref="R21" r:id="rId11" display="https://trt15-jus-br.zoom.us/j/83059104477?pwd=h7VDkteaYgzZ4FIU9CoepcQo5ErUHA.1%20ID%20da%20reunião:%20830%205910%204477%20Senha:%20005974" xr:uid="{7D025A64-EF88-422E-85BA-3BA2E7D7D038}"/>
+    <hyperlink ref="R22" r:id="rId12" xr:uid="{B27F959D-344E-4229-9F6E-560E84A07838}"/>
+    <hyperlink ref="R23" r:id="rId13" xr:uid="{8101604F-708D-4C9F-ACFB-C20518FE2CA9}"/>
+    <hyperlink ref="R24" r:id="rId14" xr:uid="{4BF75E21-7027-4917-8732-5A69B1D3C610}"/>
+    <hyperlink ref="R25" r:id="rId15" xr:uid="{6F76C995-CA33-4E14-A445-EDE616279E65}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/Pauta_de_Audiencias.xlsx
+++ b/Pauta_de_Audiencias.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\blu\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EEE00D9F-36E1-4979-B942-8AA30026107F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{49334A71-1D9C-442E-881A-F50F700FA893}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A8406919-E204-4FFE-A1BD-A8C2FFC627D7}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{71ACA0ED-DFD1-4CCA-81B3-5204ACD80980}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="164">
   <si>
     <t>Código P&amp;C</t>
   </si>
@@ -95,274 +95,449 @@
     <t>Link/Observações</t>
   </si>
   <si>
+    <t>Audiência Instrução - Telepresencial</t>
+  </si>
+  <si>
+    <t>0000504-21.2026.5.18.0211</t>
+  </si>
+  <si>
+    <t>Syngenta Seeds Ltda.</t>
+  </si>
+  <si>
+    <t>Dayanne Campera</t>
+  </si>
+  <si>
+    <t>FORMOSA</t>
+  </si>
+  <si>
+    <t>GO</t>
+  </si>
+  <si>
+    <t>VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>1ª Instância</t>
+  </si>
+  <si>
+    <t>Reclamação Trabalhista</t>
+  </si>
+  <si>
+    <t>CENTRAL</t>
+  </si>
+  <si>
+    <t>R$          1.152.545,37</t>
+  </si>
+  <si>
+    <t>Grupo E1</t>
+  </si>
+  <si>
+    <t>VRO</t>
+  </si>
+  <si>
+    <t>https://trt18-jus-br.zoom.us/j/86900317711</t>
+  </si>
+  <si>
+    <t>Audiência Una - Presencial</t>
+  </si>
+  <si>
+    <t>1001393-07.2026.5.02.0080</t>
+  </si>
+  <si>
+    <t>L. Sant'Angelo Pinturas Ltda.</t>
+  </si>
+  <si>
+    <t>Tiago De Souza Vieira</t>
+  </si>
+  <si>
+    <t>SÃO PAULO</t>
+  </si>
+  <si>
+    <t>SP</t>
+  </si>
+  <si>
+    <t>80ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>Conhecimento</t>
+  </si>
+  <si>
+    <t>R$               45.292,92</t>
+  </si>
+  <si>
+    <t>Grupo E2</t>
+  </si>
+  <si>
+    <t>CAL</t>
+  </si>
+  <si>
+    <t>Presencial</t>
+  </si>
+  <si>
+    <t>0011544-18.2025.5.15.0017</t>
+  </si>
+  <si>
+    <t>Moema Bioenergia S.A. - Moema</t>
+  </si>
+  <si>
+    <t>Anderson Sanches Dos Santos</t>
+  </si>
+  <si>
+    <t>SÃO JOSÉ DO RIO PRETO</t>
+  </si>
+  <si>
+    <t>01ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>Instrução</t>
+  </si>
+  <si>
+    <t>R$               60.797,04</t>
+  </si>
+  <si>
+    <t>MBF</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/81715388288?pwd=UFAwUGVFQkN1bGNXcStQUEovR2VZUT09 ID da Reunião 817 1538 8288 Senha 198674</t>
+  </si>
+  <si>
     <t>Audiência Inicial -  Telepresencial</t>
   </si>
   <si>
-    <t>0011229-05.2026.5.03.0044</t>
-  </si>
-  <si>
-    <t>Syngenta Seeds Ltda.</t>
-  </si>
-  <si>
-    <t>Gilvania Ferraz</t>
-  </si>
-  <si>
-    <t>UBERLÂNDIA</t>
+    <t>0010832-56.2026.5.03.0072</t>
+  </si>
+  <si>
+    <t>Usina Fotovoltaica Arinos</t>
+  </si>
+  <si>
+    <t>Leonardo Rocha Braga</t>
+  </si>
+  <si>
+    <t>PIRAPORA</t>
   </si>
   <si>
     <t>MG</t>
   </si>
   <si>
+    <t>R$          1.018.759,39</t>
+  </si>
+  <si>
+    <t>Grupo C</t>
+  </si>
+  <si>
+    <t>ECO</t>
+  </si>
+  <si>
+    <t>https://trt3-jus-br.zoom.us/j/87213692922</t>
+  </si>
+  <si>
+    <t>Audiência Instrução - Presencial</t>
+  </si>
+  <si>
+    <t>0021040-47.2025.5.04.0124</t>
+  </si>
+  <si>
+    <t>Fertilizantes Heringer S.A.</t>
+  </si>
+  <si>
+    <t>Wesley Astrogildo Alves</t>
+  </si>
+  <si>
+    <t>RIO GRANDE</t>
+  </si>
+  <si>
+    <t>RS</t>
+  </si>
+  <si>
+    <t>04ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$               23.800,00</t>
+  </si>
+  <si>
+    <t>Correspondente - doc9</t>
+  </si>
+  <si>
+    <t>BBO</t>
+  </si>
+  <si>
+    <t>Presencial | Advogada - Luciane Veiga Cozza Neves lucianecozza@gmail.com 53984740466</t>
+  </si>
+  <si>
+    <t>0021125-33.2025.5.04.0124</t>
+  </si>
+  <si>
+    <t>R$             180.000,00</t>
+  </si>
+  <si>
+    <t>ARC</t>
+  </si>
+  <si>
+    <t>0012834-08.2024.5.15.0016</t>
+  </si>
+  <si>
+    <t>De Nora Do Brasil Ltda.</t>
+  </si>
+  <si>
+    <t>Luiz Henrique Marques De Arruda</t>
+  </si>
+  <si>
+    <t>SOROCABA</t>
+  </si>
+  <si>
     <t>02ª VARA DO TRABALHO</t>
   </si>
   <si>
-    <t>1ª Instância</t>
-  </si>
-  <si>
-    <t>Reclamação Trabalhista</t>
-  </si>
-  <si>
-    <t>CENTRAL</t>
-  </si>
-  <si>
-    <t>R$             600.000,00</t>
-  </si>
-  <si>
-    <t>Grupo E1</t>
+    <t>R$               64.530,11</t>
+  </si>
+  <si>
+    <t>AAP</t>
   </si>
   <si>
     <t>JPL</t>
   </si>
   <si>
-    <t>GVM</t>
-  </si>
-  <si>
-    <t>https://trt3-jus-br.zoom.us/j/89965522514?pwd=E84WVH0QChjzl3IpQzW7Z5L8So4lbA.1</t>
-  </si>
-  <si>
-    <t>Perícia Técnica</t>
-  </si>
-  <si>
-    <t>0012958-34.2025.5.15.0152</t>
-  </si>
-  <si>
-    <t>Dell Computadores Do Brasil Ltda.</t>
-  </si>
-  <si>
-    <t>Daisy Ferreira Da Silva</t>
-  </si>
-  <si>
-    <t>HORTOLÂNDIA</t>
-  </si>
-  <si>
-    <t>SP</t>
-  </si>
-  <si>
-    <t>VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>Instrução</t>
-  </si>
-  <si>
-    <t>R$             218.600,00</t>
-  </si>
-  <si>
-    <t>AAP</t>
-  </si>
-  <si>
-    <t>Iremos acompanhar</t>
-  </si>
-  <si>
-    <t>Audiência Una - Presencial</t>
-  </si>
-  <si>
-    <t>1001633-10.2026.5.02.0431</t>
+    <t>https://trt15-jus-br.zoom.us/j/87095656771?pwd=aU9LaTBPcFd4aFAydkZSRVlpcWlRQT09 ID da reunião: 87095656771 Senha de acesso: 493462</t>
+  </si>
+  <si>
+    <t>Audiência de Instrução - Semipresencial</t>
+  </si>
+  <si>
+    <t>0000439-62.2026.5.05.0122</t>
+  </si>
+  <si>
+    <t>Fertilizantes Heringer S.A</t>
+  </si>
+  <si>
+    <t>Vagner Bitencourt Dantas</t>
+  </si>
+  <si>
+    <t>CANDEIAS</t>
+  </si>
+  <si>
+    <t>BA</t>
+  </si>
+  <si>
+    <t>Inicial</t>
+  </si>
+  <si>
+    <t>R$             115.000,00</t>
+  </si>
+  <si>
+    <t>https://trt5-jus-br.zoom.us/j/81384816334?pwd=apkqLttWhpydFq87kabYZHeapeGXQE.1</t>
+  </si>
+  <si>
+    <t>1001194-59.2026.5.02.0411</t>
+  </si>
+  <si>
+    <t>Companhia Brasileira De Cartuchos</t>
+  </si>
+  <si>
+    <t>Darcio Junior De Souza Oliveira</t>
+  </si>
+  <si>
+    <t>RIBEIRÃO PIRES</t>
+  </si>
+  <si>
+    <t>R$               56.580,72</t>
+  </si>
+  <si>
+    <t>Grupo B3</t>
+  </si>
+  <si>
+    <t>LMI</t>
+  </si>
+  <si>
+    <t>Audiência de Conciliação - Telepresencial</t>
+  </si>
+  <si>
+    <t>0000112-27.2025.5.19.0005</t>
+  </si>
+  <si>
+    <t>Pedro Afonso Bioenergia Ltda.</t>
+  </si>
+  <si>
+    <t>Gildo Florencio De Melo</t>
+  </si>
+  <si>
+    <t>MACEIÓ</t>
+  </si>
+  <si>
+    <t>AL</t>
+  </si>
+  <si>
+    <t>CEJUSC 2º GRAU</t>
+  </si>
+  <si>
+    <t>R$             123.314,66</t>
+  </si>
+  <si>
+    <t>RYL</t>
+  </si>
+  <si>
+    <t>https://trt19-jus-br.zoom.us/my/cejusc02</t>
+  </si>
+  <si>
+    <t>1000773-09.2026.5.02.0431</t>
   </si>
   <si>
     <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
   </si>
   <si>
-    <t>Irinaldo Jose Barbosa Da Silva</t>
+    <t>Jonathan Wanus Batista Santos</t>
   </si>
   <si>
     <t>SANTO ANDRÉ</t>
   </si>
   <si>
-    <t>01ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$             666.224,50</t>
+    <t>R$             138.909,67</t>
   </si>
   <si>
     <t>Grupo B1</t>
   </si>
   <si>
-    <t>JPE</t>
-  </si>
-  <si>
-    <t>TAM</t>
-  </si>
-  <si>
-    <t>Presencial</t>
-  </si>
-  <si>
-    <t>Audiência Inicial - Presencial</t>
-  </si>
-  <si>
-    <t>1001298-51.2026.5.02.0411</t>
-  </si>
-  <si>
-    <t>Companhia Brasileira De Cartuchos</t>
-  </si>
-  <si>
-    <t>Bianca Carvalho De Macedo</t>
-  </si>
-  <si>
-    <t>RIBEIRÃO PIRES</t>
-  </si>
-  <si>
-    <t>R$             573.916,58</t>
-  </si>
-  <si>
-    <t>Grupo B3</t>
-  </si>
-  <si>
-    <t>LMI</t>
-  </si>
-  <si>
-    <t>1001290-74.2026.5.02.0411</t>
-  </si>
-  <si>
-    <t>Deoclecio Queiroz Batista</t>
-  </si>
-  <si>
-    <t>R$             225.333,51</t>
+    <t>Correspondente - Hebert</t>
+  </si>
+  <si>
+    <t>RFE</t>
+  </si>
+  <si>
+    <t>Audiência Una- Telepresencial</t>
+  </si>
+  <si>
+    <t>0010626-75.2025.5.15.0126</t>
+  </si>
+  <si>
+    <t>Syngenta Proteção De Cultivos Ltda.</t>
+  </si>
+  <si>
+    <t>Joao Paulo Paiva Azevedo</t>
+  </si>
+  <si>
+    <t>PAULÍNIA</t>
+  </si>
+  <si>
+    <t>R$             122.179,31</t>
+  </si>
+  <si>
+    <t>JRM</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/9973700634?pwd=dENDekhCNjFLekRnSExiTzhmK1VLdz09 ID da reunião: 997 370 0634 Senha: 592209</t>
+  </si>
+  <si>
+    <t>0024912-96.2026.5.24.0021</t>
+  </si>
+  <si>
+    <t>Moema Bioenergia S.A. - Monteverde</t>
+  </si>
+  <si>
+    <t>Eduardo Galdino De Souza Junior</t>
+  </si>
+  <si>
+    <t>DOURADOS</t>
+  </si>
+  <si>
+    <t>MS</t>
+  </si>
+  <si>
+    <t>R$             351.071,44</t>
+  </si>
+  <si>
+    <t>BTF</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/my/trt24douvt1sala2</t>
   </si>
   <si>
     <t>Audiência Inicial - Semipresencial</t>
   </si>
   <si>
-    <t>1001006-66.2026.5.02.0411</t>
-  </si>
-  <si>
-    <t>Cbc - Companhia Brasileira De Cartuchos</t>
-  </si>
-  <si>
-    <t>Fernando Aparecido Pimenta</t>
-  </si>
-  <si>
-    <t>R$             154.012,70</t>
-  </si>
-  <si>
-    <t>Audiência Inicial -  Presencial</t>
-  </si>
-  <si>
-    <t>1001258-69.2026.5.02.0411</t>
-  </si>
-  <si>
-    <t>Patricia Da Silva Martins</t>
-  </si>
-  <si>
-    <t>R$               92.029,52</t>
-  </si>
-  <si>
-    <t>1001303-73.2026.5.02.0411</t>
-  </si>
-  <si>
-    <t>Alexsandro Oliveira Lima</t>
-  </si>
-  <si>
-    <t>R$             148.019,33</t>
-  </si>
-  <si>
-    <t>Audiência Instrução - Presencial</t>
-  </si>
-  <si>
-    <t>0016948-37.2026.5.16.0001</t>
-  </si>
-  <si>
-    <t>Fertilizantes Tocantins S.A</t>
-  </si>
-  <si>
-    <t>Jorge Rayr Goncalves Do Nascimento</t>
-  </si>
-  <si>
-    <t>SÃO LUIS</t>
-  </si>
-  <si>
-    <t>MA</t>
-  </si>
-  <si>
-    <t>R$             218.153,71</t>
-  </si>
-  <si>
-    <t>Grupo E2</t>
-  </si>
-  <si>
-    <t>Correspondente - doc9</t>
-  </si>
-  <si>
-    <t>RYL</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Presencial | Advogada - Raiane Costa Correia </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF467886"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>raianecorreia.adv@hotmail.com</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 98985305143 | Preposto - Katicianne da Encarnação Ferreira </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF467886"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>correspondenciasferreira30@gmail.com</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 98 70231725</t>
-    </r>
-  </si>
-  <si>
-    <t>Audiência de Instrução - Presencial</t>
-  </si>
-  <si>
-    <t>1000681-91.2026.5.02.0411</t>
-  </si>
-  <si>
-    <t>Bruno Henrique Rossani</t>
-  </si>
-  <si>
-    <t>R$             163.554,59</t>
+    <t>0001060-98.2026.5.17.0001</t>
+  </si>
+  <si>
+    <t>Jose Rodrigues Pereira</t>
+  </si>
+  <si>
+    <t>VITÓRIA</t>
+  </si>
+  <si>
+    <t>ES</t>
+  </si>
+  <si>
+    <t>R$               76.053,43</t>
+  </si>
+  <si>
+    <t>https://trt17-jus-br.zoom.us/j/88071082197?pwd=3Jyy9TzvvP7udba72jiNuaL9ge2cbv.1</t>
+  </si>
+  <si>
+    <t>Audiência Una - Telepresencial</t>
+  </si>
+  <si>
+    <t>0024341-87.2026.5.24.0066</t>
+  </si>
+  <si>
+    <t>Adriano Da Paixao Silva</t>
+  </si>
+  <si>
+    <t>PONTA PORÃ</t>
+  </si>
+  <si>
+    <t>R$               37.755,18</t>
+  </si>
+  <si>
+    <t>https://trt24-jus-br.zoom.us/j/88280656823</t>
+  </si>
+  <si>
+    <t>Audiência Inicial - Telepresencial</t>
+  </si>
+  <si>
+    <t>0011020-25.2026.5.03.0080</t>
+  </si>
+  <si>
+    <t>Salitre Fertilizantes Ltda</t>
+  </si>
+  <si>
+    <t>Jadir Goncalves Junior</t>
+  </si>
+  <si>
+    <t>PATROCÍNIO</t>
+  </si>
+  <si>
+    <t>R$             313.300,00</t>
+  </si>
+  <si>
+    <t>https://trt3-jus-br.zoom.us/my/vt.patrocinio</t>
+  </si>
+  <si>
+    <t>0000475-80.2026.5.10.0861</t>
+  </si>
+  <si>
+    <t>Pedro Afonso Acucar &amp; Bioenergia Ltda.</t>
+  </si>
+  <si>
+    <t>Ronildo Raposo Bastos</t>
+  </si>
+  <si>
+    <t>GUARAÍ</t>
+  </si>
+  <si>
+    <t>TO</t>
+  </si>
+  <si>
+    <t>R$               92.000,00</t>
+  </si>
+  <si>
+    <t>Correspondente</t>
+  </si>
+  <si>
+    <t>Presencial | Advogada - Claudia Rafaela Vieira claudiarafaelav@hotmail.com 63 99930-0380</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -380,12 +555,6 @@
     <font>
       <sz val="9"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF467886"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -452,16 +621,14 @@
     </border>
     <border>
       <left style="medium">
-        <color rgb="FFBFBFBF"/>
+        <color indexed="64"/>
       </left>
       <right style="medium">
-        <color rgb="FFBFBFBF"/>
+        <color indexed="64"/>
       </right>
-      <top style="medium">
-        <color rgb="FFBFBFBF"/>
-      </top>
+      <top/>
       <bottom style="medium">
-        <color rgb="FFBFBFBF"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -470,9 +637,7 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
+      <top/>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
@@ -481,7 +646,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -506,7 +671,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -843,11 +1008,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7507D9D-F2E3-4822-8706-B52CC5514B69}">
-  <dimension ref="A1:R11"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB99119E-E3CC-43FC-8617-A2A6D6422781}">
+  <dimension ref="A1:R18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="38.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="26.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.21875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="27.109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="28.88671875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -903,12 +1087,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4">
-        <v>105527</v>
+        <v>104347</v>
       </c>
       <c r="B2" s="5">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="C2" s="6">
         <v>0.33333333333333331</v>
@@ -953,45 +1137,45 @@
         <v>30</v>
       </c>
       <c r="Q2" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="R2" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="R2" s="8" t="s">
+    </row>
+    <row r="3" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="4">
+        <v>105842</v>
+      </c>
+      <c r="B3" s="5">
+        <v>46293</v>
+      </c>
+      <c r="C3" s="6">
+        <v>0.34722222222222221</v>
+      </c>
+      <c r="D3" s="7" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="3" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="4">
-        <v>103560</v>
-      </c>
-      <c r="B3" s="5">
-        <v>46290</v>
-      </c>
-      <c r="C3" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D3" s="7" t="s">
+      <c r="E3" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="F3" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="G3" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="H3" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="I3" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="J3" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="K3" s="7" t="s">
         <v>39</v>
-      </c>
-      <c r="K3" s="7" t="s">
-        <v>40</v>
       </c>
       <c r="L3" s="7" t="s">
         <v>26</v>
@@ -1000,54 +1184,54 @@
         <v>27</v>
       </c>
       <c r="N3" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="O3" s="7" t="s">
         <v>41</v>
-      </c>
-      <c r="O3" s="7" t="s">
-        <v>29</v>
       </c>
       <c r="P3" s="7" t="s">
         <v>42</v>
       </c>
       <c r="Q3" s="7" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="R3" s="8" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4">
-        <v>105857</v>
+        <v>101961</v>
       </c>
       <c r="B4" s="5">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="C4" s="6">
-        <v>0.36458333333333331</v>
+        <v>0.36805555555555558</v>
       </c>
       <c r="D4" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="F4" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="G4" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="H4" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="I4" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J4" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="I4" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="J4" s="7" t="s">
+      <c r="K4" s="7" t="s">
         <v>49</v>
-      </c>
-      <c r="K4" s="7" t="s">
-        <v>40</v>
       </c>
       <c r="L4" s="7" t="s">
         <v>26</v>
@@ -1059,51 +1243,51 @@
         <v>50</v>
       </c>
       <c r="O4" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="P4" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="P4" s="7" t="s">
+      <c r="Q4" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="R4" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="Q4" s="7" t="s">
+    </row>
+    <row r="5" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="4">
+        <v>106156</v>
+      </c>
+      <c r="B5" s="5">
+        <v>46293</v>
+      </c>
+      <c r="C5" s="6">
+        <v>0.38194444444444442</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="R4" s="8" t="s">
+      <c r="E5" s="7" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="5" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="4">
-        <v>106013</v>
-      </c>
-      <c r="B5" s="5">
-        <v>46290</v>
-      </c>
-      <c r="C5" s="6">
-        <v>0.375</v>
-      </c>
-      <c r="D5" s="7" t="s">
+      <c r="F5" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="G5" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="H5" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="I5" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="H5" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>38</v>
-      </c>
       <c r="J5" s="7" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="L5" s="7" t="s">
         <v>26</v>
@@ -1112,54 +1296,54 @@
         <v>27</v>
       </c>
       <c r="N5" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="O5" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="O5" s="7" t="s">
+      <c r="P5" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="P5" s="7" t="s">
+      <c r="Q5" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="R5" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="Q5" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="R5" s="8" t="s">
-        <v>54</v>
-      </c>
     </row>
-    <row r="6" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4">
-        <v>105995</v>
+        <v>103302</v>
       </c>
       <c r="B6" s="5">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="C6" s="6">
-        <v>0.38194444444444442</v>
+        <v>0.39583333333333331</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="L6" s="7" t="s">
         <v>26</v>
@@ -1168,54 +1352,54 @@
         <v>27</v>
       </c>
       <c r="N6" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="O6" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="P6" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q6" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="R6" s="8" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="4">
+        <v>103580</v>
+      </c>
+      <c r="B7" s="5">
+        <v>46293</v>
+      </c>
+      <c r="C7" s="6">
+        <v>0.40972222222222221</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="F7" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="O6" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="P6" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q6" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="R6" s="8" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="4">
-        <v>105505</v>
-      </c>
-      <c r="B7" s="5">
-        <v>46290</v>
-      </c>
-      <c r="C7" s="6">
-        <v>0.39583333333333331</v>
-      </c>
-      <c r="D7" s="7" t="s">
+      <c r="G7" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="H7" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="I7" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="J7" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="H7" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>39</v>
-      </c>
       <c r="K7" s="7" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="L7" s="7" t="s">
         <v>26</v>
@@ -1224,54 +1408,54 @@
         <v>27</v>
       </c>
       <c r="N7" s="7" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="O7" s="7" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="P7" s="7" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="Q7" s="7" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="R7" s="8" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4">
-        <v>105949</v>
+        <v>99247</v>
       </c>
       <c r="B8" s="5">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="C8" s="6">
-        <v>0.40277777777777779</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>71</v>
+        <v>18</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="L8" s="7" t="s">
         <v>26</v>
@@ -1280,54 +1464,54 @@
         <v>27</v>
       </c>
       <c r="N8" s="7" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="O8" s="7" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="P8" s="7" t="s">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="Q8" s="7" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="R8" s="8" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4">
-        <v>106021</v>
+        <v>105260</v>
       </c>
       <c r="B9" s="5">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="C9" s="6">
-        <v>0.40972222222222221</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>55</v>
+        <v>86</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>57</v>
+        <v>88</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>59</v>
+        <v>90</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>40</v>
+        <v>92</v>
       </c>
       <c r="L9" s="7" t="s">
         <v>26</v>
@@ -1336,54 +1520,54 @@
         <v>27</v>
       </c>
       <c r="N9" s="7" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="O9" s="7" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="P9" s="7" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="Q9" s="7" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="R9" s="8" t="s">
-        <v>54</v>
+        <v>94</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4">
-        <v>104853</v>
+        <v>105848</v>
       </c>
       <c r="B10" s="5">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="C10" s="6">
         <v>0.41666666666666669</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>83</v>
+        <v>37</v>
       </c>
       <c r="J10" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K10" s="7" t="s">
         <v>49</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>40</v>
       </c>
       <c r="L10" s="7" t="s">
         <v>26</v>
@@ -1392,54 +1576,54 @@
         <v>27</v>
       </c>
       <c r="N10" s="7" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="O10" s="7" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="P10" s="7" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="Q10" s="7" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="R10" s="8" t="s">
-        <v>88</v>
+        <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4">
-        <v>104946</v>
+        <v>99928</v>
       </c>
       <c r="B11" s="5">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="C11" s="6">
-        <v>0.4236111111111111</v>
+        <v>0.42708333333333331</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>57</v>
+        <v>104</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>59</v>
+        <v>106</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>38</v>
+        <v>107</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>39</v>
+        <v>108</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="L11" s="7" t="s">
         <v>26</v>
@@ -1448,26 +1632,430 @@
         <v>27</v>
       </c>
       <c r="N11" s="7" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="O11" s="7" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="P11" s="7" t="s">
-        <v>62</v>
+        <v>110</v>
       </c>
       <c r="Q11" s="7" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="R11" s="8" t="s">
-        <v>54</v>
+        <v>111</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="4">
+        <v>104809</v>
+      </c>
+      <c r="B12" s="5">
+        <v>46293</v>
+      </c>
+      <c r="C12" s="6">
+        <v>0.4861111111111111</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="L12" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M12" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N12" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="O12" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="P12" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q12" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="R12" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="4">
+        <v>100924</v>
+      </c>
+      <c r="B13" s="5">
+        <v>46293</v>
+      </c>
+      <c r="C13" s="6">
+        <v>0.56944444444444442</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J13" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L13" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M13" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N13" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="O13" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P13" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q13" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="R13" s="8" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="4">
+        <v>105019</v>
+      </c>
+      <c r="B14" s="5">
+        <v>46293</v>
+      </c>
+      <c r="C14" s="6">
+        <v>0.57291666666666663</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="J14" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="L14" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M14" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N14" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="O14" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="P14" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q14" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="R14" s="8" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="4">
+        <v>105568</v>
+      </c>
+      <c r="B15" s="5">
+        <v>46293</v>
+      </c>
+      <c r="C15" s="6">
+        <v>0.57638888888888884</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="J15" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="L15" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M15" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N15" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="O15" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="P15" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q15" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="R15" s="8" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="4">
+        <v>105432</v>
+      </c>
+      <c r="B16" s="5">
+        <v>46293</v>
+      </c>
+      <c r="C16" s="6">
+        <v>0.59375</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="J16" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K16" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="L16" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M16" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N16" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="O16" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="P16" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q16" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="R16" s="8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="4">
+        <v>105998</v>
+      </c>
+      <c r="B17" s="5">
+        <v>46293</v>
+      </c>
+      <c r="C17" s="6">
+        <v>0.60069444444444442</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="J17" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="L17" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M17" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N17" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="O17" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="P17" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q17" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="R17" s="8" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="4">
+        <v>105893</v>
+      </c>
+      <c r="B18" s="5">
+        <v>46293</v>
+      </c>
+      <c r="C18" s="6">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="I18" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="J18" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="L18" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M18" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N18" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="O18" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="P18" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q18" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="R18" s="8" t="s">
+        <v>163</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="R2" r:id="rId1" xr:uid="{FEE4FA16-F4EF-4884-84C9-5E21EDF0EF3F}"/>
+    <hyperlink ref="R2" r:id="rId1" xr:uid="{95C41F58-3842-4941-84C0-4E41CF3BF528}"/>
+    <hyperlink ref="R4" r:id="rId2" display="https://trt15-jus-br.zoom.us/j/81715388288?pwd=UFAwUGVFQkN1bGNXcStQUEovR2VZUT09%20ID%20da%20Reunião%20817%201538%208288%20Senha%20198674" xr:uid="{66F6AC30-2DD9-4D73-A693-58FD44C7E513}"/>
+    <hyperlink ref="R5" r:id="rId3" xr:uid="{F28160D0-1A3B-4008-93FB-5D6BA38DCEA6}"/>
+    <hyperlink ref="R6" r:id="rId4" display="mailto:lucianecozza@gmail.com" xr:uid="{B07A87C9-1834-49BD-9549-EF7989F4D3F2}"/>
+    <hyperlink ref="R7" r:id="rId5" display="mailto:lucianecozza@gmail.com" xr:uid="{F5744966-D984-4380-86DB-E4714149FD62}"/>
+    <hyperlink ref="R8" r:id="rId6" display="https://trt15-jus-br.zoom.us/j/87095656771?pwd=aU9LaTBPcFd4aFAydkZSRVlpcWlRQT09%20ID%20da%20reunião:%2087095656771%20Senha%20de%20acesso:%20493462" xr:uid="{935FB631-F272-4CC4-B92D-6F73074C488A}"/>
+    <hyperlink ref="R9" r:id="rId7" xr:uid="{8D9DD257-B0B0-43F8-83EE-C8694A826464}"/>
+    <hyperlink ref="R11" r:id="rId8" xr:uid="{C865ADBB-9361-4C89-A64E-9BF22550947D}"/>
+    <hyperlink ref="R13" r:id="rId9" display="https://trt15-jus-br.zoom.us/j/9973700634?pwd=dENDekhCNjFLekRnSExiTzhmK1VLdz09%20ID%20da%20reunião:%20997%20370%200634%20Senha:%20592209" xr:uid="{6CF8C3D3-A3B6-4309-9DBC-94DB4B1068ED}"/>
+    <hyperlink ref="R14" r:id="rId10" xr:uid="{5FB6E6AA-19E1-4D53-A5B8-AE44970377D1}"/>
+    <hyperlink ref="R15" r:id="rId11" xr:uid="{16B8370C-655D-4F27-BD1C-3DEBDF8824DA}"/>
+    <hyperlink ref="R16" r:id="rId12" xr:uid="{A3AD2B59-8F70-46C7-9DD3-618BD825C254}"/>
+    <hyperlink ref="R17" r:id="rId13" xr:uid="{AA190877-4F5D-481B-A13A-290FDB73C5F0}"/>
+    <hyperlink ref="R18" r:id="rId14" display="mailto:claudiarafaelav@hotmail.com" xr:uid="{CF44BEFF-5A69-42C2-A487-F1067A570948}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId2"/>
 </worksheet>
 </file>
--- a/Pauta_de_Audiencias.xlsx
+++ b/Pauta_de_Audiencias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\blu\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{49334A71-1D9C-442E-881A-F50F700FA893}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DDAE2A53-DBC4-41AE-9E19-33BD53F9EC0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{71ACA0ED-DFD1-4CCA-81B3-5204ACD80980}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E71D9670-29F1-495F-9DB0-C365E02F020A}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="201">
   <si>
     <t>Código P&amp;C</t>
   </si>
@@ -95,449 +95,560 @@
     <t>Link/Observações</t>
   </si>
   <si>
-    <t>Audiência Instrução - Telepresencial</t>
-  </si>
-  <si>
-    <t>0000504-21.2026.5.18.0211</t>
+    <t>Audiência de Conciliação - Telepresencial</t>
+  </si>
+  <si>
+    <t>1000751-74.2024.5.02.0445</t>
+  </si>
+  <si>
+    <t>Syngenta Proteção De Cultivos Ltda.</t>
+  </si>
+  <si>
+    <t>Adilson Isoldino Da Rocha</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>SP</t>
+  </si>
+  <si>
+    <t>CEJUSC TST</t>
+  </si>
+  <si>
+    <t>3ª Instância</t>
+  </si>
+  <si>
+    <t>Reclamação Trabalhista</t>
+  </si>
+  <si>
+    <t>CENTRAL</t>
+  </si>
+  <si>
+    <t>R$             285.601,67</t>
+  </si>
+  <si>
+    <t>Grupo E1</t>
+  </si>
+  <si>
+    <t>GVM</t>
+  </si>
+  <si>
+    <t>bit.ly/Cejusc2026</t>
+  </si>
+  <si>
+    <t>Audiência Una- Telepresencial</t>
+  </si>
+  <si>
+    <t>0000652-71.2026.5.05.0024</t>
+  </si>
+  <si>
+    <t>Salitre Fertilizantes Ltda.</t>
+  </si>
+  <si>
+    <t>Leonardo Felix Do Nascimento</t>
+  </si>
+  <si>
+    <t>SALVADOR</t>
+  </si>
+  <si>
+    <t>BA</t>
+  </si>
+  <si>
+    <t>24ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>Conhecimento</t>
+  </si>
+  <si>
+    <t>R$               15.684,57</t>
+  </si>
+  <si>
+    <t>Grupo E2</t>
+  </si>
+  <si>
+    <t>CAL</t>
+  </si>
+  <si>
+    <t>https://trt5-jus-br.zoom.us/my/sl24vtssa</t>
+  </si>
+  <si>
+    <t>Audiência Una - Presencial</t>
+  </si>
+  <si>
+    <t>1001161-06.2026.5.02.0432</t>
+  </si>
+  <si>
+    <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
+  </si>
+  <si>
+    <t>Ronaldo Alves De Lima</t>
+  </si>
+  <si>
+    <t>SANTO ANDRÉ</t>
+  </si>
+  <si>
+    <t>02ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>Instrução</t>
+  </si>
+  <si>
+    <t>R$             143.204,39</t>
+  </si>
+  <si>
+    <t>Grupo B1</t>
+  </si>
+  <si>
+    <t>JPE</t>
+  </si>
+  <si>
+    <t>BSO</t>
+  </si>
+  <si>
+    <t>Presencial</t>
+  </si>
+  <si>
+    <t>1004851-31.2025.5.02.0221</t>
   </si>
   <si>
     <t>Syngenta Seeds Ltda.</t>
   </si>
   <si>
-    <t>Dayanne Campera</t>
-  </si>
-  <si>
-    <t>FORMOSA</t>
+    <t>Daniel Soares Correa</t>
+  </si>
+  <si>
+    <t>CAJAMAR</t>
+  </si>
+  <si>
+    <t>VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>1ª Instância</t>
+  </si>
+  <si>
+    <t>R$               92.151,91</t>
+  </si>
+  <si>
+    <t>Correspondente - Carlos Florian</t>
+  </si>
+  <si>
+    <t>Presencial | Advogado - Dr. Wellington Picinatto, (11) 97507-6655 | Preposto - Nilma Terezinha da Silva, (11) 98409-2456</t>
+  </si>
+  <si>
+    <t>Audiência Inicial -  Presencial</t>
+  </si>
+  <si>
+    <t>1001592-34.2026.5.02.0434</t>
+  </si>
+  <si>
+    <t>Leandro Sinvaldo De Sousa</t>
+  </si>
+  <si>
+    <t>04ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             193.028,00</t>
+  </si>
+  <si>
+    <t>Correspondente - Hebert</t>
+  </si>
+  <si>
+    <t>TAM</t>
+  </si>
+  <si>
+    <t>Audiência Instrução - Presencial</t>
+  </si>
+  <si>
+    <t>0011061-55.2025.5.15.0124</t>
+  </si>
+  <si>
+    <t>Viterra Bioenergia S.A.</t>
+  </si>
+  <si>
+    <t>Epifanio Pereira</t>
+  </si>
+  <si>
+    <t>ARAÇATUBA</t>
+  </si>
+  <si>
+    <t>R$             240.908,10</t>
+  </si>
+  <si>
+    <t>Correspondente - Carla</t>
+  </si>
+  <si>
+    <t>RYL</t>
+  </si>
+  <si>
+    <t>1001171-50.2026.5.02.0432</t>
+  </si>
+  <si>
+    <t>Cristiano Alves De Melo</t>
+  </si>
+  <si>
+    <t>R$          1.032.642,64</t>
+  </si>
+  <si>
+    <t>GSM</t>
+  </si>
+  <si>
+    <t>Audiência Inicial -  Telepresencial</t>
+  </si>
+  <si>
+    <t>0001135-17.2026.5.18.0129</t>
+  </si>
+  <si>
+    <t>Spic Brasil Energia Participacoes S.A.</t>
+  </si>
+  <si>
+    <t>Silvio Martins De Jesus</t>
+  </si>
+  <si>
+    <t>QUIRINÓPOLIS</t>
   </si>
   <si>
     <t>GO</t>
   </si>
   <si>
-    <t>VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>1ª Instância</t>
-  </si>
-  <si>
-    <t>Reclamação Trabalhista</t>
-  </si>
-  <si>
-    <t>CENTRAL</t>
-  </si>
-  <si>
-    <t>R$          1.152.545,37</t>
-  </si>
-  <si>
-    <t>Grupo E1</t>
-  </si>
-  <si>
-    <t>VRO</t>
-  </si>
-  <si>
-    <t>https://trt18-jus-br.zoom.us/j/86900317711</t>
-  </si>
-  <si>
-    <t>Audiência Una - Presencial</t>
-  </si>
-  <si>
-    <t>1001393-07.2026.5.02.0080</t>
+    <t>R$               30.621,66</t>
+  </si>
+  <si>
+    <t>Grupo C</t>
+  </si>
+  <si>
+    <t>ECO</t>
+  </si>
+  <si>
+    <t>https://trt18-jus-br.zoom.us/my/cejuscdigital.manha</t>
+  </si>
+  <si>
+    <t>Audiência Una - Telepresencial</t>
+  </si>
+  <si>
+    <t>0010365-66.2026.5.15.0097</t>
+  </si>
+  <si>
+    <t>Itw Chemical Products Ltda.</t>
+  </si>
+  <si>
+    <t>Aline Evelyn De Bastos Xavier</t>
+  </si>
+  <si>
+    <t>JUNDIAÍ</t>
+  </si>
+  <si>
+    <t>R$               93.662,38</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/85290954703?pwd=ZldYYzczVnhUbm1VN3BPVzAvRmY5QT ID da reunião: 852 9095 4703 senha de acesso: 517309</t>
+  </si>
+  <si>
+    <t>0001161-41.2025.5.19.0058</t>
+  </si>
+  <si>
+    <t>Marcio Henrique Dos Santos</t>
+  </si>
+  <si>
+    <t>SANTANA DO IPANEMA</t>
+  </si>
+  <si>
+    <t>AL</t>
+  </si>
+  <si>
+    <t>CEJUSC 2º GRAU</t>
+  </si>
+  <si>
+    <t>Recursal</t>
+  </si>
+  <si>
+    <t>R$               34.524,00</t>
+  </si>
+  <si>
+    <t>AAP</t>
+  </si>
+  <si>
+    <t>MBF</t>
+  </si>
+  <si>
+    <t>https://trt19-jus-br.zoom.us/my/cejusc03</t>
+  </si>
+  <si>
+    <t>Audiência Inicial - Telepresencial</t>
+  </si>
+  <si>
+    <t>0011446-53.2026.5.15.0096</t>
+  </si>
+  <si>
+    <t>A. Raymond Brasil Ltda</t>
+  </si>
+  <si>
+    <t>Andressa Pereira Dos Santos</t>
+  </si>
+  <si>
+    <t>03ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             260.365,00</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/84713424685?pwd=eEZTakhrSWFNN2RKYVFDcWU1K3ZmZz09 ID da reunião: 847 1342 4685 Senha de acesso: 525290</t>
+  </si>
+  <si>
+    <t>1000782-90.2025.5.02.0047</t>
   </si>
   <si>
     <t>L. Sant'Angelo Pinturas Ltda.</t>
   </si>
   <si>
-    <t>Tiago De Souza Vieira</t>
+    <t>Eliseu De Jesus Santos</t>
   </si>
   <si>
     <t>SÃO PAULO</t>
   </si>
   <si>
-    <t>SP</t>
-  </si>
-  <si>
-    <t>80ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>Conhecimento</t>
-  </si>
-  <si>
-    <t>R$               45.292,92</t>
-  </si>
-  <si>
-    <t>Grupo E2</t>
-  </si>
-  <si>
-    <t>CAL</t>
-  </si>
-  <si>
-    <t>Presencial</t>
-  </si>
-  <si>
-    <t>0011544-18.2025.5.15.0017</t>
-  </si>
-  <si>
-    <t>Moema Bioenergia S.A. - Moema</t>
-  </si>
-  <si>
-    <t>Anderson Sanches Dos Santos</t>
-  </si>
-  <si>
-    <t>SÃO JOSÉ DO RIO PRETO</t>
+    <t>47ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             218.847,34</t>
+  </si>
+  <si>
+    <t>BBO</t>
+  </si>
+  <si>
+    <t>1001596-71.2026.5.02.0434</t>
+  </si>
+  <si>
+    <t>Fernando Henrique Alves Da Silva</t>
+  </si>
+  <si>
+    <t>R$             150.186,70</t>
+  </si>
+  <si>
+    <t>RFE</t>
+  </si>
+  <si>
+    <t>0010490-40.2026.5.15.0095</t>
+  </si>
+  <si>
+    <t>Evelyn Karine Mendes</t>
+  </si>
+  <si>
+    <t>CAMPINAS</t>
+  </si>
+  <si>
+    <t>08ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$               83.890,77</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/85312873319?pwd=eERLQVlQVmhJT2JRVmJGTjd2SFFoZz09</t>
+  </si>
+  <si>
+    <t>Sessão de Julgamento TRT - Presencial</t>
+  </si>
+  <si>
+    <t>1001106-27.2018.5.02.0435</t>
+  </si>
+  <si>
+    <t>Damasio Dias Cordeiro</t>
+  </si>
+  <si>
+    <t>12ª TURMA</t>
+  </si>
+  <si>
+    <t>R$             215.049,10</t>
+  </si>
+  <si>
+    <t>BCF</t>
+  </si>
+  <si>
+    <t>1001768-53.2025.5.02.0432</t>
+  </si>
+  <si>
+    <t>Manoel Donizete De Oliveira</t>
+  </si>
+  <si>
+    <t>R$          2.558.032,56</t>
+  </si>
+  <si>
+    <t>1001794-73.2025.5.02.0069</t>
+  </si>
+  <si>
+    <t>Telefonica Brasil S.A.</t>
+  </si>
+  <si>
+    <t>Sueli Aparecida Dourado</t>
+  </si>
+  <si>
+    <t>R$          2.139.761,00</t>
+  </si>
+  <si>
+    <t>TFR</t>
+  </si>
+  <si>
+    <t>0012048-80.2026.5.15.0084</t>
+  </si>
+  <si>
+    <t>Embraer S.A.</t>
+  </si>
+  <si>
+    <t>Natassia Ramos Da Silveira</t>
+  </si>
+  <si>
+    <t>SÃO JOSÉ DOS CAMPOS</t>
+  </si>
+  <si>
+    <t>Homologação de Transação Extrajudicial</t>
+  </si>
+  <si>
+    <t>R$                 1.000,00</t>
+  </si>
+  <si>
+    <t>Grupo B2</t>
+  </si>
+  <si>
+    <t>VCR</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/83881577714?pwd=enl5OVBJWjJwaHQyTGI5Vy9URVlaUT09</t>
+  </si>
+  <si>
+    <t>0010713-70.2026.5.15.0037</t>
+  </si>
+  <si>
+    <t>Ouroeste Bioenergia Ltda.</t>
+  </si>
+  <si>
+    <t>Eric Miler Nunes Sales</t>
+  </si>
+  <si>
+    <t>FERNANDÓPOLIS</t>
+  </si>
+  <si>
+    <t>R$             205.000,00</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/89770082465?pwd=K09aQWhUOW5ESytiRUdCOUFSa2E4dz09</t>
+  </si>
+  <si>
+    <t>0001264-08.2026.5.23.0121</t>
+  </si>
+  <si>
+    <t>Inpasa Agroindustrial S/A</t>
+  </si>
+  <si>
+    <t>Andriw Farley Batista Oliveira</t>
+  </si>
+  <si>
+    <t>NOVA MUTUM</t>
+  </si>
+  <si>
+    <t>MT</t>
+  </si>
+  <si>
+    <t>R$             597.732,94</t>
+  </si>
+  <si>
+    <t>RRU</t>
+  </si>
+  <si>
+    <t>https://trt23-jus-br.zoom.us/my/vtnovamutum?pwd=YUtIQWQ2T2h2U2Fya0lNZ2M1dkJodz09</t>
+  </si>
+  <si>
+    <t>0024175-55.2026.5.24.0066</t>
+  </si>
+  <si>
+    <t>Moema Bioenergia S.A. - Monteverde</t>
+  </si>
+  <si>
+    <t>Dionaty Sousa Dos Santos</t>
+  </si>
+  <si>
+    <t>PONTA PORÃ</t>
+  </si>
+  <si>
+    <t>MS</t>
+  </si>
+  <si>
+    <t>R$               55.756,42</t>
+  </si>
+  <si>
+    <t>BTF</t>
+  </si>
+  <si>
+    <t>LWP</t>
+  </si>
+  <si>
+    <t>https://trt24-jus-br.zoom.us/j/88062331360</t>
+  </si>
+  <si>
+    <t>0010735-30.2026.5.15.0005</t>
+  </si>
+  <si>
+    <t>Renato Tamarozi Goncalves</t>
+  </si>
+  <si>
+    <t>BAURU</t>
   </si>
   <si>
     <t>01ª VARA DO TRABALHO</t>
   </si>
   <si>
-    <t>Instrução</t>
-  </si>
-  <si>
-    <t>R$               60.797,04</t>
-  </si>
-  <si>
-    <t>MBF</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/81715388288?pwd=UFAwUGVFQkN1bGNXcStQUEovR2VZUT09 ID da Reunião 817 1538 8288 Senha 198674</t>
-  </si>
-  <si>
-    <t>Audiência Inicial -  Telepresencial</t>
-  </si>
-  <si>
-    <t>0010832-56.2026.5.03.0072</t>
-  </si>
-  <si>
-    <t>Usina Fotovoltaica Arinos</t>
-  </si>
-  <si>
-    <t>Leonardo Rocha Braga</t>
-  </si>
-  <si>
-    <t>PIRAPORA</t>
-  </si>
-  <si>
-    <t>MG</t>
-  </si>
-  <si>
-    <t>R$          1.018.759,39</t>
-  </si>
-  <si>
-    <t>Grupo C</t>
-  </si>
-  <si>
-    <t>ECO</t>
-  </si>
-  <si>
-    <t>https://trt3-jus-br.zoom.us/j/87213692922</t>
-  </si>
-  <si>
-    <t>Audiência Instrução - Presencial</t>
-  </si>
-  <si>
-    <t>0021040-47.2025.5.04.0124</t>
-  </si>
-  <si>
-    <t>Fertilizantes Heringer S.A.</t>
-  </si>
-  <si>
-    <t>Wesley Astrogildo Alves</t>
-  </si>
-  <si>
-    <t>RIO GRANDE</t>
-  </si>
-  <si>
-    <t>RS</t>
-  </si>
-  <si>
-    <t>04ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$               23.800,00</t>
-  </si>
-  <si>
-    <t>Correspondente - doc9</t>
-  </si>
-  <si>
-    <t>BBO</t>
-  </si>
-  <si>
-    <t>Presencial | Advogada - Luciane Veiga Cozza Neves lucianecozza@gmail.com 53984740466</t>
-  </si>
-  <si>
-    <t>0021125-33.2025.5.04.0124</t>
-  </si>
-  <si>
-    <t>R$             180.000,00</t>
-  </si>
-  <si>
-    <t>ARC</t>
-  </si>
-  <si>
-    <t>0012834-08.2024.5.15.0016</t>
-  </si>
-  <si>
-    <t>De Nora Do Brasil Ltda.</t>
-  </si>
-  <si>
-    <t>Luiz Henrique Marques De Arruda</t>
-  </si>
-  <si>
-    <t>SOROCABA</t>
-  </si>
-  <si>
-    <t>02ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$               64.530,11</t>
-  </si>
-  <si>
-    <t>AAP</t>
-  </si>
-  <si>
-    <t>JPL</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/87095656771?pwd=aU9LaTBPcFd4aFAydkZSRVlpcWlRQT09 ID da reunião: 87095656771 Senha de acesso: 493462</t>
-  </si>
-  <si>
-    <t>Audiência de Instrução - Semipresencial</t>
-  </si>
-  <si>
-    <t>0000439-62.2026.5.05.0122</t>
-  </si>
-  <si>
-    <t>Fertilizantes Heringer S.A</t>
-  </si>
-  <si>
-    <t>Vagner Bitencourt Dantas</t>
-  </si>
-  <si>
-    <t>CANDEIAS</t>
-  </si>
-  <si>
-    <t>BA</t>
-  </si>
-  <si>
-    <t>Inicial</t>
-  </si>
-  <si>
-    <t>R$             115.000,00</t>
-  </si>
-  <si>
-    <t>https://trt5-jus-br.zoom.us/j/81384816334?pwd=apkqLttWhpydFq87kabYZHeapeGXQE.1</t>
-  </si>
-  <si>
-    <t>1001194-59.2026.5.02.0411</t>
-  </si>
-  <si>
-    <t>Companhia Brasileira De Cartuchos</t>
-  </si>
-  <si>
-    <t>Darcio Junior De Souza Oliveira</t>
-  </si>
-  <si>
-    <t>RIBEIRÃO PIRES</t>
-  </si>
-  <si>
-    <t>R$               56.580,72</t>
-  </si>
-  <si>
-    <t>Grupo B3</t>
-  </si>
-  <si>
-    <t>LMI</t>
-  </si>
-  <si>
-    <t>Audiência de Conciliação - Telepresencial</t>
-  </si>
-  <si>
-    <t>0000112-27.2025.5.19.0005</t>
-  </si>
-  <si>
-    <t>Pedro Afonso Bioenergia Ltda.</t>
-  </si>
-  <si>
-    <t>Gildo Florencio De Melo</t>
-  </si>
-  <si>
-    <t>MACEIÓ</t>
-  </si>
-  <si>
-    <t>AL</t>
-  </si>
-  <si>
-    <t>CEJUSC 2º GRAU</t>
-  </si>
-  <si>
-    <t>R$             123.314,66</t>
-  </si>
-  <si>
-    <t>RYL</t>
-  </si>
-  <si>
-    <t>https://trt19-jus-br.zoom.us/my/cejusc02</t>
-  </si>
-  <si>
-    <t>1000773-09.2026.5.02.0431</t>
-  </si>
-  <si>
-    <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
-  </si>
-  <si>
-    <t>Jonathan Wanus Batista Santos</t>
-  </si>
-  <si>
-    <t>SANTO ANDRÉ</t>
-  </si>
-  <si>
-    <t>R$             138.909,67</t>
-  </si>
-  <si>
-    <t>Grupo B1</t>
-  </si>
-  <si>
-    <t>Correspondente - Hebert</t>
-  </si>
-  <si>
-    <t>RFE</t>
-  </si>
-  <si>
-    <t>Audiência Una- Telepresencial</t>
-  </si>
-  <si>
-    <t>0010626-75.2025.5.15.0126</t>
-  </si>
-  <si>
-    <t>Syngenta Proteção De Cultivos Ltda.</t>
-  </si>
-  <si>
-    <t>Joao Paulo Paiva Azevedo</t>
-  </si>
-  <si>
-    <t>PAULÍNIA</t>
-  </si>
-  <si>
-    <t>R$             122.179,31</t>
-  </si>
-  <si>
-    <t>JRM</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/9973700634?pwd=dENDekhCNjFLekRnSExiTzhmK1VLdz09 ID da reunião: 997 370 0634 Senha: 592209</t>
-  </si>
-  <si>
-    <t>0024912-96.2026.5.24.0021</t>
-  </si>
-  <si>
-    <t>Moema Bioenergia S.A. - Monteverde</t>
-  </si>
-  <si>
-    <t>Eduardo Galdino De Souza Junior</t>
-  </si>
-  <si>
-    <t>DOURADOS</t>
-  </si>
-  <si>
-    <t>MS</t>
-  </si>
-  <si>
-    <t>R$             351.071,44</t>
-  </si>
-  <si>
-    <t>BTF</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/my/trt24douvt1sala2</t>
-  </si>
-  <si>
-    <t>Audiência Inicial - Semipresencial</t>
-  </si>
-  <si>
-    <t>0001060-98.2026.5.17.0001</t>
-  </si>
-  <si>
-    <t>Jose Rodrigues Pereira</t>
-  </si>
-  <si>
-    <t>VITÓRIA</t>
-  </si>
-  <si>
-    <t>ES</t>
-  </si>
-  <si>
-    <t>R$               76.053,43</t>
-  </si>
-  <si>
-    <t>https://trt17-jus-br.zoom.us/j/88071082197?pwd=3Jyy9TzvvP7udba72jiNuaL9ge2cbv.1</t>
-  </si>
-  <si>
-    <t>Audiência Una - Telepresencial</t>
-  </si>
-  <si>
-    <t>0024341-87.2026.5.24.0066</t>
-  </si>
-  <si>
-    <t>Adriano Da Paixao Silva</t>
-  </si>
-  <si>
-    <t>PONTA PORÃ</t>
-  </si>
-  <si>
-    <t>R$               37.755,18</t>
-  </si>
-  <si>
-    <t>https://trt24-jus-br.zoom.us/j/88280656823</t>
-  </si>
-  <si>
-    <t>Audiência Inicial - Telepresencial</t>
-  </si>
-  <si>
-    <t>0011020-25.2026.5.03.0080</t>
-  </si>
-  <si>
-    <t>Salitre Fertilizantes Ltda</t>
-  </si>
-  <si>
-    <t>Jadir Goncalves Junior</t>
-  </si>
-  <si>
-    <t>PATROCÍNIO</t>
-  </si>
-  <si>
-    <t>R$             313.300,00</t>
-  </si>
-  <si>
-    <t>https://trt3-jus-br.zoom.us/my/vt.patrocinio</t>
-  </si>
-  <si>
-    <t>0000475-80.2026.5.10.0861</t>
-  </si>
-  <si>
-    <t>Pedro Afonso Acucar &amp; Bioenergia Ltda.</t>
-  </si>
-  <si>
-    <t>Ronildo Raposo Bastos</t>
-  </si>
-  <si>
-    <t>GUARAÍ</t>
-  </si>
-  <si>
-    <t>TO</t>
-  </si>
-  <si>
-    <t>R$               92.000,00</t>
-  </si>
-  <si>
-    <t>Correspondente</t>
-  </si>
-  <si>
-    <t>Presencial | Advogada - Claudia Rafaela Vieira claudiarafaelav@hotmail.com 63 99930-0380</t>
+    <t>R$             105.575,58</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/82335308963?pwd=ZzJhaVZQdFpUWFFQbUgrdFd3c3k3Zz0</t>
+  </si>
+  <si>
+    <t>0011041-46.2026.5.15.0151</t>
+  </si>
+  <si>
+    <t>Embraer S.A</t>
+  </si>
+  <si>
+    <t>Bruno Menon</t>
+  </si>
+  <si>
+    <t>ARARAQUARA</t>
+  </si>
+  <si>
+    <t>R$             489.085,98</t>
+  </si>
+  <si>
+    <t>ANB</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/88029879844?pwd=NDNXMkZ2QzJQdzc2MmVkRmdJcEFJdz09</t>
+  </si>
+  <si>
+    <t>1001341-81.2026.5.02.0089</t>
+  </si>
+  <si>
+    <t>Andre Luiz Dos Santos</t>
+  </si>
+  <si>
+    <t>89ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$               91.750,11</t>
+  </si>
+  <si>
+    <t>1000597-21.2026.5.02.0434</t>
+  </si>
+  <si>
+    <t>Rogerio Medeiros</t>
+  </si>
+  <si>
+    <t>R$          1.502.000,00</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -557,14 +668,6 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -644,11 +747,10 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -671,12 +773,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1008,8 +1106,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB99119E-E3CC-43FC-8617-A2A6D6422781}">
-  <dimension ref="A1:R18"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE990739-3485-43FF-8937-583D09DE1938}">
+  <dimension ref="A1:R26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
@@ -1017,18 +1115,18 @@
     <col min="4" max="4" width="33.77734375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="38.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="26.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="27.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.77734375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="5.5546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="18.5546875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11.77734375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="32.33203125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="7.21875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="15.77734375" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14.33203125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="27.109375" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="28.88671875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="111.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.3">
@@ -1087,15 +1185,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4">
-        <v>104347</v>
+        <v>98420</v>
       </c>
       <c r="B2" s="5">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="C2" s="6">
-        <v>0.33333333333333331</v>
+        <v>0.37916666666666665</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>18</v>
@@ -1139,19 +1237,19 @@
       <c r="Q2" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="R2" s="8" t="s">
+      <c r="R2" s="7" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4">
-        <v>105842</v>
+        <v>105654</v>
       </c>
       <c r="B3" s="5">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="C3" s="6">
-        <v>0.34722222222222221</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>32</v>
@@ -1195,43 +1293,43 @@
       <c r="Q3" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="R3" s="8" t="s">
+      <c r="R3" s="7" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4">
-        <v>101961</v>
+        <v>105304</v>
       </c>
       <c r="B4" s="5">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="C4" s="6">
-        <v>0.36805555555555558</v>
+        <v>0.39930555555555558</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L4" s="7" t="s">
         <v>26</v>
@@ -1240,54 +1338,54 @@
         <v>27</v>
       </c>
       <c r="N4" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O4" s="7" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="P4" s="7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="Q4" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="R4" s="8" t="s">
-        <v>52</v>
+        <v>54</v>
+      </c>
+      <c r="R4" s="7" t="s">
+        <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4">
-        <v>106156</v>
+        <v>103641</v>
       </c>
       <c r="B5" s="5">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="C5" s="6">
-        <v>0.38194444444444442</v>
+        <v>0.40277777777777779</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="L5" s="7" t="s">
         <v>26</v>
@@ -1296,54 +1394,54 @@
         <v>27</v>
       </c>
       <c r="N5" s="7" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="O5" s="7" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="P5" s="7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="Q5" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="R5" s="8" t="s">
-        <v>62</v>
+        <v>30</v>
+      </c>
+      <c r="R5" s="7" t="s">
+        <v>64</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4">
-        <v>103302</v>
+        <v>106078</v>
       </c>
       <c r="B6" s="5">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="C6" s="6">
-        <v>0.39583333333333331</v>
+        <v>0.40972222222222221</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="I6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J6" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="J6" s="7" t="s">
-        <v>69</v>
-      </c>
       <c r="K6" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L6" s="7" t="s">
         <v>26</v>
@@ -1352,54 +1450,54 @@
         <v>27</v>
       </c>
       <c r="N6" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="O6" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="P6" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="O6" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="P6" s="7" t="s">
+      <c r="Q6" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="Q6" s="7" t="s">
+      <c r="R6" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="4">
+        <v>103194</v>
+      </c>
+      <c r="B7" s="5">
+        <v>46294</v>
+      </c>
+      <c r="C7" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D7" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="R6" s="8" t="s">
+      <c r="E7" s="7" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="7" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="4">
-        <v>103580</v>
-      </c>
-      <c r="B7" s="5">
-        <v>46293</v>
-      </c>
-      <c r="C7" s="6">
-        <v>0.40972222222222221</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="E7" s="7" t="s">
+      <c r="F7" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="F7" s="7" t="s">
-        <v>65</v>
-      </c>
       <c r="G7" s="7" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L7" s="7" t="s">
         <v>26</v>
@@ -1408,54 +1506,54 @@
         <v>27</v>
       </c>
       <c r="N7" s="7" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="O7" s="7" t="s">
         <v>41</v>
       </c>
       <c r="P7" s="7" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="Q7" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="R7" s="8" t="s">
-        <v>73</v>
+        <v>79</v>
+      </c>
+      <c r="R7" s="7" t="s">
+        <v>55</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4">
-        <v>99247</v>
+        <v>105335</v>
       </c>
       <c r="B8" s="5">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="C8" s="6">
-        <v>0.41666666666666669</v>
+        <v>0.43055555555555558</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L8" s="7" t="s">
         <v>26</v>
@@ -1467,51 +1565,51 @@
         <v>82</v>
       </c>
       <c r="O8" s="7" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="P8" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q8" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="Q8" s="7" t="s">
+      <c r="R8" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="4">
+        <v>106186</v>
+      </c>
+      <c r="B9" s="5">
+        <v>46294</v>
+      </c>
+      <c r="C9" s="6">
+        <v>0.43055555555555558</v>
+      </c>
+      <c r="D9" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="R8" s="8" t="s">
+      <c r="E9" s="7" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="4">
-        <v>105260</v>
-      </c>
-      <c r="B9" s="5">
-        <v>46293</v>
-      </c>
-      <c r="C9" s="6">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D9" s="7" t="s">
+      <c r="F9" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="G9" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="H9" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="I9" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="H9" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>91</v>
-      </c>
       <c r="J9" s="7" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>92</v>
+        <v>50</v>
       </c>
       <c r="L9" s="7" t="s">
         <v>26</v>
@@ -1520,33 +1618,33 @@
         <v>27</v>
       </c>
       <c r="N9" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="O9" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="P9" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q9" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="R9" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="O9" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="P9" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q9" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="R9" s="8" t="s">
+    </row>
+    <row r="10" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="4">
+        <v>104754</v>
+      </c>
+      <c r="B10" s="5">
+        <v>46294</v>
+      </c>
+      <c r="C10" s="6">
+        <v>0.4513888888888889</v>
+      </c>
+      <c r="D10" s="7" t="s">
         <v>94</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="4">
-        <v>105848</v>
-      </c>
-      <c r="B10" s="5">
-        <v>46293</v>
-      </c>
-      <c r="C10" s="6">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>32</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>95</v>
@@ -1561,13 +1659,13 @@
         <v>98</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L10" s="7" t="s">
         <v>26</v>
@@ -1579,51 +1677,51 @@
         <v>99</v>
       </c>
       <c r="O10" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="P10" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q10" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="R10" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="P10" s="7" t="s">
+    </row>
+    <row r="11" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="4">
+        <v>103519</v>
+      </c>
+      <c r="B11" s="5">
+        <v>46294</v>
+      </c>
+      <c r="C11" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="Q10" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="R10" s="8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="4">
-        <v>99928</v>
-      </c>
-      <c r="B11" s="5">
-        <v>46293</v>
-      </c>
-      <c r="C11" s="6">
-        <v>0.42708333333333331</v>
-      </c>
-      <c r="D11" s="7" t="s">
+      <c r="F11" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="G11" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="H11" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="I11" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="J11" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="H11" s="7" t="s">
+      <c r="K11" s="7" t="s">
         <v>106</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="J11" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="K11" s="7" t="s">
-        <v>49</v>
       </c>
       <c r="L11" s="7" t="s">
         <v>26</v>
@@ -1632,33 +1730,33 @@
         <v>27</v>
       </c>
       <c r="N11" s="7" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="O11" s="7" t="s">
         <v>41</v>
       </c>
       <c r="P11" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q11" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="R11" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="Q11" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="R11" s="8" t="s">
+    </row>
+    <row r="12" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="4">
+        <v>105149</v>
+      </c>
+      <c r="B12" s="5">
+        <v>46294</v>
+      </c>
+      <c r="C12" s="6">
+        <v>0.4597222222222222</v>
+      </c>
+      <c r="D12" s="7" t="s">
         <v>111</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="4">
-        <v>104809</v>
-      </c>
-      <c r="B12" s="5">
-        <v>46293</v>
-      </c>
-      <c r="C12" s="6">
-        <v>0.4861111111111111</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>63</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>112</v>
@@ -1670,16 +1768,16 @@
         <v>114</v>
       </c>
       <c r="H12" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J12" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="I12" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="J12" s="7" t="s">
-        <v>48</v>
-      </c>
       <c r="K12" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L12" s="7" t="s">
         <v>26</v>
@@ -1691,51 +1789,51 @@
         <v>116</v>
       </c>
       <c r="O12" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="P12" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q12" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="R12" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="P12" s="7" t="s">
+    </row>
+    <row r="13" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="4">
+        <v>101032</v>
+      </c>
+      <c r="B13" s="5">
+        <v>46294</v>
+      </c>
+      <c r="C13" s="6">
+        <v>0.46875</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="E13" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="Q12" s="7" t="s">
+      <c r="F13" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="R12" s="8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="4">
-        <v>100924</v>
-      </c>
-      <c r="B13" s="5">
-        <v>46293</v>
-      </c>
-      <c r="C13" s="6">
-        <v>0.56944444444444442</v>
-      </c>
-      <c r="D13" s="7" t="s">
+      <c r="G13" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="H13" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="I13" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J13" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="G13" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="J13" s="7" t="s">
-        <v>81</v>
-      </c>
       <c r="K13" s="7" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="L13" s="7" t="s">
         <v>26</v>
@@ -1744,54 +1842,54 @@
         <v>27</v>
       </c>
       <c r="N13" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="O13" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="P13" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q13" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="R13" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="4">
+        <v>105871</v>
+      </c>
+      <c r="B14" s="5">
+        <v>46294</v>
+      </c>
+      <c r="C14" s="6">
+        <v>0.47222222222222221</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E14" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="O13" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="P13" s="7" t="s">
+      <c r="F14" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="G14" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="Q13" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="R13" s="8" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="4">
-        <v>105019</v>
-      </c>
-      <c r="B14" s="5">
-        <v>46293</v>
-      </c>
-      <c r="C14" s="6">
-        <v>0.57291666666666663</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>130</v>
-      </c>
       <c r="H14" s="7" t="s">
-        <v>131</v>
+        <v>48</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L14" s="7" t="s">
         <v>26</v>
@@ -1800,54 +1898,54 @@
         <v>27</v>
       </c>
       <c r="N14" s="7" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="O14" s="7" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="P14" s="7" t="s">
-        <v>134</v>
+        <v>70</v>
       </c>
       <c r="Q14" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="R14" s="8" t="s">
-        <v>135</v>
+        <v>128</v>
+      </c>
+      <c r="R14" s="7" t="s">
+        <v>55</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4">
-        <v>105568</v>
+        <v>104434</v>
       </c>
       <c r="B15" s="5">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="C15" s="6">
-        <v>0.57638888888888884</v>
+        <v>0.49305555555555558</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>136</v>
+        <v>111</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>88</v>
+        <v>46</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>140</v>
+        <v>23</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>48</v>
+        <v>132</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="L15" s="7" t="s">
         <v>26</v>
@@ -1856,54 +1954,54 @@
         <v>27</v>
       </c>
       <c r="N15" s="7" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="O15" s="7" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="P15" s="7" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="Q15" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="R15" s="8" t="s">
-        <v>142</v>
+        <v>53</v>
+      </c>
+      <c r="R15" s="7" t="s">
+        <v>134</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="4">
-        <v>105432</v>
+        <v>61949</v>
       </c>
       <c r="B16" s="5">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="C16" s="6">
-        <v>0.59375</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>129</v>
+        <v>46</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>146</v>
+        <v>48</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>24</v>
+        <v>138</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>49</v>
+        <v>106</v>
       </c>
       <c r="L16" s="7" t="s">
         <v>26</v>
@@ -1912,54 +2010,54 @@
         <v>27</v>
       </c>
       <c r="N16" s="7" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="O16" s="7" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="P16" s="7" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="Q16" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="R16" s="8" t="s">
-        <v>148</v>
+        <v>140</v>
+      </c>
+      <c r="R16" s="7" t="s">
+        <v>55</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="4">
-        <v>105998</v>
+        <v>102781</v>
       </c>
       <c r="B17" s="5">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="C17" s="6">
-        <v>0.60069444444444442</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>151</v>
+        <v>46</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>153</v>
+        <v>48</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>24</v>
+        <v>138</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>49</v>
+        <v>106</v>
       </c>
       <c r="L17" s="7" t="s">
         <v>26</v>
@@ -1968,54 +2066,54 @@
         <v>27</v>
       </c>
       <c r="N17" s="7" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="O17" s="7" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="P17" s="7" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="Q17" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="R17" s="8" t="s">
-        <v>155</v>
+        <v>83</v>
+      </c>
+      <c r="R17" s="7" t="s">
+        <v>55</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="4">
-        <v>105893</v>
+        <v>104177</v>
       </c>
       <c r="B18" s="5">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="C18" s="6">
-        <v>0.60416666666666663</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>63</v>
+        <v>135</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>159</v>
+        <v>121</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>160</v>
+        <v>23</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>24</v>
+        <v>138</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>39</v>
+        <v>106</v>
       </c>
       <c r="L18" s="7" t="s">
         <v>26</v>
@@ -2024,38 +2122,485 @@
         <v>27</v>
       </c>
       <c r="N18" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="O18" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="P18" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q18" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="R18" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="4">
+        <v>106095</v>
+      </c>
+      <c r="B19" s="5">
+        <v>46294</v>
+      </c>
+      <c r="C19" s="6">
+        <v>0.55902777777777779</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="L19" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="M19" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N19" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="O19" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="P19" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q19" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="R19" s="7" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="4">
+        <v>105443</v>
+      </c>
+      <c r="B20" s="5">
+        <v>46294</v>
+      </c>
+      <c r="C20" s="6">
+        <v>0.5625</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="H20" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="O18" s="7" t="s">
+      <c r="I20" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J20" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="L20" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M20" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N20" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="O20" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="P18" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="Q18" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="R18" s="8" t="s">
+      <c r="P20" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q20" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="R20" s="7" t="s">
         <v>163</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="4">
+        <v>106179</v>
+      </c>
+      <c r="B21" s="5">
+        <v>46294</v>
+      </c>
+      <c r="C21" s="6">
+        <v>0.5625</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="K21" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="L21" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M21" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N21" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="O21" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="P21" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="Q21" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="R21" s="7" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="4">
+        <v>104492</v>
+      </c>
+      <c r="B22" s="5">
+        <v>46294</v>
+      </c>
+      <c r="C22" s="6">
+        <v>0.5625</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="I22" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="J22" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="K22" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="L22" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M22" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N22" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="O22" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="P22" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q22" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="R22" s="7" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="4">
+        <v>104912</v>
+      </c>
+      <c r="B23" s="5">
+        <v>46294</v>
+      </c>
+      <c r="C23" s="6">
+        <v>0.56944444444444442</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="I23" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J23" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="K23" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="L23" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M23" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N23" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="O23" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="P23" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q23" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="R23" s="7" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="4">
+        <v>105393</v>
+      </c>
+      <c r="B24" s="5">
+        <v>46294</v>
+      </c>
+      <c r="C24" s="6">
+        <v>0.625</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="I24" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J24" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="L24" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M24" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N24" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="O24" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="P24" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="Q24" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="R24" s="7" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="4">
+        <v>105823</v>
+      </c>
+      <c r="B25" s="5">
+        <v>46294</v>
+      </c>
+      <c r="C25" s="6">
+        <v>0.63541666666666663</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="I25" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J25" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="K25" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="L25" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M25" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N25" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="O25" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="P25" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q25" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="R25" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="4">
+        <v>104638</v>
+      </c>
+      <c r="B26" s="5">
+        <v>46294</v>
+      </c>
+      <c r="C26" s="6">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="I26" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J26" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="K26" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="L26" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M26" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N26" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="O26" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="P26" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q26" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="R26" s="7" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="R2" r:id="rId1" xr:uid="{95C41F58-3842-4941-84C0-4E41CF3BF528}"/>
-    <hyperlink ref="R4" r:id="rId2" display="https://trt15-jus-br.zoom.us/j/81715388288?pwd=UFAwUGVFQkN1bGNXcStQUEovR2VZUT09%20ID%20da%20Reunião%20817%201538%208288%20Senha%20198674" xr:uid="{66F6AC30-2DD9-4D73-A693-58FD44C7E513}"/>
-    <hyperlink ref="R5" r:id="rId3" xr:uid="{F28160D0-1A3B-4008-93FB-5D6BA38DCEA6}"/>
-    <hyperlink ref="R6" r:id="rId4" display="mailto:lucianecozza@gmail.com" xr:uid="{B07A87C9-1834-49BD-9549-EF7989F4D3F2}"/>
-    <hyperlink ref="R7" r:id="rId5" display="mailto:lucianecozza@gmail.com" xr:uid="{F5744966-D984-4380-86DB-E4714149FD62}"/>
-    <hyperlink ref="R8" r:id="rId6" display="https://trt15-jus-br.zoom.us/j/87095656771?pwd=aU9LaTBPcFd4aFAydkZSRVlpcWlRQT09%20ID%20da%20reunião:%2087095656771%20Senha%20de%20acesso:%20493462" xr:uid="{935FB631-F272-4CC4-B92D-6F73074C488A}"/>
-    <hyperlink ref="R9" r:id="rId7" xr:uid="{8D9DD257-B0B0-43F8-83EE-C8694A826464}"/>
-    <hyperlink ref="R11" r:id="rId8" xr:uid="{C865ADBB-9361-4C89-A64E-9BF22550947D}"/>
-    <hyperlink ref="R13" r:id="rId9" display="https://trt15-jus-br.zoom.us/j/9973700634?pwd=dENDekhCNjFLekRnSExiTzhmK1VLdz09%20ID%20da%20reunião:%20997%20370%200634%20Senha:%20592209" xr:uid="{6CF8C3D3-A3B6-4309-9DBC-94DB4B1068ED}"/>
-    <hyperlink ref="R14" r:id="rId10" xr:uid="{5FB6E6AA-19E1-4D53-A5B8-AE44970377D1}"/>
-    <hyperlink ref="R15" r:id="rId11" xr:uid="{16B8370C-655D-4F27-BD1C-3DEBDF8824DA}"/>
-    <hyperlink ref="R16" r:id="rId12" xr:uid="{A3AD2B59-8F70-46C7-9DD3-618BD825C254}"/>
-    <hyperlink ref="R17" r:id="rId13" xr:uid="{AA190877-4F5D-481B-A13A-290FDB73C5F0}"/>
-    <hyperlink ref="R18" r:id="rId14" display="mailto:claudiarafaelav@hotmail.com" xr:uid="{CF44BEFF-5A69-42C2-A487-F1067A570948}"/>
+    <hyperlink ref="R3" r:id="rId1" xr:uid="{B6FD9883-1638-4FC9-B723-3594B8559744}"/>
+    <hyperlink ref="R9" r:id="rId2" xr:uid="{23895C54-61FA-4A69-82F8-FAB04627F069}"/>
+    <hyperlink ref="R10" r:id="rId3" display="https://trt15-jus-br.zoom.us/j/85290954703?pwd=ZldYYzczVnhUbm1VN3BPVzAvRmY5QT%20ID%20da%20reunião:%20852%209095%204703%20senha%20de%20acesso:%20517309" xr:uid="{51D50BED-507E-4575-B21A-746F1EC8535D}"/>
+    <hyperlink ref="R11" r:id="rId4" xr:uid="{667B816E-49F2-4066-BD71-B59BAA6D6CF4}"/>
+    <hyperlink ref="R12" r:id="rId5" display="https://trt15-jus-br.zoom.us/j/84713424685?pwd=eEZTakhrSWFNN2RKYVFDcWU1K3ZmZz09%20ID%20da%20reunião:%20847%201342%204685%20Senha%20de%20acesso:%20525290" xr:uid="{F9713C29-CE3F-4193-9053-63E38AA42EEF}"/>
+    <hyperlink ref="R15" r:id="rId6" xr:uid="{29C6F7DD-CAE3-4EBC-849C-0BC1A2467564}"/>
+    <hyperlink ref="R19" r:id="rId7" xr:uid="{4C919C29-E0AD-4D2F-AB83-14564932DB4B}"/>
+    <hyperlink ref="R20" r:id="rId8" xr:uid="{1F6AA1D4-EDC6-4BC5-A7E9-BE2970F8EC8D}"/>
+    <hyperlink ref="R21" r:id="rId9" xr:uid="{35ADB188-5B0D-40BB-A0AF-B403B9AF94CB}"/>
+    <hyperlink ref="R22" r:id="rId10" xr:uid="{58367F68-1282-4F08-A74F-C7687071E77E}"/>
+    <hyperlink ref="R23" r:id="rId11" xr:uid="{43E32FDD-7488-4460-B14F-D75EB29B2326}"/>
+    <hyperlink ref="R24" r:id="rId12" xr:uid="{8012A771-6009-4F8B-813B-C90EFD00B3A1}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId13"/>
 </worksheet>
 </file>
--- a/Pauta_de_Audiencias.xlsx
+++ b/Pauta_de_Audiencias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\blu\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8A4A1CA0-8BE0-4755-AA35-59DABE595CF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B983A487-7B73-4AA1-8492-92DD0928A756}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E26630DF-7025-4C67-9939-633F9CC7DFF4}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F708F57B-CDFA-44D6-BDAB-F111C37C5FFA}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="222">
   <si>
     <t>Código P&amp;C</t>
   </si>
@@ -95,379 +95,616 @@
     <t>Link/Observações</t>
   </si>
   <si>
+    <t>Audiência Inicial - Presencial</t>
+  </si>
+  <si>
+    <t>0000477-55.2026.5.23.0031</t>
+  </si>
+  <si>
+    <t>Dipagro Ltda</t>
+  </si>
+  <si>
+    <t>Kleber Garcia Barbara</t>
+  </si>
+  <si>
+    <t>CÁCERES</t>
+  </si>
+  <si>
+    <t>MT</t>
+  </si>
+  <si>
+    <t>VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>Instrução</t>
+  </si>
+  <si>
+    <t>Reclamação Trabalhista</t>
+  </si>
+  <si>
+    <t>CENTRAL</t>
+  </si>
+  <si>
+    <t>R$             212.847,22</t>
+  </si>
+  <si>
+    <t>Grupo E1</t>
+  </si>
+  <si>
+    <t>Correspondente</t>
+  </si>
+  <si>
+    <t>VRO</t>
+  </si>
+  <si>
+    <t>Presencial</t>
+  </si>
+  <si>
+    <t>Audiência Inicial -  Telepresencial</t>
+  </si>
+  <si>
+    <t>0001131-63.2026.5.23.0121</t>
+  </si>
+  <si>
+    <t>Inpasa Agroindustrial S/A.</t>
+  </si>
+  <si>
+    <t>Vanildes Souza De Santana</t>
+  </si>
+  <si>
+    <t>NOVA MUTUM</t>
+  </si>
+  <si>
+    <t>R$          3.691.382,47</t>
+  </si>
+  <si>
+    <t>Grupo E2</t>
+  </si>
+  <si>
+    <t>BTF</t>
+  </si>
+  <si>
+    <t>RCF</t>
+  </si>
+  <si>
+    <t>https://trt23-jus-br.zoom.us/my/vtnovamutum ID da reunião: 525 746 4936 Senha de acesso: @Nm121</t>
+  </si>
+  <si>
+    <t>Audiência Inicial - Telepresencial</t>
+  </si>
+  <si>
+    <t>0001133-71.2026.5.23.0076</t>
+  </si>
+  <si>
+    <t>Agropecuaria Infiniti Ltda.</t>
+  </si>
+  <si>
+    <t>Welison Vasconcelos Candido</t>
+  </si>
+  <si>
+    <t>PRIMAVERA DO LESTE</t>
+  </si>
+  <si>
+    <t>CEJUSC</t>
+  </si>
+  <si>
+    <t>R$             200.038,28</t>
+  </si>
+  <si>
+    <t>RRU</t>
+  </si>
+  <si>
+    <t>https://trt23-jus-br.zoom.us/my/salanobres?pwd=NmdUWFBwaGtBZHpucTdWSFQyR2oxUT09 ID: 269 890 9821 Senha geral: Nobres1@</t>
+  </si>
+  <si>
+    <t>Audiência de Instrução - Telepresencial</t>
+  </si>
+  <si>
+    <t>0012362-43.2025.5.15.0122</t>
+  </si>
+  <si>
+    <t>Pilkington Brasil Ltda.</t>
+  </si>
+  <si>
+    <t>Raphael Decanio Amancio</t>
+  </si>
+  <si>
+    <t>SUMARÉ</t>
+  </si>
+  <si>
+    <t>SP</t>
+  </si>
+  <si>
+    <t>R$               40.946,58</t>
+  </si>
+  <si>
+    <t>MBF</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/84993384241?pwd=5k1SoEXEWUkAMtV6ck51bpX3LIg8Yz.1</t>
+  </si>
+  <si>
+    <t>Audiência Instrução - Presencial</t>
+  </si>
+  <si>
+    <t>1001555-22.2025.5.02.0020</t>
+  </si>
+  <si>
+    <t>Telefonica Brasil S.A.</t>
+  </si>
+  <si>
+    <t>Giovanni Alessandro Ribeiro Ramos</t>
+  </si>
+  <si>
+    <t>SÃO PAULO</t>
+  </si>
+  <si>
+    <t>20ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>Inicial</t>
+  </si>
+  <si>
+    <t>R$             878.026,00</t>
+  </si>
+  <si>
+    <t>Grupo C</t>
+  </si>
+  <si>
+    <t>TFR</t>
+  </si>
+  <si>
+    <t>Audiência Una - Presencial</t>
+  </si>
+  <si>
+    <t>1001173-20.2026.5.02.0432</t>
+  </si>
+  <si>
+    <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
+  </si>
+  <si>
+    <t>Jose Roberto Lopes Da Silva</t>
+  </si>
+  <si>
+    <t>SANTO ANDRÉ</t>
+  </si>
+  <si>
+    <t>02ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             152.575,89</t>
+  </si>
+  <si>
+    <t>Grupo B1</t>
+  </si>
+  <si>
+    <t>GSM</t>
+  </si>
+  <si>
+    <t>RFE</t>
+  </si>
+  <si>
+    <t>0001513-14.2026.5.18.0083</t>
+  </si>
+  <si>
+    <t>Syngenta Proteção De Cultivos Ltda.</t>
+  </si>
+  <si>
+    <t>Jose Madalena Justiniano</t>
+  </si>
+  <si>
+    <t>RIO VERDE</t>
+  </si>
+  <si>
+    <t>GO</t>
+  </si>
+  <si>
+    <t>1ª Instância</t>
+  </si>
+  <si>
+    <t>R$             100.441,80</t>
+  </si>
+  <si>
+    <t>JPL</t>
+  </si>
+  <si>
+    <t>JRM</t>
+  </si>
+  <si>
+    <t>https://trt18-jus-br.zoom.us/my/cejuscrioverde</t>
+  </si>
+  <si>
+    <t>1000694-21.2026.5.02.0434</t>
+  </si>
+  <si>
+    <t>Rubens Bernardes Da Silva</t>
+  </si>
+  <si>
+    <t>04ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             278.000,00</t>
+  </si>
+  <si>
+    <t>Correspondente - Hebert</t>
+  </si>
+  <si>
+    <t>TAM</t>
+  </si>
+  <si>
+    <t>Audiência Una - Telepresencial</t>
+  </si>
+  <si>
+    <t>0100938-16.2026.5.01.0203</t>
+  </si>
+  <si>
+    <t>Bruno Do Nascimento Monteiro</t>
+  </si>
+  <si>
+    <t>DUQUE DE CAXIAS</t>
+  </si>
+  <si>
+    <t>RJ</t>
+  </si>
+  <si>
+    <t>03ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             612.615,41</t>
+  </si>
+  <si>
+    <t>BSO</t>
+  </si>
+  <si>
+    <t>https://trt1-jus-br.zoom.us/my/vtdc03?pwd=all4TmdCN01CRGliVlp5dkh6aTBBdz09</t>
+  </si>
+  <si>
+    <t>0012105-48.2026.5.15.0133</t>
+  </si>
+  <si>
+    <t>Moema Bioenergia S.A.</t>
+  </si>
+  <si>
+    <t>Manoel Correia Dias</t>
+  </si>
+  <si>
+    <t>SÃO JOSÉ DO RIO PRETO</t>
+  </si>
+  <si>
+    <t>R$             568.813,56</t>
+  </si>
+  <si>
+    <t>RYL</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/82214057803?pwd=Yk9reERlOGxwRk1wVjE2cHYzN29sQT09</t>
+  </si>
+  <si>
+    <t>0010052-17.2026.5.15.0094</t>
+  </si>
+  <si>
+    <t>Embraer S.A.</t>
+  </si>
+  <si>
+    <t>Priscila Pereira De Medeiros</t>
+  </si>
+  <si>
+    <t>CAMPINAS</t>
+  </si>
+  <si>
+    <t>07ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>Ação de Consignação em Pagamento</t>
+  </si>
+  <si>
+    <t>R$               17.118,32</t>
+  </si>
+  <si>
+    <t>Grupo B2</t>
+  </si>
+  <si>
+    <t>VCR</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/4525285196?pwd=cG1ieCtlVVdHZERxcVRTM2lzSGt3dz09 ID da reunião: 452 528 5196 Senha de acesso: 702632</t>
+  </si>
+  <si>
+    <t>1001372-08.2026.5.02.0411</t>
+  </si>
+  <si>
+    <t>Companhia Brasileira De Cartuchos</t>
+  </si>
+  <si>
+    <t>Weslley Igor Antonio Lopes Dos Santos</t>
+  </si>
+  <si>
+    <t>RIBEIRÃO PIRES</t>
+  </si>
+  <si>
+    <t>R$               45.484,31</t>
+  </si>
+  <si>
+    <t>Grupo B3</t>
+  </si>
+  <si>
+    <t>LMI</t>
+  </si>
+  <si>
+    <t>1000515-59.2026.5.02.0411</t>
+  </si>
+  <si>
+    <t>Cbc - Companhia Brasileira De Cartuchos</t>
+  </si>
+  <si>
+    <t>Vinicius De Souza Franca</t>
+  </si>
+  <si>
+    <t>R$             282.024,58</t>
+  </si>
+  <si>
+    <t>Audiência de Instrução - Semipresencial</t>
+  </si>
+  <si>
+    <t>1001486-48.2025.5.02.0421</t>
+  </si>
+  <si>
+    <t>3Corp Technology Infraestrutura De Telecom Ltda.</t>
+  </si>
+  <si>
+    <t>Gabriel Tavares Parreira De Paula</t>
+  </si>
+  <si>
+    <t>SANTANA DE PARNAÍBA</t>
+  </si>
+  <si>
+    <t>01ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             157.171,00</t>
+  </si>
+  <si>
+    <t>Grupo A2</t>
+  </si>
+  <si>
+    <t>NBG</t>
+  </si>
+  <si>
+    <t>0010223-72.2026.5.15.0126</t>
+  </si>
+  <si>
+    <t>Sofia Da Silva Assis</t>
+  </si>
+  <si>
+    <t>PAULÍNIA</t>
+  </si>
+  <si>
+    <t>R$             176.547,57</t>
+  </si>
+  <si>
+    <t>TLI</t>
+  </si>
+  <si>
+    <t>GVM</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/86534999498?pwd=N3RZZXpkTE5laWxEREEvWjBVYVg0Zz09 ID da reunião: 865 3499 9498 Senha: 13579</t>
+  </si>
+  <si>
+    <t>Audiência Inicial -  Presencial</t>
+  </si>
+  <si>
+    <t>0010976-96.2026.5.03.0147</t>
+  </si>
+  <si>
+    <t>Fertilizantes Heringer S.A</t>
+  </si>
+  <si>
+    <t>Marcio Rezende Fonseca</t>
+  </si>
+  <si>
+    <t>TRÊS CORAÇÕES</t>
+  </si>
+  <si>
+    <t>MG</t>
+  </si>
+  <si>
+    <t>Conhecimento</t>
+  </si>
+  <si>
+    <t>R$          1.435.000,00</t>
+  </si>
+  <si>
+    <t>Correspondente - doc9</t>
+  </si>
+  <si>
+    <t>ARC</t>
+  </si>
+  <si>
+    <t>Presencial | Advogado - Matheus Pimenta Barros matheuspb26@live.com 35999092279</t>
+  </si>
+  <si>
+    <t>Perícia Técnica</t>
+  </si>
+  <si>
+    <t>0012829-61.2025.5.15.0109</t>
+  </si>
+  <si>
+    <t>Umberto Aparecido Lima</t>
+  </si>
+  <si>
+    <t>SOROCABA</t>
+  </si>
+  <si>
+    <t>R$             856.425,61</t>
+  </si>
+  <si>
+    <t>ANB</t>
+  </si>
+  <si>
+    <t>Iremos acompanhar</t>
+  </si>
+  <si>
+    <t>Audiência de Conciliação - Telepresencial</t>
+  </si>
+  <si>
+    <t>1000179-05.2020.5.02.0431</t>
+  </si>
+  <si>
+    <t>Jose Ricardo Silva</t>
+  </si>
+  <si>
+    <t>CEJUSC ABC</t>
+  </si>
+  <si>
+    <t>Recursal</t>
+  </si>
+  <si>
+    <t>R$             151.781,01</t>
+  </si>
+  <si>
+    <t>JPE</t>
+  </si>
+  <si>
+    <t>https://trt2-jus-br.zoom.us/j/81026971770?pwd=WlJ4VkMvUUhBa1QxWUN1eldWeFNKQT09 ID da reunião: 810 2697 1770 Senha de acesso: 820150</t>
+  </si>
+  <si>
+    <t>1001462-42.2026.5.02.0467</t>
+  </si>
+  <si>
+    <t>Mahle Metal Leve S.A.</t>
+  </si>
+  <si>
+    <t>Fernando Lopes Bento</t>
+  </si>
+  <si>
+    <t>SÃO BERNARDO DO CAMPO</t>
+  </si>
+  <si>
+    <t>R$               45.442,32</t>
+  </si>
+  <si>
+    <t>Correspondente - Carlos Florian</t>
+  </si>
+  <si>
+    <t>Presencial | Advogada - Dra. Luciana França, (11) 96351-8524</t>
+  </si>
+  <si>
     <t>Audiência Instrução - Telepresencial</t>
   </si>
   <si>
-    <t>1001687-31.2025.5.02.0521</t>
-  </si>
-  <si>
-    <t>Mahle Thermal And Fluid Systems Brazil Ltda.</t>
-  </si>
-  <si>
-    <t>Rafael De Oliveira Andrade</t>
-  </si>
-  <si>
-    <t>ARUJÁ</t>
-  </si>
-  <si>
-    <t>SP</t>
-  </si>
-  <si>
-    <t>VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>Instrução</t>
-  </si>
-  <si>
-    <t>Reclamação Trabalhista</t>
-  </si>
-  <si>
-    <t>CENTRAL</t>
-  </si>
-  <si>
-    <t>R$             440.000,00</t>
-  </si>
-  <si>
-    <t>Grupo E1</t>
-  </si>
-  <si>
-    <t>PSI</t>
-  </si>
-  <si>
-    <t>TLI</t>
-  </si>
-  <si>
-    <t>https://trt2-jus-br.zoom.us/j/86789289821?pwd=hmNmYn6ZPr5UBUkTREU7WbLud20xkY.1 ID da reunião: 867 8928 9821 Senha de acesso: vtaruja01</t>
-  </si>
-  <si>
-    <t>1001571-25.2025.5.02.0521</t>
-  </si>
-  <si>
-    <t>R$               87.965,00</t>
-  </si>
-  <si>
-    <t>https://trt2-jus-br.zoom.us/j/86826984343?pwd=vqkjCTDTofwYe3zhKsVzowS3Wcmu4J.1 ID da reunião: 868 2698 4343 Senha de acesso: vtaruja01</t>
-  </si>
-  <si>
-    <t>Audiência Una - Presencial</t>
-  </si>
-  <si>
-    <t>1001457-38.2025.5.02.0052</t>
-  </si>
-  <si>
-    <t>Mccann Erickson Publicidade Ltda.</t>
-  </si>
-  <si>
-    <t>Ministério Público Do Trabalho</t>
-  </si>
-  <si>
-    <t>SÃO PAULO</t>
-  </si>
-  <si>
-    <t>52ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>Ação Civil Pública</t>
-  </si>
-  <si>
-    <t>R$          3.655.206,00</t>
-  </si>
-  <si>
-    <t>Grupo C</t>
-  </si>
-  <si>
-    <t>NBG</t>
+    <t>0010335-20.2026.5.15.0133</t>
+  </si>
+  <si>
+    <t>Moema Bioenergia S.A. - Moema</t>
+  </si>
+  <si>
+    <t>Renato Jose Dias</t>
+  </si>
+  <si>
+    <t>R$             418.460,00</t>
+  </si>
+  <si>
+    <t>CAL</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/7871570572?pwd=KzBzUnVURkZwc0gxd21YU3pUWWhJQT09 ID da reunião: 787 157 0572 Senha de acesso: 674353</t>
+  </si>
+  <si>
+    <t>0010667-75.2026.5.03.0147</t>
+  </si>
+  <si>
+    <t>Julio Henrique Dionisio</t>
+  </si>
+  <si>
+    <t>R$             712.000,00</t>
+  </si>
+  <si>
+    <t>BBO</t>
+  </si>
+  <si>
+    <t>0010664-23.2026.5.03.0147</t>
+  </si>
+  <si>
+    <t>Breno Heleno Da Silva Mariano</t>
+  </si>
+  <si>
+    <t>R$             521.000,00</t>
+  </si>
+  <si>
+    <t>0010380-36.2026.5.03.0140</t>
+  </si>
+  <si>
+    <t>Sistenge Construções E Comércio Ltda.</t>
+  </si>
+  <si>
+    <t>Alex Alves Da Silva Batista</t>
+  </si>
+  <si>
+    <t>CONTAGEM</t>
+  </si>
+  <si>
+    <t>R$             114.705,18</t>
+  </si>
+  <si>
+    <t>https://trt3-jus-br.zoom.us/my/vt1.contagem</t>
+  </si>
+  <si>
+    <t>0012594-95.2025.5.15.0044</t>
+  </si>
+  <si>
+    <t>Alex Cruz De Souza</t>
+  </si>
+  <si>
+    <t>R$             292.000,00</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/83908187251?pwd=Ty9tcHNFb0pLZk5WQ0l2Y0V3ZHhhdz09</t>
+  </si>
+  <si>
+    <t>1001057-08.2026.5.02.0434</t>
+  </si>
+  <si>
+    <t>Elizeu Luiz Freire</t>
+  </si>
+  <si>
+    <t>R$             158.737,00</t>
+  </si>
+  <si>
+    <t>0024006-50.2026.5.24.0072</t>
+  </si>
+  <si>
+    <t>Rio Paraná Energia S.A.</t>
+  </si>
+  <si>
+    <t>Edson Barbosa</t>
+  </si>
+  <si>
+    <t>TRÊS LAGOAS</t>
+  </si>
+  <si>
+    <t>MS</t>
+  </si>
+  <si>
+    <t>R$             192.773,33</t>
   </si>
   <si>
     <t>ECO</t>
   </si>
   <si>
-    <t>Presencial</t>
-  </si>
-  <si>
-    <t>Audiência Instrução - Presencial</t>
-  </si>
-  <si>
-    <t>1000890-85.2026.5.02.0435</t>
-  </si>
-  <si>
-    <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
-  </si>
-  <si>
-    <t>Joel Marcos Jose De Souza</t>
-  </si>
-  <si>
-    <t>SANTO ANDRÉ</t>
-  </si>
-  <si>
-    <t>05ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$             832.800,15</t>
-  </si>
-  <si>
-    <t>Grupo B1</t>
-  </si>
-  <si>
-    <t>GSM</t>
-  </si>
-  <si>
-    <t>Audiência Inicial -  Presencial</t>
-  </si>
-  <si>
-    <t>1001113-13.2026.5.02.0411</t>
-  </si>
-  <si>
-    <t>Companhia Brasileira De Cartuchos</t>
-  </si>
-  <si>
-    <t>Gustavo Souza Da Silva</t>
-  </si>
-  <si>
-    <t>RIBEIRÃO PIRES</t>
-  </si>
-  <si>
-    <t>R$             191.930,23</t>
-  </si>
-  <si>
-    <t>Grupo B3</t>
-  </si>
-  <si>
-    <t>LMI</t>
-  </si>
-  <si>
-    <t>0010906-32.2026.5.15.0087</t>
-  </si>
-  <si>
-    <t>Fertilizantes Heringer S.A</t>
-  </si>
-  <si>
-    <t>Antonio Carlos Da Costa Oliveira</t>
-  </si>
-  <si>
-    <t>PAULÍNIA</t>
-  </si>
-  <si>
-    <t>01ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>Conhecimento</t>
-  </si>
-  <si>
-    <t>R$             427.015,86</t>
-  </si>
-  <si>
-    <t>Grupo E2</t>
-  </si>
-  <si>
-    <t>AAP</t>
-  </si>
-  <si>
-    <t>ARC</t>
-  </si>
-  <si>
-    <t>Audiência Inicial -  Telepresencial</t>
-  </si>
-  <si>
-    <t>0016784-42.2026.5.16.0011</t>
-  </si>
-  <si>
-    <t>Syngenta Proteção De Cultivos Ltda.</t>
-  </si>
-  <si>
-    <t>Jorge De Oliveira Santos</t>
-  </si>
-  <si>
-    <t>BALSAS</t>
-  </si>
-  <si>
-    <t>MA</t>
-  </si>
-  <si>
-    <t>1ª Instância</t>
-  </si>
-  <si>
-    <t>R$               85.170,87</t>
-  </si>
-  <si>
-    <t>JRM</t>
-  </si>
-  <si>
-    <t>GVM</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/84680881845?pwd=2uHgFIbgHPhxy5JJEP3uHrbe96HPcI.1 ID da reunião: 846 8088 1845 Senha: 960717</t>
-  </si>
-  <si>
-    <t>0011220-26.2022.5.15.0084</t>
-  </si>
-  <si>
-    <t>Eleb Equipamentos Ltda.</t>
-  </si>
-  <si>
-    <t>Carlos Eduardo Da Silva</t>
-  </si>
-  <si>
-    <t>SÃO JOSÉ DOS CAMPOS</t>
-  </si>
-  <si>
-    <t>04ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>Inicial</t>
-  </si>
-  <si>
-    <t>R$             296.615,60</t>
-  </si>
-  <si>
-    <t>Grupo B2</t>
-  </si>
-  <si>
-    <t>VCR</t>
-  </si>
-  <si>
-    <t>ANB</t>
-  </si>
-  <si>
-    <t>0010579-44.2026.5.03.0080</t>
-  </si>
-  <si>
-    <t>Salitre Fertilizantes Ltda</t>
-  </si>
-  <si>
-    <t>Danilo Alves Vieira Junior</t>
-  </si>
-  <si>
-    <t>PATROCÍNIO</t>
-  </si>
-  <si>
-    <t>MG</t>
-  </si>
-  <si>
-    <t>R$               80.346,37</t>
-  </si>
-  <si>
-    <t>MBF</t>
-  </si>
-  <si>
-    <t>CAL</t>
-  </si>
-  <si>
-    <t>https://trt3-jus-br.zoom.us/my/vt.patrocinio</t>
-  </si>
-  <si>
-    <t>1000805-11.2026.5.02.0432</t>
-  </si>
-  <si>
-    <t>Luis Guilherme Da Silva</t>
-  </si>
-  <si>
-    <t>02ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$             955.048,98</t>
-  </si>
-  <si>
-    <t>Correspondente - Hebert</t>
-  </si>
-  <si>
-    <t>Audiência de Instrução - Semipresencial</t>
-  </si>
-  <si>
-    <t>0011464-69.2025.5.15.0012</t>
-  </si>
-  <si>
-    <t>Rafael De Oliveira Silva</t>
-  </si>
-  <si>
-    <t>PIRACICABA</t>
-  </si>
-  <si>
-    <t>R$             112.641,97</t>
-  </si>
-  <si>
-    <t>RFE</t>
-  </si>
-  <si>
-    <t>JPE</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/88307820364?pwd=S2FSa2QyaUQvZVBqRThqT25PeFNXQT09 ID da reunião: 88307820364 Senha de acesso: 277454</t>
-  </si>
-  <si>
-    <t>0011050-05.2025.5.15.0131</t>
-  </si>
-  <si>
-    <t>Aderson Jose Ferreira</t>
-  </si>
-  <si>
-    <t>R$               65.358,00</t>
-  </si>
-  <si>
-    <t>0010938-37.2026.5.15.0087</t>
-  </si>
-  <si>
-    <t>Israel Leandro Firmino Da Silva</t>
-  </si>
-  <si>
-    <t>R$             241.555,32</t>
-  </si>
-  <si>
-    <t>0000310-55.2026.5.09.0022</t>
-  </si>
-  <si>
-    <t>Rhian Carlos Dos Santos Rosa</t>
-  </si>
-  <si>
-    <t>PARANAGUÁ</t>
-  </si>
-  <si>
-    <t>PR</t>
-  </si>
-  <si>
-    <t>R$               77.625,00</t>
-  </si>
-  <si>
-    <t>BBO</t>
-  </si>
-  <si>
-    <t>https://url.trt9.jus.br/tcxf3 ID da reunião: 84009977944 Senha de acesso: j4DeUgYBbf</t>
-  </si>
-  <si>
-    <t>Audiência Inicial - Presencial</t>
-  </si>
-  <si>
-    <t>0010945-29.2026.5.15.0087</t>
-  </si>
-  <si>
-    <t>Almir Rogerio Barbosa Da Silva</t>
-  </si>
-  <si>
-    <t>R$          1.139.691,67</t>
-  </si>
-  <si>
-    <t>Audiência Una- Telepresencial</t>
-  </si>
-  <si>
-    <t>1001294-49.2026.5.02.0464</t>
-  </si>
-  <si>
-    <t>Mahle Metal Leve S.A.</t>
-  </si>
-  <si>
-    <t>Deivmayk Aragao Dos Santos</t>
-  </si>
-  <si>
-    <t>SÃO BERNARDO DO CAMPO</t>
-  </si>
-  <si>
-    <t>R$               13.854,40</t>
-  </si>
-  <si>
-    <t>VRO</t>
-  </si>
-  <si>
-    <t>https://trt2-jus-br.zoom.us/j/88393016008?pwd=TqCbvr2qbyfEpGCVS8ebEjSzAZFmrj.1</t>
+    <t>0011493-69.2022.5.15.0095</t>
+  </si>
+  <si>
+    <t>Jose Roberto Francisco</t>
+  </si>
+  <si>
+    <t>Execução</t>
+  </si>
+  <si>
+    <t>R$             157.477,74</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/89925839124?pwd=HehXMRH0LyTAyjb9t6axbYz7RHoBqz.1</t>
   </si>
 </sst>
 </file>
@@ -945,8 +1182,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B498F49-C313-495C-B427-786E56BC4DA7}">
-  <dimension ref="A1:R17"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{012C189B-2E60-4599-964A-781DD785386B}">
+  <dimension ref="A1:R28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:18" ht="60" x14ac:dyDescent="0.3">
@@ -1005,12 +1242,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="245.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4">
-        <v>101949</v>
+        <v>106670</v>
       </c>
       <c r="B2" s="5">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="C2" s="6">
         <v>0.34027777777777779</v>
@@ -1057,34 +1294,34 @@
       <c r="Q2" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="R2" s="8" t="s">
+      <c r="R2" s="7" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="245.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18" ht="173.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4">
-        <v>101858</v>
+        <v>106002</v>
       </c>
       <c r="B3" s="5">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="C3" s="6">
-        <v>0.35416666666666669</v>
+        <v>0.34375</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="I3" s="7" t="s">
         <v>23</v>
@@ -1102,107 +1339,107 @@
         <v>27</v>
       </c>
       <c r="N3" s="7" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="O3" s="7" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="P3" s="7" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="Q3" s="7" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="R3" s="8" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:18" ht="245.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4">
-        <v>102088</v>
+        <v>105723</v>
       </c>
       <c r="B4" s="5">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="C4" s="6">
-        <v>0.3611111111111111</v>
+        <v>0.35069444444444442</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="I4" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="K4" s="7" t="s">
         <v>25</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="M4" s="7" t="s">
         <v>27</v>
       </c>
       <c r="N4" s="7" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="O4" s="7" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="P4" s="7" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="Q4" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="R4" s="7" t="s">
-        <v>47</v>
+        <v>40</v>
+      </c>
+      <c r="R4" s="8" t="s">
+        <v>51</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:18" ht="144.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4">
-        <v>104972</v>
+        <v>101761</v>
       </c>
       <c r="B5" s="5">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="C5" s="6">
-        <v>0.3611111111111111</v>
+        <v>0.39583333333333331</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="K5" s="7" t="s">
         <v>25</v>
@@ -1214,54 +1451,54 @@
         <v>27</v>
       </c>
       <c r="N5" s="7" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="O5" s="7" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="P5" s="7" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="Q5" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="R5" s="7" t="s">
-        <v>47</v>
+        <v>59</v>
+      </c>
+      <c r="R5" s="8" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4">
-        <v>105685</v>
+        <v>104087</v>
       </c>
       <c r="B6" s="5">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="C6" s="6">
-        <v>0.3888888888888889</v>
+        <v>0.39583333333333331</v>
       </c>
       <c r="D6" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="I6" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="E6" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>23</v>
-      </c>
       <c r="J6" s="7" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>25</v>
+        <v>67</v>
       </c>
       <c r="L6" s="7" t="s">
         <v>26</v>
@@ -1270,54 +1507,54 @@
         <v>27</v>
       </c>
       <c r="N6" s="7" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="O6" s="7" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="P6" s="7" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="Q6" s="7" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="R6" s="7" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4">
-        <v>105358</v>
+        <v>105336</v>
       </c>
       <c r="B7" s="5">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="C7" s="6">
-        <v>0.41666666666666669</v>
+        <v>0.39930555555555558</v>
       </c>
       <c r="D7" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="I7" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="E7" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>23</v>
-      </c>
       <c r="J7" s="7" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="L7" s="7" t="s">
         <v>26</v>
@@ -1326,54 +1563,54 @@
         <v>27</v>
       </c>
       <c r="N7" s="7" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="O7" s="7" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="P7" s="7" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="Q7" s="7" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="R7" s="7" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="216.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:18" ht="87" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4">
-        <v>105337</v>
+        <v>105773</v>
       </c>
       <c r="B8" s="5">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="C8" s="6">
-        <v>0.4375</v>
+        <v>0.40277777777777779</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>75</v>
+        <v>33</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="L8" s="7" t="s">
         <v>26</v>
@@ -1382,54 +1619,54 @@
         <v>27</v>
       </c>
       <c r="N8" s="7" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="O8" s="7" t="s">
         <v>29</v>
       </c>
       <c r="P8" s="7" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="Q8" s="7" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="R8" s="8" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4">
-        <v>88925</v>
+        <v>104747</v>
       </c>
       <c r="B9" s="5">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="C9" s="6">
-        <v>0.4375</v>
+        <v>0.4236111111111111</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>91</v>
+        <v>25</v>
       </c>
       <c r="L9" s="7" t="s">
         <v>26</v>
@@ -1438,54 +1675,54 @@
         <v>27</v>
       </c>
       <c r="N9" s="7" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="O9" s="7" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="P9" s="7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q9" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="R9" s="7" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="87" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:18" ht="144.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4">
-        <v>105082</v>
+        <v>105434</v>
       </c>
       <c r="B10" s="5">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="C10" s="6">
-        <v>0.45833333333333331</v>
+        <v>0.4236111111111111</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>18</v>
+        <v>97</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>24</v>
+        <v>102</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="L10" s="7" t="s">
         <v>26</v>
@@ -1494,51 +1731,51 @@
         <v>27</v>
       </c>
       <c r="N10" s="7" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="O10" s="7" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="P10" s="7" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="Q10" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="R10" s="8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:18" ht="144.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4">
-        <v>104859</v>
+        <v>106022</v>
       </c>
       <c r="B11" s="5">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="C11" s="6">
-        <v>0.46180555555555558</v>
+        <v>0.43055555555555558</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>50</v>
+        <v>107</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>52</v>
+        <v>109</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="K11" s="7" t="s">
         <v>25</v>
@@ -1550,110 +1787,110 @@
         <v>27</v>
       </c>
       <c r="N11" s="7" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="O11" s="7" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="P11" s="7" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="Q11" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="R11" s="7" t="s">
-        <v>47</v>
+        <v>111</v>
+      </c>
+      <c r="R11" s="8" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="245.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="4">
-        <v>101549</v>
+        <v>103770</v>
       </c>
       <c r="B12" s="5">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="C12" s="6">
-        <v>0.5</v>
+        <v>0.43055555555555558</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>50</v>
+        <v>114</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>69</v>
+        <v>117</v>
       </c>
       <c r="K12" s="7" t="s">
         <v>25</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>26</v>
+        <v>118</v>
       </c>
       <c r="M12" s="7" t="s">
         <v>27</v>
       </c>
       <c r="N12" s="7" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O12" s="7" t="s">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="P12" s="7" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="Q12" s="7" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R12" s="8" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4">
-        <v>105027</v>
+        <v>106134</v>
       </c>
       <c r="B13" s="5">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="C13" s="6">
-        <v>0.56944444444444442</v>
+        <v>0.4375</v>
       </c>
       <c r="D13" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="I13" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="E13" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>23</v>
-      </c>
       <c r="J13" s="7" t="s">
-        <v>69</v>
+        <v>24</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>81</v>
+        <v>25</v>
       </c>
       <c r="L13" s="7" t="s">
         <v>26</v>
@@ -1662,54 +1899,54 @@
         <v>27</v>
       </c>
       <c r="N13" s="7" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="O13" s="7" t="s">
-        <v>29</v>
+        <v>128</v>
       </c>
       <c r="P13" s="7" t="s">
-        <v>84</v>
+        <v>129</v>
       </c>
       <c r="Q13" s="7" t="s">
-        <v>84</v>
+        <v>129</v>
       </c>
       <c r="R13" s="7" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="4">
-        <v>105340</v>
+        <v>104671</v>
       </c>
       <c r="B14" s="5">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="C14" s="6">
-        <v>0.57013888888888886</v>
+        <v>0.44444444444444442</v>
       </c>
       <c r="D14" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="I14" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="E14" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="H14" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="I14" s="7" t="s">
-        <v>23</v>
-      </c>
       <c r="J14" s="7" t="s">
-        <v>69</v>
+        <v>24</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>81</v>
+        <v>25</v>
       </c>
       <c r="L14" s="7" t="s">
         <v>26</v>
@@ -1718,54 +1955,54 @@
         <v>27</v>
       </c>
       <c r="N14" s="7" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="O14" s="7" t="s">
-        <v>29</v>
+        <v>128</v>
       </c>
       <c r="P14" s="7" t="s">
-        <v>84</v>
+        <v>129</v>
       </c>
       <c r="Q14" s="7" t="s">
-        <v>84</v>
+        <v>129</v>
       </c>
       <c r="R14" s="7" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="159" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:18" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4">
-        <v>104852</v>
+        <v>102963</v>
       </c>
       <c r="B15" s="5">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="C15" s="6">
-        <v>0.58333333333333337</v>
+        <v>0.5</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>75</v>
+        <v>134</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>66</v>
+        <v>136</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>127</v>
+        <v>57</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>69</v>
+        <v>139</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="L15" s="7" t="s">
         <v>26</v>
@@ -1774,54 +2011,54 @@
         <v>27</v>
       </c>
       <c r="N15" s="7" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="O15" s="7" t="s">
-        <v>72</v>
+        <v>141</v>
       </c>
       <c r="P15" s="7" t="s">
-        <v>102</v>
+        <v>142</v>
       </c>
       <c r="Q15" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="R15" s="8" t="s">
-        <v>130</v>
+        <v>142</v>
+      </c>
+      <c r="R15" s="7" t="s">
+        <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:18" ht="231" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="4">
-        <v>105374</v>
+        <v>104206</v>
       </c>
       <c r="B16" s="5">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="C16" s="6">
-        <v>0.60416666666666663</v>
+        <v>0.52777777777777779</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>131</v>
+        <v>33</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>68</v>
+        <v>145</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="L16" s="7" t="s">
         <v>26</v>
@@ -1830,54 +2067,54 @@
         <v>27</v>
       </c>
       <c r="N16" s="7" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="O16" s="7" t="s">
         <v>29</v>
       </c>
       <c r="P16" s="7" t="s">
-        <v>84</v>
+        <v>147</v>
       </c>
       <c r="Q16" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="R16" s="7" t="s">
-        <v>47</v>
+        <v>148</v>
+      </c>
+      <c r="R16" s="8" t="s">
+        <v>149</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="144.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:18" ht="159" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="4">
-        <v>105793</v>
+        <v>106041</v>
       </c>
       <c r="B17" s="5">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="C17" s="6">
-        <v>0.60416666666666663</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>23</v>
+        <v>155</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>90</v>
+        <v>24</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>91</v>
+        <v>156</v>
       </c>
       <c r="L17" s="7" t="s">
         <v>26</v>
@@ -1886,30 +2123,655 @@
         <v>27</v>
       </c>
       <c r="N17" s="7" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="O17" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P17" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q17" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="R17" s="8" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="4">
+        <v>103165</v>
+      </c>
+      <c r="B18" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C18" s="6">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="I18" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="J18" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="L18" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M18" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N18" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="O18" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="P18" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="Q18" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="R18" s="7" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" ht="245.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="4">
+        <v>76146</v>
+      </c>
+      <c r="B19" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C19" s="6">
+        <v>0.5444444444444444</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="L19" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M19" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N19" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="O19" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="P19" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q19" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="R19" s="8" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="4">
+        <v>106007</v>
+      </c>
+      <c r="B20" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C20" s="6">
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="I20" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="J20" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="L20" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M20" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N20" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="O20" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="P17" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="Q17" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="R17" s="8" t="s">
-        <v>142</v>
+      <c r="P20" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="Q20" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="R20" s="7" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" ht="245.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="4">
+        <v>104554</v>
+      </c>
+      <c r="B21" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C21" s="6">
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="K21" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L21" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M21" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N21" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="O21" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P21" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="Q21" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="R21" s="8" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" ht="159" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="4">
+        <v>105356</v>
+      </c>
+      <c r="B22" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C22" s="6">
+        <v>0.5625</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="I22" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="J22" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K22" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="L22" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M22" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N22" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="O22" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P22" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q22" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="R22" s="8" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" ht="159" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="4">
+        <v>105355</v>
+      </c>
+      <c r="B23" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C23" s="6">
+        <v>0.57638888888888884</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="I23" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="J23" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K23" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L23" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M23" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N23" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="O23" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P23" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q23" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="R23" s="8" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" ht="87" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="4">
+        <v>104705</v>
+      </c>
+      <c r="B24" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C24" s="6">
+        <v>0.58750000000000002</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="I24" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="J24" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L24" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M24" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N24" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="O24" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P24" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q24" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="R24" s="8" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" ht="144.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="4">
+        <v>103161</v>
+      </c>
+      <c r="B25" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C25" s="6">
+        <v>0.59722222222222221</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="I25" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="J25" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K25" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L25" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M25" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N25" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="O25" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P25" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q25" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="R25" s="8" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="4">
+        <v>105230</v>
+      </c>
+      <c r="B26" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C26" s="6">
+        <v>0.625</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="I26" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="J26" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="K26" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L26" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M26" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N26" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="O26" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="P26" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q26" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="R26" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="4">
+        <v>103734</v>
+      </c>
+      <c r="B27" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C27" s="6">
+        <v>0.65972222222222221</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="I27" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="J27" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K27" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L27" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M27" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N27" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="O27" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="P27" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="Q27" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="R27" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" ht="144.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="4">
+        <v>96644</v>
+      </c>
+      <c r="B28" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C28" s="6">
+        <v>0.66111111111111109</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="H28" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="I28" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="J28" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="K28" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="L28" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M28" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N28" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="O28" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="P28" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q28" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="R28" s="8" t="s">
+        <v>221</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="R2" r:id="rId1" display="https://trt2-jus-br.zoom.us/j/86789289821?pwd=hmNmYn6ZPr5UBUkTREU7WbLud20xkY.1%20ID%20da%20reunião:%20867%208928%209821%20Senha%20de%20acesso:%20vtaruja01" xr:uid="{E7FFCD97-24DB-43AB-9395-57087B28248F}"/>
-    <hyperlink ref="R3" r:id="rId2" display="https://trt2-jus-br.zoom.us/j/86826984343?pwd=vqkjCTDTofwYe3zhKsVzowS3Wcmu4J.1%20ID%20da%20reunião:%20868%202698%204343%20Senha%20de%20acesso:%20vtaruja01" xr:uid="{80454755-258F-43E6-A9D4-10DF4AD92B37}"/>
-    <hyperlink ref="R8" r:id="rId3" display="https://us02web.zoom.us/j/84680881845?pwd=2uHgFIbgHPhxy5JJEP3uHrbe96HPcI.1%20ID%20da%20reunião:%20846%208088%201845%20Senha:%20960717" xr:uid="{8AAD73CB-208E-436C-BB5A-24992423B349}"/>
-    <hyperlink ref="R10" r:id="rId4" xr:uid="{96DEECF1-4D10-4741-8773-D9C26F477D09}"/>
-    <hyperlink ref="R12" r:id="rId5" display="https://trt15-jus-br.zoom.us/j/88307820364?pwd=S2FSa2QyaUQvZVBqRThqT25PeFNXQT09%20ID%20da%20reunião:%2088307820364%20Senha%20de%20acesso:%20277454" xr:uid="{2E307451-92D6-4ABF-9243-28C015D7F693}"/>
-    <hyperlink ref="R15" r:id="rId6" xr:uid="{B64BBBFC-C518-451D-A498-513B0DEED800}"/>
-    <hyperlink ref="R17" r:id="rId7" xr:uid="{D9FE39BB-B3B9-46E2-9419-191D17FE1C87}"/>
+    <hyperlink ref="R3" r:id="rId1" xr:uid="{9145FE9B-8F7D-4B88-B76E-C894EF6F7E6C}"/>
+    <hyperlink ref="R4" r:id="rId2" display="https://trt23-jus-br.zoom.us/my/salanobres?pwd=NmdUWFBwaGtBZHpucTdWSFQyR2oxUT09" xr:uid="{F6FC0837-52FC-4D2A-8BE7-925D92285230}"/>
+    <hyperlink ref="R5" r:id="rId3" xr:uid="{EAF25487-F171-4499-BCD6-E01F1F87CEEB}"/>
+    <hyperlink ref="R8" r:id="rId4" xr:uid="{E3F8ABC5-B8A5-4735-848E-07FF20AADDE0}"/>
+    <hyperlink ref="R10" r:id="rId5" xr:uid="{E7D8DE9F-E84E-4EEA-BDD4-D52F4DC82248}"/>
+    <hyperlink ref="R11" r:id="rId6" xr:uid="{0372A527-6999-4904-B1B1-7A43C807ADA5}"/>
+    <hyperlink ref="R12" r:id="rId7" display="https://trt15-jus-br.zoom.us/j/4525285196?pwd=cG1ieCtlVVdHZERxcVRTM2lzSGt3dz09%20ID%20da%20reunião:%20452%20528%205196%20Senha%20de%20acesso:%20702632" xr:uid="{61BAF5AF-4A3D-4EC6-A380-749DB18C1040}"/>
+    <hyperlink ref="R16" r:id="rId8" display="https://trt15-jus-br.zoom.us/j/86534999498?pwd=N3RZZXpkTE5laWxEREEvWjBVYVg0Zz09%20ID%20da%20reunião:%20865%203499%209498%20Senha:%2013579" xr:uid="{8576BC53-723C-4BBA-A067-698A9A809409}"/>
+    <hyperlink ref="R17" r:id="rId9" display="mailto:matheuspb26@live.com" xr:uid="{D2BB5679-0297-4404-B611-B94B28CF6974}"/>
+    <hyperlink ref="R19" r:id="rId10" display="https://trt2-jus-br.zoom.us/j/81026971770?pwd=WlJ4VkMvUUhBa1QxWUN1eldWeFNKQT09%20ID%20da%20reunião:%20810%202697%201770%20Senha%20de%20acesso:%20820150" xr:uid="{D6F1EA05-92C1-4A4E-AF5E-73A29FE5501C}"/>
+    <hyperlink ref="R21" r:id="rId11" display="https://trt15-jus-br.zoom.us/j/7871570572?pwd=KzBzUnVURkZwc0gxd21YU3pUWWhJQT09%20ID%20da%20reunião:%20787%20157%200572%20Senha%20de%20acesso:%20674353" xr:uid="{2364E6AF-97A0-4AEB-B8F5-FDB625C0747E}"/>
+    <hyperlink ref="R22" r:id="rId12" display="mailto:matheuspb26@live.com" xr:uid="{1E125AA0-242B-4E78-A958-7CAF776E5B63}"/>
+    <hyperlink ref="R23" r:id="rId13" display="mailto:matheuspb26@live.com" xr:uid="{DC503282-8A2D-4497-80CB-09659BD83F7C}"/>
+    <hyperlink ref="R24" r:id="rId14" xr:uid="{C9A4610A-B736-450F-AC71-6739F0C3ACE7}"/>
+    <hyperlink ref="R25" r:id="rId15" xr:uid="{B4D0ED84-C030-4D8F-B51A-DE31A3EE6F96}"/>
+    <hyperlink ref="R28" r:id="rId16" xr:uid="{9B47D63E-A368-4AE6-A9BF-4488A381A077}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/Pauta_de_Audiencias.xlsx
+++ b/Pauta_de_Audiencias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\blu\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B983A487-7B73-4AA1-8492-92DD0928A756}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{952C0791-04E1-4BE8-973B-F91C52BD5F17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F708F57B-CDFA-44D6-BDAB-F111C37C5FFA}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{81B53A79-9403-4F51-98D0-74604AB2D88D}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="205">
   <si>
     <t>Código P&amp;C</t>
   </si>
@@ -95,623 +95,610 @@
     <t>Link/Observações</t>
   </si>
   <si>
-    <t>Audiência Inicial - Presencial</t>
-  </si>
-  <si>
-    <t>0000477-55.2026.5.23.0031</t>
-  </si>
-  <si>
-    <t>Dipagro Ltda</t>
-  </si>
-  <si>
-    <t>Kleber Garcia Barbara</t>
-  </si>
-  <si>
-    <t>CÁCERES</t>
+    <t>Perícia Técnica</t>
+  </si>
+  <si>
+    <t>0010300-33.2026.5.15.0045</t>
+  </si>
+  <si>
+    <t>Embraer S.A.</t>
+  </si>
+  <si>
+    <t>Matheus Alberto Silva</t>
+  </si>
+  <si>
+    <t>SÃO JOSÉ DOS CAMPOS</t>
+  </si>
+  <si>
+    <t>SP</t>
+  </si>
+  <si>
+    <t>03ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>Instrução</t>
+  </si>
+  <si>
+    <t>Reclamação Trabalhista</t>
+  </si>
+  <si>
+    <t>CENTRAL</t>
+  </si>
+  <si>
+    <t>R$               96.000,00</t>
+  </si>
+  <si>
+    <t>Grupo B2</t>
+  </si>
+  <si>
+    <t>BCF</t>
+  </si>
+  <si>
+    <t>Iremos acompanhar</t>
+  </si>
+  <si>
+    <t>Audiência Inicial -  Telepresencial</t>
+  </si>
+  <si>
+    <t>0010800-71.2026.5.15.0119</t>
+  </si>
+  <si>
+    <t>Pilkington Brasil Ltda</t>
+  </si>
+  <si>
+    <t>Anderson Lopes Mendes</t>
+  </si>
+  <si>
+    <t>CAÇAPAVA</t>
+  </si>
+  <si>
+    <t>VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             128.238,02</t>
+  </si>
+  <si>
+    <t>Grupo E2</t>
+  </si>
+  <si>
+    <t>MBF</t>
+  </si>
+  <si>
+    <t>ARC</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/85809471767?pwd=MmQzbk9PTzZvOVltR01QYVE2SHZWQT09 ID da reunião: 858 0947 1767 Senha: 199094</t>
+  </si>
+  <si>
+    <t>Audiência Inicial - Telepresencial</t>
+  </si>
+  <si>
+    <t>0001531-40.2025.5.09.0303</t>
+  </si>
+  <si>
+    <t>Companhia Act De Participações E Companhia Aix De Participações</t>
+  </si>
+  <si>
+    <t>Cicero Aparecido Xavier</t>
+  </si>
+  <si>
+    <t>FOZ DO IGUAÇU</t>
+  </si>
+  <si>
+    <t>PR</t>
+  </si>
+  <si>
+    <t>Inicial</t>
+  </si>
+  <si>
+    <t>R$             354.545,00</t>
+  </si>
+  <si>
+    <t>Grupo C</t>
+  </si>
+  <si>
+    <t>VSI</t>
+  </si>
+  <si>
+    <t>ECO</t>
+  </si>
+  <si>
+    <t>https://url.trt9.jus.br/1zby3 ID da Reunião: 83106592629 Senha: tDkgvKkg72</t>
+  </si>
+  <si>
+    <t>0001147-17.2026.5.23.0121</t>
+  </si>
+  <si>
+    <t>Inpasa Agroindustrial S/A.</t>
+  </si>
+  <si>
+    <t>Marcos Antonio Dos Santos Silva</t>
+  </si>
+  <si>
+    <t>NOVA MUTUM</t>
   </si>
   <si>
     <t>MT</t>
   </si>
   <si>
-    <t>VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>Instrução</t>
-  </si>
-  <si>
-    <t>Reclamação Trabalhista</t>
-  </si>
-  <si>
-    <t>CENTRAL</t>
-  </si>
-  <si>
-    <t>R$             212.847,22</t>
+    <t>R$             396.441,60</t>
+  </si>
+  <si>
+    <t>RRU</t>
+  </si>
+  <si>
+    <t>https://trt23-jus-br.zoom.us/my/vtnovamutum ID da reunião: 525 746 4936 Senha de acesso: @Nm121</t>
+  </si>
+  <si>
+    <t>Audiência Instrução - Telepresencial</t>
+  </si>
+  <si>
+    <t>0000504-21.2026.5.18.0211</t>
+  </si>
+  <si>
+    <t>Syngenta Seeds Ltda.</t>
+  </si>
+  <si>
+    <t>Dayanne Campera</t>
+  </si>
+  <si>
+    <t>FORMOSA</t>
+  </si>
+  <si>
+    <t>GO</t>
+  </si>
+  <si>
+    <t>1ª Instância</t>
+  </si>
+  <si>
+    <t>R$          1.152.545,37</t>
   </si>
   <si>
     <t>Grupo E1</t>
   </si>
   <si>
-    <t>Correspondente</t>
-  </si>
-  <si>
     <t>VRO</t>
   </si>
   <si>
+    <t>https://trt18-jus-br.zoom.us/j/86900317711</t>
+  </si>
+  <si>
+    <t>Audiência Instrução - Presencial</t>
+  </si>
+  <si>
+    <t>0012497-48.2024.5.15.0071</t>
+  </si>
+  <si>
+    <t>Mahle Metal Leve S.A.</t>
+  </si>
+  <si>
+    <t>Jonas Henrique De Moraes Oliveira</t>
+  </si>
+  <si>
+    <t>MOGI GUAÇU</t>
+  </si>
+  <si>
+    <t>R$               57.294,90</t>
+  </si>
+  <si>
+    <t>Correspondente - Ana</t>
+  </si>
+  <si>
+    <t>PSI</t>
+  </si>
+  <si>
     <t>Presencial</t>
   </si>
   <si>
-    <t>Audiência Inicial -  Telepresencial</t>
-  </si>
-  <si>
-    <t>0001131-63.2026.5.23.0121</t>
-  </si>
-  <si>
-    <t>Inpasa Agroindustrial S/A.</t>
-  </si>
-  <si>
-    <t>Vanildes Souza De Santana</t>
-  </si>
-  <si>
-    <t>NOVA MUTUM</t>
-  </si>
-  <si>
-    <t>R$          3.691.382,47</t>
-  </si>
-  <si>
-    <t>Grupo E2</t>
-  </si>
-  <si>
-    <t>BTF</t>
+    <t>Audiência Una- Telepresencial</t>
+  </si>
+  <si>
+    <t>0010939-02.2026.5.15.0126</t>
+  </si>
+  <si>
+    <t>Syngenta Proteção De Cultivos Ltda.</t>
+  </si>
+  <si>
+    <t>Clodio Henrique Brasil</t>
+  </si>
+  <si>
+    <t>PAULÍNIA</t>
+  </si>
+  <si>
+    <t>02ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$               45.727,50</t>
+  </si>
+  <si>
+    <t>GVM</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/83059104477?pwd=h7VDkteaYgzZ4FIU9CoepcQo5ErUHA.1 ID da reunião: 830 5910 4477 Senha: 005974</t>
+  </si>
+  <si>
+    <t>0010498-60.2026.5.15.0016</t>
+  </si>
+  <si>
+    <t>Multicel Pigmentos Indústria E Comércio Ltda.</t>
+  </si>
+  <si>
+    <t>Valter Luiz Corte</t>
+  </si>
+  <si>
+    <t>SOROCABA</t>
+  </si>
+  <si>
+    <t>R$             279.721,37</t>
   </si>
   <si>
     <t>RCF</t>
   </si>
   <si>
-    <t>https://trt23-jus-br.zoom.us/my/vtnovamutum ID da reunião: 525 746 4936 Senha de acesso: @Nm121</t>
-  </si>
-  <si>
-    <t>Audiência Inicial - Telepresencial</t>
-  </si>
-  <si>
-    <t>0001133-71.2026.5.23.0076</t>
-  </si>
-  <si>
-    <t>Agropecuaria Infiniti Ltda.</t>
-  </si>
-  <si>
-    <t>Welison Vasconcelos Candido</t>
-  </si>
-  <si>
-    <t>PRIMAVERA DO LESTE</t>
-  </si>
-  <si>
-    <t>CEJUSC</t>
-  </si>
-  <si>
-    <t>R$             200.038,28</t>
-  </si>
-  <si>
-    <t>RRU</t>
-  </si>
-  <si>
-    <t>https://trt23-jus-br.zoom.us/my/salanobres?pwd=NmdUWFBwaGtBZHpucTdWSFQyR2oxUT09 ID: 269 890 9821 Senha geral: Nobres1@</t>
-  </si>
-  <si>
-    <t>Audiência de Instrução - Telepresencial</t>
-  </si>
-  <si>
-    <t>0012362-43.2025.5.15.0122</t>
-  </si>
-  <si>
-    <t>Pilkington Brasil Ltda.</t>
-  </si>
-  <si>
-    <t>Raphael Decanio Amancio</t>
-  </si>
-  <si>
-    <t>SUMARÉ</t>
-  </si>
-  <si>
-    <t>SP</t>
-  </si>
-  <si>
-    <t>R$               40.946,58</t>
-  </si>
-  <si>
-    <t>MBF</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/84993384241?pwd=5k1SoEXEWUkAMtV6ck51bpX3LIg8Yz.1</t>
-  </si>
-  <si>
-    <t>Audiência Instrução - Presencial</t>
-  </si>
-  <si>
-    <t>1001555-22.2025.5.02.0020</t>
-  </si>
-  <si>
-    <t>Telefonica Brasil S.A.</t>
-  </si>
-  <si>
-    <t>Giovanni Alessandro Ribeiro Ramos</t>
+    <t>https://trt15-jus-br.zoom.us/j/87864754475?pwd=OUVVMGNaZzZsMUduaUswNGY0SlpJUT09 ID da reunião: 878 6475 4475 Senha de acesso: 817011</t>
+  </si>
+  <si>
+    <t>0011247-60.2026.5.15.0151</t>
+  </si>
+  <si>
+    <t>Luciano De Santana Da Silva</t>
+  </si>
+  <si>
+    <t>ARARAQUARA</t>
+  </si>
+  <si>
+    <t>R$             150.940,60</t>
+  </si>
+  <si>
+    <t>VCR</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/88029879844?pwd=NDNXMkZ2QzJQdzc2MmVkRmdJcEFJdz09</t>
+  </si>
+  <si>
+    <t>1000240-38.2026.5.02.0435</t>
+  </si>
+  <si>
+    <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
+  </si>
+  <si>
+    <t>Paulo Henrique Lazarini</t>
+  </si>
+  <si>
+    <t>SANTO ANDRÉ</t>
+  </si>
+  <si>
+    <t>05ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$          1.852.478,52</t>
+  </si>
+  <si>
+    <t>Grupo B1</t>
+  </si>
+  <si>
+    <t>Correspondente - Hebert</t>
+  </si>
+  <si>
+    <t>GSM</t>
+  </si>
+  <si>
+    <t>Audiência Inicial - Semipresencial</t>
+  </si>
+  <si>
+    <t>0000661-06.2026.5.05.0033</t>
+  </si>
+  <si>
+    <t>Salitre Fertilizantes Ltda</t>
+  </si>
+  <si>
+    <t>Mauricio Dos Santos Da Conceicao</t>
+  </si>
+  <si>
+    <t>SALVADOR</t>
+  </si>
+  <si>
+    <t>BA</t>
+  </si>
+  <si>
+    <t>33ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>Conhecimento</t>
+  </si>
+  <si>
+    <t>R$               89.025,76</t>
+  </si>
+  <si>
+    <t>Correspondente - doc9</t>
+  </si>
+  <si>
+    <t>CAL</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Presencial | Advogada - Elisangela Silva Vireira </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF467886"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>elisangelavieira.adv@gmail.com</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (71)9820-97478 | Preposto - Soraia Silva Melo </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF467886"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>soraiasilvamelo66@gmail.com</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 71984622029</t>
+    </r>
+  </si>
+  <si>
+    <t>Audiência Una - Presencial</t>
+  </si>
+  <si>
+    <t>1001359-44.2026.5.02.0076</t>
+  </si>
+  <si>
+    <t>Mitre Realty Empreendimentos E Participacoes Ltda.</t>
+  </si>
+  <si>
+    <t>Bruno Kuwahara Ferreira</t>
   </si>
   <si>
     <t>SÃO PAULO</t>
   </si>
   <si>
-    <t>20ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>Inicial</t>
-  </si>
-  <si>
-    <t>R$             878.026,00</t>
-  </si>
-  <si>
-    <t>Grupo C</t>
-  </si>
-  <si>
-    <t>TFR</t>
-  </si>
-  <si>
-    <t>Audiência Una - Presencial</t>
-  </si>
-  <si>
-    <t>1001173-20.2026.5.02.0432</t>
-  </si>
-  <si>
-    <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
-  </si>
-  <si>
-    <t>Jose Roberto Lopes Da Silva</t>
-  </si>
-  <si>
-    <t>SANTO ANDRÉ</t>
-  </si>
-  <si>
-    <t>02ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$             152.575,89</t>
-  </si>
-  <si>
-    <t>Grupo B1</t>
-  </si>
-  <si>
-    <t>GSM</t>
+    <t>76ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             402.900,00</t>
+  </si>
+  <si>
+    <t>1001296-18.2026.5.02.0432</t>
+  </si>
+  <si>
+    <t>Andre Aparecido Benedito</t>
+  </si>
+  <si>
+    <t>R$             472.990,96</t>
+  </si>
+  <si>
+    <t>JPE</t>
+  </si>
+  <si>
+    <t>Audiência Inicial -  Presencial</t>
+  </si>
+  <si>
+    <t>1001536-95.2026.5.02.0435</t>
+  </si>
+  <si>
+    <t>Michael Dos Santos Silva</t>
+  </si>
+  <si>
+    <t>R$          1.704.919,14</t>
+  </si>
+  <si>
+    <t>Audiência Una - Telepresencial</t>
+  </si>
+  <si>
+    <t>0011585-91.2026.5.15.0132</t>
+  </si>
+  <si>
+    <t>Ricardo Henrique Da Cruz</t>
+  </si>
+  <si>
+    <t>R$             468.591,40</t>
+  </si>
+  <si>
+    <t>ANB</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/88658871849?pwd=NyJfQajc5htp3TMhT1sgvoQbG7abGq.1</t>
+  </si>
+  <si>
+    <t>Audiência de Conciliação - Presencial</t>
+  </si>
+  <si>
+    <t>1000470-43.2026.5.02.0027</t>
+  </si>
+  <si>
+    <t>Colégio Curumim S/S Ltda</t>
+  </si>
+  <si>
+    <t>Dilva Vieira Dos Santos</t>
+  </si>
+  <si>
+    <t>27ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             326.400,00</t>
+  </si>
+  <si>
+    <t>JRM</t>
+  </si>
+  <si>
+    <t>JPL</t>
+  </si>
+  <si>
+    <t>1000584-41.2026.5.02.0363</t>
+  </si>
+  <si>
+    <t>Gabriel Da Corte</t>
+  </si>
+  <si>
+    <t>MAUÁ</t>
+  </si>
+  <si>
+    <t>R$             106.804,42</t>
   </si>
   <si>
     <t>RFE</t>
   </si>
   <si>
-    <t>0001513-14.2026.5.18.0083</t>
-  </si>
-  <si>
-    <t>Syngenta Proteção De Cultivos Ltda.</t>
-  </si>
-  <si>
-    <t>Jose Madalena Justiniano</t>
-  </si>
-  <si>
-    <t>RIO VERDE</t>
-  </si>
-  <si>
-    <t>GO</t>
-  </si>
-  <si>
-    <t>1ª Instância</t>
-  </si>
-  <si>
-    <t>R$             100.441,80</t>
-  </si>
-  <si>
-    <t>JPL</t>
-  </si>
-  <si>
-    <t>JRM</t>
-  </si>
-  <si>
-    <t>https://trt18-jus-br.zoom.us/my/cejuscrioverde</t>
-  </si>
-  <si>
-    <t>1000694-21.2026.5.02.0434</t>
-  </si>
-  <si>
-    <t>Rubens Bernardes Da Silva</t>
-  </si>
-  <si>
-    <t>04ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$             278.000,00</t>
-  </si>
-  <si>
-    <t>Correspondente - Hebert</t>
-  </si>
-  <si>
-    <t>TAM</t>
-  </si>
-  <si>
-    <t>Audiência Una - Telepresencial</t>
-  </si>
-  <si>
-    <t>0100938-16.2026.5.01.0203</t>
-  </si>
-  <si>
-    <t>Bruno Do Nascimento Monteiro</t>
-  </si>
-  <si>
-    <t>DUQUE DE CAXIAS</t>
-  </si>
-  <si>
-    <t>RJ</t>
-  </si>
-  <si>
-    <t>03ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$             612.615,41</t>
-  </si>
-  <si>
-    <t>BSO</t>
-  </si>
-  <si>
-    <t>https://trt1-jus-br.zoom.us/my/vtdc03?pwd=all4TmdCN01CRGliVlp5dkh6aTBBdz09</t>
-  </si>
-  <si>
-    <t>0012105-48.2026.5.15.0133</t>
-  </si>
-  <si>
-    <t>Moema Bioenergia S.A.</t>
-  </si>
-  <si>
-    <t>Manoel Correia Dias</t>
+    <t>0010140-56.2026.5.15.0126</t>
+  </si>
+  <si>
+    <t>Fertilizantes Heringer S.A.</t>
+  </si>
+  <si>
+    <t>Alvaro Cesar Alcantara Dos Santos</t>
+  </si>
+  <si>
+    <t>R$               74.287,81</t>
+  </si>
+  <si>
+    <t>BBO</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/85312873319?pwd=eERLQVlQVmhJT2JRVmJGTjd2SFFoZz09</t>
+  </si>
+  <si>
+    <t>0010651-31.2026.5.03.0080</t>
+  </si>
+  <si>
+    <t>Marcos Henrique Rodrigues</t>
+  </si>
+  <si>
+    <t>PATROCÍNIO</t>
+  </si>
+  <si>
+    <t>MG</t>
+  </si>
+  <si>
+    <t>R$             118.920,04</t>
+  </si>
+  <si>
+    <t>https://trt3-jus-br.zoom.us/my/vt.patrocinio</t>
+  </si>
+  <si>
+    <t>0012315-75.2026.5.15.0044</t>
+  </si>
+  <si>
+    <t>Moema Bioenergia S.A</t>
+  </si>
+  <si>
+    <t>Francineide Nogueira Dos Santos Alves</t>
   </si>
   <si>
     <t>SÃO JOSÉ DO RIO PRETO</t>
   </si>
   <si>
-    <t>R$             568.813,56</t>
-  </si>
-  <si>
-    <t>RYL</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/82214057803?pwd=Yk9reERlOGxwRk1wVjE2cHYzN29sQT09</t>
-  </si>
-  <si>
-    <t>0010052-17.2026.5.15.0094</t>
-  </si>
-  <si>
-    <t>Embraer S.A.</t>
-  </si>
-  <si>
-    <t>Priscila Pereira De Medeiros</t>
-  </si>
-  <si>
-    <t>CAMPINAS</t>
-  </si>
-  <si>
-    <t>07ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>Ação de Consignação em Pagamento</t>
-  </si>
-  <si>
-    <t>R$               17.118,32</t>
-  </si>
-  <si>
-    <t>Grupo B2</t>
-  </si>
-  <si>
-    <t>VCR</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/4525285196?pwd=cG1ieCtlVVdHZERxcVRTM2lzSGt3dz09 ID da reunião: 452 528 5196 Senha de acesso: 702632</t>
-  </si>
-  <si>
-    <t>1001372-08.2026.5.02.0411</t>
-  </si>
-  <si>
-    <t>Companhia Brasileira De Cartuchos</t>
-  </si>
-  <si>
-    <t>Weslley Igor Antonio Lopes Dos Santos</t>
-  </si>
-  <si>
-    <t>RIBEIRÃO PIRES</t>
-  </si>
-  <si>
-    <t>R$               45.484,31</t>
-  </si>
-  <si>
-    <t>Grupo B3</t>
-  </si>
-  <si>
-    <t>LMI</t>
-  </si>
-  <si>
-    <t>1000515-59.2026.5.02.0411</t>
-  </si>
-  <si>
-    <t>Cbc - Companhia Brasileira De Cartuchos</t>
-  </si>
-  <si>
-    <t>Vinicius De Souza Franca</t>
-  </si>
-  <si>
-    <t>R$             282.024,58</t>
-  </si>
-  <si>
-    <t>Audiência de Instrução - Semipresencial</t>
-  </si>
-  <si>
-    <t>1001486-48.2025.5.02.0421</t>
-  </si>
-  <si>
-    <t>3Corp Technology Infraestrutura De Telecom Ltda.</t>
-  </si>
-  <si>
-    <t>Gabriel Tavares Parreira De Paula</t>
-  </si>
-  <si>
-    <t>SANTANA DE PARNAÍBA</t>
+    <t>R$             231.000,00</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/83908187251?pwd=Ty9tcHNFb0pLZk5WQ0l2Y0V3ZHhhdz09</t>
+  </si>
+  <si>
+    <t>Sessão de Julgamento TRT - Semipresencial</t>
+  </si>
+  <si>
+    <t>0010020-84.2022.5.15.0083</t>
+  </si>
+  <si>
+    <t>Kleber Fernandes De Oliveira</t>
+  </si>
+  <si>
+    <t>03ª TURMA</t>
+  </si>
+  <si>
+    <t>Recursal TRT</t>
+  </si>
+  <si>
+    <t>R$               58.413,55</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/82623308570?pwd=iTwXSFzGsDODSS82A165nSmKqMEX5J.1 ID da reunião: 826 2330 8570 Senha: 197967</t>
+  </si>
+  <si>
+    <t>0011080-89.2025.5.15.0050</t>
+  </si>
+  <si>
+    <t>Guariroba Bioenergia Ltda.</t>
+  </si>
+  <si>
+    <t>Elias Messias De Santana</t>
+  </si>
+  <si>
+    <t>DRACENA</t>
+  </si>
+  <si>
+    <t>R$             100.355,17</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/87527564652?pwd=d3YrZ2diWXk5UjgzbmVkNExteWVMQT09 ID da reunião: 875 2756 4652 Senha de acesso: 246680</t>
+  </si>
+  <si>
+    <t>0012579-79.2024.5.15.0071</t>
+  </si>
+  <si>
+    <t>Alan Donizete Goncalves Dionizio</t>
+  </si>
+  <si>
+    <t>R$             280.495,40</t>
+  </si>
+  <si>
+    <t>0010104-80.2025.5.15.0083</t>
+  </si>
+  <si>
+    <t>Jesus Ferrari</t>
+  </si>
+  <si>
+    <t>01ª TURMA</t>
+  </si>
+  <si>
+    <t>Central</t>
+  </si>
+  <si>
+    <t>R$               87.800,00</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/89827978697?pwd=F58aaFmIxUm6eaHoL2nnSlNO5U91h2.1</t>
+  </si>
+  <si>
+    <t>0010591-04.2026.5.15.0087</t>
+  </si>
+  <si>
+    <t>Luciano Gomes Dos Santos</t>
   </si>
   <si>
     <t>01ª VARA DO TRABALHO</t>
   </si>
   <si>
-    <t>R$             157.171,00</t>
-  </si>
-  <si>
-    <t>Grupo A2</t>
-  </si>
-  <si>
-    <t>NBG</t>
-  </si>
-  <si>
-    <t>0010223-72.2026.5.15.0126</t>
-  </si>
-  <si>
-    <t>Sofia Da Silva Assis</t>
-  </si>
-  <si>
-    <t>PAULÍNIA</t>
-  </si>
-  <si>
-    <t>R$             176.547,57</t>
-  </si>
-  <si>
-    <t>TLI</t>
-  </si>
-  <si>
-    <t>GVM</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/86534999498?pwd=N3RZZXpkTE5laWxEREEvWjBVYVg0Zz09 ID da reunião: 865 3499 9498 Senha: 13579</t>
-  </si>
-  <si>
-    <t>Audiência Inicial -  Presencial</t>
-  </si>
-  <si>
-    <t>0010976-96.2026.5.03.0147</t>
-  </si>
-  <si>
-    <t>Fertilizantes Heringer S.A</t>
-  </si>
-  <si>
-    <t>Marcio Rezende Fonseca</t>
-  </si>
-  <si>
-    <t>TRÊS CORAÇÕES</t>
-  </si>
-  <si>
-    <t>MG</t>
-  </si>
-  <si>
-    <t>Conhecimento</t>
-  </si>
-  <si>
-    <t>R$          1.435.000,00</t>
-  </si>
-  <si>
-    <t>Correspondente - doc9</t>
-  </si>
-  <si>
-    <t>ARC</t>
-  </si>
-  <si>
-    <t>Presencial | Advogado - Matheus Pimenta Barros matheuspb26@live.com 35999092279</t>
-  </si>
-  <si>
-    <t>Perícia Técnica</t>
-  </si>
-  <si>
-    <t>0012829-61.2025.5.15.0109</t>
-  </si>
-  <si>
-    <t>Umberto Aparecido Lima</t>
-  </si>
-  <si>
-    <t>SOROCABA</t>
-  </si>
-  <si>
-    <t>R$             856.425,61</t>
-  </si>
-  <si>
-    <t>ANB</t>
-  </si>
-  <si>
-    <t>Iremos acompanhar</t>
-  </si>
-  <si>
-    <t>Audiência de Conciliação - Telepresencial</t>
-  </si>
-  <si>
-    <t>1000179-05.2020.5.02.0431</t>
-  </si>
-  <si>
-    <t>Jose Ricardo Silva</t>
-  </si>
-  <si>
-    <t>CEJUSC ABC</t>
-  </si>
-  <si>
-    <t>Recursal</t>
-  </si>
-  <si>
-    <t>R$             151.781,01</t>
-  </si>
-  <si>
-    <t>JPE</t>
-  </si>
-  <si>
-    <t>https://trt2-jus-br.zoom.us/j/81026971770?pwd=WlJ4VkMvUUhBa1QxWUN1eldWeFNKQT09 ID da reunião: 810 2697 1770 Senha de acesso: 820150</t>
-  </si>
-  <si>
-    <t>1001462-42.2026.5.02.0467</t>
-  </si>
-  <si>
-    <t>Mahle Metal Leve S.A.</t>
-  </si>
-  <si>
-    <t>Fernando Lopes Bento</t>
-  </si>
-  <si>
-    <t>SÃO BERNARDO DO CAMPO</t>
-  </si>
-  <si>
-    <t>R$               45.442,32</t>
-  </si>
-  <si>
-    <t>Correspondente - Carlos Florian</t>
-  </si>
-  <si>
-    <t>Presencial | Advogada - Dra. Luciana França, (11) 96351-8524</t>
-  </si>
-  <si>
-    <t>Audiência Instrução - Telepresencial</t>
-  </si>
-  <si>
-    <t>0010335-20.2026.5.15.0133</t>
-  </si>
-  <si>
-    <t>Moema Bioenergia S.A. - Moema</t>
-  </si>
-  <si>
-    <t>Renato Jose Dias</t>
-  </si>
-  <si>
-    <t>R$             418.460,00</t>
-  </si>
-  <si>
-    <t>CAL</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/7871570572?pwd=KzBzUnVURkZwc0gxd21YU3pUWWhJQT09 ID da reunião: 787 157 0572 Senha de acesso: 674353</t>
-  </si>
-  <si>
-    <t>0010667-75.2026.5.03.0147</t>
-  </si>
-  <si>
-    <t>Julio Henrique Dionisio</t>
-  </si>
-  <si>
-    <t>R$             712.000,00</t>
-  </si>
-  <si>
-    <t>BBO</t>
-  </si>
-  <si>
-    <t>0010664-23.2026.5.03.0147</t>
-  </si>
-  <si>
-    <t>Breno Heleno Da Silva Mariano</t>
-  </si>
-  <si>
-    <t>R$             521.000,00</t>
-  </si>
-  <si>
-    <t>0010380-36.2026.5.03.0140</t>
-  </si>
-  <si>
-    <t>Sistenge Construções E Comércio Ltda.</t>
-  </si>
-  <si>
-    <t>Alex Alves Da Silva Batista</t>
-  </si>
-  <si>
-    <t>CONTAGEM</t>
-  </si>
-  <si>
-    <t>R$             114.705,18</t>
-  </si>
-  <si>
-    <t>https://trt3-jus-br.zoom.us/my/vt1.contagem</t>
-  </si>
-  <si>
-    <t>0012594-95.2025.5.15.0044</t>
-  </si>
-  <si>
-    <t>Alex Cruz De Souza</t>
-  </si>
-  <si>
-    <t>R$             292.000,00</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/83908187251?pwd=Ty9tcHNFb0pLZk5WQ0l2Y0V3ZHhhdz09</t>
-  </si>
-  <si>
-    <t>1001057-08.2026.5.02.0434</t>
-  </si>
-  <si>
-    <t>Elizeu Luiz Freire</t>
-  </si>
-  <si>
-    <t>R$             158.737,00</t>
-  </si>
-  <si>
-    <t>0024006-50.2026.5.24.0072</t>
-  </si>
-  <si>
-    <t>Rio Paraná Energia S.A.</t>
-  </si>
-  <si>
-    <t>Edson Barbosa</t>
-  </si>
-  <si>
-    <t>TRÊS LAGOAS</t>
-  </si>
-  <si>
-    <t>MS</t>
-  </si>
-  <si>
-    <t>R$             192.773,33</t>
-  </si>
-  <si>
-    <t>ECO</t>
-  </si>
-  <si>
-    <t>0011493-69.2022.5.15.0095</t>
-  </si>
-  <si>
-    <t>Jose Roberto Francisco</t>
-  </si>
-  <si>
-    <t>Execução</t>
-  </si>
-  <si>
-    <t>R$             157.477,74</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/89925839124?pwd=HehXMRH0LyTAyjb9t6axbYz7RHoBqz.1</t>
+    <t>R$          1.170.079,33</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/85267876480?pwd=tETOC8GDaqZZdf9WNGOaW98aPE2MQx.1 ID da reunião: 852 6787 6480 Senha: TRT15</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -729,6 +716,12 @@
     <font>
       <sz val="9"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF467886"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -820,7 +813,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -845,7 +838,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1182,8 +1175,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{012C189B-2E60-4599-964A-781DD785386B}">
-  <dimension ref="A1:R28"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BD945E6-ABB8-4B29-AADC-AF15C83C80AE}">
+  <dimension ref="A1:R26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:18" ht="60" x14ac:dyDescent="0.3">
@@ -1244,13 +1237,13 @@
     </row>
     <row r="2" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4">
-        <v>106670</v>
+        <v>104065</v>
       </c>
       <c r="B2" s="5">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="C2" s="6">
-        <v>0.34027777777777779</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>18</v>
@@ -1292,42 +1285,42 @@
         <v>30</v>
       </c>
       <c r="Q2" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="R2" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="R2" s="7" t="s">
-        <v>32</v>
-      </c>
     </row>
-    <row r="3" spans="1:18" ht="173.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18" ht="231" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4">
-        <v>106002</v>
+        <v>105499</v>
       </c>
       <c r="B3" s="5">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="C3" s="6">
         <v>0.34375</v>
       </c>
       <c r="D3" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="F3" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="G3" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="H3" s="7" t="s">
         <v>36</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>37</v>
       </c>
       <c r="I3" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="K3" s="7" t="s">
         <v>25</v>
@@ -1354,15 +1347,15 @@
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="245.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:18" ht="144.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4">
-        <v>105723</v>
+        <v>103588</v>
       </c>
       <c r="B4" s="5">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="C4" s="6">
-        <v>0.35069444444444442</v>
+        <v>0.34375</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>43</v>
@@ -1380,13 +1373,13 @@
         <v>47</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="L4" s="7" t="s">
         <v>26</v>
@@ -1395,51 +1388,51 @@
         <v>27</v>
       </c>
       <c r="N4" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O4" s="7" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P4" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="Q4" s="7" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="R4" s="8" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="144.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:18" ht="173.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4">
-        <v>101761</v>
+        <v>105989</v>
       </c>
       <c r="B5" s="5">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="C5" s="6">
-        <v>0.39583333333333331</v>
+        <v>0.34375</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="K5" s="7" t="s">
         <v>25</v>
@@ -1451,54 +1444,54 @@
         <v>27</v>
       </c>
       <c r="N5" s="7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="O5" s="7" t="s">
         <v>39</v>
       </c>
       <c r="P5" s="7" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Q5" s="7" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="R5" s="8" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:18" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4">
-        <v>104087</v>
+        <v>104347</v>
       </c>
       <c r="B6" s="5">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="C6" s="6">
-        <v>0.39583333333333331</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>66</v>
+        <v>37</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="L6" s="7" t="s">
         <v>26</v>
@@ -1507,51 +1500,51 @@
         <v>27</v>
       </c>
       <c r="N6" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="O6" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="P6" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="Q6" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="R6" s="7" t="s">
-        <v>32</v>
+        <v>72</v>
+      </c>
+      <c r="R6" s="8" t="s">
+        <v>73</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4">
-        <v>105336</v>
+        <v>99863</v>
       </c>
       <c r="B7" s="5">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="C7" s="6">
-        <v>0.39930555555555558</v>
+        <v>0.375</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>76</v>
+        <v>37</v>
       </c>
       <c r="K7" s="7" t="s">
         <v>25</v>
@@ -1563,54 +1556,54 @@
         <v>27</v>
       </c>
       <c r="N7" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="O7" s="7" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="P7" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q7" s="7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="R7" s="7" t="s">
-        <v>32</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="87" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:18" ht="231" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4">
-        <v>105773</v>
+        <v>105303</v>
       </c>
       <c r="B8" s="5">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="C8" s="6">
-        <v>0.40277777777777779</v>
+        <v>0.375</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>33</v>
+        <v>83</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="L8" s="7" t="s">
         <v>26</v>
@@ -1619,51 +1612,51 @@
         <v>27</v>
       </c>
       <c r="N8" s="7" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="O8" s="7" t="s">
-        <v>29</v>
+        <v>71</v>
       </c>
       <c r="P8" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q8" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="R8" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="245.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="4">
+        <v>104615</v>
+      </c>
+      <c r="B9" s="5">
+        <v>46301</v>
+      </c>
+      <c r="C9" s="6">
+        <v>0.38541666666666669</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J9" s="7" t="s">
         <v>88</v>
-      </c>
-      <c r="Q8" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="R8" s="8" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="4">
-        <v>104747</v>
-      </c>
-      <c r="B9" s="5">
-        <v>46300</v>
-      </c>
-      <c r="C9" s="6">
-        <v>0.4236111111111111</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="J9" s="7" t="s">
-        <v>93</v>
       </c>
       <c r="K9" s="7" t="s">
         <v>25</v>
@@ -1675,51 +1668,51 @@
         <v>27</v>
       </c>
       <c r="N9" s="7" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="O9" s="7" t="s">
-        <v>78</v>
+        <v>39</v>
       </c>
       <c r="P9" s="7" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="Q9" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="R9" s="7" t="s">
-        <v>32</v>
+        <v>97</v>
+      </c>
+      <c r="R9" s="8" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="144.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4">
-        <v>105434</v>
+        <v>105705</v>
       </c>
       <c r="B10" s="5">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="C10" s="6">
-        <v>0.4236111111111111</v>
+        <v>0.38541666666666669</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>97</v>
+        <v>32</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>73</v>
+        <v>20</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>101</v>
+        <v>23</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>102</v>
+        <v>24</v>
       </c>
       <c r="K10" s="7" t="s">
         <v>25</v>
@@ -1731,51 +1724,51 @@
         <v>27</v>
       </c>
       <c r="N10" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="O10" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P10" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="O10" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="P10" s="7" t="s">
+      <c r="Q10" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="R10" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="Q10" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="R10" s="8" t="s">
+    </row>
+    <row r="11" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="4">
+        <v>104020</v>
+      </c>
+      <c r="B11" s="5">
+        <v>46301</v>
+      </c>
+      <c r="C11" s="6">
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="E11" s="7" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" ht="144.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="4">
-        <v>106022</v>
-      </c>
-      <c r="B11" s="5">
-        <v>46300</v>
-      </c>
-      <c r="C11" s="6">
-        <v>0.43055555555555558</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="E11" s="7" t="s">
+      <c r="F11" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="G11" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="H11" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="H11" s="7" t="s">
+      <c r="I11" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J11" s="7" t="s">
         <v>109</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="J11" s="7" t="s">
-        <v>93</v>
       </c>
       <c r="K11" s="7" t="s">
         <v>25</v>
@@ -1790,104 +1783,104 @@
         <v>110</v>
       </c>
       <c r="O11" s="7" t="s">
-        <v>39</v>
+        <v>111</v>
       </c>
       <c r="P11" s="7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q11" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="R11" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
+      </c>
+      <c r="R11" s="7" t="s">
+        <v>82</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="245.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:18" ht="216.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="4">
-        <v>103770</v>
+        <v>105676</v>
       </c>
       <c r="B12" s="5">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="C12" s="6">
-        <v>0.43055555555555558</v>
+        <v>0.40972222222222221</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>57</v>
+        <v>119</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>25</v>
+        <v>121</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>118</v>
+        <v>26</v>
       </c>
       <c r="M12" s="7" t="s">
         <v>27</v>
       </c>
       <c r="N12" s="7" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="O12" s="7" t="s">
-        <v>120</v>
+        <v>39</v>
       </c>
       <c r="P12" s="7" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="Q12" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="R12" s="8" t="s">
-        <v>122</v>
+        <v>124</v>
+      </c>
+      <c r="R12" s="7" t="s">
+        <v>125</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:18" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4">
-        <v>106134</v>
+        <v>105775</v>
       </c>
       <c r="B13" s="5">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="C13" s="6">
-        <v>0.4375</v>
+        <v>0.40972222222222221</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>71</v>
+        <v>126</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>24</v>
+        <v>131</v>
       </c>
       <c r="K13" s="7" t="s">
         <v>25</v>
@@ -1899,51 +1892,51 @@
         <v>27</v>
       </c>
       <c r="N13" s="7" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="O13" s="7" t="s">
-        <v>128</v>
+        <v>39</v>
       </c>
       <c r="P13" s="7" t="s">
-        <v>129</v>
+        <v>41</v>
       </c>
       <c r="Q13" s="7" t="s">
-        <v>129</v>
+        <v>41</v>
       </c>
       <c r="R13" s="7" t="s">
-        <v>32</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="4">
-        <v>104671</v>
+        <v>105501</v>
       </c>
       <c r="B14" s="5">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="C14" s="6">
-        <v>0.44444444444444442</v>
+        <v>0.40972222222222221</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>61</v>
+        <v>126</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>131</v>
+        <v>106</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>24</v>
+        <v>88</v>
       </c>
       <c r="K14" s="7" t="s">
         <v>25</v>
@@ -1955,51 +1948,51 @@
         <v>27</v>
       </c>
       <c r="N14" s="7" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="O14" s="7" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="P14" s="7" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="Q14" s="7" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="R14" s="7" t="s">
-        <v>32</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4">
-        <v>102963</v>
+        <v>105743</v>
       </c>
       <c r="B15" s="5">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="C15" s="6">
-        <v>0.5</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>136</v>
+        <v>106</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>138</v>
+        <v>108</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>139</v>
+        <v>109</v>
       </c>
       <c r="K15" s="7" t="s">
         <v>25</v>
@@ -2014,51 +2007,51 @@
         <v>140</v>
       </c>
       <c r="O15" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="P15" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q15" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="R15" s="7" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="144.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="4">
+        <v>105690</v>
+      </c>
+      <c r="B16" s="5">
+        <v>46301</v>
+      </c>
+      <c r="C16" s="6">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="D16" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="P15" s="7" t="s">
+      <c r="E16" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="Q15" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="R15" s="7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" ht="231" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="4">
-        <v>104206</v>
-      </c>
-      <c r="B16" s="5">
-        <v>46300</v>
-      </c>
-      <c r="C16" s="6">
-        <v>0.52777777777777779</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E16" s="7" t="s">
+      <c r="F16" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G16" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="F16" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>144</v>
-      </c>
       <c r="H16" s="7" t="s">
-        <v>145</v>
+        <v>22</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>76</v>
+        <v>109</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>86</v>
+        <v>25</v>
       </c>
       <c r="L16" s="7" t="s">
         <v>26</v>
@@ -2067,54 +2060,54 @@
         <v>27</v>
       </c>
       <c r="N16" s="7" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="O16" s="7" t="s">
         <v>29</v>
       </c>
       <c r="P16" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q16" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="R16" s="8" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="4">
+        <v>104565</v>
+      </c>
+      <c r="B17" s="5">
+        <v>46301</v>
+      </c>
+      <c r="C17" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D17" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="Q16" s="7" t="s">
+      <c r="E17" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="R16" s="8" t="s">
+      <c r="F17" s="7" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="17" spans="1:18" ht="159" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="4">
-        <v>106041</v>
-      </c>
-      <c r="B17" s="5">
-        <v>46300</v>
-      </c>
-      <c r="C17" s="6">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="D17" s="7" t="s">
+      <c r="G17" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="H17" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J17" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="F17" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="I17" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="J17" s="7" t="s">
-        <v>24</v>
-      </c>
       <c r="K17" s="7" t="s">
-        <v>156</v>
+        <v>25</v>
       </c>
       <c r="L17" s="7" t="s">
         <v>26</v>
@@ -2123,54 +2116,54 @@
         <v>27</v>
       </c>
       <c r="N17" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="O17" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="P17" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q17" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="R17" s="7" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="4">
+        <v>104910</v>
+      </c>
+      <c r="B18" s="5">
+        <v>46301</v>
+      </c>
+      <c r="C18" s="6">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="H18" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="O17" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="P17" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="Q17" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="R17" s="8" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="4">
-        <v>103165</v>
-      </c>
-      <c r="B18" s="5">
-        <v>46300</v>
-      </c>
-      <c r="C18" s="6">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="G18" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="H18" s="7" t="s">
-        <v>164</v>
-      </c>
       <c r="I18" s="7" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>102</v>
+        <v>24</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>67</v>
+        <v>25</v>
       </c>
       <c r="L18" s="7" t="s">
         <v>26</v>
@@ -2179,54 +2172,54 @@
         <v>27</v>
       </c>
       <c r="N18" s="7" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="O18" s="7" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="P18" s="7" t="s">
-        <v>166</v>
+        <v>113</v>
       </c>
       <c r="Q18" s="7" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="R18" s="7" t="s">
-        <v>167</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="245.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:18" ht="144.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="4">
-        <v>76146</v>
+        <v>103940</v>
       </c>
       <c r="B19" s="5">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="C19" s="6">
-        <v>0.5444444444444444</v>
+        <v>0.49305555555555558</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>168</v>
+        <v>43</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>73</v>
+        <v>161</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>171</v>
+        <v>88</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>172</v>
+        <v>25</v>
       </c>
       <c r="L19" s="7" t="s">
         <v>26</v>
@@ -2235,54 +2228,54 @@
         <v>27</v>
       </c>
       <c r="N19" s="7" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="O19" s="7" t="s">
-        <v>78</v>
+        <v>39</v>
       </c>
       <c r="P19" s="7" t="s">
-        <v>174</v>
+        <v>40</v>
       </c>
       <c r="Q19" s="7" t="s">
-        <v>80</v>
+        <v>164</v>
       </c>
       <c r="R19" s="8" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:18" ht="87" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="4">
-        <v>106007</v>
+        <v>105191</v>
       </c>
       <c r="B20" s="5">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="C20" s="6">
-        <v>0.55555555555555558</v>
+        <v>0.52083333333333337</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>177</v>
+        <v>116</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>57</v>
+        <v>169</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>93</v>
+        <v>37</v>
       </c>
       <c r="K20" s="7" t="s">
-        <v>67</v>
+        <v>121</v>
       </c>
       <c r="L20" s="7" t="s">
         <v>26</v>
@@ -2291,54 +2284,54 @@
         <v>27</v>
       </c>
       <c r="N20" s="7" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="O20" s="7" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="P20" s="7" t="s">
-        <v>181</v>
+        <v>164</v>
       </c>
       <c r="Q20" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="R20" s="7" t="s">
-        <v>182</v>
+        <v>124</v>
+      </c>
+      <c r="R20" s="8" t="s">
+        <v>171</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="245.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:18" ht="144.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="4">
-        <v>104554</v>
+        <v>105840</v>
       </c>
       <c r="B21" s="5">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="C21" s="6">
-        <v>0.55555555555555558</v>
+        <v>0.54861111111111116</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>183</v>
+        <v>32</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>109</v>
+        <v>175</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>25</v>
+        <v>121</v>
       </c>
       <c r="L21" s="7" t="s">
         <v>26</v>
@@ -2347,54 +2340,54 @@
         <v>27</v>
       </c>
       <c r="N21" s="7" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="O21" s="7" t="s">
         <v>39</v>
       </c>
       <c r="P21" s="7" t="s">
-        <v>188</v>
+        <v>124</v>
       </c>
       <c r="Q21" s="7" t="s">
-        <v>111</v>
+        <v>41</v>
       </c>
       <c r="R21" s="8" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="159" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:18" ht="231" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="4">
-        <v>105356</v>
+        <v>94993</v>
       </c>
       <c r="B22" s="5">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="C22" s="6">
         <v>0.5625</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>61</v>
+        <v>178</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>152</v>
+        <v>20</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>154</v>
+        <v>22</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>155</v>
+        <v>23</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>24</v>
+        <v>181</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>156</v>
+        <v>182</v>
       </c>
       <c r="L22" s="7" t="s">
         <v>26</v>
@@ -2403,51 +2396,51 @@
         <v>27</v>
       </c>
       <c r="N22" s="7" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="O22" s="7" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="P22" s="7" t="s">
-        <v>158</v>
+        <v>103</v>
       </c>
       <c r="Q22" s="7" t="s">
-        <v>193</v>
+        <v>103</v>
       </c>
       <c r="R22" s="8" t="s">
-        <v>160</v>
+        <v>184</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="159" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:18" ht="245.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="4">
-        <v>105355</v>
+        <v>102822</v>
       </c>
       <c r="B23" s="5">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="C23" s="6">
-        <v>0.57638888888888884</v>
+        <v>0.59375</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>152</v>
+        <v>186</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>154</v>
+        <v>188</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>155</v>
+        <v>23</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="K23" s="7" t="s">
         <v>25</v>
@@ -2459,51 +2452,51 @@
         <v>27</v>
       </c>
       <c r="N23" s="7" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="O23" s="7" t="s">
         <v>39</v>
       </c>
       <c r="P23" s="7" t="s">
-        <v>158</v>
+        <v>40</v>
       </c>
       <c r="Q23" s="7" t="s">
-        <v>193</v>
+        <v>41</v>
       </c>
       <c r="R23" s="8" t="s">
-        <v>160</v>
+        <v>190</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="87" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="4">
-        <v>104705</v>
+        <v>99872</v>
       </c>
       <c r="B24" s="5">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="C24" s="6">
-        <v>0.58750000000000002</v>
+        <v>0.61111111111111116</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>33</v>
+        <v>74</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>198</v>
+        <v>76</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>200</v>
+        <v>78</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>155</v>
+        <v>23</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>139</v>
+        <v>37</v>
       </c>
       <c r="K24" s="7" t="s">
         <v>25</v>
@@ -2515,110 +2508,110 @@
         <v>27</v>
       </c>
       <c r="N24" s="7" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="O24" s="7" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="P24" s="7" t="s">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="Q24" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="R24" s="8" t="s">
-        <v>202</v>
+        <v>81</v>
+      </c>
+      <c r="R24" s="7" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="25" spans="1:18" ht="144.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="4">
-        <v>103161</v>
+        <v>99758</v>
       </c>
       <c r="B25" s="5">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="C25" s="6">
-        <v>0.59722222222222221</v>
+        <v>0.62430555555555556</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>185</v>
+        <v>20</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>109</v>
+        <v>22</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>76</v>
+        <v>196</v>
       </c>
       <c r="K25" s="7" t="s">
-        <v>25</v>
+        <v>182</v>
       </c>
       <c r="L25" s="7" t="s">
         <v>26</v>
       </c>
       <c r="M25" s="7" t="s">
-        <v>27</v>
+        <v>197</v>
       </c>
       <c r="N25" s="7" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="O25" s="7" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="P25" s="7" t="s">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="Q25" s="7" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="R25" s="8" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:18" ht="231" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="4">
-        <v>105230</v>
+        <v>104756</v>
       </c>
       <c r="B26" s="5">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="C26" s="6">
-        <v>0.625</v>
+        <v>0.64583333333333337</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="I26" s="7" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>93</v>
+        <v>202</v>
       </c>
       <c r="K26" s="7" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="L26" s="7" t="s">
         <v>26</v>
@@ -2627,151 +2620,38 @@
         <v>27</v>
       </c>
       <c r="N26" s="7" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="O26" s="7" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="P26" s="7" t="s">
-        <v>95</v>
+        <v>153</v>
       </c>
       <c r="Q26" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="R26" s="7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="4">
-        <v>103734</v>
-      </c>
-      <c r="B27" s="5">
-        <v>46300</v>
-      </c>
-      <c r="C27" s="6">
-        <v>0.65972222222222221</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="G27" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="H27" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="I27" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="J27" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="K27" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="L27" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="M27" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="N27" s="7" t="s">
-        <v>215</v>
-      </c>
-      <c r="O27" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="P27" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="Q27" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="R27" s="7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18" ht="144.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="4">
-        <v>96644</v>
-      </c>
-      <c r="B28" s="5">
-        <v>46300</v>
-      </c>
-      <c r="C28" s="6">
-        <v>0.66111111111111109</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>217</v>
-      </c>
-      <c r="F28" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="G28" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="H28" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="I28" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="J28" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="K28" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="L28" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="M28" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="N28" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="O28" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="P28" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="Q28" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="R28" s="8" t="s">
-        <v>221</v>
+        <v>153</v>
+      </c>
+      <c r="R26" s="8" t="s">
+        <v>204</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="R3" r:id="rId1" xr:uid="{9145FE9B-8F7D-4B88-B76E-C894EF6F7E6C}"/>
-    <hyperlink ref="R4" r:id="rId2" display="https://trt23-jus-br.zoom.us/my/salanobres?pwd=NmdUWFBwaGtBZHpucTdWSFQyR2oxUT09" xr:uid="{F6FC0837-52FC-4D2A-8BE7-925D92285230}"/>
-    <hyperlink ref="R5" r:id="rId3" xr:uid="{EAF25487-F171-4499-BCD6-E01F1F87CEEB}"/>
-    <hyperlink ref="R8" r:id="rId4" xr:uid="{E3F8ABC5-B8A5-4735-848E-07FF20AADDE0}"/>
-    <hyperlink ref="R10" r:id="rId5" xr:uid="{E7D8DE9F-E84E-4EEA-BDD4-D52F4DC82248}"/>
-    <hyperlink ref="R11" r:id="rId6" xr:uid="{0372A527-6999-4904-B1B1-7A43C807ADA5}"/>
-    <hyperlink ref="R12" r:id="rId7" display="https://trt15-jus-br.zoom.us/j/4525285196?pwd=cG1ieCtlVVdHZERxcVRTM2lzSGt3dz09%20ID%20da%20reunião:%20452%20528%205196%20Senha%20de%20acesso:%20702632" xr:uid="{61BAF5AF-4A3D-4EC6-A380-749DB18C1040}"/>
-    <hyperlink ref="R16" r:id="rId8" display="https://trt15-jus-br.zoom.us/j/86534999498?pwd=N3RZZXpkTE5laWxEREEvWjBVYVg0Zz09%20ID%20da%20reunião:%20865%203499%209498%20Senha:%2013579" xr:uid="{8576BC53-723C-4BBA-A067-698A9A809409}"/>
-    <hyperlink ref="R17" r:id="rId9" display="mailto:matheuspb26@live.com" xr:uid="{D2BB5679-0297-4404-B611-B94B28CF6974}"/>
-    <hyperlink ref="R19" r:id="rId10" display="https://trt2-jus-br.zoom.us/j/81026971770?pwd=WlJ4VkMvUUhBa1QxWUN1eldWeFNKQT09%20ID%20da%20reunião:%20810%202697%201770%20Senha%20de%20acesso:%20820150" xr:uid="{D6F1EA05-92C1-4A4E-AF5E-73A29FE5501C}"/>
-    <hyperlink ref="R21" r:id="rId11" display="https://trt15-jus-br.zoom.us/j/7871570572?pwd=KzBzUnVURkZwc0gxd21YU3pUWWhJQT09%20ID%20da%20reunião:%20787%20157%200572%20Senha%20de%20acesso:%20674353" xr:uid="{2364E6AF-97A0-4AEB-B8F5-FDB625C0747E}"/>
-    <hyperlink ref="R22" r:id="rId12" display="mailto:matheuspb26@live.com" xr:uid="{1E125AA0-242B-4E78-A958-7CAF776E5B63}"/>
-    <hyperlink ref="R23" r:id="rId13" display="mailto:matheuspb26@live.com" xr:uid="{DC503282-8A2D-4497-80CB-09659BD83F7C}"/>
-    <hyperlink ref="R24" r:id="rId14" xr:uid="{C9A4610A-B736-450F-AC71-6739F0C3ACE7}"/>
-    <hyperlink ref="R25" r:id="rId15" xr:uid="{B4D0ED84-C030-4D8F-B51A-DE31A3EE6F96}"/>
-    <hyperlink ref="R28" r:id="rId16" xr:uid="{9B47D63E-A368-4AE6-A9BF-4488A381A077}"/>
+    <hyperlink ref="R3" r:id="rId1" display="https://trt15-jus-br.zoom.us/j/85809471767?pwd=MmQzbk9PTzZvOVltR01QYVE2SHZWQT09%20ID%20da%20reunião:%20858%200947%201767%20Senha:%20199094" xr:uid="{BC0A32B9-1681-4190-BD95-1F1D48B8204B}"/>
+    <hyperlink ref="R4" r:id="rId2" xr:uid="{B820DDD8-8E71-4293-9295-0AF7ADF8D96F}"/>
+    <hyperlink ref="R5" r:id="rId3" xr:uid="{774629FA-DDC3-4FD8-85E2-332857BF7BF7}"/>
+    <hyperlink ref="R6" r:id="rId4" xr:uid="{BF5BBFC6-0085-4CBF-9820-CD700DE02971}"/>
+    <hyperlink ref="R8" r:id="rId5" display="https://trt15-jus-br.zoom.us/j/83059104477?pwd=h7VDkteaYgzZ4FIU9CoepcQo5ErUHA.1%20ID%20da%20reunião:%20830%205910%204477%20Senha:%20005974" xr:uid="{43612767-D3E3-423C-B71F-9DB2EED44AD7}"/>
+    <hyperlink ref="R9" r:id="rId6" display="https://trt15-jus-br.zoom.us/j/87864754475?pwd=OUVVMGNaZzZsMUduaUswNGY0SlpJUT09%20ID%20da%20reunião:%20878%206475%204475%20Senha%20de%20acesso:%20817011" xr:uid="{3B557C00-85EA-444D-B624-735109CE075D}"/>
+    <hyperlink ref="R10" r:id="rId7" xr:uid="{30416C6D-A9AE-4544-9387-E02AEAE31C3C}"/>
+    <hyperlink ref="R16" r:id="rId8" xr:uid="{366EBD5E-F889-405A-816E-8EB8B5F5FB52}"/>
+    <hyperlink ref="R19" r:id="rId9" xr:uid="{C6879A11-4B6A-4051-B376-A0BAE2DE0427}"/>
+    <hyperlink ref="R20" r:id="rId10" xr:uid="{A20CF896-8FBC-4A6D-8FF1-750367C31335}"/>
+    <hyperlink ref="R21" r:id="rId11" xr:uid="{5CEA0959-34F5-4756-854D-8FF3FE8D86DF}"/>
+    <hyperlink ref="R22" r:id="rId12" display="https://trt15-jus-br.zoom.us/j/82623308570?pwd=iTwXSFzGsDODSS82A165nSmKqMEX5J.1%20ID%20da%20reunião:%20826%202330%208570%20Senha:%20197967" xr:uid="{BD9B52FC-EA26-481E-9E0A-6D151AD74418}"/>
+    <hyperlink ref="R23" r:id="rId13" display="https://trt15-jus-br.zoom.us/j/87527564652?pwd=d3YrZ2diWXk5UjgzbmVkNExteWVMQT09%20ID%20da%20reunião:%20875%202756%204652%20Senha%20de%20acesso:%20246680" xr:uid="{FB13F381-41B4-4A56-9E34-D6ECA1980333}"/>
+    <hyperlink ref="R25" r:id="rId14" xr:uid="{9593EF96-6A99-4D98-82E4-8CA31AC41B71}"/>
+    <hyperlink ref="R26" r:id="rId15" display="https://trt15-jus-br.zoom.us/j/85267876480?pwd=tETOC8GDaqZZdf9WNGOaW98aPE2MQx.1%20ID%20da%20reunião:%20852%206787%206480%20Senha:%20TRT15" xr:uid="{CC071F05-3499-49DA-8E9D-F4B822059FAC}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/Pauta_de_Audiencias.xlsx
+++ b/Pauta_de_Audiencias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\blu\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{952C0791-04E1-4BE8-973B-F91C52BD5F17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5B667991-3A56-48A7-ABCF-3E6E7542BDD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{81B53A79-9403-4F51-98D0-74604AB2D88D}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{503CA975-5C66-49D6-8C23-BB7166661661}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="180">
   <si>
     <t>Código P&amp;C</t>
   </si>
@@ -98,13 +98,13 @@
     <t>Perícia Técnica</t>
   </si>
   <si>
-    <t>0010300-33.2026.5.15.0045</t>
+    <t>0010736-88.2026.5.15.0013</t>
   </si>
   <si>
     <t>Embraer S.A.</t>
   </si>
   <si>
-    <t>Matheus Alberto Silva</t>
+    <t>Maxwell Stefano Silva</t>
   </si>
   <si>
     <t>SÃO JOSÉ DOS CAMPOS</t>
@@ -113,7 +113,7 @@
     <t>SP</t>
   </si>
   <si>
-    <t>03ª VARA DO TRABALHO</t>
+    <t>01ª VARA DO TRABALHO</t>
   </si>
   <si>
     <t>Instrução</t>
@@ -125,121 +125,394 @@
     <t>CENTRAL</t>
   </si>
   <si>
-    <t>R$               96.000,00</t>
+    <t>R$             152.361,70</t>
   </si>
   <si>
     <t>Grupo B2</t>
   </si>
   <si>
+    <t>VCR</t>
+  </si>
+  <si>
+    <t>ANB</t>
+  </si>
+  <si>
+    <t>Iremos acompanhar</t>
+  </si>
+  <si>
+    <t>Audiência Instrução - Telepresencial</t>
+  </si>
+  <si>
+    <t>1000272-07.2026.5.02.0059</t>
+  </si>
+  <si>
+    <t>Telefonica Brasil S.A.</t>
+  </si>
+  <si>
+    <t>Alexandre Guilherme Villares</t>
+  </si>
+  <si>
+    <t>SÃO PAULO</t>
+  </si>
+  <si>
+    <t>59ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>Conhecimento</t>
+  </si>
+  <si>
+    <t>R$          1.228.241,00</t>
+  </si>
+  <si>
+    <t>Grupo C</t>
+  </si>
+  <si>
+    <t>VSI</t>
+  </si>
+  <si>
+    <t>TFR</t>
+  </si>
+  <si>
+    <t>https://trt2-jus-br.zoom.us/j/81341467392?pwd=K3xMQjEEXDEXaXGI6Labb8HB8JhoaV.1 ID da reunião: 813 4146 7392 Senha de acesso: 0830</t>
+  </si>
+  <si>
+    <t>Audiência Instrução - Presencial</t>
+  </si>
+  <si>
+    <t>1002098-07.2025.5.02.0705</t>
+  </si>
+  <si>
+    <t>Syngenta Proteção De Cultivos Ltda.</t>
+  </si>
+  <si>
+    <t>Michele Dos Santos Gabriel</t>
+  </si>
+  <si>
+    <t>05ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>1ª Instância</t>
+  </si>
+  <si>
+    <t>R$             258.770,13</t>
+  </si>
+  <si>
+    <t>Grupo E1</t>
+  </si>
+  <si>
+    <t>PSI</t>
+  </si>
+  <si>
+    <t>VRO</t>
+  </si>
+  <si>
+    <t>Presencial</t>
+  </si>
+  <si>
+    <t>Audiência Inicial -  Presencial</t>
+  </si>
+  <si>
+    <t>1001176-38.2026.5.02.0411</t>
+  </si>
+  <si>
+    <t>Companhia Brasileira De Cartuchos</t>
+  </si>
+  <si>
+    <t>Rodrigo Silva Mariano</t>
+  </si>
+  <si>
+    <t>RIBEIRÃO PIRES</t>
+  </si>
+  <si>
+    <t>VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$               96.478,92</t>
+  </si>
+  <si>
+    <t>Grupo B3</t>
+  </si>
+  <si>
+    <t>LMI</t>
+  </si>
+  <si>
+    <t>Audiência Una - Presencial</t>
+  </si>
+  <si>
+    <t>1001812-41.2026.5.02.0431</t>
+  </si>
+  <si>
+    <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
+  </si>
+  <si>
+    <t>Chandols Bezerra Simplicio</t>
+  </si>
+  <si>
+    <t>SANTO ANDRÉ</t>
+  </si>
+  <si>
+    <t>R$             169.917,75</t>
+  </si>
+  <si>
+    <t>Grupo B1</t>
+  </si>
+  <si>
+    <t>Correspondente - Hebert</t>
+  </si>
+  <si>
+    <t>TAM</t>
+  </si>
+  <si>
+    <t>0010233-79.2023.5.15.0140</t>
+  </si>
+  <si>
+    <t>Grammer Do Brasil Ltda.</t>
+  </si>
+  <si>
+    <t>Bruno Rodrigues De Souza</t>
+  </si>
+  <si>
+    <t>ATIBAIA</t>
+  </si>
+  <si>
+    <t>R$             222.616,99</t>
+  </si>
+  <si>
+    <t>AAP</t>
+  </si>
+  <si>
+    <t>JPL</t>
+  </si>
+  <si>
+    <t>1001862-67.2026.5.02.0431</t>
+  </si>
+  <si>
+    <t>Matheus Aparecido Dos Santos</t>
+  </si>
+  <si>
+    <t>R$             294.353,67</t>
+  </si>
+  <si>
+    <t>GSM</t>
+  </si>
+  <si>
+    <t>0010685-65.2026.5.15.0017</t>
+  </si>
+  <si>
+    <t>Moema Bioenergia S.A. - Moema</t>
+  </si>
+  <si>
+    <t>Dione Souza Queluz</t>
+  </si>
+  <si>
+    <t>SÃO JOSÉ DO RIO PRETO</t>
+  </si>
+  <si>
+    <t>R$             225.000,00</t>
+  </si>
+  <si>
+    <t>Grupo E2</t>
+  </si>
+  <si>
+    <t>MBF</t>
+  </si>
+  <si>
+    <t>RYL</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/81715388288?pwd=UFAwUGVFQkN1bGNXcStQUEovR2VZUT09 ID da Reunião 817 1538 8288 Senha 198674</t>
+  </si>
+  <si>
+    <t>0013196-86.2025.5.15.0044</t>
+  </si>
+  <si>
+    <t>Osmar Lucianelli</t>
+  </si>
+  <si>
+    <t>02ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             554.185,00</t>
+  </si>
+  <si>
+    <t>BTF</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/85763756385?pwd=ZTBCT3ZkZVg1QUVqMFVBNFcxUDdmQT0</t>
+  </si>
+  <si>
+    <t>0010915-61.2026.5.15.0097</t>
+  </si>
+  <si>
+    <t>A. Raymond Brasil Ltda.</t>
+  </si>
+  <si>
+    <t>Wesley Klaesner</t>
+  </si>
+  <si>
+    <t>JUNDIAÍ</t>
+  </si>
+  <si>
+    <t>04ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             102.250,39</t>
+  </si>
+  <si>
+    <t>1000743-40.2026.5.02.0021</t>
+  </si>
+  <si>
+    <t>Mahle Metal Leve S.A.</t>
+  </si>
+  <si>
+    <t>Aldineia Guedes Da Silva Souza</t>
+  </si>
+  <si>
+    <t>21ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>Inicial</t>
+  </si>
+  <si>
+    <t>R$             140.134,75</t>
+  </si>
+  <si>
+    <t>TLI</t>
+  </si>
+  <si>
+    <t>Audiência Inicial -  Telepresencial</t>
+  </si>
+  <si>
+    <t>0010884-95.2026.5.15.0079</t>
+  </si>
+  <si>
+    <t>Embraer S.A</t>
+  </si>
+  <si>
+    <t>Caroline Mariano Silva</t>
+  </si>
+  <si>
+    <t>ARARAQUARA</t>
+  </si>
+  <si>
+    <t>R$             117.300,00</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/86527943015?pwd=d1B4cVdTSlZVOWozZU9ITmN1L1RTZz09</t>
+  </si>
+  <si>
+    <t>0010307-24.2026.5.15.0013</t>
+  </si>
+  <si>
+    <t>Douglas De Almeida</t>
+  </si>
+  <si>
+    <t>R$             218.000,00</t>
+  </si>
+  <si>
     <t>BCF</t>
   </si>
   <si>
-    <t>Iremos acompanhar</t>
-  </si>
-  <si>
-    <t>Audiência Inicial -  Telepresencial</t>
-  </si>
-  <si>
-    <t>0010800-71.2026.5.15.0119</t>
-  </si>
-  <si>
-    <t>Pilkington Brasil Ltda</t>
-  </si>
-  <si>
-    <t>Anderson Lopes Mendes</t>
-  </si>
-  <si>
-    <t>CAÇAPAVA</t>
-  </si>
-  <si>
-    <t>VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$             128.238,02</t>
-  </si>
-  <si>
-    <t>Grupo E2</t>
-  </si>
-  <si>
-    <t>MBF</t>
-  </si>
-  <si>
-    <t>ARC</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/85809471767?pwd=MmQzbk9PTzZvOVltR01QYVE2SHZWQT09 ID da reunião: 858 0947 1767 Senha: 199094</t>
+    <t>0000449-70.2026.5.09.0195</t>
+  </si>
+  <si>
+    <t>Companhia Act De Participações E Companhia Aix De Participações</t>
+  </si>
+  <si>
+    <t>Carlos Henrique De Andrade Rocha</t>
+  </si>
+  <si>
+    <t>CASCAVEL</t>
+  </si>
+  <si>
+    <t>PR</t>
+  </si>
+  <si>
+    <t>R$             562.000,00</t>
+  </si>
+  <si>
+    <t>ECO</t>
+  </si>
+  <si>
+    <t>https://url.trt9.jus.br/zfgvj ID da Reunião: 88328173538 Senha: g6ZILWJaA4</t>
+  </si>
+  <si>
+    <t>0011736-31.2025.5.15.0152</t>
+  </si>
+  <si>
+    <t>Sistenge Construções E Comércio Ltda.</t>
+  </si>
+  <si>
+    <t>Eder Vilas De Jesus Ribeiro</t>
+  </si>
+  <si>
+    <t>HORTOLÂNDIA</t>
+  </si>
+  <si>
+    <t>R$               35.921,65</t>
+  </si>
+  <si>
+    <t>Correspondente - doc9</t>
+  </si>
+  <si>
+    <t>Presencial | Advogado - Victor Sousa da Rocha vs.rocha@hotmail.com 19997799266</t>
+  </si>
+  <si>
+    <t>0001189-66.2026.5.23.0121</t>
+  </si>
+  <si>
+    <t>Dipagro Ltda.</t>
+  </si>
+  <si>
+    <t>Domingos Marlon Almeida Rodrigues</t>
+  </si>
+  <si>
+    <t>NOVA MUTUM</t>
+  </si>
+  <si>
+    <t>MT</t>
+  </si>
+  <si>
+    <t>R$               52.027,97</t>
+  </si>
+  <si>
+    <t>JRM</t>
+  </si>
+  <si>
+    <t>https://trt23-jus-br.zoom.us/my/vtnovamutum ID da reunião: 525 746 4936 Senha de acesso: @Nm121</t>
+  </si>
+  <si>
+    <t>Audiência Una - Telepresencial</t>
+  </si>
+  <si>
+    <t>0012573-92.2025.5.15.0053</t>
+  </si>
+  <si>
+    <t>Fabricio Henrique Gallo</t>
+  </si>
+  <si>
+    <t>CAMPINAS</t>
+  </si>
+  <si>
+    <t>R$             147.157,09</t>
+  </si>
+  <si>
+    <t>JPE</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/82059322072?pwd=dVZ2QmVkTWh3clg4MmVxOCttUkVpdz09 ID da reunião: 820 5932 2072 Senha: 704451</t>
   </si>
   <si>
     <t>Audiência Inicial - Telepresencial</t>
   </si>
   <si>
-    <t>0001531-40.2025.5.09.0303</t>
-  </si>
-  <si>
-    <t>Companhia Act De Participações E Companhia Aix De Participações</t>
-  </si>
-  <si>
-    <t>Cicero Aparecido Xavier</t>
-  </si>
-  <si>
-    <t>FOZ DO IGUAÇU</t>
-  </si>
-  <si>
-    <t>PR</t>
-  </si>
-  <si>
-    <t>Inicial</t>
-  </si>
-  <si>
-    <t>R$             354.545,00</t>
-  </si>
-  <si>
-    <t>Grupo C</t>
-  </si>
-  <si>
-    <t>VSI</t>
-  </si>
-  <si>
-    <t>ECO</t>
-  </si>
-  <si>
-    <t>https://url.trt9.jus.br/1zby3 ID da Reunião: 83106592629 Senha: tDkgvKkg72</t>
-  </si>
-  <si>
-    <t>0001147-17.2026.5.23.0121</t>
-  </si>
-  <si>
-    <t>Inpasa Agroindustrial S/A.</t>
-  </si>
-  <si>
-    <t>Marcos Antonio Dos Santos Silva</t>
-  </si>
-  <si>
-    <t>NOVA MUTUM</t>
-  </si>
-  <si>
-    <t>MT</t>
-  </si>
-  <si>
-    <t>R$             396.441,60</t>
-  </si>
-  <si>
-    <t>RRU</t>
-  </si>
-  <si>
-    <t>https://trt23-jus-br.zoom.us/my/vtnovamutum ID da reunião: 525 746 4936 Senha de acesso: @Nm121</t>
-  </si>
-  <si>
-    <t>Audiência Instrução - Telepresencial</t>
-  </si>
-  <si>
-    <t>0000504-21.2026.5.18.0211</t>
+    <t>0001944-52.2026.5.18.0211</t>
   </si>
   <si>
     <t>Syngenta Seeds Ltda.</t>
   </si>
   <si>
-    <t>Dayanne Campera</t>
+    <t>Maria Leticia Ribeiro De Paiva</t>
   </si>
   <si>
     <t>FORMOSA</t>
@@ -248,450 +521,64 @@
     <t>GO</t>
   </si>
   <si>
-    <t>1ª Instância</t>
-  </si>
-  <si>
-    <t>R$          1.152.545,37</t>
-  </si>
-  <si>
-    <t>Grupo E1</t>
-  </si>
-  <si>
-    <t>VRO</t>
-  </si>
-  <si>
-    <t>https://trt18-jus-br.zoom.us/j/86900317711</t>
-  </si>
-  <si>
-    <t>Audiência Instrução - Presencial</t>
-  </si>
-  <si>
-    <t>0012497-48.2024.5.15.0071</t>
-  </si>
-  <si>
-    <t>Mahle Metal Leve S.A.</t>
-  </si>
-  <si>
-    <t>Jonas Henrique De Moraes Oliveira</t>
-  </si>
-  <si>
-    <t>MOGI GUAÇU</t>
-  </si>
-  <si>
-    <t>R$               57.294,90</t>
-  </si>
-  <si>
-    <t>Correspondente - Ana</t>
-  </si>
-  <si>
-    <t>PSI</t>
-  </si>
-  <si>
-    <t>Presencial</t>
-  </si>
-  <si>
-    <t>Audiência Una- Telepresencial</t>
-  </si>
-  <si>
-    <t>0010939-02.2026.5.15.0126</t>
-  </si>
-  <si>
-    <t>Syngenta Proteção De Cultivos Ltda.</t>
-  </si>
-  <si>
-    <t>Clodio Henrique Brasil</t>
-  </si>
-  <si>
-    <t>PAULÍNIA</t>
-  </si>
-  <si>
-    <t>02ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$               45.727,50</t>
+    <t>R$             101.133,92</t>
   </si>
   <si>
     <t>GVM</t>
   </si>
   <si>
-    <t>https://trt15-jus-br.zoom.us/j/83059104477?pwd=h7VDkteaYgzZ4FIU9CoepcQo5ErUHA.1 ID da reunião: 830 5910 4477 Senha: 005974</t>
-  </si>
-  <si>
-    <t>0010498-60.2026.5.15.0016</t>
-  </si>
-  <si>
-    <t>Multicel Pigmentos Indústria E Comércio Ltda.</t>
-  </si>
-  <si>
-    <t>Valter Luiz Corte</t>
-  </si>
-  <si>
-    <t>SOROCABA</t>
-  </si>
-  <si>
-    <t>R$             279.721,37</t>
-  </si>
-  <si>
-    <t>RCF</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/87864754475?pwd=OUVVMGNaZzZsMUduaUswNGY0SlpJUT09 ID da reunião: 878 6475 4475 Senha de acesso: 817011</t>
-  </si>
-  <si>
-    <t>0011247-60.2026.5.15.0151</t>
-  </si>
-  <si>
-    <t>Luciano De Santana Da Silva</t>
-  </si>
-  <si>
-    <t>ARARAQUARA</t>
-  </si>
-  <si>
-    <t>R$             150.940,60</t>
-  </si>
-  <si>
-    <t>VCR</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/88029879844?pwd=NDNXMkZ2QzJQdzc2MmVkRmdJcEFJdz09</t>
-  </si>
-  <si>
-    <t>1000240-38.2026.5.02.0435</t>
-  </si>
-  <si>
-    <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
-  </si>
-  <si>
-    <t>Paulo Henrique Lazarini</t>
-  </si>
-  <si>
-    <t>SANTO ANDRÉ</t>
-  </si>
-  <si>
-    <t>05ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$          1.852.478,52</t>
-  </si>
-  <si>
-    <t>Grupo B1</t>
-  </si>
-  <si>
-    <t>Correspondente - Hebert</t>
-  </si>
-  <si>
-    <t>GSM</t>
-  </si>
-  <si>
-    <t>Audiência Inicial - Semipresencial</t>
-  </si>
-  <si>
-    <t>0000661-06.2026.5.05.0033</t>
-  </si>
-  <si>
-    <t>Salitre Fertilizantes Ltda</t>
-  </si>
-  <si>
-    <t>Mauricio Dos Santos Da Conceicao</t>
-  </si>
-  <si>
-    <t>SALVADOR</t>
-  </si>
-  <si>
-    <t>BA</t>
-  </si>
-  <si>
-    <t>33ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>Conhecimento</t>
-  </si>
-  <si>
-    <t>R$               89.025,76</t>
-  </si>
-  <si>
-    <t>Correspondente - doc9</t>
-  </si>
-  <si>
-    <t>CAL</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Presencial | Advogada - Elisangela Silva Vireira </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF467886"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>elisangelavieira.adv@gmail.com</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (71)9820-97478 | Preposto - Soraia Silva Melo </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF467886"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>soraiasilvamelo66@gmail.com</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 71984622029</t>
-    </r>
-  </si>
-  <si>
-    <t>Audiência Una - Presencial</t>
-  </si>
-  <si>
-    <t>1001359-44.2026.5.02.0076</t>
-  </si>
-  <si>
-    <t>Mitre Realty Empreendimentos E Participacoes Ltda.</t>
-  </si>
-  <si>
-    <t>Bruno Kuwahara Ferreira</t>
-  </si>
-  <si>
-    <t>SÃO PAULO</t>
-  </si>
-  <si>
-    <t>76ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$             402.900,00</t>
-  </si>
-  <si>
-    <t>1001296-18.2026.5.02.0432</t>
-  </si>
-  <si>
-    <t>Andre Aparecido Benedito</t>
-  </si>
-  <si>
-    <t>R$             472.990,96</t>
-  </si>
-  <si>
-    <t>JPE</t>
-  </si>
-  <si>
-    <t>Audiência Inicial -  Presencial</t>
-  </si>
-  <si>
-    <t>1001536-95.2026.5.02.0435</t>
-  </si>
-  <si>
-    <t>Michael Dos Santos Silva</t>
-  </si>
-  <si>
-    <t>R$          1.704.919,14</t>
-  </si>
-  <si>
-    <t>Audiência Una - Telepresencial</t>
-  </si>
-  <si>
-    <t>0011585-91.2026.5.15.0132</t>
-  </si>
-  <si>
-    <t>Ricardo Henrique Da Cruz</t>
-  </si>
-  <si>
-    <t>R$             468.591,40</t>
-  </si>
-  <si>
-    <t>ANB</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/88658871849?pwd=NyJfQajc5htp3TMhT1sgvoQbG7abGq.1</t>
-  </si>
-  <si>
-    <t>Audiência de Conciliação - Presencial</t>
-  </si>
-  <si>
-    <t>1000470-43.2026.5.02.0027</t>
-  </si>
-  <si>
-    <t>Colégio Curumim S/S Ltda</t>
-  </si>
-  <si>
-    <t>Dilva Vieira Dos Santos</t>
-  </si>
-  <si>
-    <t>27ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$             326.400,00</t>
-  </si>
-  <si>
-    <t>JRM</t>
-  </si>
-  <si>
-    <t>JPL</t>
-  </si>
-  <si>
-    <t>1000584-41.2026.5.02.0363</t>
-  </si>
-  <si>
-    <t>Gabriel Da Corte</t>
-  </si>
-  <si>
-    <t>MAUÁ</t>
-  </si>
-  <si>
-    <t>R$             106.804,42</t>
-  </si>
-  <si>
-    <t>RFE</t>
-  </si>
-  <si>
-    <t>0010140-56.2026.5.15.0126</t>
-  </si>
-  <si>
-    <t>Fertilizantes Heringer S.A.</t>
-  </si>
-  <si>
-    <t>Alvaro Cesar Alcantara Dos Santos</t>
-  </si>
-  <si>
-    <t>R$               74.287,81</t>
-  </si>
-  <si>
-    <t>BBO</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/85312873319?pwd=eERLQVlQVmhJT2JRVmJGTjd2SFFoZz09</t>
-  </si>
-  <si>
-    <t>0010651-31.2026.5.03.0080</t>
-  </si>
-  <si>
-    <t>Marcos Henrique Rodrigues</t>
-  </si>
-  <si>
-    <t>PATROCÍNIO</t>
-  </si>
-  <si>
-    <t>MG</t>
-  </si>
-  <si>
-    <t>R$             118.920,04</t>
-  </si>
-  <si>
-    <t>https://trt3-jus-br.zoom.us/my/vt.patrocinio</t>
-  </si>
-  <si>
-    <t>0012315-75.2026.5.15.0044</t>
+    <t>https://trt18-jus-br.zoom.us/my/cejuscdigital.tarde</t>
+  </si>
+  <si>
+    <t>0010473-04.2024.5.15.0053</t>
+  </si>
+  <si>
+    <t>Darciana Cristina Correa</t>
+  </si>
+  <si>
+    <t>R$             262.014,73</t>
+  </si>
+  <si>
+    <t>Correspondente - Carlos Florian</t>
+  </si>
+  <si>
+    <t>Presencial | Advogada - Dra. Vivian dos Santos Ramos (19) 97151-1777 | Preposto - Juliana da Silva Oliveira (19) 98743-4081</t>
+  </si>
+  <si>
+    <t>Audiência de Conciliação - Telepresencial</t>
+  </si>
+  <si>
+    <t>0010611-62.2023.5.15.0131</t>
+  </si>
+  <si>
+    <t>Robert Bosch Ltda.</t>
+  </si>
+  <si>
+    <t>Tania Raquel Oliveira De Campos</t>
+  </si>
+  <si>
+    <t>CEJUSC</t>
+  </si>
+  <si>
+    <t>R$               29.971,25</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/89925839124?pwd=HehXMRH0LyTAyjb9t6axbYz7RHoBqz.1</t>
+  </si>
+  <si>
+    <t>0011325-68.2026.5.15.0017</t>
   </si>
   <si>
     <t>Moema Bioenergia S.A</t>
   </si>
   <si>
-    <t>Francineide Nogueira Dos Santos Alves</t>
-  </si>
-  <si>
-    <t>SÃO JOSÉ DO RIO PRETO</t>
-  </si>
-  <si>
-    <t>R$             231.000,00</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/83908187251?pwd=Ty9tcHNFb0pLZk5WQ0l2Y0V3ZHhhdz09</t>
-  </si>
-  <si>
-    <t>Sessão de Julgamento TRT - Semipresencial</t>
-  </si>
-  <si>
-    <t>0010020-84.2022.5.15.0083</t>
-  </si>
-  <si>
-    <t>Kleber Fernandes De Oliveira</t>
-  </si>
-  <si>
-    <t>03ª TURMA</t>
-  </si>
-  <si>
-    <t>Recursal TRT</t>
-  </si>
-  <si>
-    <t>R$               58.413,55</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/82623308570?pwd=iTwXSFzGsDODSS82A165nSmKqMEX5J.1 ID da reunião: 826 2330 8570 Senha: 197967</t>
-  </si>
-  <si>
-    <t>0011080-89.2025.5.15.0050</t>
-  </si>
-  <si>
-    <t>Guariroba Bioenergia Ltda.</t>
-  </si>
-  <si>
-    <t>Elias Messias De Santana</t>
-  </si>
-  <si>
-    <t>DRACENA</t>
-  </si>
-  <si>
-    <t>R$             100.355,17</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/87527564652?pwd=d3YrZ2diWXk5UjgzbmVkNExteWVMQT09 ID da reunião: 875 2756 4652 Senha de acesso: 246680</t>
-  </si>
-  <si>
-    <t>0012579-79.2024.5.15.0071</t>
-  </si>
-  <si>
-    <t>Alan Donizete Goncalves Dionizio</t>
-  </si>
-  <si>
-    <t>R$             280.495,40</t>
-  </si>
-  <si>
-    <t>0010104-80.2025.5.15.0083</t>
-  </si>
-  <si>
-    <t>Jesus Ferrari</t>
-  </si>
-  <si>
-    <t>01ª TURMA</t>
-  </si>
-  <si>
-    <t>Central</t>
-  </si>
-  <si>
-    <t>R$               87.800,00</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/89827978697?pwd=F58aaFmIxUm6eaHoL2nnSlNO5U91h2.1</t>
-  </si>
-  <si>
-    <t>0010591-04.2026.5.15.0087</t>
-  </si>
-  <si>
-    <t>Luciano Gomes Dos Santos</t>
-  </si>
-  <si>
-    <t>01ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$          1.170.079,33</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/85267876480?pwd=tETOC8GDaqZZdf9WNGOaW98aPE2MQx.1 ID da reunião: 852 6787 6480 Senha: TRT15</t>
+    <t>Lucio Mauro Breda</t>
+  </si>
+  <si>
+    <t>R$             112.531,98</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/89099322953?pwd=TDFoQ1FqaENlUit2YXptSTJwa2lnZz</t>
   </si>
 </sst>
 </file>
@@ -721,7 +608,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <color rgb="FF467886"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -815,7 +702,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -836,6 +723,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
@@ -1175,8 +1065,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BD945E6-ABB8-4B29-AADC-AF15C83C80AE}">
-  <dimension ref="A1:R26"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{523BA3A7-4D16-4CD3-AFBF-85203CF35B74}">
+  <dimension ref="A1:R22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:18" ht="60" x14ac:dyDescent="0.3">
@@ -1237,10 +1127,10 @@
     </row>
     <row r="2" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4">
-        <v>104065</v>
+        <v>104530</v>
       </c>
       <c r="B2" s="5">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="C2" s="6">
         <v>0.33333333333333331</v>
@@ -1285,45 +1175,45 @@
         <v>30</v>
       </c>
       <c r="Q2" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="R2" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="231" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18" ht="245.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4">
-        <v>105499</v>
+        <v>104265</v>
       </c>
       <c r="B3" s="5">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="C3" s="6">
-        <v>0.34375</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I3" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="L3" s="7" t="s">
         <v>26</v>
@@ -1332,54 +1222,54 @@
         <v>27</v>
       </c>
       <c r="N3" s="7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="O3" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="P3" s="7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="Q3" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="R3" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R3" s="9" t="s">
+        <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="144.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4">
-        <v>103588</v>
+        <v>103508</v>
       </c>
       <c r="B4" s="5">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="C4" s="6">
-        <v>0.34375</v>
+        <v>0.375</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L4" s="7" t="s">
         <v>26</v>
@@ -1388,51 +1278,51 @@
         <v>27</v>
       </c>
       <c r="N4" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O4" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="P4" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q4" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="R4" s="8" t="s">
         <v>54</v>
       </c>
+      <c r="R4" s="7" t="s">
+        <v>55</v>
+      </c>
     </row>
-    <row r="5" spans="1:18" ht="173.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4">
-        <v>105989</v>
+        <v>105858</v>
       </c>
       <c r="B5" s="5">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="C5" s="6">
-        <v>0.34375</v>
+        <v>0.375</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="K5" s="7" t="s">
         <v>25</v>
@@ -1444,54 +1334,54 @@
         <v>27</v>
       </c>
       <c r="N5" s="7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="O5" s="7" t="s">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="P5" s="7" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="Q5" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="R5" s="8" t="s">
-        <v>62</v>
+        <v>64</v>
+      </c>
+      <c r="R5" s="7" t="s">
+        <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4">
-        <v>104347</v>
+        <v>106202</v>
       </c>
       <c r="B6" s="5">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="C6" s="6">
-        <v>0.35416666666666669</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>69</v>
+        <v>25</v>
       </c>
       <c r="L6" s="7" t="s">
         <v>26</v>
@@ -1509,45 +1399,45 @@
         <v>72</v>
       </c>
       <c r="Q6" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="R6" s="8" t="s">
         <v>73</v>
       </c>
+      <c r="R6" s="7" t="s">
+        <v>55</v>
+      </c>
     </row>
-    <row r="7" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4">
-        <v>99863</v>
+        <v>90698</v>
       </c>
       <c r="B7" s="5">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="C7" s="6">
-        <v>0.375</v>
+        <v>0.40625</v>
       </c>
       <c r="D7" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="F7" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="G7" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="H7" s="7" t="s">
         <v>77</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>78</v>
       </c>
       <c r="I7" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="L7" s="7" t="s">
         <v>26</v>
@@ -1556,54 +1446,54 @@
         <v>27</v>
       </c>
       <c r="N7" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="O7" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="P7" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="O7" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="P7" s="7" t="s">
+      <c r="Q7" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="Q7" s="7" t="s">
+      <c r="R7" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="4">
+        <v>106204</v>
+      </c>
+      <c r="B8" s="5">
+        <v>46302</v>
+      </c>
+      <c r="C8" s="6">
+        <v>0.40972222222222221</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E8" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="R7" s="7" t="s">
+      <c r="F8" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="G8" s="7" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" ht="231" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="4">
-        <v>105303</v>
-      </c>
-      <c r="B8" s="5">
-        <v>46301</v>
-      </c>
-      <c r="C8" s="6">
-        <v>0.375</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>86</v>
-      </c>
       <c r="H8" s="7" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="I8" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>88</v>
+        <v>24</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>69</v>
+        <v>25</v>
       </c>
       <c r="L8" s="7" t="s">
         <v>26</v>
@@ -1612,51 +1502,51 @@
         <v>27</v>
       </c>
       <c r="N8" s="7" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="O8" s="7" t="s">
         <v>71</v>
       </c>
       <c r="P8" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q8" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="R8" s="8" t="s">
-        <v>91</v>
+        <v>72</v>
+      </c>
+      <c r="Q8" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="R8" s="7" t="s">
+        <v>55</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="245.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:18" ht="231" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4">
-        <v>104615</v>
+        <v>104585</v>
       </c>
       <c r="B9" s="5">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="C9" s="6">
-        <v>0.38541666666666669</v>
+        <v>0.4236111111111111</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="I9" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>88</v>
+        <v>24</v>
       </c>
       <c r="K9" s="7" t="s">
         <v>25</v>
@@ -1668,51 +1558,51 @@
         <v>27</v>
       </c>
       <c r="N9" s="7" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="O9" s="7" t="s">
-        <v>39</v>
+        <v>90</v>
       </c>
       <c r="P9" s="7" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="Q9" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="R9" s="8" t="s">
-        <v>98</v>
+        <v>92</v>
+      </c>
+      <c r="R9" s="9" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="144.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4">
-        <v>105705</v>
+        <v>103787</v>
       </c>
       <c r="B10" s="5">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="C10" s="6">
-        <v>0.38541666666666669</v>
+        <v>0.44444444444444442</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="I10" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>24</v>
+        <v>96</v>
       </c>
       <c r="K10" s="7" t="s">
         <v>25</v>
@@ -1724,51 +1614,51 @@
         <v>27</v>
       </c>
       <c r="N10" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="O10" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="P10" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q10" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="R10" s="9" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="4">
+        <v>104698</v>
+      </c>
+      <c r="B11" s="5">
+        <v>46302</v>
+      </c>
+      <c r="C11" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="G11" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="O10" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="P10" s="7" t="s">
+      <c r="H11" s="7" t="s">
         <v>103</v>
-      </c>
-      <c r="Q10" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="R10" s="8" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="4">
-        <v>104020</v>
-      </c>
-      <c r="B11" s="5">
-        <v>46301</v>
-      </c>
-      <c r="C11" s="6">
-        <v>0.3888888888888889</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>108</v>
       </c>
       <c r="I11" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="K11" s="7" t="s">
         <v>25</v>
@@ -1780,54 +1670,54 @@
         <v>27</v>
       </c>
       <c r="N11" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="O11" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="P11" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q11" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="R11" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="4">
+        <v>104865</v>
+      </c>
+      <c r="B12" s="5">
+        <v>46302</v>
+      </c>
+      <c r="C12" s="6">
+        <v>0.46527777777777779</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="K12" s="7" t="s">
         <v>110</v>
-      </c>
-      <c r="O11" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="P11" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="Q11" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="R11" s="7" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" ht="216.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="4">
-        <v>105676</v>
-      </c>
-      <c r="B12" s="5">
-        <v>46301</v>
-      </c>
-      <c r="C12" s="6">
-        <v>0.40972222222222221</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="I12" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="J12" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="K12" s="7" t="s">
-        <v>121</v>
       </c>
       <c r="L12" s="7" t="s">
         <v>26</v>
@@ -1836,51 +1726,51 @@
         <v>27</v>
       </c>
       <c r="N12" s="7" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="O12" s="7" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="P12" s="7" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="Q12" s="7" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="R12" s="7" t="s">
-        <v>125</v>
+        <v>55</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:18" ht="144.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4">
-        <v>105775</v>
+        <v>105152</v>
       </c>
       <c r="B13" s="5">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="C13" s="6">
-        <v>0.40972222222222221</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="I13" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>131</v>
+        <v>96</v>
       </c>
       <c r="K13" s="7" t="s">
         <v>25</v>
@@ -1892,51 +1782,51 @@
         <v>27</v>
       </c>
       <c r="N13" s="7" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="O13" s="7" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="P13" s="7" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="Q13" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="R13" s="7" t="s">
-        <v>82</v>
+        <v>31</v>
+      </c>
+      <c r="R13" s="9" t="s">
+        <v>119</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="4">
-        <v>105501</v>
+        <v>104304</v>
       </c>
       <c r="B14" s="5">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="C14" s="6">
-        <v>0.40972222222222221</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>126</v>
+        <v>18</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>106</v>
+        <v>20</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>108</v>
+        <v>22</v>
       </c>
       <c r="I14" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>88</v>
+        <v>24</v>
       </c>
       <c r="K14" s="7" t="s">
         <v>25</v>
@@ -1948,51 +1838,51 @@
         <v>27</v>
       </c>
       <c r="N14" s="7" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="O14" s="7" t="s">
-        <v>111</v>
+        <v>29</v>
       </c>
       <c r="P14" s="7" t="s">
-        <v>136</v>
+        <v>30</v>
       </c>
       <c r="Q14" s="7" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="R14" s="7" t="s">
-        <v>82</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:18" ht="144.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4">
-        <v>105743</v>
+        <v>104522</v>
       </c>
       <c r="B15" s="5">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="C15" s="6">
-        <v>0.41666666666666669</v>
+        <v>0.5625</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>137</v>
+        <v>33</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>23</v>
+        <v>128</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="K15" s="7" t="s">
         <v>25</v>
@@ -2004,51 +1894,51 @@
         <v>27</v>
       </c>
       <c r="N15" s="7" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="O15" s="7" t="s">
-        <v>111</v>
+        <v>41</v>
       </c>
       <c r="P15" s="7" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="Q15" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="R15" s="7" t="s">
-        <v>82</v>
+        <v>42</v>
+      </c>
+      <c r="R15" s="9" t="s">
+        <v>131</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="144.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:18" ht="159" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="4">
-        <v>105690</v>
+        <v>101737</v>
       </c>
       <c r="B16" s="5">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="C16" s="6">
-        <v>0.42708333333333331</v>
+        <v>0.56944444444444442</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>141</v>
+        <v>45</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>20</v>
+        <v>133</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>22</v>
+        <v>135</v>
       </c>
       <c r="I16" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>109</v>
+        <v>61</v>
       </c>
       <c r="K16" s="7" t="s">
         <v>25</v>
@@ -2060,54 +1950,54 @@
         <v>27</v>
       </c>
       <c r="N16" s="7" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="O16" s="7" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="P16" s="7" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="Q16" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="R16" s="8" t="s">
-        <v>146</v>
+        <v>92</v>
+      </c>
+      <c r="R16" s="9" t="s">
+        <v>138</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:18" ht="173.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="4">
-        <v>104565</v>
+        <v>106042</v>
       </c>
       <c r="B17" s="5">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="C17" s="6">
-        <v>0.45833333333333331</v>
+        <v>0.57291666666666663</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>147</v>
+        <v>113</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>23</v>
+        <v>143</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>151</v>
+        <v>61</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="L17" s="7" t="s">
         <v>26</v>
@@ -2116,51 +2006,51 @@
         <v>27</v>
       </c>
       <c r="N17" s="7" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="O17" s="7" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="P17" s="7" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="Q17" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="R17" s="7" t="s">
-        <v>82</v>
+        <v>145</v>
+      </c>
+      <c r="R17" s="9" t="s">
+        <v>146</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:18" ht="231" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="4">
-        <v>104910</v>
+        <v>103421</v>
       </c>
       <c r="B18" s="5">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="C18" s="6">
-        <v>0.47916666666666669</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>74</v>
+        <v>147</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>106</v>
+        <v>67</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="I18" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>24</v>
+        <v>104</v>
       </c>
       <c r="K18" s="7" t="s">
         <v>25</v>
@@ -2172,54 +2062,54 @@
         <v>27</v>
       </c>
       <c r="N18" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="O18" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="P18" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="Q18" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="R18" s="9" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" ht="87" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="4">
+        <v>106020</v>
+      </c>
+      <c r="B19" s="5">
+        <v>46302</v>
+      </c>
+      <c r="C19" s="6">
+        <v>0.59722222222222221</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="H19" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="O18" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="P18" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q18" s="7" t="s">
+      <c r="I19" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="R18" s="7" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" ht="144.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="4">
-        <v>103940</v>
-      </c>
-      <c r="B19" s="5">
-        <v>46301</v>
-      </c>
-      <c r="C19" s="6">
-        <v>0.49305555555555558</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="I19" s="7" t="s">
-        <v>23</v>
-      </c>
       <c r="J19" s="7" t="s">
-        <v>88</v>
+        <v>61</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="L19" s="7" t="s">
         <v>26</v>
@@ -2228,54 +2118,54 @@
         <v>27</v>
       </c>
       <c r="N19" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="O19" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="P19" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q19" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="R19" s="9" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" ht="156.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="4">
+        <v>98148</v>
+      </c>
+      <c r="B20" s="5">
+        <v>46302</v>
+      </c>
+      <c r="C20" s="6">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E20" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="O19" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="P19" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q19" s="7" t="s">
+      <c r="F20" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="G20" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="R19" s="8" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" ht="87" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="4">
-        <v>105191</v>
-      </c>
-      <c r="B20" s="5">
-        <v>46301</v>
-      </c>
-      <c r="C20" s="6">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="F20" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>167</v>
-      </c>
       <c r="H20" s="7" t="s">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>169</v>
+        <v>23</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>37</v>
+        <v>104</v>
       </c>
       <c r="K20" s="7" t="s">
-        <v>121</v>
+        <v>25</v>
       </c>
       <c r="L20" s="7" t="s">
         <v>26</v>
@@ -2284,54 +2174,54 @@
         <v>27</v>
       </c>
       <c r="N20" s="7" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="O20" s="7" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="P20" s="7" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q20" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="R20" s="8" t="s">
-        <v>171</v>
+        <v>152</v>
+      </c>
+      <c r="R20" s="7" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="21" spans="1:18" ht="144.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="4">
-        <v>105840</v>
+        <v>92098</v>
       </c>
       <c r="B21" s="5">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="C21" s="6">
-        <v>0.54861111111111116</v>
+        <v>0.66111111111111109</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>32</v>
+        <v>168</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="I21" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>88</v>
+        <v>172</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>121</v>
+        <v>25</v>
       </c>
       <c r="L21" s="7" t="s">
         <v>26</v>
@@ -2340,54 +2230,54 @@
         <v>27</v>
       </c>
       <c r="N21" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="O21" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="P21" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q21" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="R21" s="9" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" ht="144.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="4">
+        <v>105939</v>
+      </c>
+      <c r="B22" s="5">
+        <v>46302</v>
+      </c>
+      <c r="C22" s="6">
+        <v>0.6875</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="F22" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="O21" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="P21" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="Q21" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="R21" s="8" t="s">
+      <c r="G22" s="7" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="22" spans="1:18" ht="231" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="4">
-        <v>94993</v>
-      </c>
-      <c r="B22" s="5">
-        <v>46301</v>
-      </c>
-      <c r="C22" s="6">
-        <v>0.5625</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="F22" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G22" s="7" t="s">
-        <v>180</v>
-      </c>
       <c r="H22" s="7" t="s">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="I22" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>181</v>
+        <v>24</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>182</v>
+        <v>25</v>
       </c>
       <c r="L22" s="7" t="s">
         <v>26</v>
@@ -2396,262 +2286,34 @@
         <v>27</v>
       </c>
       <c r="N22" s="7" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="O22" s="7" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="P22" s="7" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="Q22" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="R22" s="8" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" ht="245.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="4">
-        <v>102822</v>
-      </c>
-      <c r="B23" s="5">
-        <v>46301</v>
-      </c>
-      <c r="C23" s="6">
-        <v>0.59375</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="H23" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="I23" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="J23" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="K23" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="L23" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="M23" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="N23" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="O23" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="P23" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q23" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="R23" s="8" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="4">
-        <v>99872</v>
-      </c>
-      <c r="B24" s="5">
-        <v>46301</v>
-      </c>
-      <c r="C24" s="6">
-        <v>0.61111111111111116</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="F24" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="G24" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="H24" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="I24" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="J24" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="K24" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="L24" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="M24" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="N24" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="O24" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="P24" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q24" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="R24" s="7" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" ht="144.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="4">
-        <v>99758</v>
-      </c>
-      <c r="B25" s="5">
-        <v>46301</v>
-      </c>
-      <c r="C25" s="6">
-        <v>0.62430555555555556</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="H25" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="I25" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="J25" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="K25" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="L25" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="M25" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="N25" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="O25" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="P25" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q25" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="R25" s="8" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18" ht="231" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="4">
-        <v>104756</v>
-      </c>
-      <c r="B26" s="5">
-        <v>46301</v>
-      </c>
-      <c r="C26" s="6">
-        <v>0.64583333333333337</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="G26" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="H26" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="I26" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="J26" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="K26" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="L26" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="M26" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="N26" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="O26" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="P26" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="Q26" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="R26" s="8" t="s">
-        <v>204</v>
+        <v>92</v>
+      </c>
+      <c r="R22" s="9" t="s">
+        <v>179</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="R3" r:id="rId1" display="https://trt15-jus-br.zoom.us/j/85809471767?pwd=MmQzbk9PTzZvOVltR01QYVE2SHZWQT09%20ID%20da%20reunião:%20858%200947%201767%20Senha:%20199094" xr:uid="{BC0A32B9-1681-4190-BD95-1F1D48B8204B}"/>
-    <hyperlink ref="R4" r:id="rId2" xr:uid="{B820DDD8-8E71-4293-9295-0AF7ADF8D96F}"/>
-    <hyperlink ref="R5" r:id="rId3" xr:uid="{774629FA-DDC3-4FD8-85E2-332857BF7BF7}"/>
-    <hyperlink ref="R6" r:id="rId4" xr:uid="{BF5BBFC6-0085-4CBF-9820-CD700DE02971}"/>
-    <hyperlink ref="R8" r:id="rId5" display="https://trt15-jus-br.zoom.us/j/83059104477?pwd=h7VDkteaYgzZ4FIU9CoepcQo5ErUHA.1%20ID%20da%20reunião:%20830%205910%204477%20Senha:%20005974" xr:uid="{43612767-D3E3-423C-B71F-9DB2EED44AD7}"/>
-    <hyperlink ref="R9" r:id="rId6" display="https://trt15-jus-br.zoom.us/j/87864754475?pwd=OUVVMGNaZzZsMUduaUswNGY0SlpJUT09%20ID%20da%20reunião:%20878%206475%204475%20Senha%20de%20acesso:%20817011" xr:uid="{3B557C00-85EA-444D-B624-735109CE075D}"/>
-    <hyperlink ref="R10" r:id="rId7" xr:uid="{30416C6D-A9AE-4544-9387-E02AEAE31C3C}"/>
-    <hyperlink ref="R16" r:id="rId8" xr:uid="{366EBD5E-F889-405A-816E-8EB8B5F5FB52}"/>
-    <hyperlink ref="R19" r:id="rId9" xr:uid="{C6879A11-4B6A-4051-B376-A0BAE2DE0427}"/>
-    <hyperlink ref="R20" r:id="rId10" xr:uid="{A20CF896-8FBC-4A6D-8FF1-750367C31335}"/>
-    <hyperlink ref="R21" r:id="rId11" xr:uid="{5CEA0959-34F5-4756-854D-8FF3FE8D86DF}"/>
-    <hyperlink ref="R22" r:id="rId12" display="https://trt15-jus-br.zoom.us/j/82623308570?pwd=iTwXSFzGsDODSS82A165nSmKqMEX5J.1%20ID%20da%20reunião:%20826%202330%208570%20Senha:%20197967" xr:uid="{BD9B52FC-EA26-481E-9E0A-6D151AD74418}"/>
-    <hyperlink ref="R23" r:id="rId13" display="https://trt15-jus-br.zoom.us/j/87527564652?pwd=d3YrZ2diWXk5UjgzbmVkNExteWVMQT09%20ID%20da%20reunião:%20875%202756%204652%20Senha%20de%20acesso:%20246680" xr:uid="{FB13F381-41B4-4A56-9E34-D6ECA1980333}"/>
-    <hyperlink ref="R25" r:id="rId14" xr:uid="{9593EF96-6A99-4D98-82E4-8CA31AC41B71}"/>
-    <hyperlink ref="R26" r:id="rId15" display="https://trt15-jus-br.zoom.us/j/85267876480?pwd=tETOC8GDaqZZdf9WNGOaW98aPE2MQx.1%20ID%20da%20reunião:%20852%206787%206480%20Senha:%20TRT15" xr:uid="{CC071F05-3499-49DA-8E9D-F4B822059FAC}"/>
+    <hyperlink ref="R3" r:id="rId1" display="https://trt2-jus-br.zoom.us/j/81341467392?pwd=K3xMQjEEXDEXaXGI6Labb8HB8JhoaV.1%20ID%20da%20reunião:%20813%204146%207392%20Senha%20de%20acesso:%200830" xr:uid="{3914F161-06F9-447A-A2CA-89105D09F63E}"/>
+    <hyperlink ref="R9" r:id="rId2" display="https://trt15-jus-br.zoom.us/j/81715388288?pwd=UFAwUGVFQkN1bGNXcStQUEovR2VZUT09%20ID%20da%20Reunião%20817%201538%208288%20Senha%20198674" xr:uid="{C70C5C64-3AD1-4400-8AE1-36163FB990D1}"/>
+    <hyperlink ref="R10" r:id="rId3" xr:uid="{980714BC-17E8-40B9-8CC9-8191D8A0C1F5}"/>
+    <hyperlink ref="R13" r:id="rId4" xr:uid="{6403D227-FA8F-4FCD-A28E-B8FC52CA183B}"/>
+    <hyperlink ref="R15" r:id="rId5" xr:uid="{692CF638-4EAF-4FBB-B2FA-8EEF2E4B75CC}"/>
+    <hyperlink ref="R16" r:id="rId6" display="mailto:vs.rocha@hotmail.com" xr:uid="{E027620C-FB9D-467F-BD0A-49496D075465}"/>
+    <hyperlink ref="R17" r:id="rId7" xr:uid="{A2ECF340-DCA3-42A1-86EE-44D7EDD0A05A}"/>
+    <hyperlink ref="R18" r:id="rId8" display="https://trt15-jus-br.zoom.us/j/82059322072?pwd=dVZ2QmVkTWh3clg4MmVxOCttUkVpdz09%20ID%20da%20reunião:%20820%205932%202072%20Senha:%20704451" xr:uid="{81EFC5CE-7D69-431F-9EA9-134DCA79F431}"/>
+    <hyperlink ref="R19" r:id="rId9" xr:uid="{88117121-C570-4BE0-BDA9-7D1DD0980B27}"/>
+    <hyperlink ref="R21" r:id="rId10" xr:uid="{D588952B-6B8B-4F70-ADE3-8C73C2ABCCD2}"/>
+    <hyperlink ref="R22" r:id="rId11" xr:uid="{8A1CDE39-E5F4-47FF-B3D6-2A4B92CFCBB5}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/Pauta_de_Audiencias.xlsx
+++ b/Pauta_de_Audiencias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\blu\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5B667991-3A56-48A7-ABCF-3E6E7542BDD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{ABB7ED04-593F-41EC-95CF-BFBEBFF324DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{503CA975-5C66-49D6-8C23-BB7166661661}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{055C21FD-CA26-4D21-80F8-6AC9374F6363}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="158">
   <si>
     <t>Código P&amp;C</t>
   </si>
@@ -95,37 +95,412 @@
     <t>Link/Observações</t>
   </si>
   <si>
-    <t>Perícia Técnica</t>
-  </si>
-  <si>
-    <t>0010736-88.2026.5.15.0013</t>
-  </si>
-  <si>
-    <t>Embraer S.A.</t>
-  </si>
-  <si>
-    <t>Maxwell Stefano Silva</t>
+    <t>Audiência Una - Telepresencial</t>
+  </si>
+  <si>
+    <t>0012548-72.2026.5.15.0044</t>
+  </si>
+  <si>
+    <t>Moema Bioenergia S.A</t>
+  </si>
+  <si>
+    <t>Albertina Maria De Jesus</t>
+  </si>
+  <si>
+    <t>SÃO JOSÉ DO RIO PRETO</t>
+  </si>
+  <si>
+    <t>SP</t>
+  </si>
+  <si>
+    <t>02ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>Instrução</t>
+  </si>
+  <si>
+    <t>Ação de Consignação em Pagamento</t>
+  </si>
+  <si>
+    <t>CENTRAL</t>
+  </si>
+  <si>
+    <t>R$               13.488,96</t>
+  </si>
+  <si>
+    <t>Grupo E2</t>
+  </si>
+  <si>
+    <t>MBF</t>
+  </si>
+  <si>
+    <t>RYL</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/81757243738?pwd=UXAvdEpveHlrNU05M2ZsZnRrYy9Vdz09 ID da reunião: 817 5724 3738 Senha de acesso: 954332</t>
+  </si>
+  <si>
+    <t>Audiência Instrução - Telepresencial</t>
+  </si>
+  <si>
+    <t>0011186-18.2026.5.15.0082</t>
+  </si>
+  <si>
+    <t>Moema Bioenergia S.A. - Moema</t>
+  </si>
+  <si>
+    <t>Adilson Maximiano Nogueira</t>
+  </si>
+  <si>
+    <t>03ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>Reclamação Trabalhista</t>
+  </si>
+  <si>
+    <t>R$             112.227,97</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/81757243738?pwd=UXAvdEpveHlrNU05M2ZsZnRrYy9Vdz09 ID DA REUNIÃO: 817 5724 3738 SENHA: 954332</t>
+  </si>
+  <si>
+    <t>Audiência Inicial -  Telepresencial</t>
+  </si>
+  <si>
+    <t>0010319-87.2026.5.15.0126</t>
+  </si>
+  <si>
+    <t>Fertilizantes Heringer S.A.</t>
+  </si>
+  <si>
+    <t>Diego De Sousa</t>
+  </si>
+  <si>
+    <t>CAMPINAS</t>
+  </si>
+  <si>
+    <t>R$             230.978,33</t>
+  </si>
+  <si>
+    <t>BBO</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/4525285196?pwd=cG1ieCtlVVdHZERxcVRTM2lzSGt3dz09 ID da reunião: 452 528 5196 Senha de acesso: 702632</t>
+  </si>
+  <si>
+    <t>0010615-62.2026.5.15.0077</t>
+  </si>
+  <si>
+    <t>Syngenta Proteção De Cultivos Ltda.</t>
+  </si>
+  <si>
+    <t>Bruno Henrique Santos Duraes</t>
+  </si>
+  <si>
+    <t>INDAIATUBA</t>
+  </si>
+  <si>
+    <t>VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>1ª Instância</t>
+  </si>
+  <si>
+    <t>R$               21.133,41</t>
+  </si>
+  <si>
+    <t>Grupo E1</t>
+  </si>
+  <si>
+    <t>TLI</t>
+  </si>
+  <si>
+    <t>GVM</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/87004676496?pwd=YVNxVjhNUTZLZi9rOEFOQ3VrOEVYUT09</t>
+  </si>
+  <si>
+    <t>Audiência Instrução - Presencial</t>
+  </si>
+  <si>
+    <t>0000505-67.2026.5.10.0004</t>
+  </si>
+  <si>
+    <t>3Corp Technology Infraestrutura De Telecom Ltda.</t>
+  </si>
+  <si>
+    <t>Arthur Araujo Perpetuo</t>
+  </si>
+  <si>
+    <t>BRASÍLIA</t>
+  </si>
+  <si>
+    <t>DF</t>
+  </si>
+  <si>
+    <t>04ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             141.016,17</t>
+  </si>
+  <si>
+    <t>Grupo A2</t>
+  </si>
+  <si>
+    <t>Correspondente</t>
+  </si>
+  <si>
+    <t>NBG</t>
+  </si>
+  <si>
+    <t>Presencial | Correspondente - Miguel Augusto Marçano Galdino</t>
+  </si>
+  <si>
+    <t>Audiência Una- Telepresencial</t>
+  </si>
+  <si>
+    <t>0010088-80.2026.5.15.0087</t>
+  </si>
+  <si>
+    <t>Claudio Cicero Santos Santana</t>
+  </si>
+  <si>
+    <t>PAULÍNIA</t>
+  </si>
+  <si>
+    <t>01ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             359.948,73</t>
+  </si>
+  <si>
+    <t>JRM</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/84146096644?pwd=STloZzBJSTFaMW5PeXZRYlIrRGlIdz09</t>
+  </si>
+  <si>
+    <t>0012230-76.2025.5.15.0092</t>
+  </si>
+  <si>
+    <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
+  </si>
+  <si>
+    <t>Gabriel Mendes De Araujo</t>
+  </si>
+  <si>
+    <t>05ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$               52.695,41</t>
+  </si>
+  <si>
+    <t>Grupo B1</t>
+  </si>
+  <si>
+    <t>Correspondente - Dani Prandi</t>
+  </si>
+  <si>
+    <t>JPE</t>
+  </si>
+  <si>
+    <t>Presencial</t>
+  </si>
+  <si>
+    <t>0010684-79.2026.5.15.0082</t>
+  </si>
+  <si>
+    <t>Arcanjo Marcos Alves Pereira</t>
+  </si>
+  <si>
+    <t>R$             302.000,00</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/81869084210?pwd=V0EwalRCY0V5ZFhUY0lCMEU1QVBJQT09 ID da reunião: 818 6908 4210 Senha de acesso: 306523</t>
+  </si>
+  <si>
+    <t>Audiência Una - Presencial</t>
+  </si>
+  <si>
+    <t>1000981-85.2026.5.02.0465</t>
+  </si>
+  <si>
+    <t>Mahle Metal Leve S.A.</t>
+  </si>
+  <si>
+    <t>Claudio Oliveira Monte</t>
+  </si>
+  <si>
+    <t>SÃO BERNARDO DO CAMPO</t>
+  </si>
+  <si>
+    <t>06ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>Inicial</t>
+  </si>
+  <si>
+    <t>R$             398.204,14</t>
+  </si>
+  <si>
+    <t>VRO</t>
+  </si>
+  <si>
+    <t>Presencial | Advogada - Dra. Luciana França, (11) 96351-8524</t>
+  </si>
+  <si>
+    <t>Audiência Inicial - Presencial</t>
+  </si>
+  <si>
+    <t>1001478-95.2026.5.02.0434</t>
+  </si>
+  <si>
+    <t>Flavio Eduardo Basilio</t>
+  </si>
+  <si>
+    <t>SANTO ANDRÉ</t>
+  </si>
+  <si>
+    <t>R$             693.419,84</t>
+  </si>
+  <si>
+    <t>RFE</t>
+  </si>
+  <si>
+    <t>0010925-05.2026.5.15.0001</t>
+  </si>
+  <si>
+    <t>Fertilizantes Tocantins S.A</t>
+  </si>
+  <si>
+    <t>Cleverson Augusto Ferreira</t>
+  </si>
+  <si>
+    <t>Conhecimento</t>
+  </si>
+  <si>
+    <t>R$          1.405.684,17</t>
+  </si>
+  <si>
+    <t>CAL</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/83464575337?pwd=bldja1FHQm1tcTVXaVBSazRMUlpHdz0 ID da reunião: 834 6457 5337 Senha: 835403</t>
+  </si>
+  <si>
+    <t>Audiência Inicial -  Presencial</t>
+  </si>
+  <si>
+    <t>1001622-72.2026.5.02.0433</t>
+  </si>
+  <si>
+    <t>Sidnei Pereira De Souza</t>
+  </si>
+  <si>
+    <t>Tutela Cautelar Antecedente</t>
+  </si>
+  <si>
+    <t>R$                 3.000,00</t>
+  </si>
+  <si>
+    <t>GSM</t>
+  </si>
+  <si>
+    <t>1001563-81.2026.5.02.0434</t>
+  </si>
+  <si>
+    <t>Matheus Vinicios Barros De Freitas Souza</t>
+  </si>
+  <si>
+    <t>R$                 8.954,40</t>
+  </si>
+  <si>
+    <t>Correspondente - Hebert</t>
+  </si>
+  <si>
+    <t>BSO</t>
+  </si>
+  <si>
+    <t>0010601-48.2026.5.15.0087</t>
+  </si>
+  <si>
+    <t>Anderson Luiz Fitipaldi</t>
+  </si>
+  <si>
+    <t>R$             806.040,64</t>
+  </si>
+  <si>
+    <t>JPL</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/81792542599? pwd=dWt0TnU2UXVUYXdKTU1CU2gzUTVZQT09 ID da reunião: 817 9254 2599 Senha: 692443</t>
+  </si>
+  <si>
+    <t>Despacho</t>
+  </si>
+  <si>
+    <t>0000687-77.2025.5.12.0054</t>
+  </si>
+  <si>
+    <t>Wickbold &amp; Nosso Pão Indústrias Alimentícias Ltda</t>
+  </si>
+  <si>
+    <t>Jailson Cardoso</t>
+  </si>
+  <si>
+    <t>SÃO JOSÉ</t>
+  </si>
+  <si>
+    <t>SC</t>
+  </si>
+  <si>
+    <t>03ª TURMA</t>
+  </si>
+  <si>
+    <t>Recursal</t>
+  </si>
+  <si>
+    <t>R$             474.999,97</t>
+  </si>
+  <si>
+    <t>Grupo B3</t>
+  </si>
+  <si>
+    <t>https://meet.google.com/tmx-nnyp-tmn </t>
+  </si>
+  <si>
+    <t>1000439-72.2026.5.02.0431</t>
+  </si>
+  <si>
+    <t>Renaldo Nery De Souza</t>
+  </si>
+  <si>
+    <t>R$             857.312,90</t>
+  </si>
+  <si>
+    <t>Audiência de Conciliação - Telepresencial</t>
+  </si>
+  <si>
+    <t>0010326-06.2021.5.15.0013</t>
+  </si>
+  <si>
+    <t>Yaborã Indústria Aeronáutica S.A.</t>
+  </si>
+  <si>
+    <t>Ronaldo Natalino Helbusto</t>
   </si>
   <si>
     <t>SÃO JOSÉ DOS CAMPOS</t>
   </si>
   <si>
-    <t>SP</t>
-  </si>
-  <si>
-    <t>01ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>Instrução</t>
-  </si>
-  <si>
-    <t>Reclamação Trabalhista</t>
-  </si>
-  <si>
-    <t>CENTRAL</t>
-  </si>
-  <si>
-    <t>R$             152.361,70</t>
+    <t>CEJUSC TST</t>
+  </si>
+  <si>
+    <t>Recursal TST</t>
+  </si>
+  <si>
+    <t>R$             121.498,52</t>
   </si>
   <si>
     <t>Grupo B2</t>
@@ -134,458 +509,17 @@
     <t>VCR</t>
   </si>
   <si>
-    <t>ANB</t>
-  </si>
-  <si>
-    <t>Iremos acompanhar</t>
-  </si>
-  <si>
-    <t>Audiência Instrução - Telepresencial</t>
-  </si>
-  <si>
-    <t>1000272-07.2026.5.02.0059</t>
-  </si>
-  <si>
-    <t>Telefonica Brasil S.A.</t>
-  </si>
-  <si>
-    <t>Alexandre Guilherme Villares</t>
-  </si>
-  <si>
-    <t>SÃO PAULO</t>
-  </si>
-  <si>
-    <t>59ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>Conhecimento</t>
-  </si>
-  <si>
-    <t>R$          1.228.241,00</t>
-  </si>
-  <si>
-    <t>Grupo C</t>
-  </si>
-  <si>
-    <t>VSI</t>
-  </si>
-  <si>
-    <t>TFR</t>
-  </si>
-  <si>
-    <t>https://trt2-jus-br.zoom.us/j/81341467392?pwd=K3xMQjEEXDEXaXGI6Labb8HB8JhoaV.1 ID da reunião: 813 4146 7392 Senha de acesso: 0830</t>
-  </si>
-  <si>
-    <t>Audiência Instrução - Presencial</t>
-  </si>
-  <si>
-    <t>1002098-07.2025.5.02.0705</t>
-  </si>
-  <si>
-    <t>Syngenta Proteção De Cultivos Ltda.</t>
-  </si>
-  <si>
-    <t>Michele Dos Santos Gabriel</t>
-  </si>
-  <si>
-    <t>05ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>1ª Instância</t>
-  </si>
-  <si>
-    <t>R$             258.770,13</t>
-  </si>
-  <si>
-    <t>Grupo E1</t>
-  </si>
-  <si>
-    <t>PSI</t>
-  </si>
-  <si>
-    <t>VRO</t>
-  </si>
-  <si>
-    <t>Presencial</t>
-  </si>
-  <si>
-    <t>Audiência Inicial -  Presencial</t>
-  </si>
-  <si>
-    <t>1001176-38.2026.5.02.0411</t>
-  </si>
-  <si>
-    <t>Companhia Brasileira De Cartuchos</t>
-  </si>
-  <si>
-    <t>Rodrigo Silva Mariano</t>
-  </si>
-  <si>
-    <t>RIBEIRÃO PIRES</t>
-  </si>
-  <si>
-    <t>VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$               96.478,92</t>
-  </si>
-  <si>
-    <t>Grupo B3</t>
-  </si>
-  <si>
-    <t>LMI</t>
-  </si>
-  <si>
-    <t>Audiência Una - Presencial</t>
-  </si>
-  <si>
-    <t>1001812-41.2026.5.02.0431</t>
-  </si>
-  <si>
-    <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
-  </si>
-  <si>
-    <t>Chandols Bezerra Simplicio</t>
-  </si>
-  <si>
-    <t>SANTO ANDRÉ</t>
-  </si>
-  <si>
-    <t>R$             169.917,75</t>
-  </si>
-  <si>
-    <t>Grupo B1</t>
-  </si>
-  <si>
-    <t>Correspondente - Hebert</t>
-  </si>
-  <si>
-    <t>TAM</t>
-  </si>
-  <si>
-    <t>0010233-79.2023.5.15.0140</t>
-  </si>
-  <si>
-    <t>Grammer Do Brasil Ltda.</t>
-  </si>
-  <si>
-    <t>Bruno Rodrigues De Souza</t>
-  </si>
-  <si>
-    <t>ATIBAIA</t>
-  </si>
-  <si>
-    <t>R$             222.616,99</t>
-  </si>
-  <si>
-    <t>AAP</t>
-  </si>
-  <si>
-    <t>JPL</t>
-  </si>
-  <si>
-    <t>1001862-67.2026.5.02.0431</t>
-  </si>
-  <si>
-    <t>Matheus Aparecido Dos Santos</t>
-  </si>
-  <si>
-    <t>R$             294.353,67</t>
-  </si>
-  <si>
-    <t>GSM</t>
-  </si>
-  <si>
-    <t>0010685-65.2026.5.15.0017</t>
-  </si>
-  <si>
-    <t>Moema Bioenergia S.A. - Moema</t>
-  </si>
-  <si>
-    <t>Dione Souza Queluz</t>
-  </si>
-  <si>
-    <t>SÃO JOSÉ DO RIO PRETO</t>
-  </si>
-  <si>
-    <t>R$             225.000,00</t>
-  </si>
-  <si>
-    <t>Grupo E2</t>
-  </si>
-  <si>
-    <t>MBF</t>
-  </si>
-  <si>
-    <t>RYL</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/81715388288?pwd=UFAwUGVFQkN1bGNXcStQUEovR2VZUT09 ID da Reunião 817 1538 8288 Senha 198674</t>
-  </si>
-  <si>
-    <t>0013196-86.2025.5.15.0044</t>
-  </si>
-  <si>
-    <t>Osmar Lucianelli</t>
-  </si>
-  <si>
-    <t>02ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$             554.185,00</t>
-  </si>
-  <si>
-    <t>BTF</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/85763756385?pwd=ZTBCT3ZkZVg1QUVqMFVBNFcxUDdmQT0</t>
-  </si>
-  <si>
-    <t>0010915-61.2026.5.15.0097</t>
-  </si>
-  <si>
-    <t>A. Raymond Brasil Ltda.</t>
-  </si>
-  <si>
-    <t>Wesley Klaesner</t>
-  </si>
-  <si>
-    <t>JUNDIAÍ</t>
-  </si>
-  <si>
-    <t>04ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$             102.250,39</t>
-  </si>
-  <si>
-    <t>1000743-40.2026.5.02.0021</t>
-  </si>
-  <si>
-    <t>Mahle Metal Leve S.A.</t>
-  </si>
-  <si>
-    <t>Aldineia Guedes Da Silva Souza</t>
-  </si>
-  <si>
-    <t>21ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>Inicial</t>
-  </si>
-  <si>
-    <t>R$             140.134,75</t>
-  </si>
-  <si>
-    <t>TLI</t>
-  </si>
-  <si>
-    <t>Audiência Inicial -  Telepresencial</t>
-  </si>
-  <si>
-    <t>0010884-95.2026.5.15.0079</t>
-  </si>
-  <si>
-    <t>Embraer S.A</t>
-  </si>
-  <si>
-    <t>Caroline Mariano Silva</t>
-  </si>
-  <si>
-    <t>ARARAQUARA</t>
-  </si>
-  <si>
-    <t>R$             117.300,00</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/86527943015?pwd=d1B4cVdTSlZVOWozZU9ITmN1L1RTZz09</t>
-  </si>
-  <si>
-    <t>0010307-24.2026.5.15.0013</t>
-  </si>
-  <si>
-    <t>Douglas De Almeida</t>
-  </si>
-  <si>
-    <t>R$             218.000,00</t>
-  </si>
-  <si>
     <t>BCF</t>
   </si>
   <si>
-    <t>0000449-70.2026.5.09.0195</t>
-  </si>
-  <si>
-    <t>Companhia Act De Participações E Companhia Aix De Participações</t>
-  </si>
-  <si>
-    <t>Carlos Henrique De Andrade Rocha</t>
-  </si>
-  <si>
-    <t>CASCAVEL</t>
-  </si>
-  <si>
-    <t>PR</t>
-  </si>
-  <si>
-    <t>R$             562.000,00</t>
-  </si>
-  <si>
-    <t>ECO</t>
-  </si>
-  <si>
-    <t>https://url.trt9.jus.br/zfgvj ID da Reunião: 88328173538 Senha: g6ZILWJaA4</t>
-  </si>
-  <si>
-    <t>0011736-31.2025.5.15.0152</t>
-  </si>
-  <si>
-    <t>Sistenge Construções E Comércio Ltda.</t>
-  </si>
-  <si>
-    <t>Eder Vilas De Jesus Ribeiro</t>
-  </si>
-  <si>
-    <t>HORTOLÂNDIA</t>
-  </si>
-  <si>
-    <t>R$               35.921,65</t>
-  </si>
-  <si>
-    <t>Correspondente - doc9</t>
-  </si>
-  <si>
-    <t>Presencial | Advogado - Victor Sousa da Rocha vs.rocha@hotmail.com 19997799266</t>
-  </si>
-  <si>
-    <t>0001189-66.2026.5.23.0121</t>
-  </si>
-  <si>
-    <t>Dipagro Ltda.</t>
-  </si>
-  <si>
-    <t>Domingos Marlon Almeida Rodrigues</t>
-  </si>
-  <si>
-    <t>NOVA MUTUM</t>
-  </si>
-  <si>
-    <t>MT</t>
-  </si>
-  <si>
-    <t>R$               52.027,97</t>
-  </si>
-  <si>
-    <t>JRM</t>
-  </si>
-  <si>
-    <t>https://trt23-jus-br.zoom.us/my/vtnovamutum ID da reunião: 525 746 4936 Senha de acesso: @Nm121</t>
-  </si>
-  <si>
-    <t>Audiência Una - Telepresencial</t>
-  </si>
-  <si>
-    <t>0012573-92.2025.5.15.0053</t>
-  </si>
-  <si>
-    <t>Fabricio Henrique Gallo</t>
-  </si>
-  <si>
-    <t>CAMPINAS</t>
-  </si>
-  <si>
-    <t>R$             147.157,09</t>
-  </si>
-  <si>
-    <t>JPE</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/82059322072?pwd=dVZ2QmVkTWh3clg4MmVxOCttUkVpdz09 ID da reunião: 820 5932 2072 Senha: 704451</t>
-  </si>
-  <si>
-    <t>Audiência Inicial - Telepresencial</t>
-  </si>
-  <si>
-    <t>0001944-52.2026.5.18.0211</t>
-  </si>
-  <si>
-    <t>Syngenta Seeds Ltda.</t>
-  </si>
-  <si>
-    <t>Maria Leticia Ribeiro De Paiva</t>
-  </si>
-  <si>
-    <t>FORMOSA</t>
-  </si>
-  <si>
-    <t>GO</t>
-  </si>
-  <si>
-    <t>R$             101.133,92</t>
-  </si>
-  <si>
-    <t>GVM</t>
-  </si>
-  <si>
-    <t>https://trt18-jus-br.zoom.us/my/cejuscdigital.tarde</t>
-  </si>
-  <si>
-    <t>0010473-04.2024.5.15.0053</t>
-  </si>
-  <si>
-    <t>Darciana Cristina Correa</t>
-  </si>
-  <si>
-    <t>R$             262.014,73</t>
-  </si>
-  <si>
-    <t>Correspondente - Carlos Florian</t>
-  </si>
-  <si>
-    <t>Presencial | Advogada - Dra. Vivian dos Santos Ramos (19) 97151-1777 | Preposto - Juliana da Silva Oliveira (19) 98743-4081</t>
-  </si>
-  <si>
-    <t>Audiência de Conciliação - Telepresencial</t>
-  </si>
-  <si>
-    <t>0010611-62.2023.5.15.0131</t>
-  </si>
-  <si>
-    <t>Robert Bosch Ltda.</t>
-  </si>
-  <si>
-    <t>Tania Raquel Oliveira De Campos</t>
-  </si>
-  <si>
-    <t>CEJUSC</t>
-  </si>
-  <si>
-    <t>R$               29.971,25</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/89925839124?pwd=HehXMRH0LyTAyjb9t6axbYz7RHoBqz.1</t>
-  </si>
-  <si>
-    <t>0011325-68.2026.5.15.0017</t>
-  </si>
-  <si>
-    <t>Moema Bioenergia S.A</t>
-  </si>
-  <si>
-    <t>Lucio Mauro Breda</t>
-  </si>
-  <si>
-    <t>R$             112.531,98</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/89099322953?pwd=TDFoQ1FqaENlUit2YXptSTJwa2lnZz</t>
+    <t>bit.ly/Cejusc2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -603,12 +537,6 @@
     <font>
       <sz val="9"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -700,9 +628,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -725,10 +653,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1065,8 +990,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{523BA3A7-4D16-4CD3-AFBF-85203CF35B74}">
-  <dimension ref="A1:R22"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45948356-8ADD-4780-95B6-C41B616D73AA}">
+  <dimension ref="A1:R18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:18" ht="60" x14ac:dyDescent="0.3">
@@ -1125,15 +1050,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" ht="231" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4">
-        <v>104530</v>
+        <v>106014</v>
       </c>
       <c r="B2" s="5">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="C2" s="6">
-        <v>0.33333333333333331</v>
+        <v>0.34375</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>18</v>
@@ -1177,16 +1102,16 @@
       <c r="Q2" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="R2" s="7" t="s">
+      <c r="R2" s="8" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="245.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18" ht="231" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4">
-        <v>104265</v>
+        <v>104994</v>
       </c>
       <c r="B3" s="5">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="C3" s="6">
         <v>0.35416666666666669</v>
@@ -1204,691 +1129,691 @@
         <v>36</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="I3" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J3" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L3" s="7" t="s">
         <v>38</v>
-      </c>
-      <c r="K3" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="L3" s="7" t="s">
-        <v>26</v>
       </c>
       <c r="M3" s="7" t="s">
         <v>27</v>
       </c>
       <c r="N3" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="O3" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P3" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q3" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="R3" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="O3" s="7" t="s">
+    </row>
+    <row r="4" spans="1:18" ht="245.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="4">
+        <v>104713</v>
+      </c>
+      <c r="B4" s="5">
+        <v>46303</v>
+      </c>
+      <c r="C4" s="6">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="P3" s="7" t="s">
+      <c r="E4" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="Q3" s="7" t="s">
+      <c r="F4" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="R3" s="9" t="s">
+      <c r="G4" s="7" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="4" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="4">
-        <v>103508</v>
-      </c>
-      <c r="B4" s="5">
-        <v>46302</v>
-      </c>
-      <c r="C4" s="6">
-        <v>0.375</v>
-      </c>
-      <c r="D4" s="7" t="s">
+      <c r="H4" s="7" t="s">
         <v>45</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>37</v>
       </c>
       <c r="I4" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="M4" s="7" t="s">
         <v>27</v>
       </c>
       <c r="N4" s="7" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="O4" s="7" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="P4" s="7" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="Q4" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="R4" s="7" t="s">
-        <v>55</v>
+        <v>47</v>
+      </c>
+      <c r="R4" s="8" t="s">
+        <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:18" ht="144.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4">
-        <v>105858</v>
+        <v>104207</v>
       </c>
       <c r="B5" s="5">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="C5" s="6">
         <v>0.375</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="I5" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="M5" s="7" t="s">
         <v>27</v>
       </c>
       <c r="N5" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="O5" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="P5" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q5" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="R5" s="8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="96.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="4">
+        <v>104990</v>
+      </c>
+      <c r="B6" s="5">
+        <v>46303</v>
+      </c>
+      <c r="C6" s="6">
+        <v>0.37847222222222221</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="F6" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="O5" s="7" t="s">
+      <c r="G6" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="P5" s="7" t="s">
+      <c r="H6" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="Q5" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="R5" s="7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="4">
-        <v>106202</v>
-      </c>
-      <c r="B6" s="5">
-        <v>46302</v>
-      </c>
-      <c r="C6" s="6">
-        <v>0.3888888888888889</v>
-      </c>
-      <c r="D6" s="7" t="s">
+      <c r="I6" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="J6" s="7" t="s">
         <v>66</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>24</v>
       </c>
       <c r="K6" s="7" t="s">
         <v>25</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="M6" s="7" t="s">
         <v>27</v>
       </c>
       <c r="N6" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="O6" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="P6" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q6" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="O6" s="7" t="s">
+      <c r="R6" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="P6" s="7" t="s">
+    </row>
+    <row r="7" spans="1:18" ht="144.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="4">
+        <v>103840</v>
+      </c>
+      <c r="B7" s="5">
+        <v>46303</v>
+      </c>
+      <c r="C7" s="6">
+        <v>0.37986111111111109</v>
+      </c>
+      <c r="D7" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="Q6" s="7" t="s">
+      <c r="E7" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="R6" s="7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="4">
-        <v>90698</v>
-      </c>
-      <c r="B7" s="5">
-        <v>46302</v>
-      </c>
-      <c r="C7" s="6">
-        <v>0.40625</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="E7" s="7" t="s">
+      <c r="F7" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="G7" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="H7" s="7" t="s">
         <v>75</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>77</v>
       </c>
       <c r="I7" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>24</v>
+        <v>76</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="M7" s="7" t="s">
         <v>27</v>
       </c>
       <c r="N7" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="O7" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="P7" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="O7" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="P7" s="7" t="s">
+      <c r="Q7" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="R7" s="8" t="s">
         <v>79</v>
-      </c>
-      <c r="Q7" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="R7" s="7" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4">
-        <v>106204</v>
+        <v>103267</v>
       </c>
       <c r="B8" s="5">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="C8" s="6">
-        <v>0.40972222222222221</v>
+        <v>0.39374999999999999</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E8" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="F8" s="7" t="s">
         <v>81</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>67</v>
       </c>
       <c r="G8" s="7" t="s">
         <v>82</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="I8" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="K8" s="7" t="s">
         <v>25</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="M8" s="7" t="s">
         <v>27</v>
       </c>
       <c r="N8" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O8" s="7" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="P8" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q8" s="8" t="s">
-        <v>84</v>
+        <v>86</v>
+      </c>
+      <c r="Q8" s="7" t="s">
+        <v>87</v>
       </c>
       <c r="R8" s="7" t="s">
-        <v>55</v>
+        <v>88</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="231" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:18" ht="245.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4">
-        <v>104585</v>
+        <v>104688</v>
       </c>
       <c r="B9" s="5">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="C9" s="6">
-        <v>0.4236111111111111</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>33</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>86</v>
+        <v>35</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>88</v>
+        <v>22</v>
       </c>
       <c r="I9" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="K9" s="7" t="s">
         <v>25</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="M9" s="7" t="s">
         <v>27</v>
       </c>
       <c r="N9" s="7" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="O9" s="7" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="P9" s="7" t="s">
-        <v>91</v>
+        <v>31</v>
       </c>
       <c r="Q9" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="R9" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="R9" s="9" t="s">
+    </row>
+    <row r="10" spans="1:18" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="4">
+        <v>105369</v>
+      </c>
+      <c r="B10" s="5">
+        <v>46303</v>
+      </c>
+      <c r="C10" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D10" s="7" t="s">
         <v>93</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" ht="144.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="4">
-        <v>103787</v>
-      </c>
-      <c r="B10" s="5">
-        <v>46302</v>
-      </c>
-      <c r="C10" s="6">
-        <v>0.44444444444444442</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>33</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>94</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="I10" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>25</v>
+        <v>99</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="M10" s="7" t="s">
         <v>27</v>
       </c>
       <c r="N10" s="7" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="O10" s="7" t="s">
-        <v>90</v>
+        <v>56</v>
       </c>
       <c r="P10" s="7" t="s">
-        <v>98</v>
+        <v>69</v>
       </c>
       <c r="Q10" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="R10" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
+      </c>
+      <c r="R10" s="7" t="s">
+        <v>102</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4">
-        <v>104698</v>
+        <v>105698</v>
       </c>
       <c r="B11" s="5">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="C11" s="6">
-        <v>0.45833333333333331</v>
+        <v>0.4375</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>18</v>
+        <v>103</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="I11" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="K11" s="7" t="s">
         <v>25</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="M11" s="7" t="s">
         <v>27</v>
       </c>
       <c r="N11" s="7" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="O11" s="7" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="P11" s="7" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="Q11" s="7" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="R11" s="7" t="s">
-        <v>32</v>
+        <v>88</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:18" ht="231" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="4">
-        <v>104865</v>
+        <v>105066</v>
       </c>
       <c r="B12" s="5">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="C12" s="6">
         <v>0.46527777777777779</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="I12" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="M12" s="7" t="s">
         <v>27</v>
       </c>
       <c r="N12" s="7" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="O12" s="7" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="P12" s="7" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="Q12" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="R12" s="7" t="s">
-        <v>55</v>
+        <v>31</v>
+      </c>
+      <c r="R12" s="8" t="s">
+        <v>115</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="144.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4">
-        <v>105152</v>
+        <v>105993</v>
       </c>
       <c r="B13" s="5">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="C13" s="6">
-        <v>0.54166666666666663</v>
+        <v>0.51388888888888884</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="I13" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>96</v>
+        <v>37</v>
       </c>
       <c r="K13" s="7" t="s">
         <v>25</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>26</v>
+        <v>119</v>
       </c>
       <c r="M13" s="7" t="s">
         <v>27</v>
       </c>
       <c r="N13" s="7" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="O13" s="7" t="s">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="P13" s="7" t="s">
-        <v>31</v>
+        <v>121</v>
       </c>
       <c r="Q13" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R13" s="9" t="s">
-        <v>119</v>
+        <v>108</v>
+      </c>
+      <c r="R13" s="7" t="s">
+        <v>88</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="4">
-        <v>104304</v>
+        <v>105807</v>
       </c>
       <c r="B14" s="5">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="C14" s="6">
-        <v>0.54166666666666663</v>
+        <v>0.55555555555555558</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>18</v>
+        <v>93</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>22</v>
+        <v>106</v>
       </c>
       <c r="I14" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="K14" s="7" t="s">
         <v>25</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="M14" s="7" t="s">
         <v>27</v>
       </c>
       <c r="N14" s="7" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="O14" s="7" t="s">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="P14" s="7" t="s">
-        <v>30</v>
+        <v>125</v>
       </c>
       <c r="Q14" s="7" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="R14" s="7" t="s">
-        <v>32</v>
+        <v>88</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="144.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:18" ht="231" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4">
-        <v>104522</v>
+        <v>104779</v>
       </c>
       <c r="B15" s="5">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="C15" s="6">
-        <v>0.5625</v>
+        <v>0.625</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>125</v>
+        <v>50</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>127</v>
+        <v>75</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>128</v>
+        <v>23</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="M15" s="7" t="s">
         <v>27</v>
@@ -1897,148 +1822,148 @@
         <v>129</v>
       </c>
       <c r="O15" s="7" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="P15" s="7" t="s">
         <v>130</v>
       </c>
       <c r="Q15" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="R15" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="R15" s="8" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="159" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:18" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="4">
-        <v>101737</v>
+        <v>100814</v>
       </c>
       <c r="B16" s="5">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="C16" s="6">
-        <v>0.56944444444444442</v>
+        <v>0.625</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>45</v>
+        <v>132</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>23</v>
+        <v>137</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>61</v>
+        <v>138</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>25</v>
+        <v>139</v>
       </c>
       <c r="L16" s="7" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="M16" s="7" t="s">
         <v>27</v>
       </c>
       <c r="N16" s="7" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="O16" s="7" t="s">
-        <v>90</v>
+        <v>141</v>
       </c>
       <c r="P16" s="7" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="Q16" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="R16" s="9" t="s">
-        <v>138</v>
+        <v>121</v>
+      </c>
+      <c r="R16" s="8" t="s">
+        <v>142</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="173.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="4">
-        <v>106042</v>
+        <v>104419</v>
       </c>
       <c r="B17" s="5">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="C17" s="6">
-        <v>0.57291666666666663</v>
+        <v>0.63888888888888884</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>113</v>
+        <v>60</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>140</v>
+        <v>81</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>142</v>
+        <v>106</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>143</v>
+        <v>23</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="L17" s="7" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="M17" s="7" t="s">
         <v>27</v>
       </c>
       <c r="N17" s="7" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O17" s="7" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="P17" s="7" t="s">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="Q17" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="R17" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="R17" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="4">
+        <v>93920</v>
+      </c>
+      <c r="B18" s="5">
+        <v>46303</v>
+      </c>
+      <c r="C18" s="6">
+        <v>0.64375000000000004</v>
+      </c>
+      <c r="D18" s="7" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="18" spans="1:18" ht="231" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="4">
-        <v>103421</v>
-      </c>
-      <c r="B18" s="5">
-        <v>46302</v>
-      </c>
-      <c r="C18" s="6">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="D18" s="7" t="s">
+      <c r="E18" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="F18" s="7" t="s">
         <v>148</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>67</v>
       </c>
       <c r="G18" s="7" t="s">
         <v>149</v>
@@ -2050,270 +1975,44 @@
         <v>23</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>104</v>
+        <v>151</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>25</v>
+        <v>152</v>
       </c>
       <c r="L18" s="7" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="M18" s="7" t="s">
         <v>27</v>
       </c>
       <c r="N18" s="7" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="O18" s="7" t="s">
-        <v>71</v>
+        <v>154</v>
       </c>
       <c r="P18" s="7" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="Q18" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="R18" s="9" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" ht="87" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="4">
-        <v>106020</v>
-      </c>
-      <c r="B19" s="5">
-        <v>46302</v>
-      </c>
-      <c r="C19" s="6">
-        <v>0.59722222222222221</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="F19" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="G19" s="7" t="s">
+      <c r="R18" s="7" t="s">
         <v>157</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="I19" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="J19" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="K19" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="L19" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="M19" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="N19" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="O19" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="P19" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q19" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="R19" s="9" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" ht="156.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="4">
-        <v>98148</v>
-      </c>
-      <c r="B20" s="5">
-        <v>46302</v>
-      </c>
-      <c r="C20" s="6">
-        <v>0.60416666666666663</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="F20" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="H20" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="I20" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="J20" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="K20" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="L20" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="M20" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="N20" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="O20" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="P20" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="Q20" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="R20" s="7" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" ht="144.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="4">
-        <v>92098</v>
-      </c>
-      <c r="B21" s="5">
-        <v>46302</v>
-      </c>
-      <c r="C21" s="6">
-        <v>0.66111111111111109</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="G21" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="H21" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="I21" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="J21" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="K21" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="L21" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="M21" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="N21" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="O21" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="P21" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q21" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="R21" s="9" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" ht="144.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="4">
-        <v>105939</v>
-      </c>
-      <c r="B22" s="5">
-        <v>46302</v>
-      </c>
-      <c r="C22" s="6">
-        <v>0.6875</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="F22" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="G22" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="H22" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="I22" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="J22" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="K22" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="L22" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="M22" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="N22" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="O22" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="P22" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="Q22" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="R22" s="9" t="s">
-        <v>179</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="R3" r:id="rId1" display="https://trt2-jus-br.zoom.us/j/81341467392?pwd=K3xMQjEEXDEXaXGI6Labb8HB8JhoaV.1%20ID%20da%20reunião:%20813%204146%207392%20Senha%20de%20acesso:%200830" xr:uid="{3914F161-06F9-447A-A2CA-89105D09F63E}"/>
-    <hyperlink ref="R9" r:id="rId2" display="https://trt15-jus-br.zoom.us/j/81715388288?pwd=UFAwUGVFQkN1bGNXcStQUEovR2VZUT09%20ID%20da%20Reunião%20817%201538%208288%20Senha%20198674" xr:uid="{C70C5C64-3AD1-4400-8AE1-36163FB990D1}"/>
-    <hyperlink ref="R10" r:id="rId3" xr:uid="{980714BC-17E8-40B9-8CC9-8191D8A0C1F5}"/>
-    <hyperlink ref="R13" r:id="rId4" xr:uid="{6403D227-FA8F-4FCD-A28E-B8FC52CA183B}"/>
-    <hyperlink ref="R15" r:id="rId5" xr:uid="{692CF638-4EAF-4FBB-B2FA-8EEF2E4B75CC}"/>
-    <hyperlink ref="R16" r:id="rId6" display="mailto:vs.rocha@hotmail.com" xr:uid="{E027620C-FB9D-467F-BD0A-49496D075465}"/>
-    <hyperlink ref="R17" r:id="rId7" xr:uid="{A2ECF340-DCA3-42A1-86EE-44D7EDD0A05A}"/>
-    <hyperlink ref="R18" r:id="rId8" display="https://trt15-jus-br.zoom.us/j/82059322072?pwd=dVZ2QmVkTWh3clg4MmVxOCttUkVpdz09%20ID%20da%20reunião:%20820%205932%202072%20Senha:%20704451" xr:uid="{81EFC5CE-7D69-431F-9EA9-134DCA79F431}"/>
-    <hyperlink ref="R19" r:id="rId9" xr:uid="{88117121-C570-4BE0-BDA9-7D1DD0980B27}"/>
-    <hyperlink ref="R21" r:id="rId10" xr:uid="{D588952B-6B8B-4F70-ADE3-8C73C2ABCCD2}"/>
-    <hyperlink ref="R22" r:id="rId11" xr:uid="{8A1CDE39-E5F4-47FF-B3D6-2A4B92CFCBB5}"/>
+    <hyperlink ref="R2" r:id="rId1" display="https://us02web.zoom.us/j/81757243738?pwd=UXAvdEpveHlrNU05M2ZsZnRrYy9Vdz09%20ID%20da%20reunião:%20817%205724%203738%20Senha%20de%20acesso:%20954332" xr:uid="{391FFE1A-08B2-4BCD-BB6A-F57526D8E02A}"/>
+    <hyperlink ref="R3" r:id="rId2" display="https://us02web.zoom.us/j/81757243738?pwd=UXAvdEpveHlrNU05M2ZsZnRrYy9Vdz09%20ID%20DA%20REUNIÃO:%20817%205724%203738%20SENHA:%20954332" xr:uid="{C1DA3419-3739-4A67-B7C4-5F6BFFD3C42B}"/>
+    <hyperlink ref="R4" r:id="rId3" display="https://trt15-jus-br.zoom.us/j/4525285196?pwd=cG1ieCtlVVdHZERxcVRTM2lzSGt3dz09%20ID%20da%20reunião:%20452%20528%205196%20Senha%20de%20acesso:%20702632" xr:uid="{D6F64675-7755-42D4-BA67-78562CEB44F6}"/>
+    <hyperlink ref="R5" r:id="rId4" xr:uid="{DCDFC5AD-CE52-4295-9C7E-7CC6AC118734}"/>
+    <hyperlink ref="R7" r:id="rId5" xr:uid="{53D62F46-9D32-4E02-BF08-8C2B380E4D04}"/>
+    <hyperlink ref="R9" r:id="rId6" display="https://trt15-jus-br.zoom.us/j/81869084210?pwd=V0EwalRCY0V5ZFhUY0lCMEU1QVBJQT09%20ID%20da%20reunião:%20818%206908%204210%20Senha%20de%20acesso:%20306523" xr:uid="{D83AB27D-68E2-473A-8A55-8436DB81CAAE}"/>
+    <hyperlink ref="R12" r:id="rId7" display="https://trt15-jus-br.zoom.us/j/83464575337?pwd=bldja1FHQm1tcTVXaVBSazRMUlpHdz0%20ID%20da%20reunião:%20834%206457%205337%20Senha:%20835403" xr:uid="{56237511-D044-42F6-84E7-A2F3EBD911A0}"/>
+    <hyperlink ref="R15" r:id="rId8" display="https://trt15-jus-br.zoom.us/j/81792542599?%20pwd=dWt0TnU2UXVUYXdKTU1CU2gzUTVZQT09%20ID%20da%20reunião:%20817%209254%202599%20Senha:%20692443" xr:uid="{821D8902-09E5-4257-AA74-64FD77D36168}"/>
+    <hyperlink ref="R16" r:id="rId9" display="https://meet.google.com/tmx-nnyp-tmn" xr:uid="{7F36D296-8E26-4B58-91A5-6A4BC5F16EE8}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/Pauta_de_Audiencias.xlsx
+++ b/Pauta_de_Audiencias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\blu\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{63C06E1E-C725-41C3-8C62-2E541EE4A9FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{931DB7A8-D032-4F01-85F3-02334A245A59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9D782BEA-4731-472A-B1C4-FBA531634020}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0D68274D-A94B-4137-BA4F-C6EB2A6D96FA}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="188">
   <si>
     <t>Código P&amp;C</t>
   </si>
@@ -95,142 +95,514 @@
     <t>Link/Observações</t>
   </si>
   <si>
+    <t>Audiência Inicial -  Presencial</t>
+  </si>
+  <si>
+    <t>1001831-47.2026.5.02.0431</t>
+  </si>
+  <si>
+    <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
+  </si>
+  <si>
+    <t>Rodrigo Ventura Da Silva</t>
+  </si>
+  <si>
+    <t>SANTO ANDRÉ</t>
+  </si>
+  <si>
+    <t>SP</t>
+  </si>
+  <si>
+    <t>05ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>Instrução</t>
+  </si>
+  <si>
+    <t>Reclamação Trabalhista</t>
+  </si>
+  <si>
+    <t>CENTRAL</t>
+  </si>
+  <si>
+    <t>R$             184.477,10</t>
+  </si>
+  <si>
+    <t>Grupo B1</t>
+  </si>
+  <si>
+    <t>JPE</t>
+  </si>
+  <si>
+    <t>BSO</t>
+  </si>
+  <si>
+    <t>Presencial</t>
+  </si>
+  <si>
+    <t>Audiência Instrução - Presencial</t>
+  </si>
+  <si>
+    <t>0012499-18.2024.5.15.0071</t>
+  </si>
+  <si>
+    <t>Mahle Metal Leve S.A.</t>
+  </si>
+  <si>
+    <t>Artur Alberto Chieregatti Junior</t>
+  </si>
+  <si>
+    <t>MOGI GUAÇU</t>
+  </si>
+  <si>
+    <t>VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             345.912,99</t>
+  </si>
+  <si>
+    <t>Grupo E1</t>
+  </si>
+  <si>
+    <t>Correspondente - Ana Carolina Teresani</t>
+  </si>
+  <si>
+    <t>PSI</t>
+  </si>
+  <si>
     <t>Audiência Inicial -  Telepresencial</t>
   </si>
   <si>
-    <t>0011449-03.2026.5.03.0044</t>
-  </si>
-  <si>
-    <t>Syngenta Seeds Ltda.</t>
-  </si>
-  <si>
-    <t>Rafael Vidal Da Silva</t>
-  </si>
-  <si>
-    <t>UBERLÂNDIA</t>
+    <t>0000573-66.2026.5.09.0126</t>
+  </si>
+  <si>
+    <t>Companhia Act De Participações E Companhia Aix De Participações</t>
+  </si>
+  <si>
+    <t>Osnilto Teodoro Dos Santos</t>
+  </si>
+  <si>
+    <t>PALMAS</t>
+  </si>
+  <si>
+    <t>PR</t>
+  </si>
+  <si>
+    <t>R$             576.500,00</t>
+  </si>
+  <si>
+    <t>Grupo C</t>
+  </si>
+  <si>
+    <t>ECO</t>
+  </si>
+  <si>
+    <t>VSI</t>
+  </si>
+  <si>
+    <t>https://url.trt9.jus.br/as9c5 ID da Reunião: 87076063050 Senha: 8rWy03lvY1</t>
+  </si>
+  <si>
+    <t>0011080-53.2026.5.15.0083</t>
+  </si>
+  <si>
+    <t>Embraer S.A.</t>
+  </si>
+  <si>
+    <t>Leandro Borduchi</t>
+  </si>
+  <si>
+    <t>SÃO JOSÉ DOS CAMPOS</t>
+  </si>
+  <si>
+    <t>03ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             115.000,00</t>
+  </si>
+  <si>
+    <t>Grupo B2</t>
+  </si>
+  <si>
+    <t>VCR</t>
+  </si>
+  <si>
+    <t>0011089-15.2026.5.15.0083</t>
+  </si>
+  <si>
+    <t>Gilberto Anderson Pereira</t>
+  </si>
+  <si>
+    <t>R$             172.500,00</t>
+  </si>
+  <si>
+    <t>BCF</t>
+  </si>
+  <si>
+    <t>Audiência de Instrução - Semipresencial</t>
+  </si>
+  <si>
+    <t>0024705-94.2026.5.24.0022</t>
+  </si>
+  <si>
+    <t>Moema Bioenergia S.A. - Monteverde</t>
+  </si>
+  <si>
+    <t>Gabriel Florenciano Da Silva</t>
+  </si>
+  <si>
+    <t>DOURADOS</t>
+  </si>
+  <si>
+    <t>MS</t>
+  </si>
+  <si>
+    <t>02ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             245.432,47</t>
+  </si>
+  <si>
+    <t>Grupo E2</t>
+  </si>
+  <si>
+    <t>MBF</t>
+  </si>
+  <si>
+    <t>https://trt24-jus-br.zoom.us/my/trt24douvt2sala1</t>
+  </si>
+  <si>
+    <t>Audiência Una - Presencial</t>
+  </si>
+  <si>
+    <t>1000798-23.2026.5.02.0075</t>
+  </si>
+  <si>
+    <t>T4F Entretenimento S.A</t>
+  </si>
+  <si>
+    <t>Diego Monteiro Santos Prado</t>
+  </si>
+  <si>
+    <t>SÃO PAULO</t>
+  </si>
+  <si>
+    <t>75ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>1ª Instância</t>
+  </si>
+  <si>
+    <t>R$             166.195,36</t>
+  </si>
+  <si>
+    <t>Grupo B3</t>
+  </si>
+  <si>
+    <t>ANB</t>
+  </si>
+  <si>
+    <t>1001909-41.2026.5.02.0431</t>
+  </si>
+  <si>
+    <t>Antonio Idalbancir Dias Coelho</t>
+  </si>
+  <si>
+    <t>01ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             487.482,55</t>
+  </si>
+  <si>
+    <t>Correspondente - Hebert</t>
+  </si>
+  <si>
+    <t>Audiência de Instrução - Presencial</t>
+  </si>
+  <si>
+    <t>0010209-93.2025.5.15.0071</t>
+  </si>
+  <si>
+    <t>Archimedes Barbosa Siqueira</t>
+  </si>
+  <si>
+    <t>Central</t>
+  </si>
+  <si>
+    <t>R$             125.701,08</t>
+  </si>
+  <si>
+    <t>1000724-56.2026.5.02.0434</t>
+  </si>
+  <si>
+    <t>Wilson Aparecido Sant Ana</t>
+  </si>
+  <si>
+    <t>04ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$               79.500,00</t>
+  </si>
+  <si>
+    <t>GSM</t>
+  </si>
+  <si>
+    <t>0011122-47.2026.5.03.0080</t>
+  </si>
+  <si>
+    <t>Salitre Fertilizantes Ltda</t>
+  </si>
+  <si>
+    <t>Joao Paulo De Oliveira Faria</t>
+  </si>
+  <si>
+    <t>PATROCÍNIO</t>
   </si>
   <si>
     <t>MG</t>
   </si>
   <si>
-    <t>02ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>1ª Instância</t>
-  </si>
-  <si>
-    <t>Reclamação Trabalhista</t>
-  </si>
-  <si>
-    <t>CENTRAL</t>
-  </si>
-  <si>
-    <t>R$               78.008,71</t>
-  </si>
-  <si>
-    <t>Grupo E1</t>
+    <t>R$             122.727,28</t>
+  </si>
+  <si>
+    <t>CAL</t>
+  </si>
+  <si>
+    <t>https://trt3-jus-br.zoom.us/my/vt.patrocinio</t>
+  </si>
+  <si>
+    <t>1000557-62.2026.5.02.0006</t>
+  </si>
+  <si>
+    <t>Telefonica Brasil S.A.</t>
+  </si>
+  <si>
+    <t>Mario Roberto De Lima</t>
+  </si>
+  <si>
+    <t>06ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$          1.582.455,98</t>
+  </si>
+  <si>
+    <t>TFR</t>
+  </si>
+  <si>
+    <t>0011123-32.2026.5.03.0080</t>
+  </si>
+  <si>
+    <t>Matheus Finetti Zanardo</t>
+  </si>
+  <si>
+    <t>1001053-77.2026.5.02.0431</t>
+  </si>
+  <si>
+    <t>Graziele Novais Dos Santos</t>
+  </si>
+  <si>
+    <t>R$             200.175,46</t>
+  </si>
+  <si>
+    <t>RFE</t>
+  </si>
+  <si>
+    <t>1002323-73.2025.5.02.0431</t>
+  </si>
+  <si>
+    <t>Higor Dos Santos</t>
+  </si>
+  <si>
+    <t>R$             582.095,16</t>
+  </si>
+  <si>
+    <t>Audiência Instrução - Telepresencial</t>
+  </si>
+  <si>
+    <t>0010613-19.2026.5.03.0080</t>
+  </si>
+  <si>
+    <t>Salitre Fetilizantes Ltda</t>
+  </si>
+  <si>
+    <t>Maria Izabel Amorim Costa</t>
+  </si>
+  <si>
+    <t>Conhecimento</t>
+  </si>
+  <si>
+    <t>R$               34.420,70</t>
+  </si>
+  <si>
+    <t>Sessão de Julgamento TRT - Semipresencial</t>
+  </si>
+  <si>
+    <t>0011790-44.2024.5.15.0083</t>
+  </si>
+  <si>
+    <t>Kennedy Carvalho Lucas</t>
+  </si>
+  <si>
+    <t>02ª TURMA</t>
+  </si>
+  <si>
+    <t>Recursal TRT</t>
+  </si>
+  <si>
+    <t>R$             147.500,00</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/launch/jc/86986668664 ID da reunião: 869 8666 8664 Senha: 410044</t>
+  </si>
+  <si>
+    <t>Audiência Una - Telepresencial</t>
+  </si>
+  <si>
+    <t>0012495-75.2025.5.15.0093</t>
+  </si>
+  <si>
+    <t>Salitre Fertilizantes Ltda.</t>
+  </si>
+  <si>
+    <t>Eduardo Henrique Maia Carnauba</t>
+  </si>
+  <si>
+    <t>CAMPINAS</t>
+  </si>
+  <si>
+    <t>R$             596.014,50</t>
+  </si>
+  <si>
+    <t>ARC</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/81469918489?pwd=NmNHNVdhSERvZHorOXRIdmJCWU5MQT09 ID da reunião: 814 6991 8489 Senha: 059291</t>
+  </si>
+  <si>
+    <t>0010133-49.2026.5.15.0131</t>
+  </si>
+  <si>
+    <t>Alex Gomes De Sousa</t>
+  </si>
+  <si>
+    <t>12ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             179.903,44</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/86534999498?pwd=N3RZZXpkTE5laWxEREEvWjBVYVg0Zz0</t>
+  </si>
+  <si>
+    <t>0010841-17.2026.5.15.0126</t>
+  </si>
+  <si>
+    <t>Syngenta Proteção De Cultivos Ltda.</t>
+  </si>
+  <si>
+    <t>Claudinei Dos Santos</t>
+  </si>
+  <si>
+    <t>PAULÍNIA</t>
+  </si>
+  <si>
+    <t>R$               38.195,57</t>
+  </si>
+  <si>
+    <t>JPL</t>
   </si>
   <si>
     <t>GVM</t>
   </si>
   <si>
-    <t>https://trt3-jus-br.zoom.us/j/81879397512?pwd=VdlZu0aH7a5vBp2FDhtwnWTDjaiSns.1</t>
-  </si>
-  <si>
-    <t>Audiência Una - Presencial</t>
-  </si>
-  <si>
-    <t>1001319-56.2026.5.02.0466</t>
-  </si>
-  <si>
-    <t>Mahle Metal Leve S.A.</t>
-  </si>
-  <si>
-    <t>Everton Aparecido Dos Santos</t>
-  </si>
-  <si>
-    <t>SÃO BERNARDO DO CAMPO</t>
-  </si>
-  <si>
-    <t>SP</t>
-  </si>
-  <si>
-    <t>06ª VARA DO TRABALHO</t>
+    <t>https://trt15-jus-br.zoom.us/j/83059104477?pwd=h7VDkteaYgzZ4FIU9CoepcQo5ErUHA.1 ID da reunião: 830 5910 4477 Senha: 005974</t>
+  </si>
+  <si>
+    <t>0012011-90.2025.5.15.0083</t>
+  </si>
+  <si>
+    <t>Maria Fernanda Vila Nova Marson Schuller</t>
   </si>
   <si>
     <t>Inicial</t>
   </si>
   <si>
-    <t>R$               64.827,60</t>
-  </si>
-  <si>
-    <t>Correspondente - Carlos Florian</t>
-  </si>
-  <si>
-    <t>TLI</t>
-  </si>
-  <si>
-    <t>Presencial | Advogada - Dra. Luciana França, (11) 96351-8524</t>
-  </si>
-  <si>
-    <t>Audiência Inicial -  Presencial</t>
-  </si>
-  <si>
-    <t>1001656-47.2026.5.02.0433</t>
-  </si>
-  <si>
-    <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
-  </si>
-  <si>
-    <t>Marcos Rogerio Romero</t>
-  </si>
-  <si>
-    <t>SANTO ANDRÉ</t>
-  </si>
-  <si>
-    <t>03ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>Instrução</t>
-  </si>
-  <si>
-    <t>R$          1.346.621,89</t>
-  </si>
-  <si>
-    <t>Grupo B1</t>
-  </si>
-  <si>
-    <t>Correspondente - Hebert</t>
-  </si>
-  <si>
-    <t>GSM</t>
-  </si>
-  <si>
-    <t>Presencial</t>
-  </si>
-  <si>
-    <t>1001394-66.2026.5.02.0411</t>
-  </si>
-  <si>
-    <t>Companhia Brasileira De Cartuchos</t>
-  </si>
-  <si>
-    <t>Luciano Rodrigues Da Costa</t>
-  </si>
-  <si>
-    <t>RIBEIRÃO PIRES</t>
-  </si>
-  <si>
-    <t>VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$               31.230,99</t>
-  </si>
-  <si>
-    <t>Grupo B3</t>
-  </si>
-  <si>
-    <t>LMI</t>
+    <t>R$             149.105,07</t>
+  </si>
+  <si>
+    <t>0011989-36.2024.5.15.0093</t>
+  </si>
+  <si>
+    <t>Gregory Ragosta Cassiano De Souza</t>
+  </si>
+  <si>
+    <t>05ª TURMA</t>
+  </si>
+  <si>
+    <t>Recursal</t>
+  </si>
+  <si>
+    <t>R$          1.066.473,00</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/88116222157?pwd=oFe1QBH0rStbUhO7ngHqYzIDE9abay.1</t>
+  </si>
+  <si>
+    <t>0010618-84.2026.5.15.0087</t>
+  </si>
+  <si>
+    <t>Rogerio Cordeiro</t>
+  </si>
+  <si>
+    <t>R$          1.150.491,32</t>
+  </si>
+  <si>
+    <t>JRM</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/81792542599?pwd=dWt0TnU2UXVUYXdKTU1CU2gzUTVZQT09 ID da reunião: 817 9254 2599 Senha: 692443</t>
+  </si>
+  <si>
+    <t>0001673-47.2025.5.09.0011</t>
+  </si>
+  <si>
+    <t>Jose Aparecido Dos Santos Wermer</t>
+  </si>
+  <si>
+    <t>CURITIBA</t>
+  </si>
+  <si>
+    <t>11ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             303.594,35</t>
+  </si>
+  <si>
+    <t>RCF</t>
+  </si>
+  <si>
+    <t>1000994-20.2025.5.02.0433</t>
+  </si>
+  <si>
+    <t>Sidinei De Souza Oliveira</t>
+  </si>
+  <si>
+    <t>R$             400.000,00</t>
+  </si>
+  <si>
+    <t>0012474-76.2025.5.15.0133</t>
+  </si>
+  <si>
+    <t>Marcelo Luiz Teixeira</t>
+  </si>
+  <si>
+    <t>SÃO JOSÉ DO RIO PRETO</t>
+  </si>
+  <si>
+    <t>Produção Antecipada de Prova</t>
+  </si>
+  <si>
+    <t>R$                    500,00</t>
   </si>
 </sst>
 </file>
@@ -708,8 +1080,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{687A6575-026E-42C4-A52B-49D3364B11A4}">
-  <dimension ref="A1:R5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49ED9DFC-A4C8-407F-936A-93E44AF2209F}">
+  <dimension ref="A1:R27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:18" ht="60" x14ac:dyDescent="0.3">
@@ -768,12 +1140,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="144.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4">
-        <v>105829</v>
+        <v>106140</v>
       </c>
       <c r="B2" s="5">
-        <v>46304</v>
+        <v>46308</v>
       </c>
       <c r="C2" s="6">
         <v>0.375</v>
@@ -818,45 +1190,45 @@
         <v>30</v>
       </c>
       <c r="Q2" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="R2" s="8" t="s">
         <v>31</v>
       </c>
+      <c r="R2" s="7" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="3" spans="1:18" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4">
-        <v>105792</v>
+        <v>99850</v>
       </c>
       <c r="B3" s="5">
-        <v>46304</v>
+        <v>46308</v>
       </c>
       <c r="C3" s="6">
-        <v>0.44791666666666669</v>
+        <v>0.375</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="J3" s="7" t="s">
         <v>38</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="L3" s="7" t="s">
         <v>26</v>
@@ -865,10 +1237,10 @@
         <v>27</v>
       </c>
       <c r="N3" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="O3" s="7" t="s">
         <v>40</v>
-      </c>
-      <c r="O3" s="7" t="s">
-        <v>29</v>
       </c>
       <c r="P3" s="7" t="s">
         <v>41</v>
@@ -877,42 +1249,42 @@
         <v>42</v>
       </c>
       <c r="R3" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="144.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="4">
+        <v>105023</v>
+      </c>
+      <c r="B4" s="5">
+        <v>46308</v>
+      </c>
+      <c r="C4" s="6">
+        <v>0.375</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="4" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="4">
-        <v>106139</v>
-      </c>
-      <c r="B4" s="5">
-        <v>46304</v>
-      </c>
-      <c r="C4" s="6">
-        <v>0.49305555555555558</v>
-      </c>
-      <c r="D4" s="7" t="s">
+      <c r="E4" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="F4" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="G4" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="H4" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="I4" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="I4" s="7" t="s">
-        <v>37</v>
-      </c>
       <c r="J4" s="7" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="L4" s="7" t="s">
         <v>26</v>
@@ -921,54 +1293,54 @@
         <v>27</v>
       </c>
       <c r="N4" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="O4" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="P4" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="O4" s="7" t="s">
+      <c r="Q4" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="P4" s="7" t="s">
+      <c r="R4" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="Q4" s="7" t="s">
+    </row>
+    <row r="5" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="4">
+        <v>105032</v>
+      </c>
+      <c r="B5" s="5">
+        <v>46308</v>
+      </c>
+      <c r="C5" s="6">
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="R4" s="7" t="s">
+      <c r="F5" s="7" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="5" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="4">
-        <v>106211</v>
-      </c>
-      <c r="B5" s="5">
-        <v>46304</v>
-      </c>
-      <c r="C5" s="6">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" s="7" t="s">
+      <c r="G5" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="H5" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="I5" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J5" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="H5" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>60</v>
-      </c>
       <c r="K5" s="7" t="s">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="L5" s="7" t="s">
         <v>26</v>
@@ -977,24 +1349,1267 @@
         <v>27</v>
       </c>
       <c r="N5" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="O5" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="P5" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="O5" s="7" t="s">
+      <c r="Q5" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="R5" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="4">
+        <v>105033</v>
+      </c>
+      <c r="B6" s="5">
+        <v>46308</v>
+      </c>
+      <c r="C6" s="6">
+        <v>0.3923611111111111</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="P5" s="7" t="s">
+      <c r="F6" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="G6" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="Q5" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="R5" s="7" t="s">
+      <c r="H6" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M6" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N6" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="O6" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="P6" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q6" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="R6" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="87" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="4">
+        <v>104774</v>
+      </c>
+      <c r="B7" s="5">
+        <v>46308</v>
+      </c>
+      <c r="C7" s="6">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M7" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N7" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="O7" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="P7" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q7" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="R7" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="4">
+        <v>105223</v>
+      </c>
+      <c r="B8" s="5">
+        <v>46308</v>
+      </c>
+      <c r="C8" s="6">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M8" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N8" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="O8" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="P8" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q8" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="R8" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="4">
+        <v>106263</v>
+      </c>
+      <c r="B9" s="5">
+        <v>46308</v>
+      </c>
+      <c r="C9" s="6">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M9" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N9" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="O9" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P9" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q9" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="R9" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="4">
+        <v>99950</v>
+      </c>
+      <c r="B10" s="5">
+        <v>46308</v>
+      </c>
+      <c r="C10" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L10" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M10" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="N10" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="O10" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="P10" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q10" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="R10" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="4">
+        <v>104771</v>
+      </c>
+      <c r="B11" s="5">
+        <v>46308</v>
+      </c>
+      <c r="C11" s="6">
+        <v>0.4201388888888889</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M11" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N11" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="O11" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P11" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q11" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="R11" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="87" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="4">
+        <v>106063</v>
+      </c>
+      <c r="B12" s="5">
+        <v>46308</v>
+      </c>
+      <c r="C12" s="6">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L12" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M12" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N12" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="O12" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="P12" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q12" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="R12" s="8" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="4">
+        <v>104667</v>
+      </c>
+      <c r="B13" s="5">
+        <v>46308</v>
+      </c>
+      <c r="C13" s="6">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J13" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L13" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M13" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N13" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="O13" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="P13" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q13" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="R13" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="87" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="4">
+        <v>106100</v>
+      </c>
+      <c r="B14" s="5">
+        <v>46308</v>
+      </c>
+      <c r="C14" s="6">
+        <v>0.43055555555555558</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="J14" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L14" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M14" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N14" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="O14" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="P14" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q14" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="R14" s="8" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="4">
+        <v>105182</v>
+      </c>
+      <c r="B15" s="5">
+        <v>46308</v>
+      </c>
+      <c r="C15" s="6">
+        <v>0.47222222222222221</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J15" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L15" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M15" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N15" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="O15" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P15" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q15" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="R15" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="4">
+        <v>103551</v>
+      </c>
+      <c r="B16" s="5">
+        <v>46308</v>
+      </c>
+      <c r="C16" s="6">
+        <v>0.4861111111111111</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J16" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="K16" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L16" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M16" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N16" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="O16" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P16" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q16" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="R16" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="87" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="4">
+        <v>105174</v>
+      </c>
+      <c r="B17" s="5">
+        <v>46308</v>
+      </c>
+      <c r="C17" s="6">
+        <v>0.5625</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="J17" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="L17" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M17" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N17" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="O17" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="P17" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q17" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="R17" s="8" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="173.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="4">
+        <v>98816</v>
+      </c>
+      <c r="B18" s="5">
+        <v>46308</v>
+      </c>
+      <c r="C18" s="6">
+        <v>0.5625</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="F18" s="7" t="s">
         <v>55</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="I18" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J18" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="L18" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M18" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N18" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="O18" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="P18" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q18" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="R18" s="8" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" ht="231" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="4">
+        <v>103490</v>
+      </c>
+      <c r="B19" s="5">
+        <v>46308</v>
+      </c>
+      <c r="C19" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L19" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M19" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N19" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="O19" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="P19" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q19" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="R19" s="8" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" ht="144.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="4">
+        <v>103858</v>
+      </c>
+      <c r="B20" s="5">
+        <v>46308</v>
+      </c>
+      <c r="C20" s="6">
+        <v>0.59722222222222221</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="I20" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J20" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L20" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M20" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N20" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="O20" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P20" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q20" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="R20" s="8" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" ht="231" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="4">
+        <v>105111</v>
+      </c>
+      <c r="B21" s="5">
+        <v>46308</v>
+      </c>
+      <c r="C21" s="6">
+        <v>0.59722222222222221</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="K21" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="L21" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M21" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N21" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="O21" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="P21" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q21" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="R21" s="8" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="4">
+        <v>102063</v>
+      </c>
+      <c r="B22" s="5">
+        <v>46308</v>
+      </c>
+      <c r="C22" s="6">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="I22" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J22" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="K22" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="L22" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M22" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N22" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="O22" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="P22" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q22" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="R22" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" ht="144.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="4">
+        <v>104088</v>
+      </c>
+      <c r="B23" s="5">
+        <v>46308</v>
+      </c>
+      <c r="C23" s="6">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="I23" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J23" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="K23" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="L23" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M23" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N23" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="O23" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="P23" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q23" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="R23" s="8" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" ht="231" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="4">
+        <v>104804</v>
+      </c>
+      <c r="B24" s="5">
+        <v>46308</v>
+      </c>
+      <c r="C24" s="6">
+        <v>0.61805555555555558</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="I24" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J24" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="L24" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M24" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N24" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="O24" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="P24" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q24" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="R24" s="8" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" ht="96.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="4">
+        <v>103582</v>
+      </c>
+      <c r="B25" s="5">
+        <v>46308</v>
+      </c>
+      <c r="C25" s="6">
+        <v>0.625</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="I25" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="J25" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="K25" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="L25" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M25" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N25" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="O25" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="P25" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q25" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="R25" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="4">
+        <v>101364</v>
+      </c>
+      <c r="B26" s="5">
+        <v>46308</v>
+      </c>
+      <c r="C26" s="6">
+        <v>0.63888888888888884</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I26" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J26" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="K26" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L26" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M26" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N26" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="O26" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P26" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q26" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="R26" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" ht="173.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="4">
+        <v>104114</v>
+      </c>
+      <c r="B27" s="5">
+        <v>46308</v>
+      </c>
+      <c r="C27" s="6">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="I27" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J27" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="K27" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="L27" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="M27" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N27" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="O27" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="P27" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q27" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="R27" s="8" t="s">
+        <v>137</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="R2" r:id="rId1" xr:uid="{C89B7E5D-4D81-4675-BD34-71D697924965}"/>
+    <hyperlink ref="R4" r:id="rId1" xr:uid="{310473BB-B8CD-4DD8-8B8D-401BBE0BFB8D}"/>
+    <hyperlink ref="R7" r:id="rId2" xr:uid="{ADC369A2-DDBB-427A-8792-139A5490DAEB}"/>
+    <hyperlink ref="R12" r:id="rId3" xr:uid="{F5A0AD32-BCCB-4E63-97FF-CEEEA8E86AAB}"/>
+    <hyperlink ref="R14" r:id="rId4" xr:uid="{7C10BA1F-B68E-4AFB-8778-6CC1142B93A2}"/>
+    <hyperlink ref="R17" r:id="rId5" xr:uid="{96BB691E-FBB2-4A4D-8513-4B1CF0268199}"/>
+    <hyperlink ref="R18" r:id="rId6" xr:uid="{1B78F597-5AE0-4860-A993-4CEB4BF32486}"/>
+    <hyperlink ref="R19" r:id="rId7" display="https://trt15-jus-br.zoom.us/j/81469918489?pwd=NmNHNVdhSERvZHorOXRIdmJCWU5MQT09%20ID%20da%20reunião:%20814%206991%208489%20Senha:%20059291" xr:uid="{54D7A758-1309-469C-B422-56A798998E2F}"/>
+    <hyperlink ref="R20" r:id="rId8" xr:uid="{A9451B6D-1FCD-4B0B-94BB-C1F1BD247588}"/>
+    <hyperlink ref="R21" r:id="rId9" display="https://trt15-jus-br.zoom.us/j/83059104477?pwd=h7VDkteaYgzZ4FIU9CoepcQo5ErUHA.1%20ID%20da%20reunião:%20830%205910%204477%20Senha:%20005974" xr:uid="{9A116859-DC0B-4508-A064-B9E8DFF3843D}"/>
+    <hyperlink ref="R23" r:id="rId10" xr:uid="{4CB3E34E-FC69-47E4-BCF5-7FE5E6492AD6}"/>
+    <hyperlink ref="R24" r:id="rId11" display="https://trt15-jus-br.zoom.us/j/81792542599?pwd=dWt0TnU2UXVUYXdKTU1CU2gzUTVZQT09%20ID%20da%20reunião:%20817%209254%202599%20Senha:%20692443" xr:uid="{59384DEE-FAC9-4D0C-B7ED-78FE9ABEF94D}"/>
+    <hyperlink ref="R27" r:id="rId12" xr:uid="{40C6B6EB-5908-4C50-8E3D-9AC500DFFA27}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/Pauta_de_Audiencias.xlsx
+++ b/Pauta_de_Audiencias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\blu\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{931DB7A8-D032-4F01-85F3-02334A245A59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{45815E3B-F138-4721-B61D-892D22D06F2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0D68274D-A94B-4137-BA4F-C6EB2A6D96FA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3CB4E181-A3C7-4A68-81AE-A573CE9FE004}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="227">
   <si>
     <t>Código P&amp;C</t>
   </si>
@@ -95,514 +95,631 @@
     <t>Link/Observações</t>
   </si>
   <si>
+    <t>Audiência de Conciliação - Telepresencial</t>
+  </si>
+  <si>
+    <t>0010728-44.2023.5.15.0037</t>
+  </si>
+  <si>
+    <t>Ouroeste Bioenergia Ltda.</t>
+  </si>
+  <si>
+    <t>Grazielly Olivia Venancio</t>
+  </si>
+  <si>
+    <t>FERNANDÓPOLIS</t>
+  </si>
+  <si>
+    <t>SP</t>
+  </si>
+  <si>
+    <t>CEJUSC</t>
+  </si>
+  <si>
+    <t>Liquidação</t>
+  </si>
+  <si>
+    <t>Reclamação Trabalhista</t>
+  </si>
+  <si>
+    <t>CENTRAL</t>
+  </si>
+  <si>
+    <t>R$             333.194,18</t>
+  </si>
+  <si>
+    <t>Grupo E2</t>
+  </si>
+  <si>
+    <t>CAL</t>
+  </si>
+  <si>
+    <t>LWP</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/88415253122?pwd=QzlTNmxwdWpEeGVFZmdwM0lDUFJ4Zz09 ID da reunião: 884 1525 3122 Senha de acesso: 510562</t>
+  </si>
+  <si>
+    <t>Audiência Inicial - Telepresencial</t>
+  </si>
+  <si>
+    <t>0010947-07.2026.5.03.0063</t>
+  </si>
+  <si>
+    <t>Syngenta Seeds Ltda</t>
+  </si>
+  <si>
+    <t>Cleiton Baltazar De Souza</t>
+  </si>
+  <si>
+    <t>ITUIUTABA</t>
+  </si>
+  <si>
+    <t>MG</t>
+  </si>
+  <si>
+    <t>01ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>Instrução</t>
+  </si>
+  <si>
+    <t>R$               39.600,00</t>
+  </si>
+  <si>
+    <t>Grupo E1</t>
+  </si>
+  <si>
+    <t>JRM</t>
+  </si>
+  <si>
+    <t>https://trt3-jus-br.zoom.us/j/85042016732</t>
+  </si>
+  <si>
     <t>Audiência Inicial -  Presencial</t>
   </si>
   <si>
-    <t>1001831-47.2026.5.02.0431</t>
+    <t>1001918-91.2026.5.02.0434</t>
   </si>
   <si>
     <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
   </si>
   <si>
-    <t>Rodrigo Ventura Da Silva</t>
+    <t>Erik Da Silva Prado</t>
   </si>
   <si>
     <t>SANTO ANDRÉ</t>
   </si>
   <si>
-    <t>SP</t>
-  </si>
-  <si>
-    <t>05ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>Instrução</t>
-  </si>
-  <si>
-    <t>Reclamação Trabalhista</t>
-  </si>
-  <si>
-    <t>CENTRAL</t>
-  </si>
-  <si>
-    <t>R$             184.477,10</t>
+    <t>04ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             272.182,03</t>
   </si>
   <si>
     <t>Grupo B1</t>
   </si>
   <si>
+    <t>Correspondente - Hebert</t>
+  </si>
+  <si>
+    <t>GSM</t>
+  </si>
+  <si>
+    <t>Presencial</t>
+  </si>
+  <si>
+    <t>Audiência Inicial -  Telepresencial</t>
+  </si>
+  <si>
+    <t>0010948-89.2026.5.03.0063</t>
+  </si>
+  <si>
+    <t>Luis Claudio Da Silva</t>
+  </si>
+  <si>
+    <t>R$             170.500,00</t>
+  </si>
+  <si>
+    <t>Sessão de Julgamento TST - Presencial</t>
+  </si>
+  <si>
+    <t>1001280-40.2022.5.02.0065</t>
+  </si>
+  <si>
+    <t>Telefonica Brasil S.A.</t>
+  </si>
+  <si>
+    <t>Silvio Luiz Rocca Ribeiro</t>
+  </si>
+  <si>
+    <t>SÃO PAULO</t>
+  </si>
+  <si>
+    <t>01ª TURMA</t>
+  </si>
+  <si>
+    <t>Recursal</t>
+  </si>
+  <si>
+    <t>R$          2.512.192,00</t>
+  </si>
+  <si>
+    <t>Grupo C</t>
+  </si>
+  <si>
+    <t>TFR</t>
+  </si>
+  <si>
+    <t>https://tst-jus-br.zoom.us/my/setr1</t>
+  </si>
+  <si>
+    <t>Audiência Instrução - Telepresencial</t>
+  </si>
+  <si>
+    <t>0011423-72.2025.5.15.0119</t>
+  </si>
+  <si>
+    <t>Pilkington Brasil Ltda.</t>
+  </si>
+  <si>
+    <t>Richard Lopes Da Silva</t>
+  </si>
+  <si>
+    <t>CAÇAPAVA</t>
+  </si>
+  <si>
+    <t>VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$               56.759,19</t>
+  </si>
+  <si>
+    <t>MBF</t>
+  </si>
+  <si>
+    <t>ARC</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/86212862282?pwd=N2N4b3NobCtXbUxsODdmSXFlMjVCQT09 ID da reunião: 862 1286 2282 Senha: 498067</t>
+  </si>
+  <si>
+    <t>Sessão de Julgamento TRT - Presencial</t>
+  </si>
+  <si>
+    <t>0025858-49.2025.5.24.0071</t>
+  </si>
+  <si>
+    <t>Rio Paraná Energia S.A.</t>
+  </si>
+  <si>
+    <t>Orlando Homma De Souza</t>
+  </si>
+  <si>
+    <t>TRÊS LAGOAS</t>
+  </si>
+  <si>
+    <t>MS</t>
+  </si>
+  <si>
+    <t>02ª TURMA</t>
+  </si>
+  <si>
+    <t>R$               38.605,50</t>
+  </si>
+  <si>
+    <t>ECO</t>
+  </si>
+  <si>
+    <t>https://trt24-jus-br.zoom.us/j/84024327508?pwd=v3IAXTUTZyGmecL3g15WRYMaB8ufTj.1</t>
+  </si>
+  <si>
+    <t>Audiência Instrução - Presencial</t>
+  </si>
+  <si>
+    <t>1000470-81.2026.5.02.0467</t>
+  </si>
+  <si>
+    <t>Mahle Metal Leve S.A.</t>
+  </si>
+  <si>
+    <t>Nelson Luis Ribeiro</t>
+  </si>
+  <si>
+    <t>SÃO BERNARDO DO CAMPO</t>
+  </si>
+  <si>
+    <t>07ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             119.733,98</t>
+  </si>
+  <si>
+    <t>Correspondente - Carlos Florian</t>
+  </si>
+  <si>
+    <t>VRO</t>
+  </si>
+  <si>
+    <t>Presencial | Advogada - Dra. Luciana França, (11) 96351-8524</t>
+  </si>
+  <si>
+    <t>0011832-75.2026.5.15.0131</t>
+  </si>
+  <si>
+    <t>Marcelo Jacome Da Costa</t>
+  </si>
+  <si>
+    <t>CAMPINAS</t>
+  </si>
+  <si>
+    <t>12ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$               87.970,55</t>
+  </si>
+  <si>
+    <t>BSO</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/85453506049?pwd=Q0lIZFc3eS9kaGNJQ3N0cEIxdnBnZz09 ID da reunião: 854 5350 6049 Senha de acesso: 364 591</t>
+  </si>
+  <si>
+    <t>Audiência Una - Presencial</t>
+  </si>
+  <si>
+    <t>1001356-43.2026.5.02.0059</t>
+  </si>
+  <si>
+    <t>Pedro Afonso Bioenergia Ltda</t>
+  </si>
+  <si>
+    <t>Lucas Villaca Ferreira De Oliveira</t>
+  </si>
+  <si>
+    <t>59ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>Conhecimento</t>
+  </si>
+  <si>
+    <t>R$             122.575,93</t>
+  </si>
+  <si>
+    <t>BBO</t>
+  </si>
+  <si>
+    <t>1001581-08.2026.5.02.0433</t>
+  </si>
+  <si>
+    <t>Alex Dos Santos Silva</t>
+  </si>
+  <si>
+    <t>03ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$               59.798,31</t>
+  </si>
+  <si>
     <t>JPE</t>
   </si>
   <si>
-    <t>BSO</t>
-  </si>
-  <si>
-    <t>Presencial</t>
-  </si>
-  <si>
-    <t>Audiência Instrução - Presencial</t>
-  </si>
-  <si>
-    <t>0012499-18.2024.5.15.0071</t>
-  </si>
-  <si>
-    <t>Mahle Metal Leve S.A.</t>
-  </si>
-  <si>
-    <t>Artur Alberto Chieregatti Junior</t>
-  </si>
-  <si>
-    <t>MOGI GUAÇU</t>
-  </si>
-  <si>
-    <t>VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$             345.912,99</t>
-  </si>
-  <si>
-    <t>Grupo E1</t>
-  </si>
-  <si>
-    <t>Correspondente - Ana Carolina Teresani</t>
-  </si>
-  <si>
-    <t>PSI</t>
-  </si>
-  <si>
-    <t>Audiência Inicial -  Telepresencial</t>
-  </si>
-  <si>
-    <t>0000573-66.2026.5.09.0126</t>
+    <t>TAM</t>
+  </si>
+  <si>
+    <t>0000919-74.2025.5.05.0122</t>
+  </si>
+  <si>
+    <t>Salitre Fertilizantes Ltda.</t>
+  </si>
+  <si>
+    <t>Eduardo Ferreira Brito</t>
+  </si>
+  <si>
+    <t>CANDEIAS</t>
+  </si>
+  <si>
+    <t>BA</t>
+  </si>
+  <si>
+    <t>R$               26.714,27</t>
+  </si>
+  <si>
+    <t>https://trt5-jus-br.zoom.us/j/81333809109?pwd=47akSzaeNwYTr7VDOZiMN5qQCeHjkO.1 ID da reunião: 813 3380 9109 Senha de acesso: 470307</t>
+  </si>
+  <si>
+    <t>0010500-04.2018.5.15.0083</t>
+  </si>
+  <si>
+    <t>Embraer S.A.</t>
+  </si>
+  <si>
+    <t>Alexandre Aparecido De Oliveira</t>
+  </si>
+  <si>
+    <t>SÃO JOSÉ DOS CAMPOS</t>
+  </si>
+  <si>
+    <t>CEJUSC TST</t>
+  </si>
+  <si>
+    <t>Recursal TST</t>
+  </si>
+  <si>
+    <t>R$               40.000,00</t>
+  </si>
+  <si>
+    <t>Grupo B2</t>
+  </si>
+  <si>
+    <t>VCR</t>
+  </si>
+  <si>
+    <t>bit.ly/Cejusc2026</t>
+  </si>
+  <si>
+    <t>1001410-24.2025.5.02.0421</t>
+  </si>
+  <si>
+    <t>3Corp Technology Infraestrutura De Telecom Ltda.</t>
+  </si>
+  <si>
+    <t>Guilherme Arnaldo Da Silva Tomaz</t>
+  </si>
+  <si>
+    <t>SANTANA DE PARNAÍBA</t>
+  </si>
+  <si>
+    <t>R$             142.871,81</t>
+  </si>
+  <si>
+    <t>Grupo A2</t>
+  </si>
+  <si>
+    <t>NBG</t>
+  </si>
+  <si>
+    <t>Audiência de Instrução - Presencial</t>
+  </si>
+  <si>
+    <t>0010950-84.2025.5.15.0152</t>
+  </si>
+  <si>
+    <t>Sistenge Construções E Comércio Ltda.</t>
+  </si>
+  <si>
+    <t>Angelo Roberto Soares Alves</t>
+  </si>
+  <si>
+    <t>HORTOLÂNDIA</t>
+  </si>
+  <si>
+    <t>R$               12.065,80</t>
+  </si>
+  <si>
+    <t>RYL</t>
+  </si>
+  <si>
+    <t>1000533-11.2026.5.02.0434</t>
+  </si>
+  <si>
+    <t>Valmir Eleodorio Da Silva</t>
+  </si>
+  <si>
+    <t>R$             126.726,60</t>
+  </si>
+  <si>
+    <t>0010123-63.2026.5.03.0058</t>
+  </si>
+  <si>
+    <t>Fertilizantes Heringer S.A.</t>
+  </si>
+  <si>
+    <t>Nei Ponciano</t>
+  </si>
+  <si>
+    <t>FORMIGA</t>
+  </si>
+  <si>
+    <t>R$             439.815,20</t>
+  </si>
+  <si>
+    <t>https://trt3-jus-br.zoom.us/my/vt1formiga</t>
+  </si>
+  <si>
+    <t>1000973-20.2026.5.02.0462</t>
+  </si>
+  <si>
+    <t>Sonia Soares Almeida</t>
+  </si>
+  <si>
+    <t>02ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             191.275,42</t>
+  </si>
+  <si>
+    <t>TLI</t>
+  </si>
+  <si>
+    <t>0010841-91.2026.5.03.0080</t>
+  </si>
+  <si>
+    <t>Juliano Roberto Ferreira</t>
+  </si>
+  <si>
+    <t>PATROCÍNIO</t>
+  </si>
+  <si>
+    <t>R$          1.218.035,77</t>
+  </si>
+  <si>
+    <t>https://trt3-jus-br.zoom.us/my/vt.patrocinio</t>
+  </si>
+  <si>
+    <t>0000687-77.2025.5.12.0054</t>
+  </si>
+  <si>
+    <t>Wickbold &amp; Nosso Pão Indústrias Alimentícias Ltda</t>
+  </si>
+  <si>
+    <t>Jailson Cardoso</t>
+  </si>
+  <si>
+    <t>03ª TURMA</t>
+  </si>
+  <si>
+    <t>Recursal TRT</t>
+  </si>
+  <si>
+    <t>R$             474.999,97</t>
+  </si>
+  <si>
+    <t>Grupo B3</t>
+  </si>
+  <si>
+    <t>link pendente</t>
+  </si>
+  <si>
+    <t>0011127-48.2025.5.15.0152</t>
+  </si>
+  <si>
+    <t>Dell Computadores Do Brasil Ltda</t>
+  </si>
+  <si>
+    <t>Izabela Macena Serrano</t>
+  </si>
+  <si>
+    <t>R$                 4.092,39</t>
+  </si>
+  <si>
+    <t>AAP</t>
+  </si>
+  <si>
+    <t>JPL</t>
+  </si>
+  <si>
+    <t>0000787-46.2026.5.23.0036</t>
+  </si>
+  <si>
+    <t>Inpasa Agroindustrial S/A.</t>
+  </si>
+  <si>
+    <t>Washington Luis Arruda Ribeiro</t>
+  </si>
+  <si>
+    <t>SINOP</t>
+  </si>
+  <si>
+    <t>MT</t>
+  </si>
+  <si>
+    <t>R$             327.566,94</t>
+  </si>
+  <si>
+    <t>BTF</t>
+  </si>
+  <si>
+    <t>https://trt23-jus-br.zoom.us/j/81753761549?pwd=NYkhI185ab9wC4FuLVDoNH2aVuBPb3.1 ID da reunião: 817 5376 1549 Senha: @VTSinop1</t>
+  </si>
+  <si>
+    <t>0000008-81.2026.5.09.0133</t>
   </si>
   <si>
     <t>Companhia Act De Participações E Companhia Aix De Participações</t>
   </si>
   <si>
-    <t>Osnilto Teodoro Dos Santos</t>
-  </si>
-  <si>
-    <t>PALMAS</t>
+    <t>Marcelo Aparecido Ramos</t>
+  </si>
+  <si>
+    <t>APUCARANA</t>
   </si>
   <si>
     <t>PR</t>
   </si>
   <si>
-    <t>R$             576.500,00</t>
-  </si>
-  <si>
-    <t>Grupo C</t>
-  </si>
-  <si>
-    <t>ECO</t>
+    <t>06ª TURMA</t>
+  </si>
+  <si>
+    <t>R$               60.000,00</t>
+  </si>
+  <si>
+    <t>RCF</t>
   </si>
   <si>
     <t>VSI</t>
   </si>
   <si>
-    <t>https://url.trt9.jus.br/as9c5 ID da Reunião: 87076063050 Senha: 8rWy03lvY1</t>
-  </si>
-  <si>
-    <t>0011080-53.2026.5.15.0083</t>
-  </si>
-  <si>
-    <t>Embraer S.A.</t>
-  </si>
-  <si>
-    <t>Leandro Borduchi</t>
-  </si>
-  <si>
-    <t>SÃO JOSÉ DOS CAMPOS</t>
-  </si>
-  <si>
-    <t>03ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$             115.000,00</t>
-  </si>
-  <si>
-    <t>Grupo B2</t>
-  </si>
-  <si>
-    <t>VCR</t>
-  </si>
-  <si>
-    <t>0011089-15.2026.5.15.0083</t>
-  </si>
-  <si>
-    <t>Gilberto Anderson Pereira</t>
-  </si>
-  <si>
-    <t>R$             172.500,00</t>
-  </si>
-  <si>
-    <t>BCF</t>
-  </si>
-  <si>
-    <t>Audiência de Instrução - Semipresencial</t>
-  </si>
-  <si>
-    <t>0024705-94.2026.5.24.0022</t>
-  </si>
-  <si>
-    <t>Moema Bioenergia S.A. - Monteverde</t>
-  </si>
-  <si>
-    <t>Gabriel Florenciano Da Silva</t>
-  </si>
-  <si>
-    <t>DOURADOS</t>
-  </si>
-  <si>
-    <t>MS</t>
-  </si>
-  <si>
-    <t>02ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$             245.432,47</t>
-  </si>
-  <si>
-    <t>Grupo E2</t>
-  </si>
-  <si>
-    <t>MBF</t>
-  </si>
-  <si>
-    <t>https://trt24-jus-br.zoom.us/my/trt24douvt2sala1</t>
-  </si>
-  <si>
-    <t>Audiência Una - Presencial</t>
-  </si>
-  <si>
-    <t>1000798-23.2026.5.02.0075</t>
-  </si>
-  <si>
-    <t>T4F Entretenimento S.A</t>
-  </si>
-  <si>
-    <t>Diego Monteiro Santos Prado</t>
-  </si>
-  <si>
-    <t>SÃO PAULO</t>
-  </si>
-  <si>
-    <t>75ª VARA DO TRABALHO</t>
+    <t>https://trt9-jus-br.zoom.us/j/82898229693?pwd=WFk5UElWZGpDYjR0a1hTa2xwSHNjdz09 ID reunião : 828 9822 9693 Senha de acesso: 434474</t>
+  </si>
+  <si>
+    <t>0011501-63.2026.5.15.0044</t>
+  </si>
+  <si>
+    <t>Moema Bioenergia S.A. - Moema</t>
+  </si>
+  <si>
+    <t>Luciano Da Silva Duarte</t>
+  </si>
+  <si>
+    <t>SÃO JOSÉ DO RIO PRETO</t>
+  </si>
+  <si>
+    <t>R$             790.758,96</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/88542672682?pwd=7pQ4QRhZmRG9RAQAWKowymbwNawa7t.1 ID da reunião: 885 4267 2682 Senha de acesso: 050728</t>
+  </si>
+  <si>
+    <t>0011702-56.2025.5.15.0152</t>
+  </si>
+  <si>
+    <t>Dell Computadores Do Brasil Ltda.</t>
+  </si>
+  <si>
+    <t>Gabriela Bueno Constantino</t>
+  </si>
+  <si>
+    <t>R$             102.584,06</t>
+  </si>
+  <si>
+    <t>0010649-96.2026.5.15.0025</t>
+  </si>
+  <si>
+    <t>Cesar Roberto De Souza Neto</t>
+  </si>
+  <si>
+    <t>BOTUCATU</t>
+  </si>
+  <si>
+    <t>R$             190.723,91</t>
+  </si>
+  <si>
+    <t>ANB</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/87539096808?pwd=ZG9OblpFcVRDVnFiNUdrZEdkazkzQT09</t>
+  </si>
+  <si>
+    <t>0011533-70.2025.5.15.0087</t>
+  </si>
+  <si>
+    <t>Syngenta Proteção De Cultivos Ltda.</t>
+  </si>
+  <si>
+    <t>Angelo Marcos De Oliveira</t>
+  </si>
+  <si>
+    <t>PAULÍNIA</t>
   </si>
   <si>
     <t>1ª Instância</t>
   </si>
   <si>
-    <t>R$             166.195,36</t>
-  </si>
-  <si>
-    <t>Grupo B3</t>
-  </si>
-  <si>
-    <t>ANB</t>
-  </si>
-  <si>
-    <t>1001909-41.2026.5.02.0431</t>
-  </si>
-  <si>
-    <t>Antonio Idalbancir Dias Coelho</t>
-  </si>
-  <si>
-    <t>01ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$             487.482,55</t>
-  </si>
-  <si>
-    <t>Correspondente - Hebert</t>
-  </si>
-  <si>
-    <t>Audiência de Instrução - Presencial</t>
-  </si>
-  <si>
-    <t>0010209-93.2025.5.15.0071</t>
-  </si>
-  <si>
-    <t>Archimedes Barbosa Siqueira</t>
-  </si>
-  <si>
-    <t>Central</t>
-  </si>
-  <si>
-    <t>R$             125.701,08</t>
-  </si>
-  <si>
-    <t>1000724-56.2026.5.02.0434</t>
-  </si>
-  <si>
-    <t>Wilson Aparecido Sant Ana</t>
-  </si>
-  <si>
-    <t>04ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$               79.500,00</t>
-  </si>
-  <si>
-    <t>GSM</t>
-  </si>
-  <si>
-    <t>0011122-47.2026.5.03.0080</t>
-  </si>
-  <si>
-    <t>Salitre Fertilizantes Ltda</t>
-  </si>
-  <si>
-    <t>Joao Paulo De Oliveira Faria</t>
-  </si>
-  <si>
-    <t>PATROCÍNIO</t>
-  </si>
-  <si>
-    <t>MG</t>
-  </si>
-  <si>
-    <t>R$             122.727,28</t>
-  </si>
-  <si>
-    <t>CAL</t>
-  </si>
-  <si>
-    <t>https://trt3-jus-br.zoom.us/my/vt.patrocinio</t>
-  </si>
-  <si>
-    <t>1000557-62.2026.5.02.0006</t>
-  </si>
-  <si>
-    <t>Telefonica Brasil S.A.</t>
-  </si>
-  <si>
-    <t>Mario Roberto De Lima</t>
-  </si>
-  <si>
-    <t>06ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$          1.582.455,98</t>
-  </si>
-  <si>
-    <t>TFR</t>
-  </si>
-  <si>
-    <t>0011123-32.2026.5.03.0080</t>
-  </si>
-  <si>
-    <t>Matheus Finetti Zanardo</t>
-  </si>
-  <si>
-    <t>1001053-77.2026.5.02.0431</t>
-  </si>
-  <si>
-    <t>Graziele Novais Dos Santos</t>
-  </si>
-  <si>
-    <t>R$             200.175,46</t>
-  </si>
-  <si>
-    <t>RFE</t>
-  </si>
-  <si>
-    <t>1002323-73.2025.5.02.0431</t>
-  </si>
-  <si>
-    <t>Higor Dos Santos</t>
-  </si>
-  <si>
-    <t>R$             582.095,16</t>
-  </si>
-  <si>
-    <t>Audiência Instrução - Telepresencial</t>
-  </si>
-  <si>
-    <t>0010613-19.2026.5.03.0080</t>
-  </si>
-  <si>
-    <t>Salitre Fetilizantes Ltda</t>
-  </si>
-  <si>
-    <t>Maria Izabel Amorim Costa</t>
-  </si>
-  <si>
-    <t>Conhecimento</t>
-  </si>
-  <si>
-    <t>R$               34.420,70</t>
-  </si>
-  <si>
-    <t>Sessão de Julgamento TRT - Semipresencial</t>
-  </si>
-  <si>
-    <t>0011790-44.2024.5.15.0083</t>
-  </si>
-  <si>
-    <t>Kennedy Carvalho Lucas</t>
-  </si>
-  <si>
-    <t>02ª TURMA</t>
-  </si>
-  <si>
-    <t>Recursal TRT</t>
-  </si>
-  <si>
-    <t>R$             147.500,00</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/launch/jc/86986668664 ID da reunião: 869 8666 8664 Senha: 410044</t>
-  </si>
-  <si>
-    <t>Audiência Una - Telepresencial</t>
-  </si>
-  <si>
-    <t>0012495-75.2025.5.15.0093</t>
-  </si>
-  <si>
-    <t>Salitre Fertilizantes Ltda.</t>
-  </si>
-  <si>
-    <t>Eduardo Henrique Maia Carnauba</t>
-  </si>
-  <si>
-    <t>CAMPINAS</t>
-  </si>
-  <si>
-    <t>R$             596.014,50</t>
-  </si>
-  <si>
-    <t>ARC</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/81469918489?pwd=NmNHNVdhSERvZHorOXRIdmJCWU5MQT09 ID da reunião: 814 6991 8489 Senha: 059291</t>
-  </si>
-  <si>
-    <t>0010133-49.2026.5.15.0131</t>
-  </si>
-  <si>
-    <t>Alex Gomes De Sousa</t>
-  </si>
-  <si>
-    <t>12ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$             179.903,44</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/86534999498?pwd=N3RZZXpkTE5laWxEREEvWjBVYVg0Zz0</t>
-  </si>
-  <si>
-    <t>0010841-17.2026.5.15.0126</t>
-  </si>
-  <si>
-    <t>Syngenta Proteção De Cultivos Ltda.</t>
-  </si>
-  <si>
-    <t>Claudinei Dos Santos</t>
-  </si>
-  <si>
-    <t>PAULÍNIA</t>
-  </si>
-  <si>
-    <t>R$               38.195,57</t>
-  </si>
-  <si>
-    <t>JPL</t>
-  </si>
-  <si>
-    <t>GVM</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/83059104477?pwd=h7VDkteaYgzZ4FIU9CoepcQo5ErUHA.1 ID da reunião: 830 5910 4477 Senha: 005974</t>
-  </si>
-  <si>
-    <t>0012011-90.2025.5.15.0083</t>
-  </si>
-  <si>
-    <t>Maria Fernanda Vila Nova Marson Schuller</t>
-  </si>
-  <si>
-    <t>Inicial</t>
-  </si>
-  <si>
-    <t>R$             149.105,07</t>
-  </si>
-  <si>
-    <t>0011989-36.2024.5.15.0093</t>
-  </si>
-  <si>
-    <t>Gregory Ragosta Cassiano De Souza</t>
-  </si>
-  <si>
-    <t>05ª TURMA</t>
-  </si>
-  <si>
-    <t>Recursal</t>
-  </si>
-  <si>
-    <t>R$          1.066.473,00</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/88116222157?pwd=oFe1QBH0rStbUhO7ngHqYzIDE9abay.1</t>
-  </si>
-  <si>
-    <t>0010618-84.2026.5.15.0087</t>
-  </si>
-  <si>
-    <t>Rogerio Cordeiro</t>
-  </si>
-  <si>
-    <t>R$          1.150.491,32</t>
-  </si>
-  <si>
-    <t>JRM</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/81792542599?pwd=dWt0TnU2UXVUYXdKTU1CU2gzUTVZQT09 ID da reunião: 817 9254 2599 Senha: 692443</t>
-  </si>
-  <si>
-    <t>0001673-47.2025.5.09.0011</t>
-  </si>
-  <si>
-    <t>Jose Aparecido Dos Santos Wermer</t>
-  </si>
-  <si>
-    <t>CURITIBA</t>
-  </si>
-  <si>
-    <t>11ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$             303.594,35</t>
-  </si>
-  <si>
-    <t>RCF</t>
-  </si>
-  <si>
-    <t>1000994-20.2025.5.02.0433</t>
-  </si>
-  <si>
-    <t>Sidinei De Souza Oliveira</t>
-  </si>
-  <si>
-    <t>R$             400.000,00</t>
-  </si>
-  <si>
-    <t>0012474-76.2025.5.15.0133</t>
-  </si>
-  <si>
-    <t>Marcelo Luiz Teixeira</t>
-  </si>
-  <si>
-    <t>SÃO JOSÉ DO RIO PRETO</t>
-  </si>
-  <si>
-    <t>Produção Antecipada de Prova</t>
-  </si>
-  <si>
-    <t>R$                    500,00</t>
+    <t>R$             281.252,53</t>
+  </si>
+  <si>
+    <t>Presencial | Advogada - Dra. Eliane Mendes, (15) 99949-8727</t>
   </si>
 </sst>
 </file>
@@ -1080,8 +1197,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49ED9DFC-A4C8-407F-936A-93E44AF2209F}">
-  <dimension ref="A1:R27"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADEBBD58-7411-4639-9BF5-60AE082CEAAD}">
+  <dimension ref="A1:R28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:18" ht="60" x14ac:dyDescent="0.3">
@@ -1140,15 +1257,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" ht="245.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4">
-        <v>106140</v>
+        <v>93396</v>
       </c>
       <c r="B2" s="5">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="C2" s="6">
-        <v>0.375</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>18</v>
@@ -1192,19 +1309,19 @@
       <c r="Q2" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="R2" s="7" t="s">
+      <c r="R2" s="8" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4">
-        <v>99850</v>
+        <v>106294</v>
       </c>
       <c r="B3" s="5">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="C3" s="6">
-        <v>0.375</v>
+        <v>0.36180555555555555</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>33</v>
@@ -1222,13 +1339,13 @@
         <v>37</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="L3" s="7" t="s">
         <v>26</v>
@@ -1237,54 +1354,54 @@
         <v>27</v>
       </c>
       <c r="N3" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="O3" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="P3" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q3" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="R3" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="4">
+        <v>106339</v>
+      </c>
+      <c r="B4" s="5">
+        <v>46309</v>
+      </c>
+      <c r="C4" s="6">
+        <v>0.36805555555555558</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="K4" s="7" t="s">
         <v>40</v>
-      </c>
-      <c r="P3" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q3" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="R3" s="7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" ht="144.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="4">
-        <v>105023</v>
-      </c>
-      <c r="B4" s="5">
-        <v>46308</v>
-      </c>
-      <c r="C4" s="6">
-        <v>0.375</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="K4" s="7" t="s">
-        <v>25</v>
       </c>
       <c r="L4" s="7" t="s">
         <v>26</v>
@@ -1293,54 +1410,54 @@
         <v>27</v>
       </c>
       <c r="N4" s="7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O4" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="P4" s="7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="Q4" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="R4" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R4" s="7" t="s">
+        <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:18" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4">
-        <v>105032</v>
+        <v>106292</v>
       </c>
       <c r="B5" s="5">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="C5" s="6">
-        <v>0.3888888888888889</v>
+        <v>0.37222222222222223</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="L5" s="7" t="s">
         <v>26</v>
@@ -1352,51 +1469,51 @@
         <v>59</v>
       </c>
       <c r="O5" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="P5" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q5" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="R5" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="4">
+        <v>104126</v>
+      </c>
+      <c r="B6" s="5">
+        <v>46309</v>
+      </c>
+      <c r="C6" s="6">
+        <v>0.375</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="P5" s="7" t="s">
+      <c r="E6" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="Q5" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="R5" s="7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="4">
-        <v>105033</v>
-      </c>
-      <c r="B6" s="5">
-        <v>46308</v>
-      </c>
-      <c r="C6" s="6">
-        <v>0.3923611111111111</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="7" t="s">
+      <c r="F6" s="7" t="s">
         <v>62</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>55</v>
       </c>
       <c r="G6" s="7" t="s">
         <v>63</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="I6" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="L6" s="7" t="s">
         <v>26</v>
@@ -1405,54 +1522,54 @@
         <v>27</v>
       </c>
       <c r="N6" s="7" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="O6" s="7" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="P6" s="7" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="Q6" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="R6" s="7" t="s">
-        <v>32</v>
+        <v>69</v>
+      </c>
+      <c r="R6" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="87" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:18" ht="231" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4">
-        <v>104774</v>
+        <v>103238</v>
       </c>
       <c r="B7" s="5">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="C7" s="6">
-        <v>0.39583333333333331</v>
+        <v>0.375</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="L7" s="7" t="s">
         <v>26</v>
@@ -1461,54 +1578,54 @@
         <v>27</v>
       </c>
       <c r="N7" s="7" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="O7" s="7" t="s">
-        <v>74</v>
+        <v>29</v>
       </c>
       <c r="P7" s="7" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Q7" s="7" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="R7" s="8" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:18" ht="144.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4">
-        <v>105223</v>
+        <v>103681</v>
       </c>
       <c r="B8" s="5">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="C8" s="6">
-        <v>0.39583333333333331</v>
+        <v>0.375</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="L8" s="7" t="s">
         <v>26</v>
@@ -1517,54 +1634,54 @@
         <v>27</v>
       </c>
       <c r="N8" s="7" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="O8" s="7" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="P8" s="7" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="Q8" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="R8" s="7" t="s">
-        <v>32</v>
+        <v>89</v>
+      </c>
+      <c r="R8" s="8" t="s">
+        <v>90</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:18" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4">
-        <v>106263</v>
+        <v>104572</v>
       </c>
       <c r="B9" s="5">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="C9" s="6">
-        <v>0.39583333333333331</v>
+        <v>0.38194444444444442</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>22</v>
+        <v>95</v>
       </c>
       <c r="I9" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="L9" s="7" t="s">
         <v>26</v>
@@ -1573,110 +1690,110 @@
         <v>27</v>
       </c>
       <c r="N9" s="7" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="O9" s="7" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="P9" s="7" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="Q9" s="7" t="s">
-        <v>31</v>
+        <v>99</v>
       </c>
       <c r="R9" s="7" t="s">
-        <v>32</v>
+        <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:18" ht="245.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4">
-        <v>99950</v>
+        <v>106004</v>
       </c>
       <c r="B10" s="5">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="C10" s="6">
-        <v>0.41666666666666669</v>
+        <v>0.38958333333333334</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>92</v>
+        <v>33</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>37</v>
+        <v>103</v>
       </c>
       <c r="I10" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>38</v>
+        <v>104</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="L10" s="7" t="s">
         <v>26</v>
       </c>
       <c r="M10" s="7" t="s">
-        <v>95</v>
+        <v>27</v>
       </c>
       <c r="N10" s="7" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="O10" s="7" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="P10" s="7" t="s">
-        <v>41</v>
+        <v>106</v>
       </c>
       <c r="Q10" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="R10" s="7" t="s">
-        <v>32</v>
+        <v>106</v>
+      </c>
+      <c r="R10" s="8" t="s">
+        <v>107</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4">
-        <v>104771</v>
+        <v>105929</v>
       </c>
       <c r="B11" s="5">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="C11" s="6">
-        <v>0.4201388888888889</v>
+        <v>0.40972222222222221</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>20</v>
+        <v>110</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="I11" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>25</v>
+        <v>113</v>
       </c>
       <c r="L11" s="7" t="s">
         <v>26</v>
@@ -1685,54 +1802,54 @@
         <v>27</v>
       </c>
       <c r="N11" s="7" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="O11" s="7" t="s">
         <v>29</v>
       </c>
       <c r="P11" s="7" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="Q11" s="7" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="R11" s="7" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="87" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="4">
-        <v>106063</v>
+        <v>105808</v>
       </c>
       <c r="B12" s="5">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="C12" s="6">
-        <v>0.42708333333333331</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>43</v>
+        <v>108</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>103</v>
+        <v>47</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>105</v>
+        <v>49</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>106</v>
+        <v>23</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>38</v>
+        <v>118</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="L12" s="7" t="s">
         <v>26</v>
@@ -1741,54 +1858,54 @@
         <v>27</v>
       </c>
       <c r="N12" s="7" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="O12" s="7" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="P12" s="7" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="Q12" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="R12" s="8" t="s">
-        <v>109</v>
+        <v>121</v>
+      </c>
+      <c r="R12" s="7" t="s">
+        <v>55</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:18" ht="245.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4">
-        <v>104667</v>
+        <v>103274</v>
       </c>
       <c r="B13" s="5">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="C13" s="6">
-        <v>0.42708333333333331</v>
+        <v>0.4375</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>81</v>
+        <v>125</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>23</v>
+        <v>126</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>113</v>
+        <v>76</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="L13" s="7" t="s">
         <v>26</v>
@@ -1797,54 +1914,54 @@
         <v>27</v>
       </c>
       <c r="N13" s="7" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="O13" s="7" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="P13" s="7" t="s">
-        <v>115</v>
+        <v>30</v>
       </c>
       <c r="Q13" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="R13" s="7" t="s">
-        <v>32</v>
+        <v>30</v>
+      </c>
+      <c r="R13" s="8" t="s">
+        <v>128</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="87" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="4">
-        <v>106100</v>
+        <v>93603</v>
       </c>
       <c r="B14" s="5">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="C14" s="6">
-        <v>0.43055555555555558</v>
+        <v>0.44236111111111109</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>105</v>
+        <v>132</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>106</v>
+        <v>23</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>38</v>
+        <v>133</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>25</v>
+        <v>134</v>
       </c>
       <c r="L14" s="7" t="s">
         <v>26</v>
@@ -1853,54 +1970,54 @@
         <v>27</v>
       </c>
       <c r="N14" s="7" t="s">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="O14" s="7" t="s">
-        <v>74</v>
+        <v>136</v>
       </c>
       <c r="P14" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q14" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="R14" s="7" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="4">
+        <v>103106</v>
+      </c>
+      <c r="B15" s="5">
+        <v>46309</v>
+      </c>
+      <c r="C15" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D15" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="Q14" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="R14" s="8" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="4">
-        <v>105182</v>
-      </c>
-      <c r="B15" s="5">
-        <v>46308</v>
-      </c>
-      <c r="C15" s="6">
-        <v>0.47222222222222221</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>33</v>
-      </c>
       <c r="E15" s="7" t="s">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>20</v>
+        <v>140</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>119</v>
+        <v>141</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>22</v>
+        <v>142</v>
       </c>
       <c r="I15" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>89</v>
+        <v>39</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="L15" s="7" t="s">
         <v>26</v>
@@ -1909,54 +2026,54 @@
         <v>27</v>
       </c>
       <c r="N15" s="7" t="s">
-        <v>120</v>
+        <v>143</v>
       </c>
       <c r="O15" s="7" t="s">
-        <v>29</v>
+        <v>144</v>
       </c>
       <c r="P15" s="7" t="s">
-        <v>91</v>
+        <v>145</v>
       </c>
       <c r="Q15" s="7" t="s">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="R15" s="7" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="4">
-        <v>103551</v>
+        <v>100430</v>
       </c>
       <c r="B16" s="5">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="C16" s="6">
-        <v>0.4861111111111111</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>33</v>
+        <v>146</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>122</v>
+        <v>147</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>20</v>
+        <v>148</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>123</v>
+        <v>149</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>22</v>
+        <v>150</v>
       </c>
       <c r="I16" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="L16" s="7" t="s">
         <v>26</v>
@@ -1965,54 +2082,54 @@
         <v>27</v>
       </c>
       <c r="N16" s="7" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
       <c r="O16" s="7" t="s">
         <v>29</v>
       </c>
       <c r="P16" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="Q16" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="R16" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="4">
+        <v>104525</v>
+      </c>
+      <c r="B17" s="5">
+        <v>46309</v>
+      </c>
+      <c r="C17" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D17" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="Q16" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R16" s="7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" ht="87" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="4">
-        <v>105174</v>
-      </c>
-      <c r="B17" s="5">
-        <v>46308</v>
-      </c>
-      <c r="C17" s="6">
-        <v>0.5625</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>125</v>
-      </c>
       <c r="E17" s="7" t="s">
-        <v>126</v>
+        <v>153</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>127</v>
+        <v>47</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>128</v>
+        <v>154</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>105</v>
+        <v>49</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>106</v>
+        <v>23</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>129</v>
+        <v>40</v>
       </c>
       <c r="L17" s="7" t="s">
         <v>26</v>
@@ -2021,54 +2138,54 @@
         <v>27</v>
       </c>
       <c r="N17" s="7" t="s">
-        <v>130</v>
+        <v>155</v>
       </c>
       <c r="O17" s="7" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="P17" s="7" t="s">
-        <v>108</v>
+        <v>53</v>
       </c>
       <c r="Q17" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="R17" s="8" t="s">
-        <v>109</v>
+        <v>106</v>
+      </c>
+      <c r="R17" s="7" t="s">
+        <v>55</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="173.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:18" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="4">
-        <v>98816</v>
+        <v>104019</v>
       </c>
       <c r="B18" s="5">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="C18" s="6">
-        <v>0.5625</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>131</v>
+        <v>71</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>132</v>
+        <v>156</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>55</v>
+        <v>157</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>133</v>
+        <v>158</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>57</v>
+        <v>159</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>134</v>
+        <v>39</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>135</v>
+        <v>40</v>
       </c>
       <c r="L18" s="7" t="s">
         <v>26</v>
@@ -2077,54 +2194,54 @@
         <v>27</v>
       </c>
       <c r="N18" s="7" t="s">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="O18" s="7" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="P18" s="7" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="Q18" s="7" t="s">
-        <v>61</v>
+        <v>115</v>
       </c>
       <c r="R18" s="8" t="s">
-        <v>137</v>
+        <v>161</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="231" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:18" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="4">
-        <v>103490</v>
+        <v>105287</v>
       </c>
       <c r="B19" s="5">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="C19" s="6">
-        <v>0.58333333333333337</v>
+        <v>0.47986111111111113</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>138</v>
+        <v>91</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>139</v>
+        <v>162</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>140</v>
+        <v>93</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>141</v>
+        <v>163</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>142</v>
+        <v>95</v>
       </c>
       <c r="I19" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>113</v>
+        <v>164</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="L19" s="7" t="s">
         <v>26</v>
@@ -2133,54 +2250,54 @@
         <v>27</v>
       </c>
       <c r="N19" s="7" t="s">
-        <v>143</v>
+        <v>165</v>
       </c>
       <c r="O19" s="7" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="P19" s="7" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="Q19" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="R19" s="8" t="s">
-        <v>145</v>
+        <v>166</v>
+      </c>
+      <c r="R19" s="7" t="s">
+        <v>100</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="144.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:18" ht="87" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="4">
-        <v>103858</v>
+        <v>105649</v>
       </c>
       <c r="B20" s="5">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="C20" s="6">
-        <v>0.59722222222222221</v>
+        <v>0.52083333333333337</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>146</v>
+        <v>167</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>20</v>
+        <v>123</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>147</v>
+        <v>168</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>142</v>
+        <v>169</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>148</v>
+        <v>76</v>
       </c>
       <c r="K20" s="7" t="s">
-        <v>25</v>
+        <v>113</v>
       </c>
       <c r="L20" s="7" t="s">
         <v>26</v>
@@ -2189,54 +2306,54 @@
         <v>27</v>
       </c>
       <c r="N20" s="7" t="s">
-        <v>149</v>
+        <v>170</v>
       </c>
       <c r="O20" s="7" t="s">
         <v>29</v>
       </c>
       <c r="P20" s="7" t="s">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="Q20" s="7" t="s">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="R20" s="8" t="s">
-        <v>150</v>
+        <v>171</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="231" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="4">
-        <v>105111</v>
+        <v>100814</v>
       </c>
       <c r="B21" s="5">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="C21" s="6">
-        <v>0.59722222222222221</v>
+        <v>0.5444444444444444</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>154</v>
+        <v>64</v>
       </c>
       <c r="I21" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>72</v>
+        <v>175</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>83</v>
+        <v>176</v>
       </c>
       <c r="L21" s="7" t="s">
         <v>26</v>
@@ -2245,54 +2362,54 @@
         <v>27</v>
       </c>
       <c r="N21" s="7" t="s">
-        <v>155</v>
+        <v>177</v>
       </c>
       <c r="O21" s="7" t="s">
-        <v>40</v>
+        <v>178</v>
       </c>
       <c r="P21" s="7" t="s">
-        <v>156</v>
+        <v>54</v>
       </c>
       <c r="Q21" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="R21" s="8" t="s">
-        <v>158</v>
+        <v>54</v>
+      </c>
+      <c r="R21" s="7" t="s">
+        <v>179</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="4">
-        <v>102063</v>
+        <v>100830</v>
       </c>
       <c r="B22" s="5">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="C22" s="6">
-        <v>0.60416666666666663</v>
+        <v>0.55555555555555558</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>159</v>
+        <v>180</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>55</v>
+        <v>181</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>160</v>
+        <v>182</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>57</v>
+        <v>150</v>
       </c>
       <c r="I22" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>161</v>
+        <v>40</v>
       </c>
       <c r="L22" s="7" t="s">
         <v>26</v>
@@ -2301,54 +2418,54 @@
         <v>27</v>
       </c>
       <c r="N22" s="7" t="s">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="O22" s="7" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="P22" s="7" t="s">
-        <v>61</v>
+        <v>184</v>
       </c>
       <c r="Q22" s="7" t="s">
-        <v>86</v>
+        <v>185</v>
       </c>
       <c r="R22" s="7" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="144.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:18" ht="245.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="4">
-        <v>104088</v>
+        <v>105722</v>
       </c>
       <c r="B23" s="5">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="C23" s="6">
-        <v>0.60416666666666663</v>
+        <v>0.57986111111111116</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>131</v>
+        <v>33</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>163</v>
+        <v>186</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>111</v>
+        <v>187</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>164</v>
+        <v>188</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>142</v>
+        <v>189</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>23</v>
+        <v>190</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>165</v>
+        <v>39</v>
       </c>
       <c r="K23" s="7" t="s">
-        <v>166</v>
+        <v>40</v>
       </c>
       <c r="L23" s="7" t="s">
         <v>26</v>
@@ -2357,54 +2474,54 @@
         <v>27</v>
       </c>
       <c r="N23" s="7" t="s">
-        <v>167</v>
+        <v>191</v>
       </c>
       <c r="O23" s="7" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="P23" s="7" t="s">
-        <v>51</v>
+        <v>192</v>
       </c>
       <c r="Q23" s="7" t="s">
-        <v>115</v>
+        <v>192</v>
       </c>
       <c r="R23" s="8" t="s">
-        <v>168</v>
+        <v>193</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="231" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:18" ht="245.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="4">
-        <v>104804</v>
+        <v>103736</v>
       </c>
       <c r="B24" s="5">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="C24" s="6">
-        <v>0.61805555555555558</v>
+        <v>0.59027777777777779</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>43</v>
+        <v>81</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>169</v>
+        <v>194</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>152</v>
+        <v>195</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>170</v>
+        <v>196</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>154</v>
+        <v>197</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>23</v>
+        <v>198</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>89</v>
+        <v>199</v>
       </c>
       <c r="K24" s="7" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="L24" s="7" t="s">
         <v>26</v>
@@ -2413,54 +2530,54 @@
         <v>27</v>
       </c>
       <c r="N24" s="7" t="s">
-        <v>171</v>
+        <v>200</v>
       </c>
       <c r="O24" s="7" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="P24" s="7" t="s">
-        <v>156</v>
+        <v>201</v>
       </c>
       <c r="Q24" s="7" t="s">
-        <v>172</v>
+        <v>202</v>
       </c>
       <c r="R24" s="8" t="s">
-        <v>173</v>
+        <v>203</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="96.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:18" ht="259.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="4">
-        <v>103582</v>
+        <v>105342</v>
       </c>
       <c r="B25" s="5">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="C25" s="6">
-        <v>0.625</v>
+        <v>0.61805555555555558</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>33</v>
+        <v>71</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>174</v>
+        <v>204</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>45</v>
+        <v>205</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>175</v>
+        <v>206</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>176</v>
+        <v>207</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="K25" s="7" t="s">
-        <v>161</v>
+        <v>113</v>
       </c>
       <c r="L25" s="7" t="s">
         <v>26</v>
@@ -2469,54 +2586,54 @@
         <v>27</v>
       </c>
       <c r="N25" s="7" t="s">
-        <v>178</v>
+        <v>208</v>
       </c>
       <c r="O25" s="7" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="P25" s="7" t="s">
-        <v>179</v>
+        <v>78</v>
       </c>
       <c r="Q25" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="R25" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
+      </c>
+      <c r="R25" s="8" t="s">
+        <v>209</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="4">
-        <v>101364</v>
+        <v>101730</v>
       </c>
       <c r="B26" s="5">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="C26" s="6">
-        <v>0.63888888888888884</v>
+        <v>0.625</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>33</v>
+        <v>91</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>20</v>
+        <v>211</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>181</v>
+        <v>212</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>22</v>
+        <v>150</v>
       </c>
       <c r="I26" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>99</v>
+        <v>76</v>
       </c>
       <c r="K26" s="7" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="L26" s="7" t="s">
         <v>26</v>
@@ -2525,92 +2642,151 @@
         <v>27</v>
       </c>
       <c r="N26" s="7" t="s">
-        <v>182</v>
+        <v>213</v>
       </c>
       <c r="O26" s="7" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="P26" s="7" t="s">
-        <v>91</v>
+        <v>184</v>
       </c>
       <c r="Q26" s="7" t="s">
-        <v>31</v>
+        <v>184</v>
       </c>
       <c r="R26" s="7" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="173.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:18" ht="144.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="4">
-        <v>104114</v>
+        <v>105176</v>
       </c>
       <c r="B27" s="5">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="C27" s="6">
-        <v>0.64583333333333337</v>
+        <v>0.63194444444444442</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>131</v>
+        <v>56</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>183</v>
+        <v>214</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>184</v>
+        <v>215</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>185</v>
+        <v>216</v>
       </c>
       <c r="I27" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>134</v>
+        <v>76</v>
       </c>
       <c r="K27" s="7" t="s">
-        <v>166</v>
+        <v>40</v>
       </c>
       <c r="L27" s="7" t="s">
-        <v>186</v>
+        <v>26</v>
       </c>
       <c r="M27" s="7" t="s">
         <v>27</v>
       </c>
       <c r="N27" s="7" t="s">
-        <v>187</v>
+        <v>217</v>
       </c>
       <c r="O27" s="7" t="s">
-        <v>50</v>
+        <v>136</v>
       </c>
       <c r="P27" s="7" t="s">
-        <v>115</v>
+        <v>218</v>
       </c>
       <c r="Q27" s="7" t="s">
-        <v>115</v>
+        <v>218</v>
       </c>
       <c r="R27" s="8" t="s">
-        <v>137</v>
+        <v>219</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" ht="84.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="4">
+        <v>102763</v>
+      </c>
+      <c r="B28" s="5">
+        <v>46309</v>
+      </c>
+      <c r="C28" s="6">
+        <v>0.65277777777777779</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="H28" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="I28" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J28" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="K28" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="L28" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M28" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N28" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="O28" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="P28" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q28" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="R28" s="7" t="s">
+        <v>226</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="R4" r:id="rId1" xr:uid="{310473BB-B8CD-4DD8-8B8D-401BBE0BFB8D}"/>
-    <hyperlink ref="R7" r:id="rId2" xr:uid="{ADC369A2-DDBB-427A-8792-139A5490DAEB}"/>
-    <hyperlink ref="R12" r:id="rId3" xr:uid="{F5A0AD32-BCCB-4E63-97FF-CEEEA8E86AAB}"/>
-    <hyperlink ref="R14" r:id="rId4" xr:uid="{7C10BA1F-B68E-4AFB-8778-6CC1142B93A2}"/>
-    <hyperlink ref="R17" r:id="rId5" xr:uid="{96BB691E-FBB2-4A4D-8513-4B1CF0268199}"/>
-    <hyperlink ref="R18" r:id="rId6" xr:uid="{1B78F597-5AE0-4860-A993-4CEB4BF32486}"/>
-    <hyperlink ref="R19" r:id="rId7" display="https://trt15-jus-br.zoom.us/j/81469918489?pwd=NmNHNVdhSERvZHorOXRIdmJCWU5MQT09%20ID%20da%20reunião:%20814%206991%208489%20Senha:%20059291" xr:uid="{54D7A758-1309-469C-B422-56A798998E2F}"/>
-    <hyperlink ref="R20" r:id="rId8" xr:uid="{A9451B6D-1FCD-4B0B-94BB-C1F1BD247588}"/>
-    <hyperlink ref="R21" r:id="rId9" display="https://trt15-jus-br.zoom.us/j/83059104477?pwd=h7VDkteaYgzZ4FIU9CoepcQo5ErUHA.1%20ID%20da%20reunião:%20830%205910%204477%20Senha:%20005974" xr:uid="{9A116859-DC0B-4508-A064-B9E8DFF3843D}"/>
-    <hyperlink ref="R23" r:id="rId10" xr:uid="{4CB3E34E-FC69-47E4-BCF5-7FE5E6492AD6}"/>
-    <hyperlink ref="R24" r:id="rId11" display="https://trt15-jus-br.zoom.us/j/81792542599?pwd=dWt0TnU2UXVUYXdKTU1CU2gzUTVZQT09%20ID%20da%20reunião:%20817%209254%202599%20Senha:%20692443" xr:uid="{59384DEE-FAC9-4D0C-B7ED-78FE9ABEF94D}"/>
-    <hyperlink ref="R27" r:id="rId12" xr:uid="{40C6B6EB-5908-4C50-8E3D-9AC500DFFA27}"/>
+    <hyperlink ref="R2" r:id="rId1" display="https://us02web.zoom.us/j/88415253122?pwd=QzlTNmxwdWpEeGVFZmdwM0lDUFJ4Zz09%20ID%20da%20reunião:%20884%201525%203122%20Senha%20de%20acesso:%20510562" xr:uid="{04C6DBE6-636E-40EE-A9EB-95E8083BE8AD}"/>
+    <hyperlink ref="R3" r:id="rId2" xr:uid="{2057B3DE-B348-4F28-B901-4051760C1203}"/>
+    <hyperlink ref="R5" r:id="rId3" xr:uid="{E6D4827D-77F9-4A6E-80A9-976EC081B772}"/>
+    <hyperlink ref="R6" r:id="rId4" xr:uid="{A0A7A5EC-227A-4E41-B500-1ED21846AA30}"/>
+    <hyperlink ref="R7" r:id="rId5" display="https://us02web.zoom.us/j/86212862282?pwd=N2N4b3NobCtXbUxsODdmSXFlMjVCQT09%20ID%20da%20reunião:%20862%201286%202282%20Senha:%20498067" xr:uid="{3F65D060-5C15-4917-A109-9585A087E950}"/>
+    <hyperlink ref="R8" r:id="rId6" xr:uid="{CE38DE43-E683-433B-9FF3-C44BE0670FF1}"/>
+    <hyperlink ref="R10" r:id="rId7" display="https://trt15-jus-br.zoom.us/j/85453506049?pwd=Q0lIZFc3eS9kaGNJQ3N0cEIxdnBnZz09%20ID%20da%20reunião:%20854%205350%206049%20Senha%20de%20acesso:%20364%20591" xr:uid="{0AF33F79-0A5A-4131-9FD9-111D9F8D07AB}"/>
+    <hyperlink ref="R13" r:id="rId8" display="https://trt5-jus-br.zoom.us/j/81333809109?pwd=47akSzaeNwYTr7VDOZiMN5qQCeHjkO.1%20ID%20da%20reunião:%20813%203380%209109%20Senha%20de%20acesso:%20470307" xr:uid="{C78255AE-E107-4464-B07C-8BE66868B575}"/>
+    <hyperlink ref="R18" r:id="rId9" xr:uid="{027F57A3-62AC-47FB-BA74-3D64A09D0B11}"/>
+    <hyperlink ref="R20" r:id="rId10" xr:uid="{A901F86D-862B-46F6-BE8E-DF824EC89DDB}"/>
+    <hyperlink ref="R23" r:id="rId11" display="https://trt23-jus-br.zoom.us/j/81753761549?pwd=NYkhI185ab9wC4FuLVDoNH2aVuBPb3.1%20ID%20da%20reunião:%20817%205376%201549%20Senha:%20@VTSinop1" xr:uid="{A13CD3B5-9027-462F-817B-1DC66274A514}"/>
+    <hyperlink ref="R24" r:id="rId12" display="https://trt9-jus-br.zoom.us/j/82898229693?pwd=WFk5UElWZGpDYjR0a1hTa2xwSHNjdz09%20ID%20reunião%20:%20828%209822%209693%20Senha%20de%20acesso:%20434474" xr:uid="{6B1AFD8E-17E0-4D3B-8646-70CE852D44F6}"/>
+    <hyperlink ref="R25" r:id="rId13" display="https://trt15-jus-br.zoom.us/j/88542672682?pwd=7pQ4QRhZmRG9RAQAWKowymbwNawa7t.1%20ID%20da%20reunião:%20885%204267%202682%20Senha%20de%20acesso:%20050728" xr:uid="{8E3F3918-2EFE-4258-815D-3247602C5B70}"/>
+    <hyperlink ref="R27" r:id="rId14" xr:uid="{C0DAAC02-5281-481B-8717-21E720E9C40D}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId15"/>
 </worksheet>
 </file>
--- a/Pauta_de_Audiencias.xlsx
+++ b/Pauta_de_Audiencias.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\blu\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E0C84508-F6A0-4BBB-B1F1-2E8D4191AB24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{08AB1FBF-6C6E-4325-A6A4-CF1EA9993694}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{528503CC-6C06-4AE0-A20A-C716642FBBF3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{78F15355-F2C2-45F0-8FEC-846FE207DC00}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$R$27</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="208">
   <si>
     <t>Código P&amp;C</t>
   </si>
@@ -95,188 +98,610 @@
     <t>Link/Observações</t>
   </si>
   <si>
+    <t>Viterra Bioenergia S.A.</t>
+  </si>
+  <si>
+    <t>DRACENA</t>
+  </si>
+  <si>
+    <t>SP</t>
+  </si>
+  <si>
+    <t>05ª TURMA</t>
+  </si>
+  <si>
+    <t>Recursal</t>
+  </si>
+  <si>
+    <t>Reclamação Trabalhista</t>
+  </si>
+  <si>
+    <t>CENTRAL</t>
+  </si>
+  <si>
+    <t>Grupo E2</t>
+  </si>
+  <si>
+    <t>RYL</t>
+  </si>
+  <si>
+    <t>Grupo E1</t>
+  </si>
+  <si>
+    <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
+  </si>
+  <si>
+    <t>SANTO ANDRÉ</t>
+  </si>
+  <si>
+    <t>03ª TURMA</t>
+  </si>
+  <si>
+    <t>Grupo B1</t>
+  </si>
+  <si>
+    <t>JPE</t>
+  </si>
+  <si>
+    <t>Perícia Técnica</t>
+  </si>
+  <si>
+    <t>0010394-11.2026.5.15.0132</t>
+  </si>
+  <si>
+    <t>Embraer S.A.</t>
+  </si>
+  <si>
+    <t>Gilson Brito Soares</t>
+  </si>
+  <si>
+    <t>SÃO JOSÉ DOS CAMPOS</t>
+  </si>
+  <si>
+    <t>05ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>Instrução</t>
+  </si>
+  <si>
+    <t>R$             150.000,00</t>
+  </si>
+  <si>
+    <t>Grupo B2</t>
+  </si>
+  <si>
+    <t>ANB</t>
+  </si>
+  <si>
+    <t>Iremos acompanhar</t>
+  </si>
+  <si>
+    <t>Audiência Una - Presencial</t>
+  </si>
+  <si>
+    <t>1001220-59.2026.5.02.0087</t>
+  </si>
+  <si>
+    <t>Telefonica Brasil S.A.</t>
+  </si>
+  <si>
+    <t>Renata Da Rocha Cristale</t>
+  </si>
+  <si>
+    <t>SÃO PAULO</t>
+  </si>
+  <si>
+    <t>87ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>1ª Instância</t>
+  </si>
+  <si>
+    <t>R$             353.913,04</t>
+  </si>
+  <si>
+    <t>Grupo C</t>
+  </si>
+  <si>
+    <t>TFR</t>
+  </si>
+  <si>
+    <t>VSI</t>
+  </si>
+  <si>
+    <t>Presencial</t>
+  </si>
+  <si>
+    <t>VRO</t>
+  </si>
+  <si>
+    <t>Audiência Instrução - Telepresencial</t>
+  </si>
+  <si>
+    <t>0011158-89.2025.5.03.0156</t>
+  </si>
+  <si>
+    <t>Itapagipe Bioenergia Ltda.</t>
+  </si>
+  <si>
+    <t>Pamela Barcelos Oliveira</t>
+  </si>
+  <si>
+    <t>FRUTAL</t>
+  </si>
+  <si>
+    <t>MG</t>
+  </si>
+  <si>
+    <t>VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             286.833,00</t>
+  </si>
+  <si>
+    <t>MBF</t>
+  </si>
+  <si>
+    <t>https://trt3-jus-br.zoom.us/my/vtfrutal</t>
+  </si>
+  <si>
+    <t>Sessão de Julgamento TRT - Semipresencial</t>
+  </si>
+  <si>
+    <t>0010410-66.2025.5.15.0045</t>
+  </si>
+  <si>
+    <t>Rafael Augusto Pereira</t>
+  </si>
+  <si>
+    <t>06ª TURMA</t>
+  </si>
+  <si>
+    <t>Recursal TRT</t>
+  </si>
+  <si>
+    <t>R$             114.500,00</t>
+  </si>
+  <si>
+    <t>GSM</t>
+  </si>
+  <si>
+    <t>NRG</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/85339761227?pwd=9098ZbUufpnfiuDdFCDYtoCxKs12aD.1 ID da reunião: 853 3976 1227 Senha: 006441</t>
+  </si>
+  <si>
+    <t>Syngenta Seeds Ltda.</t>
+  </si>
+  <si>
+    <t>GVM</t>
+  </si>
+  <si>
+    <t>Syngenta Proteção De Cultivos Ltda.</t>
+  </si>
+  <si>
+    <t>RIO GRANDE</t>
+  </si>
+  <si>
+    <t>RS</t>
+  </si>
+  <si>
+    <t>BBO</t>
+  </si>
+  <si>
+    <t>Audiência de Conciliação - Telepresencial</t>
+  </si>
+  <si>
+    <t>0012011-82.2025.5.03.0032</t>
+  </si>
+  <si>
+    <t>Sistenge Construções E Comércio Ltda.</t>
+  </si>
+  <si>
+    <t>Ian Santos Do Amor Divino Silva</t>
+  </si>
+  <si>
+    <t>CONTAGEM</t>
+  </si>
+  <si>
+    <t>CEJUSC</t>
+  </si>
+  <si>
+    <t>Liquidação</t>
+  </si>
+  <si>
+    <t>R$               16.792,53</t>
+  </si>
+  <si>
+    <t>https://trt3-jus-br.zoom.us/my/anacjs</t>
+  </si>
+  <si>
     <t>Audiência Instrução - Presencial</t>
   </si>
   <si>
-    <t>1002420-61.2025.5.02.0435</t>
-  </si>
-  <si>
-    <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
-  </si>
-  <si>
-    <t>Alex Sandro Costa De Medeiros</t>
-  </si>
-  <si>
-    <t>SANTO ANDRÉ</t>
-  </si>
-  <si>
-    <t>SP</t>
-  </si>
-  <si>
-    <t>05ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>Instrução</t>
-  </si>
-  <si>
-    <t>Reclamação Trabalhista</t>
-  </si>
-  <si>
-    <t>CENTRAL</t>
-  </si>
-  <si>
-    <t>R$             527.971,29</t>
-  </si>
-  <si>
-    <t>Grupo B1</t>
-  </si>
-  <si>
-    <t>Correspondente - Hebert</t>
-  </si>
-  <si>
-    <t>GSM</t>
-  </si>
-  <si>
-    <t>Presencial</t>
-  </si>
-  <si>
-    <t>Audiência de Instrução - Semipresencial</t>
-  </si>
-  <si>
-    <t>1000543-85.2026.5.02.0521</t>
-  </si>
-  <si>
-    <t>Mahle Thermal And Fluid Systems Brazil Ltda.</t>
-  </si>
-  <si>
-    <t>Juliano Aguilar Pinheiro</t>
-  </si>
-  <si>
-    <t>ARUJÁ</t>
-  </si>
-  <si>
-    <t>VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$               92.588,21</t>
-  </si>
-  <si>
-    <t>Grupo E1</t>
-  </si>
-  <si>
-    <t>PSI</t>
-  </si>
-  <si>
-    <t>TLI</t>
-  </si>
-  <si>
-    <t>https://trt2-jus-br.zoom.us/j/84763743950?pwd=HBCpStvQgJxW9bsUHzE1NafpSjFa2m.1 ID da reunião: 847 6374 3950 Senha de acesso: vtaruja01</t>
-  </si>
-  <si>
-    <t>1000758-28.2026.5.02.0435</t>
-  </si>
-  <si>
-    <t>Raphael Antonio Jacinto Dos Santos</t>
-  </si>
-  <si>
-    <t>R$             137.021,58</t>
-  </si>
-  <si>
-    <t>TAM</t>
-  </si>
-  <si>
-    <t>Audiência Una - Presencial</t>
-  </si>
-  <si>
-    <t>1001355-06.2026.5.02.0432</t>
-  </si>
-  <si>
-    <t>Marcos Matheus Palda De Sousa</t>
-  </si>
-  <si>
-    <t>02ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$             113.876,67</t>
+    <t>0001026-79.2026.5.10.0014</t>
+  </si>
+  <si>
+    <t>William Roberto Dall Acqua</t>
+  </si>
+  <si>
+    <t>BRASÍLIA</t>
+  </si>
+  <si>
+    <t>DF</t>
+  </si>
+  <si>
+    <t>14ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$          7.802.649,37</t>
+  </si>
+  <si>
+    <t>KBM</t>
+  </si>
+  <si>
+    <t>Audiência Una - Telepresencial</t>
+  </si>
+  <si>
+    <t>0010386-72.2026.5.15.0087</t>
+  </si>
+  <si>
+    <t>Carlos Eduardo De Araujo</t>
+  </si>
+  <si>
+    <t>PAULÍNIA</t>
+  </si>
+  <si>
+    <t>01ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             638.884,57</t>
+  </si>
+  <si>
+    <t>JRM</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/4525285196?pwd=cG1ieCtlVVdHZERxcVRTM2lzSGt3dz09 ID da reunião: 452 528 5196 Senha de acesso: 702632</t>
+  </si>
+  <si>
+    <t>0010428-24.2026.5.15.0087</t>
+  </si>
+  <si>
+    <t>Victor Hugo Pedroso</t>
+  </si>
+  <si>
+    <t>R$               40.124,21</t>
+  </si>
+  <si>
+    <t>Correspondente - Carlos Florian</t>
+  </si>
+  <si>
+    <t>Presencial | Advogada - Dra. Eliane Mendes, (15) 99949-8727</t>
+  </si>
+  <si>
+    <t>0010320-12.2025.5.15.0125</t>
+  </si>
+  <si>
+    <t>Allef Rodrigues Santos</t>
+  </si>
+  <si>
+    <t>SERTÃOZINHO</t>
+  </si>
+  <si>
+    <t>R$               51.290,99</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/5370769847?pwd=SFJvS0RITzJHbGtlUjUveVpqV0Rrdz09 Id da reunião: 537 076 9847 Senha da sala: 151507</t>
+  </si>
+  <si>
+    <t>0012943-94.2025.5.15.0013</t>
+  </si>
+  <si>
+    <t>Eder De Andrade</t>
+  </si>
+  <si>
+    <t>Inicial</t>
+  </si>
+  <si>
+    <t>R$             100.000,00</t>
+  </si>
+  <si>
+    <t>VCR</t>
+  </si>
+  <si>
+    <t>03ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$               93.500,00</t>
+  </si>
+  <si>
+    <t>0011867-35.2025.5.15.0013</t>
+  </si>
+  <si>
+    <t>Gabriel Estevan Martins Sousa</t>
   </si>
   <si>
     <t>RFE</t>
   </si>
   <si>
-    <t>BSO</t>
+    <t>RCF</t>
+  </si>
+  <si>
+    <t>0010636-75.2024.5.15.0152</t>
+  </si>
+  <si>
+    <t>Dell Computadores Do Brasil Ltda.</t>
+  </si>
+  <si>
+    <t>Rosemeire Ribeiro</t>
+  </si>
+  <si>
+    <t>HORTOLÂNDIA</t>
+  </si>
+  <si>
+    <t>R$               85.922,67</t>
+  </si>
+  <si>
+    <t>AAP</t>
+  </si>
+  <si>
+    <t>JPL</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/84349133108?pwd=rhlBY7X5LFPEEJm6Jmapg526N0IlEm.1 ID da reunião: 843 4913 3108 Senha: 614191</t>
+  </si>
+  <si>
+    <t>1000407-68.2025.5.02.0442</t>
+  </si>
+  <si>
+    <t>Miguel Pereira Leal Neto</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>CEJUSC 2º GRAU</t>
+  </si>
+  <si>
+    <t>3ª Instância</t>
+  </si>
+  <si>
+    <t>R$             288.417,77</t>
+  </si>
+  <si>
+    <t>https://trt2-jus-br.zoom.us/j/83766953133?pwd=nhJnFb0XkEmrNGNrJJb8WUSQoDddyZ.1 ID da reunião: 837 6695 3133 Senha de acesso: 386774</t>
+  </si>
+  <si>
+    <t>0001250-52.2026.5.17.0004</t>
+  </si>
+  <si>
+    <t>Fertilizantes Heringer S/A</t>
+  </si>
+  <si>
+    <t>Rhamon Nascimento Rodrigues</t>
+  </si>
+  <si>
+    <t>VITÓRIA</t>
+  </si>
+  <si>
+    <t>ES</t>
+  </si>
+  <si>
+    <t>04ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>Conhecimento</t>
+  </si>
+  <si>
+    <t>R$               85.329,43</t>
+  </si>
+  <si>
+    <t>Correspondente - doc9</t>
+  </si>
+  <si>
+    <t>Presencial | Advogada - Grazielle Gusmão Tavares Dias grazielleadvocacia@gmail.com 27997516239</t>
+  </si>
+  <si>
+    <t>0010453-51.2026.5.15.0050</t>
+  </si>
+  <si>
+    <t>Joao Antonio Alves Bessa</t>
+  </si>
+  <si>
+    <t>R$             127.002,96</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/87527564652?pwd=d3YrZ2diWXk5UjgzbmVkNExteWVMQT09 ID da reunião: 875 2756 4652 Senha de acesso: 246680</t>
+  </si>
+  <si>
+    <t>0001801-18.2025.5.18.0011</t>
+  </si>
+  <si>
+    <t>Fertilizantes Tocantins S.A.</t>
+  </si>
+  <si>
+    <t>Cleiton Agenor Da Silva</t>
+  </si>
+  <si>
+    <t>CATALÃO</t>
+  </si>
+  <si>
+    <t>GO</t>
+  </si>
+  <si>
+    <t>R$               30.095,05</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Presencial | Advogada - Grazielle Dias Macedo </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF467886"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>graziellemacedoadv@gmail.com</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 64981693490 | Preposto - Julia de Souza Pozzebon </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF467886"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>juliadesouzapoz@gmail.com</t>
+    </r>
+  </si>
+  <si>
+    <t>0011164-38.2025.5.03.0143</t>
+  </si>
+  <si>
+    <t>Empresa Brasileira De Correios E Telégrafos</t>
+  </si>
+  <si>
+    <t>Nelida Larisa Faria Figueiredo</t>
+  </si>
+  <si>
+    <t>JUIZ DE FORA</t>
+  </si>
+  <si>
+    <t>R$          2.353.657,08</t>
+  </si>
+  <si>
+    <t>https://trt3-jus-br.zoom.us/my/trt3.turma5 ID Reunião: 562 267 4772</t>
   </si>
   <si>
     <t>Audiência de Instrução - Presencial</t>
   </si>
   <si>
-    <t>0000196-19.2026.5.10.0013</t>
-  </si>
-  <si>
-    <t>Ferrero Do Brasil Industria Doceira E Alimentar Ltda</t>
-  </si>
-  <si>
-    <t>Gisele Martins Da Rocha Silva</t>
-  </si>
-  <si>
-    <t>BRASÍLIA</t>
-  </si>
-  <si>
-    <t>DF</t>
-  </si>
-  <si>
-    <t>13ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$             279.042,46</t>
-  </si>
-  <si>
-    <t>Grupo B3</t>
-  </si>
-  <si>
-    <t>Correspondente - Carlos Florian</t>
-  </si>
-  <si>
-    <t>ANB</t>
-  </si>
-  <si>
-    <t>Presencial | Advogada - Dra. Larissa de Carvalho, (61) 98137-5115 | Preposto - Emanuel Vinicius Alves Pereira, CPF 056.965.191-30, (61) 98215-3051</t>
-  </si>
-  <si>
-    <t>0011034-70.2025.5.03.0071</t>
-  </si>
-  <si>
-    <t>Agrocerrado Produtos Agrícolas E Assistência Técnica Ltda.</t>
-  </si>
-  <si>
-    <t>Yure De Andrade Barbosa</t>
-  </si>
-  <si>
-    <t>PATOS DE MINAS</t>
-  </si>
-  <si>
-    <t>MG</t>
-  </si>
-  <si>
-    <t>1ª Instância</t>
-  </si>
-  <si>
-    <t>R$             339.933,31</t>
-  </si>
-  <si>
-    <t>KBM</t>
-  </si>
-  <si>
-    <t>VRO</t>
-  </si>
-  <si>
-    <t>Presencial | Preposto - Cecíllia Vaz Maciel cecilliamaciel123@hotmail.com (34)9840-57340</t>
+    <t>0010351-61.2025.5.15.0083</t>
+  </si>
+  <si>
+    <t>Fernando Jose Haas</t>
+  </si>
+  <si>
+    <t>R$             359.951,72</t>
+  </si>
+  <si>
+    <t>Correspondente - Camila Cruz</t>
+  </si>
+  <si>
+    <t>0000446-02.2026.5.09.0071</t>
+  </si>
+  <si>
+    <t>Companhia Act De Participações E Companhia Aix De Participações</t>
+  </si>
+  <si>
+    <t>Antonio Marcos Da Silva</t>
+  </si>
+  <si>
+    <t>CASCAVEL</t>
+  </si>
+  <si>
+    <t>PR</t>
+  </si>
+  <si>
+    <t>R$             565.000,00</t>
+  </si>
+  <si>
+    <t>ECO</t>
+  </si>
+  <si>
+    <t>https://url.trt9.jus.br/d0sil ID da Reunião: 85970264719 Senha: B8Wj59zXwk</t>
+  </si>
+  <si>
+    <t>0020065-97.2026.5.04.0121</t>
+  </si>
+  <si>
+    <t>Fertilizantes Heringer S.A. - Em Recuperacao Judicial</t>
+  </si>
+  <si>
+    <t>Wendell Moraes</t>
+  </si>
+  <si>
+    <t>R$               17.122,15</t>
+  </si>
+  <si>
+    <t>Presencial | Advogada - LUCIANE VEIGA COZZA NEVES lucianecozza@gmail.com 53984740466</t>
+  </si>
+  <si>
+    <t>0000449-54.2026.5.09.0071</t>
+  </si>
+  <si>
+    <t>Gilmar Lourenco</t>
+  </si>
+  <si>
+    <t>R$             320.000,00</t>
+  </si>
+  <si>
+    <t>https://url.trt9.jus.br/z4d6z ID da Reunião: 83957099956 Senha: PS2cloJeWE</t>
+  </si>
+  <si>
+    <t>1000878-74.2026.5.02.0434</t>
+  </si>
+  <si>
+    <t>Varnei De Jesus Da Silva</t>
+  </si>
+  <si>
+    <t>R$             206.808,97</t>
+  </si>
+  <si>
+    <t>0011238-08.2026.5.15.0084</t>
+  </si>
+  <si>
+    <t>Leonardo Rodolfo De Carvalho</t>
+  </si>
+  <si>
+    <t>R$             277.509,87</t>
+  </si>
+  <si>
+    <t>0010598-92.2026.5.03.0066</t>
+  </si>
+  <si>
+    <t>Fertilizantes Heringer S.A</t>
+  </si>
+  <si>
+    <t>Marcos Paulo Da Silva</t>
+  </si>
+  <si>
+    <t>MANHUAÇU</t>
+  </si>
+  <si>
+    <t>R$               62.608,11</t>
+  </si>
+  <si>
+    <t>https://trt3-jus-br.zoom.us/my/varamanhuacu</t>
+  </si>
+  <si>
+    <t>0010997-58.2023.5.15.0013</t>
+  </si>
+  <si>
+    <t>Anderson Deive Rodrigues Alves</t>
+  </si>
+  <si>
+    <t>Marcos Eduardo Ribeiro</t>
+  </si>
+  <si>
+    <t>link pendente</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -294,6 +719,12 @@
     <font>
       <sz val="9"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF467886"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -385,7 +816,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -410,7 +841,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -747,8 +1178,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{899485F7-6014-4843-853A-16D038A1E16A}">
-  <dimension ref="A1:R7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3180D954-4CED-4BC0-8D47-0316A0151365}">
+  <dimension ref="A1:R27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:18" ht="60" x14ac:dyDescent="0.3">
@@ -807,346 +1238,1479 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4">
-        <v>103665</v>
+        <v>104370</v>
       </c>
       <c r="B2" s="5">
-        <v>46311</v>
+        <v>46315</v>
       </c>
       <c r="C2" s="6">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="L2" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M2" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N2" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="O2" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="P2" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q2" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="R2" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="4">
+        <v>105645</v>
+      </c>
+      <c r="B3" s="5">
+        <v>46315</v>
+      </c>
+      <c r="C3" s="6">
+        <v>0.34375</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M3" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N3" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="O3" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="P3" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q3" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="R3" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="4">
+        <v>103763</v>
+      </c>
+      <c r="B4" s="5">
+        <v>46315</v>
+      </c>
+      <c r="C4" s="6">
         <v>0.3611111111111111</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D4" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M4" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N4" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="O4" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="P4" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q4" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="R4" s="8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" ht="231" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="4">
+        <v>100203</v>
+      </c>
+      <c r="B5" s="5">
+        <v>46315</v>
+      </c>
+      <c r="C5" s="6">
+        <v>0.375</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M5" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N5" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="O5" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="P5" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q5" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="R5" s="8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="4">
+        <v>103482</v>
+      </c>
+      <c r="B6" s="5">
+        <v>46315</v>
+      </c>
+      <c r="C6" s="6">
+        <v>0.39861111111111114</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M6" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N6" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="O6" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="P6" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q6" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="R6" s="8" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="4">
+        <v>105412</v>
+      </c>
+      <c r="B7" s="5">
+        <v>46315</v>
+      </c>
+      <c r="C7" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M7" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N7" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="O7" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="P7" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q7" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="R7" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="245.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="4">
+        <v>104465</v>
+      </c>
+      <c r="B8" s="5">
+        <v>46315</v>
+      </c>
+      <c r="C8" s="6">
+        <v>0.43055555555555558</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M8" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N8" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="O8" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="P8" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q8" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="R8" s="8" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="84.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="4">
+        <v>104536</v>
+      </c>
+      <c r="B9" s="5">
+        <v>46315</v>
+      </c>
+      <c r="C9" s="6">
+        <v>0.44097222222222221</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M9" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N9" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="O9" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="P9" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q9" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="R9" s="7" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="231" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="4">
+        <v>100631</v>
+      </c>
+      <c r="B10" s="5">
+        <v>46315</v>
+      </c>
+      <c r="C10" s="6">
+        <v>0.49375000000000002</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="F10" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="G10" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="L10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M10" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N10" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="O10" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="P10" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q10" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="R10" s="8" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="4">
+        <v>103363</v>
+      </c>
+      <c r="B11" s="5">
+        <v>46315</v>
+      </c>
+      <c r="C11" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M11" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N11" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="O11" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="P11" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q11" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="R11" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="4">
+        <v>101906</v>
+      </c>
+      <c r="B12" s="5">
+        <v>46315</v>
+      </c>
+      <c r="C12" s="6">
+        <v>0.52777777777777779</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="L12" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M12" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N12" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="O12" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="P12" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q12" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="R12" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="231" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="4">
+        <v>97489</v>
+      </c>
+      <c r="B13" s="5">
+        <v>46315</v>
+      </c>
+      <c r="C13" s="6">
+        <v>0.5625</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J13" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="L13" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M13" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N13" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="O13" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="P13" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q13" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="R13" s="8" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="245.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="4">
+        <v>100464</v>
+      </c>
+      <c r="B14" s="5">
+        <v>46315</v>
+      </c>
+      <c r="C14" s="6">
+        <v>0.56944444444444442</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J14" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="L14" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M14" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N14" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="O14" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="P14" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q14" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="R14" s="8" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="202.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="4">
+        <v>105903</v>
+      </c>
+      <c r="B15" s="5">
+        <v>46315</v>
+      </c>
+      <c r="C15" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="J15" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="L15" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M15" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N15" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="O15" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="P15" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q15" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="R15" s="8" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="245.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="4">
+        <v>104567</v>
+      </c>
+      <c r="B16" s="5">
+        <v>46315</v>
+      </c>
+      <c r="C16" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="H16" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="I16" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="J16" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="K16" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="L16" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M16" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N16" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="O16" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="P16" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q16" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="R16" s="8" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="204.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="4">
+        <v>103098</v>
+      </c>
+      <c r="B17" s="5">
+        <v>46315</v>
+      </c>
+      <c r="C17" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="J17" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="L17" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M17" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N17" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="O17" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="P17" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q17" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="R17" s="7" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="130.19999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="4">
+        <v>103003</v>
+      </c>
+      <c r="B18" s="5">
+        <v>46315</v>
+      </c>
+      <c r="C18" s="6">
+        <v>0.58402777777777781</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="I18" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="J18" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="K18" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="L18" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="M18" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="7" t="s">
+      <c r="N18" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="O18" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="P18" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q18" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="R18" s="8" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="4">
+        <v>100103</v>
+      </c>
+      <c r="B19" s="5">
+        <v>46315</v>
+      </c>
+      <c r="C19" s="6">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="L19" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M19" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N19" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="O19" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="P19" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q19" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="R19" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" ht="144.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="4">
+        <v>104551</v>
+      </c>
+      <c r="B20" s="5">
+        <v>46315</v>
+      </c>
+      <c r="C20" s="6">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="I20" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="J20" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="L20" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M20" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N20" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="O20" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="P20" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="Q20" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="R20" s="8" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" ht="187.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="4">
+        <v>103890</v>
+      </c>
+      <c r="B21" s="5">
+        <v>46315</v>
+      </c>
+      <c r="C21" s="6">
+        <v>0.625</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="K21" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="L21" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M21" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N21" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="O21" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="L2" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="M2" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="N2" s="7" t="s">
+      <c r="P21" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q21" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="R21" s="8" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" ht="144.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="4">
+        <v>104552</v>
+      </c>
+      <c r="B22" s="5">
+        <v>46315</v>
+      </c>
+      <c r="C22" s="6">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="I22" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="J22" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="K22" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="L22" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M22" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N22" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="O22" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="P22" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="Q22" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="R22" s="8" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="4">
+        <v>104984</v>
+      </c>
+      <c r="B23" s="5">
+        <v>46315</v>
+      </c>
+      <c r="C23" s="6">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="F23" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="O2" s="7" t="s">
+      <c r="G23" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="H23" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="P2" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q2" s="7" t="s">
+      <c r="I23" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J23" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="K23" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="L23" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M23" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N23" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="O23" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="R2" s="7" t="s">
+      <c r="P23" s="7" t="s">
         <v>32</v>
       </c>
+      <c r="Q23" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="R23" s="7" t="s">
+        <v>55</v>
+      </c>
     </row>
-    <row r="3" spans="1:18" ht="245.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="4">
-        <v>104472</v>
-      </c>
-      <c r="B3" s="5">
-        <v>46311</v>
-      </c>
-      <c r="C3" s="6">
-        <v>0.36805555555555558</v>
-      </c>
-      <c r="D3" s="7" t="s">
+    <row r="24" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="4">
+        <v>105307</v>
+      </c>
+      <c r="B24" s="5">
+        <v>46315</v>
+      </c>
+      <c r="C24" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D24" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E3" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F3" s="7" t="s">
+      <c r="E24" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="F24" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="G3" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="H3" s="7" t="s">
+      <c r="G24" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="H24" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I24" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J24" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="L24" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J3" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="K3" s="7" t="s">
+      <c r="M24" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N24" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="O24" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="P24" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q24" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="R24" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" ht="87" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="4">
+        <v>105566</v>
+      </c>
+      <c r="B25" s="5">
+        <v>46315</v>
+      </c>
+      <c r="C25" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="I25" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="J25" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="K25" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="L25" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M25" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N25" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="O25" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="L3" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="M3" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="N3" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="O3" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="P3" s="7" t="s">
+      <c r="P25" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q25" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="R25" s="8" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="4">
+        <v>100844</v>
+      </c>
+      <c r="B26" s="5">
+        <v>46315</v>
+      </c>
+      <c r="C26" s="6">
+        <v>0.6875</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="I26" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J26" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K26" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="L26" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M26" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N26" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="O26" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="Q3" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="R3" s="8" t="s">
-        <v>43</v>
+      <c r="P26" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q26" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="R26" s="7" t="s">
+        <v>207</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="4">
-        <v>104784</v>
-      </c>
-      <c r="B4" s="5">
-        <v>46311</v>
-      </c>
-      <c r="C4" s="6">
-        <v>0.375</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="F4" s="7" t="s">
+    <row r="27" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="4">
+        <v>94351</v>
+      </c>
+      <c r="B27" s="5">
+        <v>46315</v>
+      </c>
+      <c r="C27" s="6">
+        <v>0.6875</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="I27" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="I4" s="7" t="s">
+      <c r="J27" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K27" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="L27" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="M27" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="K4" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="L4" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="M4" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="N4" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="O4" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="P4" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q4" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="R4" s="7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="4">
-        <v>105557</v>
-      </c>
-      <c r="B5" s="5">
-        <v>46311</v>
-      </c>
-      <c r="C5" s="6">
-        <v>0.40972222222222221</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="L5" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="M5" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="N5" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="O5" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="P5" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q5" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="R5" s="7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" ht="192.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="4">
-        <v>104321</v>
-      </c>
-      <c r="B6" s="5">
-        <v>46311</v>
-      </c>
-      <c r="C6" s="6">
-        <v>0.42708333333333331</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="K6" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="L6" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="M6" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="N6" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="O6" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="P6" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q6" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="R6" s="7" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" ht="173.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="4">
-        <v>101625</v>
-      </c>
-      <c r="B7" s="5">
-        <v>46311</v>
-      </c>
-      <c r="C7" s="6">
-        <v>0.4375</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="L7" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="M7" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="N7" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="O7" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="P7" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q7" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="R7" s="8" t="s">
-        <v>76</v>
+      <c r="N27" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="O27" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="P27" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q27" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="R27" s="7" t="s">
+        <v>207</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:R27" xr:uid="{3180D954-4CED-4BC0-8D47-0316A0151365}"/>
   <hyperlinks>
-    <hyperlink ref="R3" r:id="rId1" display="https://trt2-jus-br.zoom.us/j/84763743950?pwd=HBCpStvQgJxW9bsUHzE1NafpSjFa2m.1%20ID%20da%20reunião:%20847%206374%203950%20Senha%20de%20acesso:%20vtaruja01" xr:uid="{D7C8DB20-8FE1-41E9-AAE3-CCFB66A778C5}"/>
-    <hyperlink ref="R7" r:id="rId2" display="mailto:cecilliamaciel123@hotmail.com" xr:uid="{D0E37E44-FB9D-4471-AE1A-9253A2929F73}"/>
+    <hyperlink ref="R4" r:id="rId1" xr:uid="{5E3A2F07-2A1E-4913-BCD3-B7BE89E282A2}"/>
+    <hyperlink ref="R5" r:id="rId2" display="https://trt15-jus-br.zoom.us/j/85339761227?pwd=9098ZbUufpnfiuDdFCDYtoCxKs12aD.1%20ID%20da%20reunião:%20853%203976%201227%20Senha:%20006441" xr:uid="{F0AC805D-44A6-4F2B-A10B-301608C370D9}"/>
+    <hyperlink ref="R6" r:id="rId3" xr:uid="{D1CAAE7A-BA13-4B8B-AC1C-540DDD3D02CC}"/>
+    <hyperlink ref="R8" r:id="rId4" display="https://trt15-jus-br.zoom.us/j/4525285196?pwd=cG1ieCtlVVdHZERxcVRTM2lzSGt3dz09%20ID%20da%20reunião:%20452%20528%205196%20Senha%20de%20acesso:%20702632" xr:uid="{8C9AE7FA-3E60-4EDE-A579-A4B51B65F25A}"/>
+    <hyperlink ref="R10" r:id="rId5" display="https://us02web.zoom.us/j/5370769847?pwd=SFJvS0RITzJHbGtlUjUveVpqV0Rrdz09%20Id%20da%20reunião:%20537%20076%209847%20Senha%20da%20sala:%20151507" xr:uid="{ED8F0215-F19B-4A3F-8242-6621E6546797}"/>
+    <hyperlink ref="R13" r:id="rId6" display="https://trt15-jus-br.zoom.us/j/84349133108?pwd=rhlBY7X5LFPEEJm6Jmapg526N0IlEm.1%20ID%20da%20reunião:%20843%204913%203108%20Senha:%20614191" xr:uid="{69EC91B3-3B93-4B9D-81BA-CF92F61300DD}"/>
+    <hyperlink ref="R14" r:id="rId7" display="https://trt2-jus-br.zoom.us/j/83766953133?pwd=nhJnFb0XkEmrNGNrJJb8WUSQoDddyZ.1%20ID%20da%20reunião:%20837%206695%203133%20Senha%20de%20acesso:%20386774" xr:uid="{3C396CED-5D42-4FA4-A37F-CEF4E3C9829D}"/>
+    <hyperlink ref="R15" r:id="rId8" display="mailto:grazielleadvocacia@gmail.com" xr:uid="{528DFA7B-C87D-4D3C-8AE2-7213D62BE4BC}"/>
+    <hyperlink ref="R16" r:id="rId9" display="https://trt15-jus-br.zoom.us/j/87527564652?pwd=d3YrZ2diWXk5UjgzbmVkNExteWVMQT09%20ID%20da%20reunião:%20875%202756%204652%20Senha%20de%20acesso:%20246680" xr:uid="{957F522D-EC15-44F0-A929-CB7DCC79FFB3}"/>
+    <hyperlink ref="R18" r:id="rId10" xr:uid="{74462791-8EAA-41AF-852E-D5393EA4C881}"/>
+    <hyperlink ref="R20" r:id="rId11" xr:uid="{3D5D2245-A8A6-4F46-82C9-93820F127BEA}"/>
+    <hyperlink ref="R21" r:id="rId12" display="mailto:lucianecozza@gmail.com" xr:uid="{9663CBCB-BAB6-4481-96F9-1168C1862E27}"/>
+    <hyperlink ref="R22" r:id="rId13" xr:uid="{E2796B07-DF4A-4957-BCCA-B6E2386487D9}"/>
+    <hyperlink ref="R25" r:id="rId14" xr:uid="{EFD258B2-DF56-4433-A542-5B7162982596}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/Pauta_de_Audiencias.xlsx
+++ b/Pauta_de_Audiencias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\blu\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5DB12E36-5FCC-40A3-9D1C-72A35A1AD21E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{435E416E-2578-420A-B06D-D4446FC76848}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29130" yWindow="4095" windowWidth="21600" windowHeight="11100" xr2:uid="{15D051F1-4BB8-4310-A08C-46B6246D8E3B}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DCD763F2-081B-471F-BC06-16FA6600FB3D}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="152">
   <si>
     <t>Código P&amp;C</t>
   </si>
@@ -95,22 +95,270 @@
     <t>Link/Observações</t>
   </si>
   <si>
+    <t>Audiência Instrução - Telepresencial</t>
+  </si>
+  <si>
+    <t>0011186-18.2026.5.15.0082</t>
+  </si>
+  <si>
+    <t>Moema Bioenergia S.A. - Moema</t>
+  </si>
+  <si>
+    <t>Adilson Maximiano Nogueira</t>
+  </si>
+  <si>
+    <t>SÃO JOSÉ DO RIO PRETO</t>
+  </si>
+  <si>
+    <t>SP</t>
+  </si>
+  <si>
+    <t>03ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>Instrução</t>
+  </si>
+  <si>
+    <t>Reclamação Trabalhista</t>
+  </si>
+  <si>
+    <t>CENTRAL</t>
+  </si>
+  <si>
+    <t>R$             112.227,97</t>
+  </si>
+  <si>
+    <t>Grupo E2</t>
+  </si>
+  <si>
+    <t>MBF</t>
+  </si>
+  <si>
+    <t>RYL</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/81757243738?pwd=UXAvdEpveHlrNU05M2ZsZnRrYy9Vdz09 ID DA REUNIÃO: 817 5724 3738 SENHA: 954332</t>
+  </si>
+  <si>
     <t>Audiência Inicial -  Telepresencial</t>
   </si>
   <si>
-    <t>0000864-54.2026.5.23.0101</t>
+    <t>0011084-92.2026.5.03.0061</t>
+  </si>
+  <si>
+    <t>Mahle Metal Leve S.A.</t>
+  </si>
+  <si>
+    <t>Leandro Dos Santos</t>
+  </si>
+  <si>
+    <t>ITAJUBÁ</t>
+  </si>
+  <si>
+    <t>MG</t>
+  </si>
+  <si>
+    <t>VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>Inicial</t>
+  </si>
+  <si>
+    <t>Ação de Consignação em Pagamento</t>
+  </si>
+  <si>
+    <t>R$                 3.262,69</t>
+  </si>
+  <si>
+    <t>Grupo E1</t>
+  </si>
+  <si>
+    <t>TLI</t>
+  </si>
+  <si>
+    <t>PSI</t>
+  </si>
+  <si>
+    <t>https://trt3-jus-br.zoom.us/my/vt.itajuba</t>
+  </si>
+  <si>
+    <t>Audiência Inicial - Telepresencial</t>
+  </si>
+  <si>
+    <t>0012242-06.2026.5.15.0044</t>
+  </si>
+  <si>
+    <t>Alessandre Lopes Da Cruz</t>
+  </si>
+  <si>
+    <t>02ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$          2.819.517,97</t>
+  </si>
+  <si>
+    <t>ARC</t>
+  </si>
+  <si>
+    <t>Audiência Una - Presencial</t>
+  </si>
+  <si>
+    <t>0001518-55.2026.5.07.0014</t>
+  </si>
+  <si>
+    <t>Companhia Act De Participações E Companhia Aix De Participações.</t>
+  </si>
+  <si>
+    <t>Ana Angelica Nunes Nogueira Tavares</t>
+  </si>
+  <si>
+    <t>FORTALEZA</t>
+  </si>
+  <si>
+    <t>CE</t>
+  </si>
+  <si>
+    <t>14ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             100.200,00</t>
+  </si>
+  <si>
+    <t>Grupo C1</t>
+  </si>
+  <si>
+    <t>Correspondente - doc9</t>
+  </si>
+  <si>
+    <t>VSI</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Presencial | Advogado - Ikaro Handersson da Costa Farias </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF467886"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>ikaro.handersson@gmail.com</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 85996385656 | Preposto - Ana Paula Barros Santos </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF467886"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>anapaulabarrossantos27@gmail.com</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (85)9982-60369</t>
+    </r>
+  </si>
+  <si>
+    <t>Audiência Instrução - Presencial</t>
+  </si>
+  <si>
+    <t>0011691-29.2025.5.15.0119</t>
+  </si>
+  <si>
+    <t>Pilkington Brasil Ltda.</t>
+  </si>
+  <si>
+    <t>Iraldenir De Oliveira Carneiro</t>
+  </si>
+  <si>
+    <t>CAÇAPAVA</t>
+  </si>
+  <si>
+    <t>R$               10.272,84</t>
+  </si>
+  <si>
+    <t>AAP</t>
+  </si>
+  <si>
+    <t>Presencial</t>
+  </si>
+  <si>
+    <t>1001239-97.2026.5.02.0432</t>
+  </si>
+  <si>
+    <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
+  </si>
+  <si>
+    <t>Elvis Filgueira De Almeida</t>
+  </si>
+  <si>
+    <t>SANTO ANDRÉ</t>
+  </si>
+  <si>
+    <t>R$             253.042,21</t>
+  </si>
+  <si>
+    <t>Grupo B1</t>
+  </si>
+  <si>
+    <t>GSM</t>
+  </si>
+  <si>
+    <t>BSO</t>
+  </si>
+  <si>
+    <t>0011577-90.2025.5.15.0119</t>
+  </si>
+  <si>
+    <t>Luis Jorge De Oliveira</t>
+  </si>
+  <si>
+    <t>R$                 3.658,27</t>
+  </si>
+  <si>
+    <t>0011552-77.2025.5.15.0119</t>
+  </si>
+  <si>
+    <t>Ernani Rita De Oliveira</t>
+  </si>
+  <si>
+    <t>R$               56.941,59</t>
+  </si>
+  <si>
+    <t>0011549-25.2025.5.15.0119</t>
+  </si>
+  <si>
+    <t>Marlene Santos Marcolino De Oliveira</t>
+  </si>
+  <si>
+    <t>R$               32.125,08</t>
+  </si>
+  <si>
+    <t>0010703-78.2026.5.03.0063</t>
   </si>
   <si>
     <t>Syngenta Seeds Ltda.</t>
   </si>
   <si>
-    <t>Iranildo Ferreira Alves Junior</t>
-  </si>
-  <si>
-    <t>LUCAS DO RIO VERDE</t>
-  </si>
-  <si>
-    <t>MT</t>
+    <t>Robert Da Silva Vilela</t>
+  </si>
+  <si>
+    <t>ITUIUTABA</t>
   </si>
   <si>
     <t>01ª VARA DO TRABALHO</t>
@@ -119,203 +367,179 @@
     <t>1ª Instância</t>
   </si>
   <si>
-    <t>Reclamação Trabalhista</t>
-  </si>
-  <si>
-    <t>CENTRAL</t>
-  </si>
-  <si>
-    <t>R$               71.937,00</t>
-  </si>
-  <si>
-    <t>Grupo E1</t>
-  </si>
-  <si>
-    <t>PSI</t>
-  </si>
-  <si>
-    <t>GVM</t>
-  </si>
-  <si>
-    <t>https://trt23-jus-br.zoom.us/my/vtlucas1?pwd=RGxVbkdtRVE2TkllOHpmcEZ2NFd5UT09</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Audiência Una - Presencial</t>
-  </si>
-  <si>
-    <t>1001652-34.2026.5.02.0037</t>
-  </si>
-  <si>
-    <t>Maricy Ciaccio Sichero</t>
-  </si>
-  <si>
-    <t>Ana Marilia Cassiano de Lima</t>
+    <t>R$               78.650,00</t>
+  </si>
+  <si>
+    <t>JRM</t>
+  </si>
+  <si>
+    <t>0011570-98.2025.5.15.0119</t>
+  </si>
+  <si>
+    <t>Martony Sampaio Ribeiro</t>
+  </si>
+  <si>
+    <t>R$               45.250,29</t>
+  </si>
+  <si>
+    <t>1001942-19.2026.5.02.0435</t>
+  </si>
+  <si>
+    <t>Ryan Furtado Nascimento</t>
+  </si>
+  <si>
+    <t>05ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             157.873,36</t>
+  </si>
+  <si>
+    <t>Correspondente - Hebert</t>
+  </si>
+  <si>
+    <t>NRG</t>
+  </si>
+  <si>
+    <t>1001442-50.2026.5.02.0435</t>
+  </si>
+  <si>
+    <t>Luiz Gustavo Da Silva Buchmeier</t>
+  </si>
+  <si>
+    <t>R$                 7.632,80</t>
+  </si>
+  <si>
+    <t>RFE</t>
+  </si>
+  <si>
+    <t>1001441-71.2026.5.02.0433</t>
+  </si>
+  <si>
+    <t>Adonias Soares Da Silva</t>
+  </si>
+  <si>
+    <t>R$               51.027,24</t>
+  </si>
+  <si>
+    <t>LMI</t>
+  </si>
+  <si>
+    <t>Audiência de Conciliação - Telepresencial</t>
+  </si>
+  <si>
+    <t>0001305-77.2026.5.09.0019</t>
+  </si>
+  <si>
+    <t>Smartfit Escola De Ginastica E Danca S.A. E Bioritmo Franqueadora Ltda.</t>
+  </si>
+  <si>
+    <t>Neusa Aparecida Longuini</t>
+  </si>
+  <si>
+    <t>LONDRINA</t>
+  </si>
+  <si>
+    <t>PR</t>
+  </si>
+  <si>
+    <t>CEJUSC</t>
+  </si>
+  <si>
+    <t>Reclamação Pré-processual</t>
+  </si>
+  <si>
+    <t>R$          2.418.775,20</t>
+  </si>
+  <si>
+    <t>Grupo A3</t>
+  </si>
+  <si>
+    <t>PBS</t>
+  </si>
+  <si>
+    <t>https://url.trt9.jus.br/9kq15 ID da reunião: 82281762201 Senha de acesso: bOs5jU2nP7</t>
+  </si>
+  <si>
+    <t>Audiência Una - Telepresencial</t>
+  </si>
+  <si>
+    <t>1001886-19.2026.5.02.0521</t>
+  </si>
+  <si>
+    <t>Mahle Thermal And Fluid Systems Brazil Ltda.</t>
+  </si>
+  <si>
+    <t>Pamela Santana Borges Da Silva</t>
+  </si>
+  <si>
+    <t>ARUJÁ</t>
+  </si>
+  <si>
+    <t>R$                 5.367,99</t>
+  </si>
+  <si>
+    <t>https://trt2-jus-br.zoom.us/j/87224949005?pwd=JbmIgbUoMHoknaZ0IapCSsc9JsarNK.1 ID da reunião: 872 2494 9005 Senha de acesso: vtaruja01</t>
+  </si>
+  <si>
+    <t>1001426-12.2025.5.02.0054</t>
+  </si>
+  <si>
+    <t>Telefonica Brasil S.A.</t>
+  </si>
+  <si>
+    <t>Flavia Dias De Oliveira Faria</t>
   </si>
   <si>
     <t>SÃO PAULO</t>
   </si>
   <si>
-    <t>SP</t>
-  </si>
-  <si>
-    <t>37ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>Instrução</t>
-  </si>
-  <si>
-    <t>R$               35.016,39</t>
-  </si>
-  <si>
-    <t>Grupo C1</t>
-  </si>
-  <si>
-    <t>NBG</t>
-  </si>
-  <si>
-    <t>Presencial</t>
-  </si>
-  <si>
-    <t>Audiência de Instrução - Telepresencial</t>
-  </si>
-  <si>
-    <t>1000642-34.2026.5.02.0431</t>
-  </si>
-  <si>
-    <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
-  </si>
-  <si>
-    <t>Bruno Alves Da Silva</t>
-  </si>
-  <si>
-    <t>SÃO CAETANO DO SUL</t>
-  </si>
-  <si>
-    <t>03ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$          1.620.000,00</t>
-  </si>
-  <si>
-    <t>Grupo B1</t>
-  </si>
-  <si>
-    <t>RFE</t>
-  </si>
-  <si>
-    <t>https://trt2-jus-br.zoom.us/j/83190569296?pwd=YjNuL2d1T1dwNzJ0RGFjR0kveEpmQT09 ID da reunião: 831 9056 9296 Senha de acesso: sala2scs</t>
-  </si>
-  <si>
-    <t>Audiência Inicial - Telepresencial</t>
-  </si>
-  <si>
-    <t>0000770-07.2026.5.23.0037</t>
-  </si>
-  <si>
-    <t>Inpasa Agroindustrial S/A.</t>
-  </si>
-  <si>
-    <t>Bruna Silva De Oliveira</t>
-  </si>
-  <si>
-    <t>SINOP</t>
-  </si>
-  <si>
-    <t>02ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$               70.111,57</t>
-  </si>
-  <si>
-    <t>Grupo E2</t>
-  </si>
-  <si>
-    <t>RRU</t>
-  </si>
-  <si>
-    <t>BTF</t>
-  </si>
-  <si>
-    <t>https://trt23-jus-br.zoom.us/j/3430107870?pwd=ZXR4a3MyUndBcjk0bnBDZ1lINThaQT09 ID da reunião: 343 010 7870 Senha de acesso: S6^vWi</t>
-  </si>
-  <si>
-    <t>Audiência Instrução - Presencial</t>
-  </si>
-  <si>
-    <t>1000618-51.2026.5.02.0319</t>
-  </si>
-  <si>
-    <t>Mahle Thermal And Fluid Systems Brazil Ltda.</t>
-  </si>
-  <si>
-    <t>Zivanildo Bezerra Barbosa</t>
-  </si>
-  <si>
-    <t>GUARULHOS</t>
-  </si>
-  <si>
-    <t>09ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$             371.655,98</t>
-  </si>
-  <si>
-    <t>Correspondente - Carlos Florian</t>
-  </si>
-  <si>
-    <t>TLI</t>
-  </si>
-  <si>
-    <t>Presencial | Advogada - Dra. Ana Caroline, (11) 96079-1682</t>
-  </si>
-  <si>
-    <t>Audiência Inicial -  Presencial</t>
-  </si>
-  <si>
-    <t>1001125-52.2026.5.02.0435</t>
-  </si>
-  <si>
-    <t>Junior Duarte Da Silva De Lima</t>
-  </si>
-  <si>
-    <t>SANTO ANDRÉ</t>
-  </si>
-  <si>
-    <t>R$             247.196,70</t>
-  </si>
-  <si>
-    <t>Correspondente - Hebert</t>
-  </si>
-  <si>
-    <t>BSO</t>
-  </si>
-  <si>
-    <t>1001761-88.2025.5.02.0035</t>
-  </si>
-  <si>
-    <t>Willian Marcelino</t>
-  </si>
-  <si>
-    <t>35ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$             573.120,80</t>
-  </si>
-  <si>
-    <t>ANB</t>
-  </si>
-  <si>
-    <t>GSM</t>
+    <t>54ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$          2.092.449,00</t>
+  </si>
+  <si>
+    <t>TFR</t>
+  </si>
+  <si>
+    <t>0001611-58.2025.5.09.0673</t>
+  </si>
+  <si>
+    <t>Syngenta Comercial Agrícola Ltda.</t>
+  </si>
+  <si>
+    <t>Helio Ricardo Bruneri</t>
+  </si>
+  <si>
+    <t>06ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             249.131,93</t>
+  </si>
+  <si>
+    <t>VRO</t>
+  </si>
+  <si>
+    <t>0011431-10.2025.5.15.0132</t>
+  </si>
+  <si>
+    <t>Marcos Douglas Dos Santos Goulart</t>
+  </si>
+  <si>
+    <t>SÃO JOSÉ DOS CAMPOS</t>
+  </si>
+  <si>
+    <t>R$             376.645,91</t>
+  </si>
+  <si>
+    <t>Presencial | Advogado - Ricardo de Souza Gonçalves ricardosgoncalves@live.com (12)9810-41449</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -333,6 +557,12 @@
     <font>
       <sz val="9"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF467886"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -424,7 +654,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -449,7 +679,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -786,8 +1016,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FA5C575-525D-41DB-88BC-DA2048DBE0C9}">
-  <dimension ref="A1:R8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BCD8069-E596-41FB-A0B1-C8286F6CD83C}">
+  <dimension ref="A1:R20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:18" ht="60" x14ac:dyDescent="0.3">
@@ -846,15 +1076,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="144.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" ht="231" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4">
-        <v>106051</v>
+        <v>104994</v>
       </c>
       <c r="B2" s="5">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="C2" s="6">
-        <v>0.34375</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>18</v>
@@ -902,42 +1132,42 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
+    <row r="3" spans="1:18" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="4">
+        <v>106674</v>
+      </c>
+      <c r="B3" s="5">
+        <v>46321</v>
+      </c>
+      <c r="C3" s="6">
+        <v>0.34027777777777779</v>
+      </c>
+      <c r="D3" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B3" s="5">
-        <v>46318</v>
-      </c>
-      <c r="C3" s="6">
-        <v>0.38194444444444442</v>
-      </c>
-      <c r="D3" s="7" t="s">
+      <c r="E3" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="F3" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="G3" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="H3" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="I3" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="J3" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="K3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="L3" s="7" t="s">
         <v>41</v>
-      </c>
-      <c r="L3" s="7" t="s">
-        <v>26</v>
       </c>
       <c r="M3" s="7" t="s">
         <v>27</v>
@@ -952,45 +1182,45 @@
         <v>44</v>
       </c>
       <c r="Q3" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="R3" s="7" t="s">
         <v>45</v>
       </c>
+      <c r="R3" s="8" t="s">
+        <v>46</v>
+      </c>
     </row>
-    <row r="4" spans="1:18" ht="245.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:18" ht="231" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4">
-        <v>104654</v>
+        <v>105784</v>
       </c>
       <c r="B4" s="5">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="C4" s="6">
-        <v>0.4236111111111111</v>
+        <v>0.375</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="G4" s="7" t="s">
         <v>49</v>
       </c>
       <c r="H4" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J4" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="I4" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>51</v>
-      </c>
       <c r="K4" s="7" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="L4" s="7" t="s">
         <v>26</v>
@@ -999,54 +1229,54 @@
         <v>27</v>
       </c>
       <c r="N4" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="O4" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P4" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="O4" s="7" t="s">
+      <c r="Q4" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="R4" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" ht="240.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="4">
+        <v>106718</v>
+      </c>
+      <c r="B5" s="5">
+        <v>46321</v>
+      </c>
+      <c r="C5" s="6">
+        <v>0.38194444444444442</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="P4" s="7" t="s">
+      <c r="E5" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="Q4" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="R4" s="8" t="s">
+      <c r="F5" s="7" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="5" spans="1:18" ht="245.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="4">
-        <v>105716</v>
-      </c>
-      <c r="B5" s="5">
-        <v>46318</v>
-      </c>
-      <c r="C5" s="6">
-        <v>0.4375</v>
-      </c>
-      <c r="D5" s="7" t="s">
+      <c r="G5" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="H5" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="I5" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="J5" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="H5" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>61</v>
-      </c>
       <c r="K5" s="7" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="L5" s="7" t="s">
         <v>26</v>
@@ -1055,54 +1285,54 @@
         <v>27</v>
       </c>
       <c r="N5" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="O5" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="P5" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="O5" s="7" t="s">
+      <c r="Q5" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="P5" s="7" t="s">
+      <c r="R5" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="Q5" s="7" t="s">
+    </row>
+    <row r="6" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="4">
+        <v>103635</v>
+      </c>
+      <c r="B6" s="5">
+        <v>46321</v>
+      </c>
+      <c r="C6" s="6">
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="R5" s="8" t="s">
+      <c r="E6" s="7" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="6" spans="1:18" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="4">
-        <v>104580</v>
-      </c>
-      <c r="B6" s="5">
-        <v>46318</v>
-      </c>
-      <c r="C6" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="D6" s="7" t="s">
+      <c r="F6" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="G6" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="H6" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="G6" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>71</v>
-      </c>
       <c r="I6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J6" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="7" t="s">
-        <v>72</v>
-      </c>
       <c r="K6" s="7" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="L6" s="7" t="s">
         <v>26</v>
@@ -1111,54 +1341,54 @@
         <v>27</v>
       </c>
       <c r="N6" s="7" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="O6" s="7" t="s">
         <v>29</v>
       </c>
       <c r="P6" s="7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="Q6" s="7" t="s">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="R6" s="7" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4">
-        <v>105256</v>
+        <v>105430</v>
       </c>
       <c r="B7" s="5">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="C7" s="6">
-        <v>0.51388888888888884</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="L7" s="7" t="s">
         <v>26</v>
@@ -1167,54 +1397,54 @@
         <v>27</v>
       </c>
       <c r="N7" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="O7" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="P7" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q7" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="R7" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="4">
+        <v>103434</v>
+      </c>
+      <c r="B8" s="5">
+        <v>46321</v>
+      </c>
+      <c r="C8" s="6">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E8" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="O7" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="P7" s="7" t="s">
+      <c r="F8" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="G8" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="Q7" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="R7" s="7" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="4">
-        <v>103266</v>
-      </c>
-      <c r="B8" s="5">
-        <v>46318</v>
-      </c>
-      <c r="C8" s="6">
-        <v>0.51388888888888884</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>85</v>
-      </c>
       <c r="H8" s="7" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="I8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J8" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="J8" s="7" t="s">
-        <v>86</v>
-      </c>
       <c r="K8" s="7" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="L8" s="7" t="s">
         <v>26</v>
@@ -1223,26 +1453,701 @@
         <v>27</v>
       </c>
       <c r="N8" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="O8" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P8" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q8" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="R8" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="4">
+        <v>103432</v>
+      </c>
+      <c r="B9" s="5">
+        <v>46321</v>
+      </c>
+      <c r="C9" s="6">
+        <v>0.40277777777777779</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M9" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N9" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="O9" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P9" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q9" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="R9" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="4">
+        <v>103428</v>
+      </c>
+      <c r="B10" s="5">
+        <v>46321</v>
+      </c>
+      <c r="C10" s="6">
+        <v>0.41319444444444442</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E10" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="O8" s="7" t="s">
+      <c r="F10" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L10" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M10" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N10" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="O10" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P10" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q10" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="R10" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="4">
+        <v>105581</v>
+      </c>
+      <c r="B11" s="5">
+        <v>46321</v>
+      </c>
+      <c r="C11" s="6">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M11" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N11" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="O11" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="P11" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q11" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="R11" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="4">
+        <v>103430</v>
+      </c>
+      <c r="B12" s="5">
+        <v>46321</v>
+      </c>
+      <c r="C12" s="6">
+        <v>0.43055555555555558</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L12" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M12" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N12" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="O12" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P12" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q12" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="R12" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="4">
+        <v>106323</v>
+      </c>
+      <c r="B13" s="5">
+        <v>46321</v>
+      </c>
+      <c r="C13" s="6">
+        <v>0.4375</v>
+      </c>
+      <c r="D13" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="P8" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q8" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="R8" s="7" t="s">
+      <c r="E13" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J13" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L13" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M13" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N13" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="O13" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="P13" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q13" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="R13" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="4">
+        <v>105627</v>
+      </c>
+      <c r="B14" s="5">
+        <v>46321</v>
+      </c>
+      <c r="C14" s="6">
+        <v>0.44444444444444442</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J14" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L14" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="M14" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N14" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="O14" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="P14" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q14" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="R14" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="4">
+        <v>105638</v>
+      </c>
+      <c r="B15" s="5">
+        <v>46321</v>
+      </c>
+      <c r="C15" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J15" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L15" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M15" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N15" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="O15" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="P15" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q15" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="R15" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="159" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="4">
+        <v>106665</v>
+      </c>
+      <c r="B16" s="5">
+        <v>46321</v>
+      </c>
+      <c r="C16" s="6">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="J16" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="K16" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="L16" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="M16" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N16" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="O16" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="P16" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q16" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="R16" s="8" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="245.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="4">
+        <v>105977</v>
+      </c>
+      <c r="B17" s="5">
+        <v>46321</v>
+      </c>
+      <c r="C17" s="6">
+        <v>0.59375</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J17" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="L17" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M17" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N17" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="O17" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="P17" s="7" t="s">
         <v>45</v>
+      </c>
+      <c r="Q17" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="R17" s="8" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="4">
+        <v>104374</v>
+      </c>
+      <c r="B18" s="5">
+        <v>46321</v>
+      </c>
+      <c r="C18" s="6">
+        <v>0.59722222222222221</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="I18" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J18" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L18" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M18" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N18" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="O18" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="P18" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q18" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="R18" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="4">
+        <v>103660</v>
+      </c>
+      <c r="B19" s="5">
+        <v>46321</v>
+      </c>
+      <c r="C19" s="6">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="L19" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M19" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N19" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="O19" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="P19" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q19" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="R19" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" ht="187.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="4">
+        <v>101865</v>
+      </c>
+      <c r="B20" s="5">
+        <v>46321</v>
+      </c>
+      <c r="C20" s="6">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="I20" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J20" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L20" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M20" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N20" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="O20" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P20" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q20" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="R20" s="8" t="s">
+        <v>151</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="R2" r:id="rId1" xr:uid="{E11FDC00-DB29-40EE-AC70-ACC67E5FBE3B}"/>
-    <hyperlink ref="R4" r:id="rId2" display="https://trt2-jus-br.zoom.us/j/83190569296?pwd=YjNuL2d1T1dwNzJ0RGFjR0kveEpmQT09%20ID%20da%20reunião:%20831%209056%209296%20Senha%20de%20acesso:%20sala2scs" xr:uid="{A918178C-3043-43F2-9310-6FE1A651DFBA}"/>
-    <hyperlink ref="R5" r:id="rId3" display="https://trt23-jus-br.zoom.us/j/3430107870?pwd=ZXR4a3MyUndBcjk0bnBDZ1lINThaQT09%20ID%20da%20reunião:%20343%20010%207870%20Senha%20de%20acesso:%20S6%5evWi" xr:uid="{EED5B41A-F611-40DB-9FC0-9038D3BA52AF}"/>
+    <hyperlink ref="R2" r:id="rId1" display="https://us02web.zoom.us/j/81757243738?pwd=UXAvdEpveHlrNU05M2ZsZnRrYy9Vdz09%20ID%20DA%20REUNIÃO:%20817%205724%203738%20SENHA:%20954332" xr:uid="{9339D929-3BF8-4217-9323-72D4549FEB39}"/>
+    <hyperlink ref="R3" r:id="rId2" xr:uid="{C38F8162-A764-4CC8-BD09-5868F4A72B0F}"/>
+    <hyperlink ref="R4" r:id="rId3" display="https://us02web.zoom.us/j/81757243738?pwd=UXAvdEpveHlrNU05M2ZsZnRrYy9Vdz09%20ID%20DA%20REUNIÃO:%20817%205724%203738%20SENHA:%20954332" xr:uid="{A36F819B-3E41-410D-B38E-809C0AB943D8}"/>
+    <hyperlink ref="R16" r:id="rId4" xr:uid="{457C9B3A-A868-4E99-93B9-E5C29FF409A2}"/>
+    <hyperlink ref="R17" r:id="rId5" display="https://trt2-jus-br.zoom.us/j/87224949005?pwd=JbmIgbUoMHoknaZ0IapCSsc9JsarNK.1%20ID%20da%20reunião:%20872%202494%209005%20Senha%20de%20acesso:%20vtaruja01" xr:uid="{6B461923-48A8-4084-B100-CEDB0FD06DB7}"/>
+    <hyperlink ref="R20" r:id="rId6" display="mailto:ricardosgoncalves@live.com" xr:uid="{CD3B731A-48AF-47AF-B7D0-49E5F513C740}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/Pauta_de_Audiencias.xlsx
+++ b/Pauta_de_Audiencias.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\blu\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{435E416E-2578-420A-B06D-D4446FC76848}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{168A89B5-15A8-49B6-B2A7-65065387B9E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DCD763F2-081B-471F-BC06-16FA6600FB3D}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{983DC53A-B337-4DA1-A7D8-F3264ADA8430}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="209">
   <si>
     <t>Código P&amp;C</t>
   </si>
@@ -95,146 +95,578 @@
     <t>Link/Observações</t>
   </si>
   <si>
+    <t>Audiência Una - Presencial</t>
+  </si>
+  <si>
+    <t>1001556-44.2026.5.02.0061</t>
+  </si>
+  <si>
+    <t>L. Sant'Angelo Pinturas Ltda</t>
+  </si>
+  <si>
+    <t>Marcos Leonio Fernandes De Queiroz</t>
+  </si>
+  <si>
+    <t>SÃO PAULO</t>
+  </si>
+  <si>
+    <t>SP</t>
+  </si>
+  <si>
+    <t>61ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>Instrução</t>
+  </si>
+  <si>
+    <t>Reclamação Trabalhista</t>
+  </si>
+  <si>
+    <t>CENTRAL</t>
+  </si>
+  <si>
+    <t>R$               32.163,75</t>
+  </si>
+  <si>
+    <t>Grupo E2</t>
+  </si>
+  <si>
+    <t>CAL</t>
+  </si>
+  <si>
+    <t>Presencial</t>
+  </si>
+  <si>
+    <t>Audiência Inicial -  Telepresencial</t>
+  </si>
+  <si>
+    <t>0000782-61.2026.5.05.0121</t>
+  </si>
+  <si>
+    <t>Salitre Fertilizantes Ltda.</t>
+  </si>
+  <si>
+    <t>Emerson Souza Dos Santos</t>
+  </si>
+  <si>
+    <t>CANDEIAS</t>
+  </si>
+  <si>
+    <t>BA</t>
+  </si>
+  <si>
+    <t>VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$               68.299,07</t>
+  </si>
+  <si>
+    <t>MBF</t>
+  </si>
+  <si>
+    <t>https://trt5-jus-br.zoom.us/my/sl1vtca</t>
+  </si>
+  <si>
+    <t>Audiência Instrução - Presencial</t>
+  </si>
+  <si>
+    <t>0012613-54.2024.5.15.0071</t>
+  </si>
+  <si>
+    <t>Mahle Metal Leve S.A.</t>
+  </si>
+  <si>
+    <t>Wanderson Cunha Coelho</t>
+  </si>
+  <si>
+    <t>MOGI GUAÇU</t>
+  </si>
+  <si>
+    <t>Central</t>
+  </si>
+  <si>
+    <t>R$               78.909,58</t>
+  </si>
+  <si>
+    <t>Grupo E1</t>
+  </si>
+  <si>
+    <t>Correspondente - Ana Carolina Teresani</t>
+  </si>
+  <si>
+    <t>PSI</t>
+  </si>
+  <si>
+    <t>0010035-84.2025.5.15.0071</t>
+  </si>
+  <si>
+    <t>Maurilio Guilherme Dippre Macedo</t>
+  </si>
+  <si>
+    <t>R$             230.000,00</t>
+  </si>
+  <si>
+    <t>1002252-70.2025.5.02.0205</t>
+  </si>
+  <si>
+    <t>Alpha1 Empreendimento Imobiliario Spe Ltda</t>
+  </si>
+  <si>
+    <t>Lucas Correia Grageiro</t>
+  </si>
+  <si>
+    <t>BARUERI</t>
+  </si>
+  <si>
+    <t>05ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>Conhecimento</t>
+  </si>
+  <si>
+    <t>R$               68.920,44</t>
+  </si>
+  <si>
+    <t>ARC</t>
+  </si>
+  <si>
+    <t>0017181-79.2025.5.15.0071</t>
+  </si>
+  <si>
+    <t>Ricardo Cesar Da Silva</t>
+  </si>
+  <si>
+    <t>Inicial</t>
+  </si>
+  <si>
+    <t>R$             501.217,75</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/5326391733?pwd=Qjc4RFBXWjZNbVd1bG5wNldjR3dWZz09</t>
+  </si>
+  <si>
+    <t>1000502-64.2026.5.02.0054</t>
+  </si>
+  <si>
+    <t>Telefonica Brasil S.A.</t>
+  </si>
+  <si>
+    <t>Barbara Servigne De Oliveira</t>
+  </si>
+  <si>
+    <t>54ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$          1.172.734,00</t>
+  </si>
+  <si>
+    <t>Grupo C1</t>
+  </si>
+  <si>
+    <t>TFR</t>
+  </si>
+  <si>
+    <t>0011014-18.2026.5.03.0080</t>
+  </si>
+  <si>
+    <t>Salitre Fertilizantes Ltda</t>
+  </si>
+  <si>
+    <t>Christian Monteiro Miranda</t>
+  </si>
+  <si>
+    <t>PATROCÍNIO</t>
+  </si>
+  <si>
+    <t>MG</t>
+  </si>
+  <si>
+    <t>R$             143.700,00</t>
+  </si>
+  <si>
+    <t>https://trt3-jus-br.zoom.us/my/vt.patrocinio</t>
+  </si>
+  <si>
+    <t>0011015-03.2026.5.03.0080</t>
+  </si>
+  <si>
+    <t>Yury Goncalves De Oliveira</t>
+  </si>
+  <si>
+    <t>R$               77.600,00</t>
+  </si>
+  <si>
+    <t>1001284-08.2026.5.02.0463</t>
+  </si>
+  <si>
+    <t>Companhia Brasileira De Cartuchos</t>
+  </si>
+  <si>
+    <t>Moises De Mattos Damazio</t>
+  </si>
+  <si>
+    <t>SÃO BERNARDO DO CAMPO</t>
+  </si>
+  <si>
+    <t>03ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             132.745,00</t>
+  </si>
+  <si>
+    <t>Grupo B3</t>
+  </si>
+  <si>
+    <t>LMI</t>
+  </si>
+  <si>
+    <t>0010799-97.2026.5.15.0083</t>
+  </si>
+  <si>
+    <t>Embraer S.A.</t>
+  </si>
+  <si>
+    <t>Carlos Alberto Moreira Dos Santos</t>
+  </si>
+  <si>
+    <t>SÃO JOSÉ DOS CAMPOS</t>
+  </si>
+  <si>
+    <t>R$             133.051,44</t>
+  </si>
+  <si>
+    <t>Grupo B2</t>
+  </si>
+  <si>
+    <t>VCR</t>
+  </si>
+  <si>
+    <t>1001154-14.2026.5.02.0432</t>
+  </si>
+  <si>
+    <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
+  </si>
+  <si>
+    <t>David Henrique Silva Fernandes</t>
+  </si>
+  <si>
+    <t>SANTO ANDRÉ</t>
+  </si>
+  <si>
+    <t>04ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$          1.194.597,35</t>
+  </si>
+  <si>
+    <t>Grupo B1</t>
+  </si>
+  <si>
+    <t>Correspondente - Hebert</t>
+  </si>
+  <si>
+    <t>BSO</t>
+  </si>
+  <si>
+    <t>0010673-85.2026.5.15.0038</t>
+  </si>
+  <si>
+    <t>Steelcorp Construction S.A</t>
+  </si>
+  <si>
+    <t>Leonardo Papait Camilo</t>
+  </si>
+  <si>
+    <t>BRAGANÇA PAULISTA</t>
+  </si>
+  <si>
+    <t>R$             173.436,46</t>
+  </si>
+  <si>
+    <t>RCF</t>
+  </si>
+  <si>
+    <t>Audiência Inicial -  Presencial</t>
+  </si>
+  <si>
+    <t>1001030-34.2026.5.02.0431</t>
+  </si>
+  <si>
+    <t>Marcio Jose Da Silva</t>
+  </si>
+  <si>
+    <t>R$          1.090.836,29</t>
+  </si>
+  <si>
+    <t>GSM</t>
+  </si>
+  <si>
+    <t>Sessão de Julgamento TRT - Presencial</t>
+  </si>
+  <si>
+    <t>1002143-77.2025.5.02.0004</t>
+  </si>
+  <si>
+    <t>Spic Brasil Energia Participações S.A.</t>
+  </si>
+  <si>
+    <t>Zenilda De Sousa Pinto</t>
+  </si>
+  <si>
+    <t>04ª TURMA</t>
+  </si>
+  <si>
+    <t>Recursal</t>
+  </si>
+  <si>
+    <t>R$               76.523,98</t>
+  </si>
+  <si>
+    <t>Grupo C2</t>
+  </si>
+  <si>
+    <t>VSI</t>
+  </si>
+  <si>
+    <t>ECO</t>
+  </si>
+  <si>
+    <t>0001807-67.2026.5.09.0002</t>
+  </si>
+  <si>
+    <t>Ferrero Do Brasil Industria Doceira E Alimentar Ltda.</t>
+  </si>
+  <si>
+    <t>Andreia Maria Gogola Albuquerque</t>
+  </si>
+  <si>
+    <t>CURITIBA</t>
+  </si>
+  <si>
+    <t>PR</t>
+  </si>
+  <si>
+    <t>02ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             280.446,50</t>
+  </si>
+  <si>
+    <t>ANB</t>
+  </si>
+  <si>
+    <t>https://url.trt9.jus.br/ddx84 ID da Reunião: 82978782974 Senha: vg5XZiFlA1a</t>
+  </si>
+  <si>
+    <t>Audiência Inicial - Telepresencial</t>
+  </si>
+  <si>
+    <t>0010522-20.2026.5.15.0071</t>
+  </si>
+  <si>
+    <t>Paulo Cesar Torres Lopes</t>
+  </si>
+  <si>
+    <t>R$          1.453.867,32</t>
+  </si>
+  <si>
+    <t>ID da reunião: 532 639 1733 Senha de acesso: 959215</t>
+  </si>
+  <si>
+    <t>0010832-56.2026.5.03.0072</t>
+  </si>
+  <si>
+    <t>Usina Fotovoltaica Arinos</t>
+  </si>
+  <si>
+    <t>Leonardo Rocha Braga</t>
+  </si>
+  <si>
+    <t>UNAÍ</t>
+  </si>
+  <si>
+    <t>R$          1.018.759,39</t>
+  </si>
+  <si>
+    <t>https://trt3-jus-br.zoom.us/my/vt.unai</t>
+  </si>
+  <si>
+    <t>Audiência de Conciliação - Telepresencial</t>
+  </si>
+  <si>
+    <t>1001576-77.2026.5.02.0435</t>
+  </si>
+  <si>
+    <t>Bridgestone Do Brasil Industria E Comercio Ltda.</t>
+  </si>
+  <si>
+    <t>Sidinei De Souza Oliveira</t>
+  </si>
+  <si>
+    <t>CEJUSC ABC</t>
+  </si>
+  <si>
+    <t>Cumprimento de Sentença</t>
+  </si>
+  <si>
+    <t>R$               19.517,93</t>
+  </si>
+  <si>
+    <t>JPE</t>
+  </si>
+  <si>
+    <t>https://trt2-jus-br.zoom.us/j/81881873237?pwd=aEs5S29DM2srNHRuRGFVM2ZEYkVUZz09 ID da reunião: 818 8187 3237 Senha de acesso: 459217</t>
+  </si>
+  <si>
+    <t>1001869-59.2026.5.02.0431</t>
+  </si>
+  <si>
+    <t>Wagner Goncalves Rosario</t>
+  </si>
+  <si>
+    <t>R$          1.064.563,78</t>
+  </si>
+  <si>
+    <t>RFE</t>
+  </si>
+  <si>
+    <t>1000886-24.2026.5.02.0443</t>
+  </si>
+  <si>
+    <t>Syngenta Proteção De Cultivos Ltda.</t>
+  </si>
+  <si>
+    <t>Everton Antonio Candido Nunes</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>1ª Instância</t>
+  </si>
+  <si>
+    <t>R$             123.100,00</t>
+  </si>
+  <si>
+    <t>Correspondente - Carlos Florian</t>
+  </si>
+  <si>
+    <t>GVM</t>
+  </si>
+  <si>
+    <t>Presencial | Advogado - Dr. Gustavo Barker, (13) 98181-1004 | Preposto - Milena Antunes dos Santos, CPF 306.966.018-50, RG 349608027, (13) 99709-1342</t>
+  </si>
+  <si>
+    <t>Audiência Una - Telepresencial</t>
+  </si>
+  <si>
+    <t>0011305-74.2026.5.03.0029</t>
+  </si>
+  <si>
+    <t>Sistenge Construcoes E Comercio Ltda</t>
+  </si>
+  <si>
+    <t>Jeronimo De Barros</t>
+  </si>
+  <si>
+    <t>CONTAGEM</t>
+  </si>
+  <si>
+    <t>01ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>Acordo</t>
+  </si>
+  <si>
+    <t>R$               43.815,14</t>
+  </si>
+  <si>
+    <t>RYL</t>
+  </si>
+  <si>
+    <t>https://trt3-jus-br.zoom.us/my/vt1.contagem</t>
+  </si>
+  <si>
     <t>Audiência Instrução - Telepresencial</t>
   </si>
   <si>
-    <t>0011186-18.2026.5.15.0082</t>
+    <t>0010866-65.2026.5.15.0082</t>
   </si>
   <si>
     <t>Moema Bioenergia S.A. - Moema</t>
   </si>
   <si>
-    <t>Adilson Maximiano Nogueira</t>
+    <t>Antonio Osorio Sontin Ferreira</t>
   </si>
   <si>
     <t>SÃO JOSÉ DO RIO PRETO</t>
   </si>
   <si>
-    <t>SP</t>
-  </si>
-  <si>
-    <t>03ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>Instrução</t>
-  </si>
-  <si>
-    <t>Reclamação Trabalhista</t>
-  </si>
-  <si>
-    <t>CENTRAL</t>
-  </si>
-  <si>
-    <t>R$             112.227,97</t>
-  </si>
-  <si>
-    <t>Grupo E2</t>
-  </si>
-  <si>
-    <t>MBF</t>
-  </si>
-  <si>
-    <t>RYL</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/81757243738?pwd=UXAvdEpveHlrNU05M2ZsZnRrYy9Vdz09 ID DA REUNIÃO: 817 5724 3738 SENHA: 954332</t>
-  </si>
-  <si>
-    <t>Audiência Inicial -  Telepresencial</t>
-  </si>
-  <si>
-    <t>0011084-92.2026.5.03.0061</t>
-  </si>
-  <si>
-    <t>Mahle Metal Leve S.A.</t>
-  </si>
-  <si>
-    <t>Leandro Dos Santos</t>
-  </si>
-  <si>
-    <t>ITAJUBÁ</t>
-  </si>
-  <si>
-    <t>MG</t>
-  </si>
-  <si>
-    <t>VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>Inicial</t>
-  </si>
-  <si>
-    <t>Ação de Consignação em Pagamento</t>
-  </si>
-  <si>
-    <t>R$                 3.262,69</t>
-  </si>
-  <si>
-    <t>Grupo E1</t>
+    <t>R$             254.000,00</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/88542672682?pwd=7pQ4QRhZmRG9RAQAWKowymbwNawa7t.1 ID da reunião: 885 4267 2682 Senha de acesso: 50728</t>
+  </si>
+  <si>
+    <t>Audiência de Conciliação - Semipresencial</t>
+  </si>
+  <si>
+    <t>0011309-25.2019.5.15.0126</t>
+  </si>
+  <si>
+    <t>Wagner De Jesus Sena</t>
+  </si>
+  <si>
+    <t>PAULÍNIA</t>
+  </si>
+  <si>
+    <t>CEJUSC CAMPINAS</t>
+  </si>
+  <si>
+    <t>Execução</t>
+  </si>
+  <si>
+    <t>R$                 9.489,28</t>
   </si>
   <si>
     <t>TLI</t>
   </si>
   <si>
-    <t>PSI</t>
-  </si>
-  <si>
-    <t>https://trt3-jus-br.zoom.us/my/vt.itajuba</t>
-  </si>
-  <si>
-    <t>Audiência Inicial - Telepresencial</t>
-  </si>
-  <si>
-    <t>0012242-06.2026.5.15.0044</t>
-  </si>
-  <si>
-    <t>Alessandre Lopes Da Cruz</t>
-  </si>
-  <si>
-    <t>02ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$          2.819.517,97</t>
-  </si>
-  <si>
-    <t>ARC</t>
-  </si>
-  <si>
-    <t>Audiência Una - Presencial</t>
-  </si>
-  <si>
-    <t>0001518-55.2026.5.07.0014</t>
-  </si>
-  <si>
-    <t>Companhia Act De Participações E Companhia Aix De Participações.</t>
-  </si>
-  <si>
-    <t>Ana Angelica Nunes Nogueira Tavares</t>
-  </si>
-  <si>
-    <t>FORTALEZA</t>
-  </si>
-  <si>
-    <t>CE</t>
-  </si>
-  <si>
-    <t>14ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$             100.200,00</t>
-  </si>
-  <si>
-    <t>Grupo C1</t>
+    <t>https://trt15-jus-br.zoom.us/j/88582969985?pwd=KDz0bWgxYzvepXfQC3ZYK8t4t1RyOY.1 ID: 885 8296 9985 Senha: 3</t>
+  </si>
+  <si>
+    <t>Audiência de Instrução - Presencial</t>
+  </si>
+  <si>
+    <t>0010821-92.2025.5.15.0083</t>
+  </si>
+  <si>
+    <t>Julio Cesar De Souza</t>
+  </si>
+  <si>
+    <t>R$             100.000,00</t>
+  </si>
+  <si>
+    <t>0010417-72.2026.5.15.0029</t>
+  </si>
+  <si>
+    <t>Viterra Bioenergia S.A.</t>
+  </si>
+  <si>
+    <t>Daniel Antonio</t>
+  </si>
+  <si>
+    <t>JABOTICABAL</t>
+  </si>
+  <si>
+    <t>R$          1.318.000,00</t>
   </si>
   <si>
     <t>Correspondente - doc9</t>
   </si>
   <si>
-    <t>VSI</t>
-  </si>
-  <si>
     <r>
-      <t xml:space="preserve">Presencial | Advogado - Ikaro Handersson da Costa Farias </t>
+      <t xml:space="preserve">Presencial | Advogado - David Barbosa Botelho </t>
     </r>
     <r>
       <rPr>
@@ -243,7 +675,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>ikaro.handersson@gmail.com</t>
+      <t>davidbarbosa572@gmail.com</t>
     </r>
     <r>
       <rPr>
@@ -252,7 +684,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> 85996385656 | Preposto - Ana Paula Barros Santos </t>
+      <t xml:space="preserve"> (16)9999-23722 | Preposto - Nayane Gambi Cezano Barbosa </t>
     </r>
     <r>
       <rPr>
@@ -261,7 +693,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>anapaulabarrossantos27@gmail.com</t>
+      <t>dra.nayanegambi@gmail.com</t>
     </r>
     <r>
       <rPr>
@@ -270,269 +702,8 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> (85)9982-60369</t>
+      <t xml:space="preserve"> (16)99164-5306</t>
     </r>
-  </si>
-  <si>
-    <t>Audiência Instrução - Presencial</t>
-  </si>
-  <si>
-    <t>0011691-29.2025.5.15.0119</t>
-  </si>
-  <si>
-    <t>Pilkington Brasil Ltda.</t>
-  </si>
-  <si>
-    <t>Iraldenir De Oliveira Carneiro</t>
-  </si>
-  <si>
-    <t>CAÇAPAVA</t>
-  </si>
-  <si>
-    <t>R$               10.272,84</t>
-  </si>
-  <si>
-    <t>AAP</t>
-  </si>
-  <si>
-    <t>Presencial</t>
-  </si>
-  <si>
-    <t>1001239-97.2026.5.02.0432</t>
-  </si>
-  <si>
-    <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
-  </si>
-  <si>
-    <t>Elvis Filgueira De Almeida</t>
-  </si>
-  <si>
-    <t>SANTO ANDRÉ</t>
-  </si>
-  <si>
-    <t>R$             253.042,21</t>
-  </si>
-  <si>
-    <t>Grupo B1</t>
-  </si>
-  <si>
-    <t>GSM</t>
-  </si>
-  <si>
-    <t>BSO</t>
-  </si>
-  <si>
-    <t>0011577-90.2025.5.15.0119</t>
-  </si>
-  <si>
-    <t>Luis Jorge De Oliveira</t>
-  </si>
-  <si>
-    <t>R$                 3.658,27</t>
-  </si>
-  <si>
-    <t>0011552-77.2025.5.15.0119</t>
-  </si>
-  <si>
-    <t>Ernani Rita De Oliveira</t>
-  </si>
-  <si>
-    <t>R$               56.941,59</t>
-  </si>
-  <si>
-    <t>0011549-25.2025.5.15.0119</t>
-  </si>
-  <si>
-    <t>Marlene Santos Marcolino De Oliveira</t>
-  </si>
-  <si>
-    <t>R$               32.125,08</t>
-  </si>
-  <si>
-    <t>0010703-78.2026.5.03.0063</t>
-  </si>
-  <si>
-    <t>Syngenta Seeds Ltda.</t>
-  </si>
-  <si>
-    <t>Robert Da Silva Vilela</t>
-  </si>
-  <si>
-    <t>ITUIUTABA</t>
-  </si>
-  <si>
-    <t>01ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>1ª Instância</t>
-  </si>
-  <si>
-    <t>R$               78.650,00</t>
-  </si>
-  <si>
-    <t>JRM</t>
-  </si>
-  <si>
-    <t>0011570-98.2025.5.15.0119</t>
-  </si>
-  <si>
-    <t>Martony Sampaio Ribeiro</t>
-  </si>
-  <si>
-    <t>R$               45.250,29</t>
-  </si>
-  <si>
-    <t>1001942-19.2026.5.02.0435</t>
-  </si>
-  <si>
-    <t>Ryan Furtado Nascimento</t>
-  </si>
-  <si>
-    <t>05ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$             157.873,36</t>
-  </si>
-  <si>
-    <t>Correspondente - Hebert</t>
-  </si>
-  <si>
-    <t>NRG</t>
-  </si>
-  <si>
-    <t>1001442-50.2026.5.02.0435</t>
-  </si>
-  <si>
-    <t>Luiz Gustavo Da Silva Buchmeier</t>
-  </si>
-  <si>
-    <t>R$                 7.632,80</t>
-  </si>
-  <si>
-    <t>RFE</t>
-  </si>
-  <si>
-    <t>1001441-71.2026.5.02.0433</t>
-  </si>
-  <si>
-    <t>Adonias Soares Da Silva</t>
-  </si>
-  <si>
-    <t>R$               51.027,24</t>
-  </si>
-  <si>
-    <t>LMI</t>
-  </si>
-  <si>
-    <t>Audiência de Conciliação - Telepresencial</t>
-  </si>
-  <si>
-    <t>0001305-77.2026.5.09.0019</t>
-  </si>
-  <si>
-    <t>Smartfit Escola De Ginastica E Danca S.A. E Bioritmo Franqueadora Ltda.</t>
-  </si>
-  <si>
-    <t>Neusa Aparecida Longuini</t>
-  </si>
-  <si>
-    <t>LONDRINA</t>
-  </si>
-  <si>
-    <t>PR</t>
-  </si>
-  <si>
-    <t>CEJUSC</t>
-  </si>
-  <si>
-    <t>Reclamação Pré-processual</t>
-  </si>
-  <si>
-    <t>R$          2.418.775,20</t>
-  </si>
-  <si>
-    <t>Grupo A3</t>
-  </si>
-  <si>
-    <t>PBS</t>
-  </si>
-  <si>
-    <t>https://url.trt9.jus.br/9kq15 ID da reunião: 82281762201 Senha de acesso: bOs5jU2nP7</t>
-  </si>
-  <si>
-    <t>Audiência Una - Telepresencial</t>
-  </si>
-  <si>
-    <t>1001886-19.2026.5.02.0521</t>
-  </si>
-  <si>
-    <t>Mahle Thermal And Fluid Systems Brazil Ltda.</t>
-  </si>
-  <si>
-    <t>Pamela Santana Borges Da Silva</t>
-  </si>
-  <si>
-    <t>ARUJÁ</t>
-  </si>
-  <si>
-    <t>R$                 5.367,99</t>
-  </si>
-  <si>
-    <t>https://trt2-jus-br.zoom.us/j/87224949005?pwd=JbmIgbUoMHoknaZ0IapCSsc9JsarNK.1 ID da reunião: 872 2494 9005 Senha de acesso: vtaruja01</t>
-  </si>
-  <si>
-    <t>1001426-12.2025.5.02.0054</t>
-  </si>
-  <si>
-    <t>Telefonica Brasil S.A.</t>
-  </si>
-  <si>
-    <t>Flavia Dias De Oliveira Faria</t>
-  </si>
-  <si>
-    <t>SÃO PAULO</t>
-  </si>
-  <si>
-    <t>54ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$          2.092.449,00</t>
-  </si>
-  <si>
-    <t>TFR</t>
-  </si>
-  <si>
-    <t>0001611-58.2025.5.09.0673</t>
-  </si>
-  <si>
-    <t>Syngenta Comercial Agrícola Ltda.</t>
-  </si>
-  <si>
-    <t>Helio Ricardo Bruneri</t>
-  </si>
-  <si>
-    <t>06ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$             249.131,93</t>
-  </si>
-  <si>
-    <t>VRO</t>
-  </si>
-  <si>
-    <t>0011431-10.2025.5.15.0132</t>
-  </si>
-  <si>
-    <t>Marcos Douglas Dos Santos Goulart</t>
-  </si>
-  <si>
-    <t>SÃO JOSÉ DOS CAMPOS</t>
-  </si>
-  <si>
-    <t>R$             376.645,91</t>
-  </si>
-  <si>
-    <t>Presencial | Advogado - Ricardo de Souza Gonçalves ricardosgoncalves@live.com (12)9810-41449</t>
   </si>
 </sst>
 </file>
@@ -1016,8 +1187,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BCD8069-E596-41FB-A0B1-C8286F6CD83C}">
-  <dimension ref="A1:R20"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C7AF8A9-DF41-4891-9826-70D604F0E7F0}">
+  <dimension ref="A1:R27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:18" ht="60" x14ac:dyDescent="0.3">
@@ -1076,15 +1247,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="231" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4">
-        <v>104994</v>
+        <v>106065</v>
       </c>
       <c r="B2" s="5">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C2" s="6">
-        <v>0.33333333333333331</v>
+        <v>0.34722222222222221</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>18</v>
@@ -1126,98 +1297,98 @@
         <v>30</v>
       </c>
       <c r="Q2" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="R2" s="7" t="s">
         <v>31</v>
-      </c>
-      <c r="R2" s="8" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4">
-        <v>106674</v>
+        <v>105789</v>
       </c>
       <c r="B3" s="5">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C3" s="6">
-        <v>0.34027777777777779</v>
+        <v>0.37152777777777779</v>
       </c>
       <c r="D3" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="F3" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="G3" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="H3" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="I3" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="J3" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="J3" s="7" t="s">
-        <v>39</v>
-      </c>
       <c r="K3" s="7" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="M3" s="7" t="s">
         <v>27</v>
       </c>
       <c r="N3" s="7" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="O3" s="7" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="P3" s="7" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="Q3" s="7" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="R3" s="8" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="231" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4">
-        <v>105784</v>
+        <v>99614</v>
       </c>
       <c r="B4" s="5">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C4" s="6">
         <v>0.375</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="I4" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="K4" s="7" t="s">
         <v>25</v>
@@ -1226,54 +1397,54 @@
         <v>26</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="N4" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="O4" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="P4" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q4" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="O4" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="P4" s="7" t="s">
+      <c r="R4" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="4">
+        <v>100140</v>
+      </c>
+      <c r="B5" s="5">
+        <v>46322</v>
+      </c>
+      <c r="C5" s="6">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="Q4" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="R4" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" ht="240.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="4">
-        <v>106718</v>
-      </c>
-      <c r="B5" s="5">
-        <v>46321</v>
-      </c>
-      <c r="C5" s="6">
-        <v>0.38194444444444442</v>
-      </c>
-      <c r="D5" s="7" t="s">
+      <c r="F5" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G5" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="E5" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>56</v>
-      </c>
       <c r="H5" s="7" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="K5" s="7" t="s">
         <v>25</v>
@@ -1285,54 +1456,54 @@
         <v>27</v>
       </c>
       <c r="N5" s="7" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="O5" s="7" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="P5" s="7" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="Q5" s="7" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="R5" s="7" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4">
-        <v>103635</v>
+        <v>105923</v>
       </c>
       <c r="B6" s="5">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C6" s="6">
-        <v>0.3888888888888889</v>
+        <v>0.39583333333333331</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>65</v>
+        <v>18</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="I6" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="L6" s="7" t="s">
         <v>26</v>
@@ -1341,54 +1512,54 @@
         <v>27</v>
       </c>
       <c r="N6" s="7" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="O6" s="7" t="s">
         <v>29</v>
       </c>
       <c r="P6" s="7" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="Q6" s="7" t="s">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="R6" s="7" t="s">
-        <v>72</v>
+        <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:18" ht="144.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4">
-        <v>105430</v>
+        <v>103541</v>
       </c>
       <c r="B7" s="5">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C7" s="6">
-        <v>0.3888888888888889</v>
+        <v>0.41319444444444442</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>76</v>
+        <v>46</v>
       </c>
       <c r="I7" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="L7" s="7" t="s">
         <v>26</v>
@@ -1397,51 +1568,51 @@
         <v>27</v>
       </c>
       <c r="N7" s="7" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="O7" s="7" t="s">
-        <v>78</v>
+        <v>49</v>
       </c>
       <c r="P7" s="7" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="Q7" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="R7" s="7" t="s">
-        <v>72</v>
+        <v>51</v>
+      </c>
+      <c r="R7" s="8" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4">
-        <v>103434</v>
+        <v>104752</v>
       </c>
       <c r="B8" s="5">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C8" s="6">
-        <v>0.39583333333333331</v>
+        <v>0.4236111111111111</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>69</v>
+        <v>22</v>
       </c>
       <c r="I8" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="K8" s="7" t="s">
         <v>25</v>
@@ -1453,54 +1624,54 @@
         <v>27</v>
       </c>
       <c r="N8" s="7" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="O8" s="7" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="P8" s="7" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="Q8" s="7" t="s">
-        <v>30</v>
+        <v>74</v>
       </c>
       <c r="R8" s="7" t="s">
-        <v>72</v>
+        <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:18" ht="87" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4">
-        <v>103432</v>
+        <v>105968</v>
       </c>
       <c r="B9" s="5">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C9" s="6">
-        <v>0.40277777777777779</v>
+        <v>0.4236111111111111</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>23</v>
+        <v>79</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="L9" s="7" t="s">
         <v>26</v>
@@ -1509,54 +1680,54 @@
         <v>27</v>
       </c>
       <c r="N9" s="7" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="O9" s="7" t="s">
         <v>29</v>
       </c>
       <c r="P9" s="7" t="s">
-        <v>71</v>
+        <v>40</v>
       </c>
       <c r="Q9" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="R9" s="7" t="s">
-        <v>72</v>
+      <c r="R9" s="8" t="s">
+        <v>81</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:18" ht="87" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4">
-        <v>103428</v>
+        <v>105967</v>
       </c>
       <c r="B10" s="5">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C10" s="6">
-        <v>0.41319444444444442</v>
+        <v>0.42708333333333331</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>23</v>
+        <v>79</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="L10" s="7" t="s">
         <v>26</v>
@@ -1565,54 +1736,54 @@
         <v>27</v>
       </c>
       <c r="N10" s="7" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="O10" s="7" t="s">
         <v>29</v>
       </c>
       <c r="P10" s="7" t="s">
-        <v>71</v>
+        <v>40</v>
       </c>
       <c r="Q10" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="R10" s="7" t="s">
-        <v>72</v>
+      <c r="R10" s="8" t="s">
+        <v>81</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4">
-        <v>105581</v>
+        <v>105741</v>
       </c>
       <c r="B11" s="5">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C11" s="6">
-        <v>0.42708333333333331</v>
+        <v>0.43055555555555558</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>65</v>
+        <v>18</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>95</v>
+        <v>25</v>
       </c>
       <c r="L11" s="7" t="s">
         <v>26</v>
@@ -1621,51 +1792,51 @@
         <v>27</v>
       </c>
       <c r="N11" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="O11" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="P11" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q11" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="R11" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="4">
+        <v>104798</v>
+      </c>
+      <c r="B12" s="5">
+        <v>46322</v>
+      </c>
+      <c r="C12" s="6">
+        <v>0.4375</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="H12" s="7" t="s">
         <v>96</v>
-      </c>
-      <c r="O11" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="P11" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q11" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="R11" s="7" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="4">
-        <v>103430</v>
-      </c>
-      <c r="B12" s="5">
-        <v>46321</v>
-      </c>
-      <c r="C12" s="6">
-        <v>0.43055555555555558</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>69</v>
       </c>
       <c r="I12" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="K12" s="7" t="s">
         <v>25</v>
@@ -1677,51 +1848,51 @@
         <v>27</v>
       </c>
       <c r="N12" s="7" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="O12" s="7" t="s">
-        <v>29</v>
+        <v>98</v>
       </c>
       <c r="P12" s="7" t="s">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="Q12" s="7" t="s">
-        <v>30</v>
+        <v>99</v>
       </c>
       <c r="R12" s="7" t="s">
-        <v>72</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4">
-        <v>106323</v>
+        <v>105292</v>
       </c>
       <c r="B13" s="5">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C13" s="6">
-        <v>0.4375</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="E13" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="F13" s="7" t="s">
         <v>101</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>74</v>
       </c>
       <c r="G13" s="7" t="s">
         <v>102</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>76</v>
+        <v>103</v>
       </c>
       <c r="I13" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K13" s="7" t="s">
         <v>25</v>
@@ -1733,107 +1904,107 @@
         <v>27</v>
       </c>
       <c r="N13" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O13" s="7" t="s">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="P13" s="7" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="Q13" s="7" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="R13" s="7" t="s">
-        <v>72</v>
+        <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="4">
-        <v>105627</v>
+        <v>105221</v>
       </c>
       <c r="B14" s="5">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C14" s="6">
-        <v>0.44444444444444442</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>76</v>
+        <v>112</v>
       </c>
       <c r="I14" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>103</v>
+        <v>38</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="M14" s="7" t="s">
         <v>27</v>
       </c>
       <c r="N14" s="7" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="O14" s="7" t="s">
-        <v>78</v>
+        <v>29</v>
       </c>
       <c r="P14" s="7" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="Q14" s="7" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="R14" s="7" t="s">
-        <v>72</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4">
-        <v>105638</v>
+        <v>105139</v>
       </c>
       <c r="B15" s="5">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C15" s="6">
-        <v>0.45833333333333331</v>
+        <v>0.5</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>53</v>
+        <v>115</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>74</v>
+        <v>101</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>76</v>
+        <v>103</v>
       </c>
       <c r="I15" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="K15" s="7" t="s">
         <v>25</v>
@@ -1845,110 +2016,110 @@
         <v>27</v>
       </c>
       <c r="N15" s="7" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="O15" s="7" t="s">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="P15" s="7" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="Q15" s="7" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="R15" s="7" t="s">
-        <v>72</v>
+        <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="159" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="4">
-        <v>106665</v>
+        <v>103634</v>
       </c>
       <c r="B16" s="5">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C16" s="6">
         <v>0.54166666666666663</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>119</v>
+        <v>22</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>120</v>
+        <v>23</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>40</v>
+        <v>125</v>
       </c>
       <c r="L16" s="7" t="s">
-        <v>122</v>
+        <v>26</v>
       </c>
       <c r="M16" s="7" t="s">
         <v>27</v>
       </c>
       <c r="N16" s="7" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="O16" s="7" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="P16" s="7" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="Q16" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="R16" s="8" t="s">
-        <v>126</v>
+        <v>129</v>
+      </c>
+      <c r="R16" s="7" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="245.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:18" ht="144.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="4">
-        <v>105977</v>
+        <v>106702</v>
       </c>
       <c r="B17" s="5">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C17" s="6">
-        <v>0.59375</v>
+        <v>0.54305555555555551</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>127</v>
+        <v>32</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>23</v>
+        <v>134</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>39</v>
+        <v>135</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="L17" s="7" t="s">
         <v>26</v>
@@ -1957,54 +2128,54 @@
         <v>27</v>
       </c>
       <c r="N17" s="7" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="O17" s="7" t="s">
-        <v>43</v>
+        <v>91</v>
       </c>
       <c r="P17" s="7" t="s">
-        <v>45</v>
+        <v>137</v>
       </c>
       <c r="Q17" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="R17" s="8" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="4">
+        <v>104515</v>
+      </c>
+      <c r="B18" s="5">
+        <v>46322</v>
+      </c>
+      <c r="C18" s="6">
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="F18" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="R17" s="8" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="4">
-        <v>104374</v>
-      </c>
-      <c r="B18" s="5">
-        <v>46321</v>
-      </c>
-      <c r="C18" s="6">
-        <v>0.59722222222222221</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>135</v>
-      </c>
       <c r="G18" s="7" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>137</v>
+        <v>46</v>
       </c>
       <c r="I18" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>138</v>
+        <v>38</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="L18" s="7" t="s">
         <v>26</v>
@@ -2013,54 +2184,54 @@
         <v>27</v>
       </c>
       <c r="N18" s="7" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="O18" s="7" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="P18" s="7" t="s">
-        <v>140</v>
+        <v>51</v>
       </c>
       <c r="Q18" s="7" t="s">
-        <v>140</v>
+        <v>51</v>
       </c>
       <c r="R18" s="7" t="s">
-        <v>72</v>
+        <v>143</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:18" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="4">
-        <v>103660</v>
+        <v>106156</v>
       </c>
       <c r="B19" s="5">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C19" s="6">
-        <v>0.60416666666666663</v>
+        <v>0.5625</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>119</v>
+        <v>147</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>120</v>
+        <v>79</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>144</v>
+        <v>38</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>95</v>
+        <v>25</v>
       </c>
       <c r="L19" s="7" t="s">
         <v>26</v>
@@ -2069,85 +2240,481 @@
         <v>27</v>
       </c>
       <c r="N19" s="7" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O19" s="7" t="s">
-        <v>43</v>
+        <v>127</v>
       </c>
       <c r="P19" s="7" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="Q19" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="R19" s="7" t="s">
-        <v>72</v>
+        <v>129</v>
+      </c>
+      <c r="R19" s="8" t="s">
+        <v>149</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="187.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:18" ht="245.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="4">
-        <v>101865</v>
+        <v>105940</v>
       </c>
       <c r="B20" s="5">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C20" s="6">
-        <v>0.60416666666666663</v>
+        <v>0.5708333333333333</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>53</v>
+        <v>150</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>67</v>
+        <v>152</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>149</v>
+        <v>103</v>
       </c>
       <c r="I20" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>103</v>
+        <v>154</v>
       </c>
       <c r="K20" s="7" t="s">
         <v>25</v>
       </c>
       <c r="L20" s="7" t="s">
-        <v>26</v>
+        <v>155</v>
       </c>
       <c r="M20" s="7" t="s">
         <v>27</v>
       </c>
       <c r="N20" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="O20" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="P20" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="Q20" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="R20" s="8" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="4">
+        <v>106206</v>
+      </c>
+      <c r="B21" s="5">
+        <v>46322</v>
+      </c>
+      <c r="C21" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="K21" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L21" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M21" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N21" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="O21" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="P21" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q21" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="R21" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" ht="192.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="4">
+        <v>105491</v>
+      </c>
+      <c r="B22" s="5">
+        <v>46322</v>
+      </c>
+      <c r="C22" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="I22" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J22" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="K22" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="L22" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M22" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N22" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="O22" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="P22" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q22" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="R22" s="7" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" ht="87" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="4">
+        <v>105540</v>
+      </c>
+      <c r="B23" s="5">
+        <v>46322</v>
+      </c>
+      <c r="C23" s="6">
+        <v>0.59791666666666665</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="I23" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="J23" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="K23" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="L23" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M23" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N23" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="O23" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="P20" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q20" s="7" t="s">
+      <c r="P23" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q23" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="R23" s="8" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" ht="259.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="4">
+        <v>104926</v>
+      </c>
+      <c r="B24" s="5">
+        <v>46322</v>
+      </c>
+      <c r="C24" s="6">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="I24" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J24" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L24" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M24" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N24" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="O24" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P24" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q24" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="R20" s="8" t="s">
-        <v>151</v>
+      <c r="R24" s="8" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" ht="202.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="4">
+        <v>74935</v>
+      </c>
+      <c r="B25" s="5">
+        <v>46322</v>
+      </c>
+      <c r="C25" s="6">
+        <v>0.62013888888888891</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="I25" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J25" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="K25" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="L25" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M25" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="N25" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="O25" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="P25" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q25" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="R25" s="8" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="4">
+        <v>106219</v>
+      </c>
+      <c r="B26" s="5">
+        <v>46322</v>
+      </c>
+      <c r="C26" s="6">
+        <v>0.625</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="I26" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J26" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="K26" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L26" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M26" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N26" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="O26" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="P26" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q26" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="R26" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" ht="240.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="4">
+        <v>104781</v>
+      </c>
+      <c r="B27" s="5">
+        <v>46322</v>
+      </c>
+      <c r="C27" s="6">
+        <v>0.65277777777777779</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="I27" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J27" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="K27" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L27" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M27" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N27" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="O27" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P27" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="Q27" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="R27" s="7" t="s">
+        <v>208</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="R2" r:id="rId1" display="https://us02web.zoom.us/j/81757243738?pwd=UXAvdEpveHlrNU05M2ZsZnRrYy9Vdz09%20ID%20DA%20REUNIÃO:%20817%205724%203738%20SENHA:%20954332" xr:uid="{9339D929-3BF8-4217-9323-72D4549FEB39}"/>
-    <hyperlink ref="R3" r:id="rId2" xr:uid="{C38F8162-A764-4CC8-BD09-5868F4A72B0F}"/>
-    <hyperlink ref="R4" r:id="rId3" display="https://us02web.zoom.us/j/81757243738?pwd=UXAvdEpveHlrNU05M2ZsZnRrYy9Vdz09%20ID%20DA%20REUNIÃO:%20817%205724%203738%20SENHA:%20954332" xr:uid="{A36F819B-3E41-410D-B38E-809C0AB943D8}"/>
-    <hyperlink ref="R16" r:id="rId4" xr:uid="{457C9B3A-A868-4E99-93B9-E5C29FF409A2}"/>
-    <hyperlink ref="R17" r:id="rId5" display="https://trt2-jus-br.zoom.us/j/87224949005?pwd=JbmIgbUoMHoknaZ0IapCSsc9JsarNK.1%20ID%20da%20reunião:%20872%202494%209005%20Senha%20de%20acesso:%20vtaruja01" xr:uid="{6B461923-48A8-4084-B100-CEDB0FD06DB7}"/>
-    <hyperlink ref="R20" r:id="rId6" display="mailto:ricardosgoncalves@live.com" xr:uid="{CD3B731A-48AF-47AF-B7D0-49E5F513C740}"/>
+    <hyperlink ref="R3" r:id="rId1" xr:uid="{E70C753C-B4AB-4DA2-8874-4D6BE15AEE9C}"/>
+    <hyperlink ref="R7" r:id="rId2" xr:uid="{8CD7349B-B768-4F32-97AD-E4C6B17FDF28}"/>
+    <hyperlink ref="R9" r:id="rId3" xr:uid="{1FEAC607-4DCB-4486-8328-9D7EE3CCD37E}"/>
+    <hyperlink ref="R10" r:id="rId4" xr:uid="{1164ACF0-76E2-4389-B572-4DED5239179C}"/>
+    <hyperlink ref="R17" r:id="rId5" xr:uid="{29BE04FB-4A65-49E6-A5EC-7CBD5FAA6837}"/>
+    <hyperlink ref="R19" r:id="rId6" xr:uid="{E56E5952-F400-4F88-A83D-F445B892AC2D}"/>
+    <hyperlink ref="R20" r:id="rId7" display="https://trt2-jus-br.zoom.us/j/81881873237?pwd=aEs5S29DM2srNHRuRGFVM2ZEYkVUZz09%20ID%20da%20reunião:%20818%208187%203237%20Senha%20de%20acesso:%20459217" xr:uid="{B2D22885-963B-4781-8C82-82555603F2AB}"/>
+    <hyperlink ref="R23" r:id="rId8" xr:uid="{11F48EB9-0F83-4108-87F4-CD040B1657FC}"/>
+    <hyperlink ref="R24" r:id="rId9" display="https://trt15-jus-br.zoom.us/j/88542672682?pwd=7pQ4QRhZmRG9RAQAWKowymbwNawa7t.1%20ID%20da%20reunião:%20885%204267%202682%20Senha%20de%20acesso:%2050728" xr:uid="{FEFA1AE1-4656-432D-92AC-8A5CABB385F7}"/>
+    <hyperlink ref="R25" r:id="rId10" display="https://trt15-jus-br.zoom.us/j/88582969985?pwd=KDz0bWgxYzvepXfQC3ZYK8t4t1RyOY.1%20ID:%20885%208296%209985%20Senha:%203" xr:uid="{65EE2F3D-CFA0-436B-B350-CD4ACCF5342D}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/Pauta_de_Audiencias.xlsx
+++ b/Pauta_de_Audiencias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\blu\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{168A89B5-15A8-49B6-B2A7-65065387B9E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AA89FA39-FE4B-4290-9B07-55F1A8C01549}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{983DC53A-B337-4DA1-A7D8-F3264ADA8430}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5112417F-4F5B-4EFF-8321-15DCCB8123A4}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="215">
   <si>
     <t>Código P&amp;C</t>
   </si>
@@ -95,578 +95,113 @@
     <t>Link/Observações</t>
   </si>
   <si>
+    <t>Perícia Técnica</t>
+  </si>
+  <si>
+    <t>0010690-03.2026.5.15.0045</t>
+  </si>
+  <si>
+    <t>Embraer S.A.</t>
+  </si>
+  <si>
+    <t>Carlos Ulisses De Almeida</t>
+  </si>
+  <si>
+    <t>SÃO JOSÉ DOS CAMPOS</t>
+  </si>
+  <si>
+    <t>SP</t>
+  </si>
+  <si>
+    <t>02ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>Instrução</t>
+  </si>
+  <si>
+    <t>Reclamação Trabalhista</t>
+  </si>
+  <si>
+    <t>CENTRAL</t>
+  </si>
+  <si>
+    <t>R$             111.462,89</t>
+  </si>
+  <si>
+    <t>Grupo B2</t>
+  </si>
+  <si>
+    <t>VCR</t>
+  </si>
+  <si>
+    <t>ANB</t>
+  </si>
+  <si>
+    <t>Iremos acompanhar</t>
+  </si>
+  <si>
+    <t>Audiência de Instrução - Semipresencial</t>
+  </si>
+  <si>
+    <t>1001353-37.2026.5.02.0464</t>
+  </si>
+  <si>
+    <t>Ferrero Do Brasil Industria Doceira E Alimentar Ltda.</t>
+  </si>
+  <si>
+    <t>Claudinei Silva</t>
+  </si>
+  <si>
+    <t>SÃO BERNARDO DO CAMPO</t>
+  </si>
+  <si>
+    <t>04ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$          1.583.882,35</t>
+  </si>
+  <si>
+    <t>Grupo B3</t>
+  </si>
+  <si>
+    <t>Presencial</t>
+  </si>
+  <si>
     <t>Audiência Una - Presencial</t>
   </si>
   <si>
-    <t>1001556-44.2026.5.02.0061</t>
-  </si>
-  <si>
-    <t>L. Sant'Angelo Pinturas Ltda</t>
-  </si>
-  <si>
-    <t>Marcos Leonio Fernandes De Queiroz</t>
-  </si>
-  <si>
-    <t>SÃO PAULO</t>
-  </si>
-  <si>
-    <t>SP</t>
-  </si>
-  <si>
-    <t>61ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>Instrução</t>
-  </si>
-  <si>
-    <t>Reclamação Trabalhista</t>
-  </si>
-  <si>
-    <t>CENTRAL</t>
-  </si>
-  <si>
-    <t>R$               32.163,75</t>
+    <t>0010940-40.2026.5.03.0184</t>
+  </si>
+  <si>
+    <t>Salitre Fertilizantes Ltda.</t>
+  </si>
+  <si>
+    <t>Gildasio Rodrigues Araujo</t>
+  </si>
+  <si>
+    <t>BELO HORIZONTE</t>
+  </si>
+  <si>
+    <t>MG</t>
+  </si>
+  <si>
+    <t>46ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$               17.506,54</t>
   </si>
   <si>
     <t>Grupo E2</t>
   </si>
   <si>
+    <t>Correspondente - doc9</t>
+  </si>
+  <si>
     <t>CAL</t>
   </si>
   <si>
-    <t>Presencial</t>
-  </si>
-  <si>
-    <t>Audiência Inicial -  Telepresencial</t>
-  </si>
-  <si>
-    <t>0000782-61.2026.5.05.0121</t>
-  </si>
-  <si>
-    <t>Salitre Fertilizantes Ltda.</t>
-  </si>
-  <si>
-    <t>Emerson Souza Dos Santos</t>
-  </si>
-  <si>
-    <t>CANDEIAS</t>
-  </si>
-  <si>
-    <t>BA</t>
-  </si>
-  <si>
-    <t>VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$               68.299,07</t>
-  </si>
-  <si>
-    <t>MBF</t>
-  </si>
-  <si>
-    <t>https://trt5-jus-br.zoom.us/my/sl1vtca</t>
-  </si>
-  <si>
-    <t>Audiência Instrução - Presencial</t>
-  </si>
-  <si>
-    <t>0012613-54.2024.5.15.0071</t>
-  </si>
-  <si>
-    <t>Mahle Metal Leve S.A.</t>
-  </si>
-  <si>
-    <t>Wanderson Cunha Coelho</t>
-  </si>
-  <si>
-    <t>MOGI GUAÇU</t>
-  </si>
-  <si>
-    <t>Central</t>
-  </si>
-  <si>
-    <t>R$               78.909,58</t>
-  </si>
-  <si>
-    <t>Grupo E1</t>
-  </si>
-  <si>
-    <t>Correspondente - Ana Carolina Teresani</t>
-  </si>
-  <si>
-    <t>PSI</t>
-  </si>
-  <si>
-    <t>0010035-84.2025.5.15.0071</t>
-  </si>
-  <si>
-    <t>Maurilio Guilherme Dippre Macedo</t>
-  </si>
-  <si>
-    <t>R$             230.000,00</t>
-  </si>
-  <si>
-    <t>1002252-70.2025.5.02.0205</t>
-  </si>
-  <si>
-    <t>Alpha1 Empreendimento Imobiliario Spe Ltda</t>
-  </si>
-  <si>
-    <t>Lucas Correia Grageiro</t>
-  </si>
-  <si>
-    <t>BARUERI</t>
-  </si>
-  <si>
-    <t>05ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>Conhecimento</t>
-  </si>
-  <si>
-    <t>R$               68.920,44</t>
-  </si>
-  <si>
-    <t>ARC</t>
-  </si>
-  <si>
-    <t>0017181-79.2025.5.15.0071</t>
-  </si>
-  <si>
-    <t>Ricardo Cesar Da Silva</t>
-  </si>
-  <si>
-    <t>Inicial</t>
-  </si>
-  <si>
-    <t>R$             501.217,75</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/5326391733?pwd=Qjc4RFBXWjZNbVd1bG5wNldjR3dWZz09</t>
-  </si>
-  <si>
-    <t>1000502-64.2026.5.02.0054</t>
-  </si>
-  <si>
-    <t>Telefonica Brasil S.A.</t>
-  </si>
-  <si>
-    <t>Barbara Servigne De Oliveira</t>
-  </si>
-  <si>
-    <t>54ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$          1.172.734,00</t>
-  </si>
-  <si>
-    <t>Grupo C1</t>
-  </si>
-  <si>
-    <t>TFR</t>
-  </si>
-  <si>
-    <t>0011014-18.2026.5.03.0080</t>
-  </si>
-  <si>
-    <t>Salitre Fertilizantes Ltda</t>
-  </si>
-  <si>
-    <t>Christian Monteiro Miranda</t>
-  </si>
-  <si>
-    <t>PATROCÍNIO</t>
-  </si>
-  <si>
-    <t>MG</t>
-  </si>
-  <si>
-    <t>R$             143.700,00</t>
-  </si>
-  <si>
-    <t>https://trt3-jus-br.zoom.us/my/vt.patrocinio</t>
-  </si>
-  <si>
-    <t>0011015-03.2026.5.03.0080</t>
-  </si>
-  <si>
-    <t>Yury Goncalves De Oliveira</t>
-  </si>
-  <si>
-    <t>R$               77.600,00</t>
-  </si>
-  <si>
-    <t>1001284-08.2026.5.02.0463</t>
-  </si>
-  <si>
-    <t>Companhia Brasileira De Cartuchos</t>
-  </si>
-  <si>
-    <t>Moises De Mattos Damazio</t>
-  </si>
-  <si>
-    <t>SÃO BERNARDO DO CAMPO</t>
-  </si>
-  <si>
-    <t>03ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$             132.745,00</t>
-  </si>
-  <si>
-    <t>Grupo B3</t>
-  </si>
-  <si>
-    <t>LMI</t>
-  </si>
-  <si>
-    <t>0010799-97.2026.5.15.0083</t>
-  </si>
-  <si>
-    <t>Embraer S.A.</t>
-  </si>
-  <si>
-    <t>Carlos Alberto Moreira Dos Santos</t>
-  </si>
-  <si>
-    <t>SÃO JOSÉ DOS CAMPOS</t>
-  </si>
-  <si>
-    <t>R$             133.051,44</t>
-  </si>
-  <si>
-    <t>Grupo B2</t>
-  </si>
-  <si>
-    <t>VCR</t>
-  </si>
-  <si>
-    <t>1001154-14.2026.5.02.0432</t>
-  </si>
-  <si>
-    <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
-  </si>
-  <si>
-    <t>David Henrique Silva Fernandes</t>
-  </si>
-  <si>
-    <t>SANTO ANDRÉ</t>
-  </si>
-  <si>
-    <t>04ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$          1.194.597,35</t>
-  </si>
-  <si>
-    <t>Grupo B1</t>
-  </si>
-  <si>
-    <t>Correspondente - Hebert</t>
-  </si>
-  <si>
-    <t>BSO</t>
-  </si>
-  <si>
-    <t>0010673-85.2026.5.15.0038</t>
-  </si>
-  <si>
-    <t>Steelcorp Construction S.A</t>
-  </si>
-  <si>
-    <t>Leonardo Papait Camilo</t>
-  </si>
-  <si>
-    <t>BRAGANÇA PAULISTA</t>
-  </si>
-  <si>
-    <t>R$             173.436,46</t>
-  </si>
-  <si>
-    <t>RCF</t>
-  </si>
-  <si>
-    <t>Audiência Inicial -  Presencial</t>
-  </si>
-  <si>
-    <t>1001030-34.2026.5.02.0431</t>
-  </si>
-  <si>
-    <t>Marcio Jose Da Silva</t>
-  </si>
-  <si>
-    <t>R$          1.090.836,29</t>
-  </si>
-  <si>
-    <t>GSM</t>
-  </si>
-  <si>
-    <t>Sessão de Julgamento TRT - Presencial</t>
-  </si>
-  <si>
-    <t>1002143-77.2025.5.02.0004</t>
-  </si>
-  <si>
-    <t>Spic Brasil Energia Participações S.A.</t>
-  </si>
-  <si>
-    <t>Zenilda De Sousa Pinto</t>
-  </si>
-  <si>
-    <t>04ª TURMA</t>
-  </si>
-  <si>
-    <t>Recursal</t>
-  </si>
-  <si>
-    <t>R$               76.523,98</t>
-  </si>
-  <si>
-    <t>Grupo C2</t>
-  </si>
-  <si>
-    <t>VSI</t>
-  </si>
-  <si>
-    <t>ECO</t>
-  </si>
-  <si>
-    <t>0001807-67.2026.5.09.0002</t>
-  </si>
-  <si>
-    <t>Ferrero Do Brasil Industria Doceira E Alimentar Ltda.</t>
-  </si>
-  <si>
-    <t>Andreia Maria Gogola Albuquerque</t>
-  </si>
-  <si>
-    <t>CURITIBA</t>
-  </si>
-  <si>
-    <t>PR</t>
-  </si>
-  <si>
-    <t>02ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$             280.446,50</t>
-  </si>
-  <si>
-    <t>ANB</t>
-  </si>
-  <si>
-    <t>https://url.trt9.jus.br/ddx84 ID da Reunião: 82978782974 Senha: vg5XZiFlA1a</t>
-  </si>
-  <si>
-    <t>Audiência Inicial - Telepresencial</t>
-  </si>
-  <si>
-    <t>0010522-20.2026.5.15.0071</t>
-  </si>
-  <si>
-    <t>Paulo Cesar Torres Lopes</t>
-  </si>
-  <si>
-    <t>R$          1.453.867,32</t>
-  </si>
-  <si>
-    <t>ID da reunião: 532 639 1733 Senha de acesso: 959215</t>
-  </si>
-  <si>
-    <t>0010832-56.2026.5.03.0072</t>
-  </si>
-  <si>
-    <t>Usina Fotovoltaica Arinos</t>
-  </si>
-  <si>
-    <t>Leonardo Rocha Braga</t>
-  </si>
-  <si>
-    <t>UNAÍ</t>
-  </si>
-  <si>
-    <t>R$          1.018.759,39</t>
-  </si>
-  <si>
-    <t>https://trt3-jus-br.zoom.us/my/vt.unai</t>
-  </si>
-  <si>
-    <t>Audiência de Conciliação - Telepresencial</t>
-  </si>
-  <si>
-    <t>1001576-77.2026.5.02.0435</t>
-  </si>
-  <si>
-    <t>Bridgestone Do Brasil Industria E Comercio Ltda.</t>
-  </si>
-  <si>
-    <t>Sidinei De Souza Oliveira</t>
-  </si>
-  <si>
-    <t>CEJUSC ABC</t>
-  </si>
-  <si>
-    <t>Cumprimento de Sentença</t>
-  </si>
-  <si>
-    <t>R$               19.517,93</t>
-  </si>
-  <si>
-    <t>JPE</t>
-  </si>
-  <si>
-    <t>https://trt2-jus-br.zoom.us/j/81881873237?pwd=aEs5S29DM2srNHRuRGFVM2ZEYkVUZz09 ID da reunião: 818 8187 3237 Senha de acesso: 459217</t>
-  </si>
-  <si>
-    <t>1001869-59.2026.5.02.0431</t>
-  </si>
-  <si>
-    <t>Wagner Goncalves Rosario</t>
-  </si>
-  <si>
-    <t>R$          1.064.563,78</t>
-  </si>
-  <si>
-    <t>RFE</t>
-  </si>
-  <si>
-    <t>1000886-24.2026.5.02.0443</t>
-  </si>
-  <si>
-    <t>Syngenta Proteção De Cultivos Ltda.</t>
-  </si>
-  <si>
-    <t>Everton Antonio Candido Nunes</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>1ª Instância</t>
-  </si>
-  <si>
-    <t>R$             123.100,00</t>
-  </si>
-  <si>
-    <t>Correspondente - Carlos Florian</t>
-  </si>
-  <si>
-    <t>GVM</t>
-  </si>
-  <si>
-    <t>Presencial | Advogado - Dr. Gustavo Barker, (13) 98181-1004 | Preposto - Milena Antunes dos Santos, CPF 306.966.018-50, RG 349608027, (13) 99709-1342</t>
-  </si>
-  <si>
-    <t>Audiência Una - Telepresencial</t>
-  </si>
-  <si>
-    <t>0011305-74.2026.5.03.0029</t>
-  </si>
-  <si>
-    <t>Sistenge Construcoes E Comercio Ltda</t>
-  </si>
-  <si>
-    <t>Jeronimo De Barros</t>
-  </si>
-  <si>
-    <t>CONTAGEM</t>
-  </si>
-  <si>
-    <t>01ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>Acordo</t>
-  </si>
-  <si>
-    <t>R$               43.815,14</t>
-  </si>
-  <si>
-    <t>RYL</t>
-  </si>
-  <si>
-    <t>https://trt3-jus-br.zoom.us/my/vt1.contagem</t>
-  </si>
-  <si>
-    <t>Audiência Instrução - Telepresencial</t>
-  </si>
-  <si>
-    <t>0010866-65.2026.5.15.0082</t>
-  </si>
-  <si>
-    <t>Moema Bioenergia S.A. - Moema</t>
-  </si>
-  <si>
-    <t>Antonio Osorio Sontin Ferreira</t>
-  </si>
-  <si>
-    <t>SÃO JOSÉ DO RIO PRETO</t>
-  </si>
-  <si>
-    <t>R$             254.000,00</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/88542672682?pwd=7pQ4QRhZmRG9RAQAWKowymbwNawa7t.1 ID da reunião: 885 4267 2682 Senha de acesso: 50728</t>
-  </si>
-  <si>
-    <t>Audiência de Conciliação - Semipresencial</t>
-  </si>
-  <si>
-    <t>0011309-25.2019.5.15.0126</t>
-  </si>
-  <si>
-    <t>Wagner De Jesus Sena</t>
-  </si>
-  <si>
-    <t>PAULÍNIA</t>
-  </si>
-  <si>
-    <t>CEJUSC CAMPINAS</t>
-  </si>
-  <si>
-    <t>Execução</t>
-  </si>
-  <si>
-    <t>R$                 9.489,28</t>
-  </si>
-  <si>
-    <t>TLI</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/88582969985?pwd=KDz0bWgxYzvepXfQC3ZYK8t4t1RyOY.1 ID: 885 8296 9985 Senha: 3</t>
-  </si>
-  <si>
-    <t>Audiência de Instrução - Presencial</t>
-  </si>
-  <si>
-    <t>0010821-92.2025.5.15.0083</t>
-  </si>
-  <si>
-    <t>Julio Cesar De Souza</t>
-  </si>
-  <si>
-    <t>R$             100.000,00</t>
-  </si>
-  <si>
-    <t>0010417-72.2026.5.15.0029</t>
-  </si>
-  <si>
-    <t>Viterra Bioenergia S.A.</t>
-  </si>
-  <si>
-    <t>Daniel Antonio</t>
-  </si>
-  <si>
-    <t>JABOTICABAL</t>
-  </si>
-  <si>
-    <t>R$          1.318.000,00</t>
-  </si>
-  <si>
-    <t>Correspondente - doc9</t>
-  </si>
-  <si>
     <r>
-      <t xml:space="preserve">Presencial | Advogado - David Barbosa Botelho </t>
+      <t xml:space="preserve">Presencial | Advogado - Carlos Adriano Pereira </t>
     </r>
     <r>
       <rPr>
@@ -675,7 +210,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>davidbarbosa572@gmail.com</t>
+      <t>carlossanttosadv@gmail.com</t>
     </r>
     <r>
       <rPr>
@@ -684,7 +219,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> (16)9999-23722 | Preposto - Nayane Gambi Cezano Barbosa </t>
+      <t xml:space="preserve"> (31)9948-83172 | Preposto - Paloma Stefane Guedes Lana </t>
     </r>
     <r>
       <rPr>
@@ -693,7 +228,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>dra.nayanegambi@gmail.com</t>
+      <t>palomaguedescorrespondente@gmail.com</t>
     </r>
     <r>
       <rPr>
@@ -702,8 +237,529 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> (16)99164-5306</t>
+      <t xml:space="preserve"> (31)9870-96152</t>
     </r>
+  </si>
+  <si>
+    <t>Sessão de Julgamento TRT - Semipresencial</t>
+  </si>
+  <si>
+    <t>0011286-39.2019.5.15.0010</t>
+  </si>
+  <si>
+    <t>Whirlpool S.A.</t>
+  </si>
+  <si>
+    <t>Ministério Público Do Trabalho</t>
+  </si>
+  <si>
+    <t>RIO CLARO</t>
+  </si>
+  <si>
+    <t>06ª TURMA</t>
+  </si>
+  <si>
+    <t>Recursal</t>
+  </si>
+  <si>
+    <t>Ação Civil Pública</t>
+  </si>
+  <si>
+    <t>R$        76.000.000,00</t>
+  </si>
+  <si>
+    <t>Grupo A3</t>
+  </si>
+  <si>
+    <t>ACA</t>
+  </si>
+  <si>
+    <t>SOF</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/83934617561?pwd=tyrlqvz6UTYj3JeQgOojDijKbDgfm9.1 ID da reunião: 839 3461 7561 Senha: 516068</t>
+  </si>
+  <si>
+    <t>0011362-15.2023.5.15.0013</t>
+  </si>
+  <si>
+    <t>Tiago Roberto Nunes</t>
+  </si>
+  <si>
+    <t>Recursal TRT</t>
+  </si>
+  <si>
+    <t>R$             329.966,55</t>
+  </si>
+  <si>
+    <t>GSM</t>
+  </si>
+  <si>
+    <t>1001256-13.2026.5.02.0084</t>
+  </si>
+  <si>
+    <t>Telefonica Brasil S.A.</t>
+  </si>
+  <si>
+    <t>Raphael Fernandes De Castro</t>
+  </si>
+  <si>
+    <t>SÃO PAULO</t>
+  </si>
+  <si>
+    <t>63ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$          1.325.921,53</t>
+  </si>
+  <si>
+    <t>Grupo C1</t>
+  </si>
+  <si>
+    <t>TFR</t>
+  </si>
+  <si>
+    <t>Audiência Una - Semipresencial</t>
+  </si>
+  <si>
+    <t>0001511-75.2026.5.07.0010</t>
+  </si>
+  <si>
+    <t>Companhia Act De Participações E Companhia Aix De Participações</t>
+  </si>
+  <si>
+    <t>Ordilei Oton Teixeira De Oliveira</t>
+  </si>
+  <si>
+    <t>FORTALEZA</t>
+  </si>
+  <si>
+    <t>CE</t>
+  </si>
+  <si>
+    <t>10ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             121.200,00</t>
+  </si>
+  <si>
+    <t>VSI</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Presencial| Advogado - OSMAR MARINHO JUNIOR </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF467886"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>osmar@advocaciamarinho.adv.br</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 85988525988 | Preposto - MARIA IVONE RODRIGUES DE SOUSA MARINHO </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF467886"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>ivone@advocaciamarinho.adv.br</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (85)9881-61124</t>
+    </r>
+  </si>
+  <si>
+    <t>0001527-50.2026.5.07.0003</t>
+  </si>
+  <si>
+    <t>Tiago Duarte Dos Santos</t>
+  </si>
+  <si>
+    <t>03ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             228.200,00</t>
+  </si>
+  <si>
+    <t>ECO</t>
+  </si>
+  <si>
+    <t>https://trt7-jus-br.zoom.us/j/85966394206?pwd=NzVHbThxN2RyenY3Vk03WTJ2MVFsUT09 ID: 859  6639  4206 Senha: 931541</t>
+  </si>
+  <si>
+    <t>Audiência de Instrução - Presencial</t>
+  </si>
+  <si>
+    <t>1002000-62.2025.5.02.0433</t>
+  </si>
+  <si>
+    <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
+  </si>
+  <si>
+    <t>Alexandre Eduardo Linares</t>
+  </si>
+  <si>
+    <t>SANTO ANDRÉ</t>
+  </si>
+  <si>
+    <t>R$             966.485,01</t>
+  </si>
+  <si>
+    <t>Grupo B1</t>
+  </si>
+  <si>
+    <t>Correspondente - Hebert</t>
+  </si>
+  <si>
+    <t>BSO</t>
+  </si>
+  <si>
+    <t>1001120-36.2026.5.02.0045</t>
+  </si>
+  <si>
+    <t>T4F Entretenimento S.A.</t>
+  </si>
+  <si>
+    <t>Joao Paulo Carvalho Paim</t>
+  </si>
+  <si>
+    <t>45ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>1ª Instância</t>
+  </si>
+  <si>
+    <t>R$               44.000,00</t>
+  </si>
+  <si>
+    <t>RFE</t>
+  </si>
+  <si>
+    <t>Audiência Inicial -  Telepresencial</t>
+  </si>
+  <si>
+    <t>0010942-09.2026.5.03.0152</t>
+  </si>
+  <si>
+    <t>Santa Juliana Bioenergia Ltda</t>
+  </si>
+  <si>
+    <t>Everton De Menezes Santos</t>
+  </si>
+  <si>
+    <t>UBERABA</t>
+  </si>
+  <si>
+    <t>R$               83.122,87</t>
+  </si>
+  <si>
+    <t>https://trt3-jus-br.zoom.us/my/vt3uberaba</t>
+  </si>
+  <si>
+    <t>Audiência Instrução - Telepresencial</t>
+  </si>
+  <si>
+    <t>0011144-08.2026.5.03.0080</t>
+  </si>
+  <si>
+    <t>Salitre Fertilizantes Ltda</t>
+  </si>
+  <si>
+    <t>Deivison Da Cruz Onofre</t>
+  </si>
+  <si>
+    <t>PATROCÍNIO</t>
+  </si>
+  <si>
+    <t>VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$               99.233,42</t>
+  </si>
+  <si>
+    <t>MBF</t>
+  </si>
+  <si>
+    <t>https://trt3-jus-br.zoom.us/my/vt.patrocinio</t>
+  </si>
+  <si>
+    <t>0010689-10.2025.5.03.0070</t>
+  </si>
+  <si>
+    <t>Syngenta Proteção De Cultivos Ltda.</t>
+  </si>
+  <si>
+    <t>Ivan Lima Da Costa</t>
+  </si>
+  <si>
+    <t>PASSOS</t>
+  </si>
+  <si>
+    <t>01ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             147.037,91</t>
+  </si>
+  <si>
+    <t>Grupo E1</t>
+  </si>
+  <si>
+    <t>JRM</t>
+  </si>
+  <si>
+    <t>GVM</t>
+  </si>
+  <si>
+    <t>https://trt3-jus-br.zoom.us/my/varapassos1</t>
+  </si>
+  <si>
+    <t>0010233-24.2025.5.15.0071</t>
+  </si>
+  <si>
+    <t>Mahle Metal Leve S.A.</t>
+  </si>
+  <si>
+    <t>Thiago Wiliam Da Silva</t>
+  </si>
+  <si>
+    <t>MOGI GUAÇU</t>
+  </si>
+  <si>
+    <t>Central</t>
+  </si>
+  <si>
+    <t>R$             761.936,04</t>
+  </si>
+  <si>
+    <t>PSI</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/5326391733?pwd=Qjc4RFBXWjZNbVd1bG5wNldjR3dWZz09 ID da reunião: 5326391733 Senha de acesso: 959215</t>
+  </si>
+  <si>
+    <t>0010966-59.2026.5.03.0080</t>
+  </si>
+  <si>
+    <t>Raniel Luis Martins</t>
+  </si>
+  <si>
+    <t>Conhecimento</t>
+  </si>
+  <si>
+    <t>R$               71.405,55</t>
+  </si>
+  <si>
+    <t>0012611-84.2024.5.15.0071</t>
+  </si>
+  <si>
+    <t>Naide Maria Lopes Almeida</t>
+  </si>
+  <si>
+    <t>R$               76.616,16</t>
+  </si>
+  <si>
+    <t>TLI</t>
+  </si>
+  <si>
+    <t>0001507-47.2026.5.07.0007</t>
+  </si>
+  <si>
+    <t>Nanisio Gomes Da Silva Neto</t>
+  </si>
+  <si>
+    <t>07ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             146.200,00</t>
+  </si>
+  <si>
+    <t>https://trt7-jus-br.zoom.us/j/7920637449</t>
+  </si>
+  <si>
+    <t>Audiência Instrução - Presencial</t>
+  </si>
+  <si>
+    <t>0010214-76.2025.5.15.0084</t>
+  </si>
+  <si>
+    <t>Francisco Da Silva Geronimo</t>
+  </si>
+  <si>
+    <t>Inicial</t>
+  </si>
+  <si>
+    <t>R$               79.870,00</t>
+  </si>
+  <si>
+    <t>NRG</t>
+  </si>
+  <si>
+    <t>Audiência Inicial -  Presencial</t>
+  </si>
+  <si>
+    <t>1001104-82.2026.5.02.0433</t>
+  </si>
+  <si>
+    <t>Felipe Siqueira Goncalves</t>
+  </si>
+  <si>
+    <t>R$             101.987,00</t>
+  </si>
+  <si>
+    <t>BCF</t>
+  </si>
+  <si>
+    <t>0010786-43.2026.5.03.0080</t>
+  </si>
+  <si>
+    <t>Milton Vieira De Almeida</t>
+  </si>
+  <si>
+    <t>R$               26.494,42</t>
+  </si>
+  <si>
+    <t>1000624-34.2026.5.02.0521</t>
+  </si>
+  <si>
+    <t>Mahle Thermal And Fluid Systems Brazil Ltda.</t>
+  </si>
+  <si>
+    <t>Clenia Aparecida Evangelista De Oliveira</t>
+  </si>
+  <si>
+    <t>ARUJÁ</t>
+  </si>
+  <si>
+    <t>R$               72.596,00</t>
+  </si>
+  <si>
+    <t>https://trt2-jus-br.zoom.us/j/85932097305?pwd=VRmOpF07r6vEKgjIgaQPtnd6XlE7ua.1 ID da reunião: 859 3209 7305 Senha de acesso: vtaruja01</t>
+  </si>
+  <si>
+    <t>0010783-88.2026.5.03.0080</t>
+  </si>
+  <si>
+    <t>Edley Henrique Silva</t>
+  </si>
+  <si>
+    <t>R$               21.434,21</t>
+  </si>
+  <si>
+    <t>Sessão de Julgamento TRT - Presencial</t>
+  </si>
+  <si>
+    <t>1001669-11.2024.5.02.0435</t>
+  </si>
+  <si>
+    <t>Raimundo Fagner Tavares Nascimento</t>
+  </si>
+  <si>
+    <t>17ª TURMA</t>
+  </si>
+  <si>
+    <t>R$          1.453.110,58</t>
+  </si>
+  <si>
+    <t>0000016-73.2026.5.09.0128</t>
+  </si>
+  <si>
+    <t>Yuri Martim Kaufmann Daverca</t>
+  </si>
+  <si>
+    <t>CASCAVEL</t>
+  </si>
+  <si>
+    <t>PR</t>
+  </si>
+  <si>
+    <t>07ª TURMA</t>
+  </si>
+  <si>
+    <t>R$               19.500,00</t>
+  </si>
+  <si>
+    <t>https://trt9-jus-br.zoom.us/j/87561159126?pwd=UDRXRjBZamVnZVBtMHM1U0lIQWtaUT09 ID da reunião: 875 6115 9126 Senha (código de acesso) 343717</t>
+  </si>
+  <si>
+    <t>Audiência Una - Telepresencial</t>
+  </si>
+  <si>
+    <t>1000517-96.2026.5.02.0421</t>
+  </si>
+  <si>
+    <t>Alpha1 Empreendimento Imobiliario Spe Ltda</t>
+  </si>
+  <si>
+    <t>Romeu Francisco Xavier</t>
+  </si>
+  <si>
+    <t>SANTANA DE PARNAÍBA</t>
+  </si>
+  <si>
+    <t>R$               64.849,87</t>
+  </si>
+  <si>
+    <t>ARC</t>
+  </si>
+  <si>
+    <t>https://trt2-jus-br.zoom.us/j/89723895437?pwd=299HRPK4b4mHSqIWSRZ6nL7kVKwZaO.1 ID da reunião: 897 2389 5437 Senha de acesso: 402582</t>
+  </si>
+  <si>
+    <t>0010685-63.2026.5.15.0050</t>
+  </si>
+  <si>
+    <t>Viterra Bioenergia S.A.</t>
+  </si>
+  <si>
+    <t>Michel Roque Martins Dias</t>
+  </si>
+  <si>
+    <t>DRACENA</t>
+  </si>
+  <si>
+    <t>R$             338.733,87</t>
+  </si>
+  <si>
+    <t>AAP</t>
+  </si>
+  <si>
+    <t>https://trt15-jus.br.zoom.us/j/87527564652?pwd=d3YrZ2diWXk5UjgzbmVkNExteWVMQT09</t>
+  </si>
+  <si>
+    <t>0010978-88.2025.5.15.0043</t>
+  </si>
+  <si>
+    <t>Tiago Nunes Lopes</t>
+  </si>
+  <si>
+    <t>CAMPINAS</t>
+  </si>
+  <si>
+    <t>R$               79.164,67</t>
+  </si>
+  <si>
+    <t>Correspondente - Carlos Florian</t>
+  </si>
+  <si>
+    <t>Presencial | Advogada - Dra. Vivian dos Santos Ramos, OAB/SP 382.437, (19) 97151-1777 | Preposta - Juliana da Silva Oliveira, CPF 285.253.868-71, RG 359894124, (19) 98743-4081</t>
   </si>
 </sst>
 </file>
@@ -1187,8 +1243,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C7AF8A9-DF41-4891-9826-70D604F0E7F0}">
-  <dimension ref="A1:R27"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C31FED7-5F89-4C3E-B6FA-FCF3DB4CEA9A}">
+  <dimension ref="A1:R28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:18" ht="60" x14ac:dyDescent="0.3">
@@ -1247,15 +1303,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4">
-        <v>106065</v>
+        <v>104623</v>
       </c>
       <c r="B2" s="5">
-        <v>46322</v>
+        <v>46324</v>
       </c>
       <c r="C2" s="6">
-        <v>0.34722222222222221</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>18</v>
@@ -1297,39 +1353,39 @@
         <v>30</v>
       </c>
       <c r="Q2" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="R2" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4">
-        <v>105789</v>
+        <v>105881</v>
       </c>
       <c r="B3" s="5">
-        <v>46322</v>
+        <v>46324</v>
       </c>
       <c r="C3" s="6">
-        <v>0.37152777777777779</v>
+        <v>0.34027777777777779</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="J3" s="7" t="s">
         <v>38</v>
@@ -1347,27 +1403,27 @@
         <v>39</v>
       </c>
       <c r="O3" s="7" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="P3" s="7" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="Q3" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="R3" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R3" s="7" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:18" ht="252.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4">
-        <v>99614</v>
+        <v>106784</v>
       </c>
       <c r="B4" s="5">
-        <v>46322</v>
+        <v>46324</v>
       </c>
       <c r="C4" s="6">
-        <v>0.375</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>42</v>
@@ -1385,10 +1441,10 @@
         <v>46</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="K4" s="7" t="s">
         <v>25</v>
@@ -1397,104 +1453,104 @@
         <v>26</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="N4" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="O4" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P4" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q4" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="R4" s="7" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:18" ht="216.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4">
-        <v>100140</v>
+        <v>78459</v>
       </c>
       <c r="B5" s="5">
-        <v>46322</v>
+        <v>46324</v>
       </c>
       <c r="C5" s="6">
-        <v>0.39583333333333331</v>
+        <v>0.375</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="I5" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="M5" s="7" t="s">
         <v>27</v>
       </c>
       <c r="N5" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="O5" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="P5" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q5" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="R5" s="8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="216.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="4">
+        <v>95139</v>
+      </c>
+      <c r="B6" s="5">
+        <v>46324</v>
+      </c>
+      <c r="C6" s="6">
+        <v>0.375</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="O5" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="P5" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q5" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="R5" s="7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="4">
-        <v>105923</v>
-      </c>
-      <c r="B6" s="5">
-        <v>46322</v>
-      </c>
-      <c r="C6" s="6">
-        <v>0.39583333333333331</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>18</v>
-      </c>
       <c r="E6" s="7" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="I6" s="7" t="s">
         <v>23</v>
@@ -1503,7 +1559,7 @@
         <v>59</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="L6" s="7" t="s">
         <v>26</v>
@@ -1512,54 +1568,54 @@
         <v>27</v>
       </c>
       <c r="N6" s="7" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="O6" s="7" t="s">
         <v>29</v>
       </c>
       <c r="P6" s="7" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="Q6" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="R6" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
+      </c>
+      <c r="R6" s="8" t="s">
+        <v>66</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="144.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4">
-        <v>103541</v>
+        <v>105787</v>
       </c>
       <c r="B7" s="5">
-        <v>46322</v>
+        <v>46324</v>
       </c>
       <c r="C7" s="6">
-        <v>0.41319444444444442</v>
+        <v>0.38194444444444442</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="I7" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="L7" s="7" t="s">
         <v>26</v>
@@ -1568,51 +1624,51 @@
         <v>27</v>
       </c>
       <c r="N7" s="7" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="O7" s="7" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="P7" s="7" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="Q7" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="R7" s="8" t="s">
-        <v>67</v>
+        <v>79</v>
+      </c>
+      <c r="R7" s="7" t="s">
+        <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:18" ht="252.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4">
-        <v>104752</v>
+        <v>106272</v>
       </c>
       <c r="B8" s="5">
-        <v>46322</v>
+        <v>46324</v>
       </c>
       <c r="C8" s="6">
-        <v>0.4236111111111111</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>22</v>
+        <v>84</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>23</v>
+        <v>85</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="K8" s="7" t="s">
         <v>25</v>
@@ -1624,54 +1680,54 @@
         <v>27</v>
       </c>
       <c r="N8" s="7" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="O8" s="7" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="P8" s="7" t="s">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="Q8" s="7" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="R8" s="7" t="s">
-        <v>31</v>
+        <v>89</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="87" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:18" ht="216.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4">
-        <v>105968</v>
+        <v>106689</v>
       </c>
       <c r="B9" s="5">
-        <v>46322</v>
+        <v>46324</v>
       </c>
       <c r="C9" s="6">
-        <v>0.4236111111111111</v>
+        <v>0.39583333333333331</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>38</v>
+        <v>92</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="L9" s="7" t="s">
         <v>26</v>
@@ -1680,54 +1736,54 @@
         <v>27</v>
       </c>
       <c r="N9" s="7" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="O9" s="7" t="s">
-        <v>29</v>
+        <v>78</v>
       </c>
       <c r="P9" s="7" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="Q9" s="7" t="s">
-        <v>30</v>
+        <v>88</v>
       </c>
       <c r="R9" s="8" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="87" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4">
-        <v>105967</v>
+        <v>103074</v>
       </c>
       <c r="B10" s="5">
-        <v>46322</v>
+        <v>46324</v>
       </c>
       <c r="C10" s="6">
-        <v>0.42708333333333331</v>
+        <v>0.40277777777777779</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>79</v>
+        <v>23</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>38</v>
+        <v>92</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="L10" s="7" t="s">
         <v>26</v>
@@ -1736,54 +1792,54 @@
         <v>27</v>
       </c>
       <c r="N10" s="7" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="O10" s="7" t="s">
-        <v>29</v>
+        <v>102</v>
       </c>
       <c r="P10" s="7" t="s">
-        <v>40</v>
+        <v>103</v>
       </c>
       <c r="Q10" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="R10" s="8" t="s">
-        <v>81</v>
+        <v>104</v>
+      </c>
+      <c r="R10" s="7" t="s">
+        <v>41</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4">
-        <v>105741</v>
+        <v>105641</v>
       </c>
       <c r="B11" s="5">
-        <v>46322</v>
+        <v>46324</v>
       </c>
       <c r="C11" s="6">
-        <v>0.43055555555555558</v>
+        <v>0.40972222222222221</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="I11" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>25</v>
+        <v>109</v>
       </c>
       <c r="L11" s="7" t="s">
         <v>26</v>
@@ -1792,51 +1848,51 @@
         <v>27</v>
       </c>
       <c r="N11" s="7" t="s">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="O11" s="7" t="s">
-        <v>91</v>
+        <v>40</v>
       </c>
       <c r="P11" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q11" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="R11" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="4">
+        <v>105936</v>
+      </c>
+      <c r="B12" s="5">
+        <v>46324</v>
+      </c>
+      <c r="C12" s="6">
+        <v>0.40972222222222221</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="J12" s="7" t="s">
         <v>92</v>
-      </c>
-      <c r="Q11" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="R11" s="7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="4">
-        <v>104798</v>
-      </c>
-      <c r="B12" s="5">
-        <v>46322</v>
-      </c>
-      <c r="C12" s="6">
-        <v>0.4375</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="I12" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="J12" s="7" t="s">
-        <v>89</v>
       </c>
       <c r="K12" s="7" t="s">
         <v>25</v>
@@ -1848,51 +1904,51 @@
         <v>27</v>
       </c>
       <c r="N12" s="7" t="s">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="O12" s="7" t="s">
-        <v>98</v>
+        <v>50</v>
       </c>
       <c r="P12" s="7" t="s">
-        <v>99</v>
+        <v>52</v>
       </c>
       <c r="Q12" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="R12" s="7" t="s">
-        <v>31</v>
+        <v>52</v>
+      </c>
+      <c r="R12" s="8" t="s">
+        <v>118</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:18" ht="87" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4">
-        <v>105292</v>
+        <v>106252</v>
       </c>
       <c r="B13" s="5">
-        <v>46322</v>
+        <v>46324</v>
       </c>
       <c r="C13" s="6">
-        <v>0.45833333333333331</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>42</v>
+        <v>119</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>104</v>
+        <v>124</v>
       </c>
       <c r="K13" s="7" t="s">
         <v>25</v>
@@ -1904,54 +1960,54 @@
         <v>27</v>
       </c>
       <c r="N13" s="7" t="s">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="O13" s="7" t="s">
-        <v>106</v>
+        <v>50</v>
       </c>
       <c r="P13" s="7" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="Q13" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="R13" s="7" t="s">
-        <v>31</v>
+        <v>52</v>
+      </c>
+      <c r="R13" s="8" t="s">
+        <v>127</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:18" ht="87" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="4">
-        <v>105221</v>
+        <v>101560</v>
       </c>
       <c r="B14" s="5">
-        <v>46322</v>
+        <v>46324</v>
       </c>
       <c r="C14" s="6">
-        <v>0.47916666666666669</v>
+        <v>0.4375</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>18</v>
+        <v>119</v>
       </c>
       <c r="E14" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="J14" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="K14" s="7" t="s">
         <v>109</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="H14" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="I14" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="J14" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="K14" s="7" t="s">
-        <v>60</v>
       </c>
       <c r="L14" s="7" t="s">
         <v>26</v>
@@ -1960,51 +2016,51 @@
         <v>27</v>
       </c>
       <c r="N14" s="7" t="s">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="O14" s="7" t="s">
-        <v>29</v>
+        <v>134</v>
       </c>
       <c r="P14" s="7" t="s">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="Q14" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="R14" s="7" t="s">
-        <v>31</v>
+        <v>136</v>
+      </c>
+      <c r="R14" s="8" t="s">
+        <v>137</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:18" ht="245.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4">
-        <v>105139</v>
+        <v>99949</v>
       </c>
       <c r="B15" s="5">
-        <v>46322</v>
+        <v>46324</v>
       </c>
       <c r="C15" s="6">
-        <v>0.5</v>
+        <v>0.4375</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>101</v>
+        <v>139</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>117</v>
+        <v>140</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>103</v>
+        <v>141</v>
       </c>
       <c r="I15" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>89</v>
+        <v>124</v>
       </c>
       <c r="K15" s="7" t="s">
         <v>25</v>
@@ -2013,57 +2069,57 @@
         <v>26</v>
       </c>
       <c r="M15" s="7" t="s">
-        <v>27</v>
+        <v>142</v>
       </c>
       <c r="N15" s="7" t="s">
-        <v>118</v>
+        <v>143</v>
       </c>
       <c r="O15" s="7" t="s">
-        <v>106</v>
+        <v>134</v>
       </c>
       <c r="P15" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q15" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="R15" s="8" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="87" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="4">
+        <v>105905</v>
+      </c>
+      <c r="B16" s="5">
+        <v>46324</v>
+      </c>
+      <c r="C16" s="6">
+        <v>0.4375</v>
+      </c>
+      <c r="D16" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="Q15" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="R15" s="7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="4">
-        <v>103634</v>
-      </c>
-      <c r="B16" s="5">
-        <v>46322</v>
-      </c>
-      <c r="C16" s="6">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>120</v>
-      </c>
       <c r="E16" s="7" t="s">
-        <v>121</v>
+        <v>146</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>122</v>
+        <v>44</v>
       </c>
       <c r="G16" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="H16" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="H16" s="7" t="s">
-        <v>22</v>
-      </c>
       <c r="I16" s="7" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="J16" s="7" t="s">
         <v>124</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>125</v>
+        <v>148</v>
       </c>
       <c r="L16" s="7" t="s">
         <v>26</v>
@@ -2072,51 +2128,51 @@
         <v>27</v>
       </c>
       <c r="N16" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="O16" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="P16" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="O16" s="7" t="s">
+      <c r="Q16" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="R16" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="P16" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="Q16" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="R16" s="7" t="s">
-        <v>31</v>
-      </c>
     </row>
-    <row r="17" spans="1:18" ht="144.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:18" ht="245.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="4">
-        <v>106702</v>
+        <v>99615</v>
       </c>
       <c r="B17" s="5">
-        <v>46322</v>
+        <v>46324</v>
       </c>
       <c r="C17" s="6">
-        <v>0.54305555555555551</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>32</v>
+        <v>119</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>134</v>
+        <v>23</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="K17" s="7" t="s">
         <v>25</v>
@@ -2125,57 +2181,57 @@
         <v>26</v>
       </c>
       <c r="M17" s="7" t="s">
-        <v>27</v>
+        <v>142</v>
       </c>
       <c r="N17" s="7" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="O17" s="7" t="s">
-        <v>91</v>
+        <v>134</v>
       </c>
       <c r="P17" s="7" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="Q17" s="7" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="R17" s="8" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:18" ht="96.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="4">
-        <v>104515</v>
+        <v>106685</v>
       </c>
       <c r="B18" s="5">
-        <v>46322</v>
+        <v>46324</v>
       </c>
       <c r="C18" s="6">
-        <v>0.55555555555555558</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>139</v>
+        <v>112</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>46</v>
+        <v>84</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>23</v>
+        <v>85</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>38</v>
+        <v>156</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="L18" s="7" t="s">
         <v>26</v>
@@ -2184,166 +2240,166 @@
         <v>27</v>
       </c>
       <c r="N18" s="7" t="s">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="O18" s="7" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="P18" s="7" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="Q18" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="R18" s="7" t="s">
-        <v>143</v>
+        <v>88</v>
+      </c>
+      <c r="R18" s="8" t="s">
+        <v>158</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="4">
-        <v>106156</v>
+        <v>99941</v>
       </c>
       <c r="B19" s="5">
-        <v>46322</v>
+        <v>46324</v>
       </c>
       <c r="C19" s="6">
-        <v>0.5625</v>
+        <v>0.4861111111111111</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>32</v>
+        <v>159</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>145</v>
+        <v>20</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>147</v>
+        <v>22</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>79</v>
+        <v>23</v>
       </c>
       <c r="J19" s="7" t="s">
         <v>38</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>25</v>
+        <v>162</v>
       </c>
       <c r="L19" s="7" t="s">
         <v>26</v>
       </c>
       <c r="M19" s="7" t="s">
-        <v>27</v>
+        <v>142</v>
       </c>
       <c r="N19" s="7" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="O19" s="7" t="s">
-        <v>127</v>
+        <v>29</v>
       </c>
       <c r="P19" s="7" t="s">
-        <v>129</v>
+        <v>30</v>
       </c>
       <c r="Q19" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="R19" s="8" t="s">
-        <v>149</v>
+        <v>164</v>
+      </c>
+      <c r="R19" s="7" t="s">
+        <v>41</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="245.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="4">
-        <v>105940</v>
+        <v>105259</v>
       </c>
       <c r="B20" s="5">
-        <v>46322</v>
+        <v>46324</v>
       </c>
       <c r="C20" s="6">
-        <v>0.5708333333333333</v>
+        <v>0.50694444444444442</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>152</v>
+        <v>98</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="I20" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>154</v>
+        <v>92</v>
       </c>
       <c r="K20" s="7" t="s">
         <v>25</v>
       </c>
       <c r="L20" s="7" t="s">
-        <v>155</v>
+        <v>26</v>
       </c>
       <c r="M20" s="7" t="s">
         <v>27</v>
       </c>
       <c r="N20" s="7" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="O20" s="7" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="P20" s="7" t="s">
-        <v>157</v>
+        <v>103</v>
       </c>
       <c r="Q20" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="R20" s="8" t="s">
-        <v>158</v>
+        <v>169</v>
+      </c>
+      <c r="R20" s="7" t="s">
+        <v>41</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:18" ht="87" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="4">
-        <v>106206</v>
+        <v>105570</v>
       </c>
       <c r="B21" s="5">
-        <v>46322</v>
+        <v>46324</v>
       </c>
       <c r="C21" s="6">
-        <v>0.58333333333333337</v>
+        <v>0.52083333333333337</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>104</v>
+        <v>124</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>25</v>
+        <v>148</v>
       </c>
       <c r="L21" s="7" t="s">
         <v>26</v>
@@ -2352,54 +2408,54 @@
         <v>27</v>
       </c>
       <c r="N21" s="7" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="O21" s="7" t="s">
-        <v>106</v>
+        <v>50</v>
       </c>
       <c r="P21" s="7" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="Q21" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="R21" s="7" t="s">
-        <v>31</v>
+        <v>52</v>
+      </c>
+      <c r="R21" s="8" t="s">
+        <v>127</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="192.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:18" ht="245.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="4">
-        <v>105491</v>
+        <v>104574</v>
       </c>
       <c r="B22" s="5">
-        <v>46322</v>
+        <v>46324</v>
       </c>
       <c r="C22" s="6">
-        <v>0.58333333333333337</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>115</v>
+        <v>33</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="I22" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>89</v>
+        <v>124</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>167</v>
+        <v>25</v>
       </c>
       <c r="L22" s="7" t="s">
         <v>26</v>
@@ -2408,54 +2464,54 @@
         <v>27</v>
       </c>
       <c r="N22" s="7" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="O22" s="7" t="s">
-        <v>49</v>
+        <v>134</v>
       </c>
       <c r="P22" s="7" t="s">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="Q22" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="R22" s="7" t="s">
-        <v>171</v>
+        <v>153</v>
+      </c>
+      <c r="R22" s="8" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="23" spans="1:18" ht="87" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="4">
-        <v>105540</v>
+        <v>105506</v>
       </c>
       <c r="B23" s="5">
-        <v>46322</v>
+        <v>46324</v>
       </c>
       <c r="C23" s="6">
-        <v>0.59791666666666665</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>172</v>
+        <v>119</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>174</v>
+        <v>121</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>176</v>
+        <v>123</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>79</v>
+        <v>47</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>177</v>
+        <v>124</v>
       </c>
       <c r="K23" s="7" t="s">
-        <v>178</v>
+        <v>148</v>
       </c>
       <c r="L23" s="7" t="s">
         <v>26</v>
@@ -2464,30 +2520,30 @@
         <v>27</v>
       </c>
       <c r="N23" s="7" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="O23" s="7" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="P23" s="7" t="s">
-        <v>180</v>
+        <v>126</v>
       </c>
       <c r="Q23" s="7" t="s">
-        <v>180</v>
+        <v>52</v>
       </c>
       <c r="R23" s="8" t="s">
-        <v>181</v>
+        <v>127</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="259.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="4">
-        <v>104926</v>
+        <v>98819</v>
       </c>
       <c r="B24" s="5">
-        <v>46322</v>
+        <v>46324</v>
       </c>
       <c r="C24" s="6">
-        <v>0.61458333333333337</v>
+        <v>0.55208333333333337</v>
       </c>
       <c r="D24" s="7" t="s">
         <v>182</v>
@@ -2496,22 +2552,22 @@
         <v>183</v>
       </c>
       <c r="F24" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="G24" s="7" t="s">
         <v>184</v>
       </c>
-      <c r="G24" s="7" t="s">
-        <v>185</v>
-      </c>
       <c r="H24" s="7" t="s">
-        <v>186</v>
+        <v>100</v>
       </c>
       <c r="I24" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>89</v>
+        <v>185</v>
       </c>
       <c r="K24" s="7" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="L24" s="7" t="s">
         <v>26</v>
@@ -2520,110 +2576,110 @@
         <v>27</v>
       </c>
       <c r="N24" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="O24" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="P24" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q24" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="R24" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" ht="274.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="4">
+        <v>103715</v>
+      </c>
+      <c r="B25" s="5">
+        <v>46324</v>
+      </c>
+      <c r="C25" s="6">
+        <v>0.56597222222222221</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="E25" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="O24" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="P24" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q24" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="R24" s="8" t="s">
+      <c r="F25" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="G25" s="7" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="25" spans="1:18" ht="202.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="4">
-        <v>74935</v>
-      </c>
-      <c r="B25" s="5">
-        <v>46322</v>
-      </c>
-      <c r="C25" s="6">
-        <v>0.62013888888888891</v>
-      </c>
-      <c r="D25" s="7" t="s">
+      <c r="H25" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="E25" s="7" t="s">
+      <c r="I25" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="F25" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="G25" s="7" t="s">
+      <c r="J25" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="H25" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="I25" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="J25" s="7" t="s">
-        <v>193</v>
-      </c>
       <c r="K25" s="7" t="s">
-        <v>194</v>
+        <v>60</v>
       </c>
       <c r="L25" s="7" t="s">
         <v>26</v>
       </c>
       <c r="M25" s="7" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="N25" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="O25" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="P25" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q25" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="R25" s="8" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" ht="245.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="4">
+        <v>105922</v>
+      </c>
+      <c r="B26" s="5">
+        <v>46324</v>
+      </c>
+      <c r="C26" s="6">
+        <v>0.59375</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="E26" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="O25" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="P25" s="7" t="s">
+      <c r="F26" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="Q25" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="R25" s="8" t="s">
+      <c r="G26" s="7" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="26" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="4">
-        <v>106219</v>
-      </c>
-      <c r="B26" s="5">
-        <v>46322</v>
-      </c>
-      <c r="C26" s="6">
-        <v>0.625</v>
-      </c>
-      <c r="D26" s="7" t="s">
+      <c r="H26" s="7" t="s">
         <v>198</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="G26" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="H26" s="7" t="s">
-        <v>96</v>
       </c>
       <c r="I26" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>89</v>
+        <v>132</v>
       </c>
       <c r="K26" s="7" t="s">
-        <v>25</v>
+        <v>148</v>
       </c>
       <c r="L26" s="7" t="s">
         <v>26</v>
@@ -2632,33 +2688,33 @@
         <v>27</v>
       </c>
       <c r="N26" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="O26" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="P26" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="Q26" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="R26" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="O26" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="P26" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q26" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="R26" s="7" t="s">
-        <v>31</v>
-      </c>
     </row>
-    <row r="27" spans="1:18" ht="240.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:18" ht="159" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="4">
-        <v>104781</v>
+        <v>105072</v>
       </c>
       <c r="B27" s="5">
-        <v>46322</v>
+        <v>46324</v>
       </c>
       <c r="C27" s="6">
-        <v>0.65277777777777779</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="E27" s="7" t="s">
         <v>202</v>
@@ -2676,10 +2732,10 @@
         <v>23</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>177</v>
+        <v>124</v>
       </c>
       <c r="K27" s="7" t="s">
-        <v>25</v>
+        <v>148</v>
       </c>
       <c r="L27" s="7" t="s">
         <v>26</v>
@@ -2691,31 +2747,94 @@
         <v>206</v>
       </c>
       <c r="O27" s="7" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="P27" s="7" t="s">
         <v>207</v>
       </c>
       <c r="Q27" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="R27" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="R27" s="8" t="s">
         <v>208</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" ht="240.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="4">
+        <v>101348</v>
+      </c>
+      <c r="B28" s="5">
+        <v>46324</v>
+      </c>
+      <c r="C28" s="6">
+        <v>0.61111111111111116</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="H28" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="I28" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J28" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="K28" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L28" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M28" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N28" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="O28" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="P28" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q28" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="R28" s="7" t="s">
+        <v>214</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="R3" r:id="rId1" xr:uid="{E70C753C-B4AB-4DA2-8874-4D6BE15AEE9C}"/>
-    <hyperlink ref="R7" r:id="rId2" xr:uid="{8CD7349B-B768-4F32-97AD-E4C6B17FDF28}"/>
-    <hyperlink ref="R9" r:id="rId3" xr:uid="{1FEAC607-4DCB-4486-8328-9D7EE3CCD37E}"/>
-    <hyperlink ref="R10" r:id="rId4" xr:uid="{1164ACF0-76E2-4389-B572-4DED5239179C}"/>
-    <hyperlink ref="R17" r:id="rId5" xr:uid="{29BE04FB-4A65-49E6-A5EC-7CBD5FAA6837}"/>
-    <hyperlink ref="R19" r:id="rId6" xr:uid="{E56E5952-F400-4F88-A83D-F445B892AC2D}"/>
-    <hyperlink ref="R20" r:id="rId7" display="https://trt2-jus-br.zoom.us/j/81881873237?pwd=aEs5S29DM2srNHRuRGFVM2ZEYkVUZz09%20ID%20da%20reunião:%20818%208187%203237%20Senha%20de%20acesso:%20459217" xr:uid="{B2D22885-963B-4781-8C82-82555603F2AB}"/>
-    <hyperlink ref="R23" r:id="rId8" xr:uid="{11F48EB9-0F83-4108-87F4-CD040B1657FC}"/>
-    <hyperlink ref="R24" r:id="rId9" display="https://trt15-jus-br.zoom.us/j/88542672682?pwd=7pQ4QRhZmRG9RAQAWKowymbwNawa7t.1%20ID%20da%20reunião:%20885%204267%202682%20Senha%20de%20acesso:%2050728" xr:uid="{FEFA1AE1-4656-432D-92AC-8A5CABB385F7}"/>
-    <hyperlink ref="R25" r:id="rId10" display="https://trt15-jus-br.zoom.us/j/88582969985?pwd=KDz0bWgxYzvepXfQC3ZYK8t4t1RyOY.1%20ID:%20885%208296%209985%20Senha:%203" xr:uid="{65EE2F3D-CFA0-436B-B350-CD4ACCF5342D}"/>
+    <hyperlink ref="R5" r:id="rId1" display="https://trt15-jus-br.zoom.us/j/83934617561?pwd=tyrlqvz6UTYj3JeQgOojDijKbDgfm9.1%20ID%20da%20reunião:%20839%203461%207561%20Senha:%20516068" xr:uid="{3814D9F8-F2DF-4E1E-AD2D-5B02D50D053D}"/>
+    <hyperlink ref="R6" r:id="rId2" display="https://trt15-jus-br.zoom.us/j/83934617561?pwd=tyrlqvz6UTYj3JeQgOojDijKbDgfm9.1%20ID%20da%20reunião:%20839%203461%207561%20Senha:%20516068" xr:uid="{D958D83A-909E-43F5-AFFF-96AC46B8C92A}"/>
+    <hyperlink ref="R9" r:id="rId3" display="https://trt7-jus-br.zoom.us/j/85966394206?pwd=NzVHbThxN2RyenY3Vk03WTJ2MVFsUT09%20ID:%20859%20%206639%20%204206%20Senha:%20931541" xr:uid="{413FF080-5B35-4CAC-A5FF-864B59E39162}"/>
+    <hyperlink ref="R12" r:id="rId4" xr:uid="{FF529050-70CA-4A9A-B7DF-78B954056254}"/>
+    <hyperlink ref="R13" r:id="rId5" xr:uid="{A679B1BE-C564-4101-8258-D3DAE253D803}"/>
+    <hyperlink ref="R14" r:id="rId6" xr:uid="{39375D64-5060-46EA-97F0-8BC2987D408F}"/>
+    <hyperlink ref="R15" r:id="rId7" display="https://trt15-jus-br.zoom.us/j/5326391733?pwd=Qjc4RFBXWjZNbVd1bG5wNldjR3dWZz09%20ID%20da%20reunião:%205326391733%20Senha%20de%20acesso:%20959215" xr:uid="{B0498F91-067E-49E7-B64B-227AA96E8190}"/>
+    <hyperlink ref="R16" r:id="rId8" xr:uid="{D0133C22-63BC-40CD-8F19-1AF381C0087A}"/>
+    <hyperlink ref="R17" r:id="rId9" display="https://trt15-jus-br.zoom.us/j/5326391733?pwd=Qjc4RFBXWjZNbVd1bG5wNldjR3dWZz09%20ID%20da%20reunião:%205326391733%20Senha%20de%20acesso:%20959215" xr:uid="{89542C5F-0A7D-44C7-966B-30DD1D34CD31}"/>
+    <hyperlink ref="R18" r:id="rId10" xr:uid="{FD26FC60-0B8C-45F0-B55A-829504EE9754}"/>
+    <hyperlink ref="R21" r:id="rId11" xr:uid="{4476EDB4-E0BF-494F-B4E4-4F9A7E9A3B7A}"/>
+    <hyperlink ref="R22" r:id="rId12" display="https://trt2-jus-br.zoom.us/j/85932097305?pwd=VRmOpF07r6vEKgjIgaQPtnd6XlE7ua.1%20ID%20da%20reunião:%20859%203209%207305%20Senha%20de%20acesso:%20vtaruja01" xr:uid="{BC07E3C7-E884-4DFC-9F17-B35E7FBE863B}"/>
+    <hyperlink ref="R23" r:id="rId13" xr:uid="{E7795CFF-1796-43E7-A038-9D8E60A9499E}"/>
+    <hyperlink ref="R25" r:id="rId14" display="https://trt9-jus-br.zoom.us/j/87561159126?pwd=UDRXRjBZamVnZVBtMHM1U0lIQWtaUT09%20ID%20da%20reunião:%20875%206115%209126%20Senha%20(código%20de%20acesso)%20343717" xr:uid="{54BDB902-47FD-48ED-9F89-4F22DCE920F3}"/>
+    <hyperlink ref="R26" r:id="rId15" display="https://trt2-jus-br.zoom.us/j/89723895437?pwd=299HRPK4b4mHSqIWSRZ6nL7kVKwZaO.1%20ID%20da%20reunião:%20897%202389%205437%20Senha%20de%20acesso:%20402582" xr:uid="{4AE169F1-8D41-413A-AA54-B9E3591443D6}"/>
+    <hyperlink ref="R27" r:id="rId16" xr:uid="{D2E98026-FC9D-4D4C-919A-2FB7180B5413}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId17"/>
 </worksheet>
 </file>